--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uaer4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B488BD-441E-4332-876F-42E91CA30BCA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29AC705-3B40-402D-9B89-4BE3482D9A50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$163</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$599</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$599</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$165</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$601</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$601</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="217">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -949,9 +949,6 @@
     <t>Заблокирован</t>
   </si>
   <si>
-    <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10 (7613)</t>
-  </si>
-  <si>
     <t>Ротация кода 6454</t>
   </si>
   <si>
@@ -977,6 +974,15 @@
   </si>
   <si>
     <t>Луганск</t>
+  </si>
+  <si>
+    <t>Грация</t>
+  </si>
+  <si>
+    <t>СЫРРРВЕЛАТ Папа может в/к в/у 0.28кг 8шт</t>
+  </si>
+  <si>
+    <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10 (7613)</t>
   </si>
 </sst>
 </file>
@@ -1973,6 +1979,9 @@
     <xf numFmtId="165" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1980,9 +1989,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6244,7 +6250,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1687"/>
+  <dimension ref="A1:BO1689"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -6266,17 +6272,17 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="157">
+      <c r="D1" s="153">
         <v>130438644</v>
       </c>
-      <c r="E1" s="153" t="s">
-        <v>213</v>
-      </c>
-      <c r="F1" s="154"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
-      <c r="I1" s="154"/>
-      <c r="J1" s="155"/>
+      <c r="E1" s="154" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="155"/>
+      <c r="J1" s="156"/>
       <c r="K1" s="121">
         <v>130438384</v>
       </c>
@@ -6307,12 +6313,12 @@
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="156" t="s">
-        <v>214</v>
-      </c>
-      <c r="H3" s="154"/>
-      <c r="I3" s="154"/>
-      <c r="J3" s="155"/>
+      <c r="G3" s="157" t="s">
+        <v>213</v>
+      </c>
+      <c r="H3" s="155"/>
+      <c r="I3" s="155"/>
+      <c r="J3" s="156"/>
       <c r="K3" s="121">
         <v>130439106</v>
       </c>
@@ -6326,6 +6332,9 @@
       </c>
       <c r="L4" s="117" t="s">
         <v>193</v>
+      </c>
+      <c r="O4" s="117" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.25">
@@ -10531,7 +10540,7 @@
     </row>
     <row r="80" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A80" s="143" t="str">
-        <f t="shared" ref="A80:A102" si="11">RIGHT(D80,4)</f>
+        <f t="shared" ref="A80:A104" si="11">RIGHT(D80,4)</f>
         <v>7564</v>
       </c>
       <c r="B80" s="53" t="s">
@@ -10548,7 +10557,7 @@
         <v>0.84</v>
       </c>
       <c r="G80" s="23">
-        <f t="shared" ref="G80:G84" si="12">E80</f>
+        <f t="shared" ref="G80:G85" si="12">E80</f>
         <v>0</v>
       </c>
       <c r="H80" s="14">
@@ -10689,54 +10698,48 @@
     <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7149</v>
+        <v>6946</v>
       </c>
       <c r="B85" s="54" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="C85" s="55" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D85" s="57">
-        <v>1001303637149</v>
+        <v>1001300456946</v>
       </c>
       <c r="E85" s="24"/>
-      <c r="F85" s="58">
-        <v>0.84</v>
-      </c>
+      <c r="F85" s="58"/>
       <c r="G85" s="23">
-        <f>E85*F85</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H85" s="59">
-        <v>5.04</v>
-      </c>
-      <c r="I85" s="59">
-        <v>50</v>
-      </c>
+      <c r="H85" s="59"/>
+      <c r="I85" s="59"/>
       <c r="J85" s="59"/>
       <c r="L85" s="120"/>
     </row>
     <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7157</v>
+        <v>7149</v>
       </c>
       <c r="B86" s="54" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="C86" s="55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D86" s="57">
-        <v>1001300387157</v>
+        <v>1001303637149</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="58">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="G86" s="23">
-        <f t="shared" ref="G86:G87" si="13">E86</f>
+        <f>E86*F86</f>
         <v>0</v>
       </c>
       <c r="H86" s="59">
@@ -10751,87 +10754,85 @@
     <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7166</v>
+        <v>7157</v>
       </c>
       <c r="B87" s="54" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C87" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D87" s="57">
-        <v>1001303987166</v>
+        <v>1001300387157</v>
       </c>
       <c r="E87" s="24"/>
       <c r="F87" s="58">
+        <v>0.63</v>
+      </c>
+      <c r="G87" s="23">
+        <f t="shared" ref="G87:G88" si="13">E87</f>
+        <v>0</v>
+      </c>
+      <c r="H87" s="59">
+        <v>5.04</v>
+      </c>
+      <c r="I87" s="59">
+        <v>50</v>
+      </c>
+      <c r="J87" s="59"/>
+      <c r="L87" s="120"/>
+    </row>
+    <row r="88" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="56" t="str">
+        <f t="shared" si="11"/>
+        <v>7166</v>
+      </c>
+      <c r="B88" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="C88" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88" s="57">
+        <v>1001303987166</v>
+      </c>
+      <c r="E88" s="24"/>
+      <c r="F88" s="58">
         <v>0.7</v>
       </c>
-      <c r="G87" s="23">
+      <c r="G88" s="23">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H87" s="59">
+      <c r="H88" s="59">
         <v>5.6</v>
       </c>
-      <c r="I87" s="59">
+      <c r="I88" s="59">
         <v>50</v>
       </c>
-      <c r="J87" s="59"/>
-      <c r="L87" s="120"/>
-    </row>
-    <row r="88" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="143" t="str">
+      <c r="J88" s="59"/>
+      <c r="L88" s="120"/>
+    </row>
+    <row r="89" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="143" t="str">
         <f t="shared" si="11"/>
         <v>7603</v>
       </c>
-      <c r="B88" s="54" t="s">
+      <c r="B89" s="54" t="s">
         <v>122</v>
-      </c>
-      <c r="C88" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="D88" s="57">
-        <v>1001303637603</v>
-      </c>
-      <c r="E88" s="24"/>
-      <c r="F88" s="23">
-        <v>0.33</v>
-      </c>
-      <c r="G88" s="23">
-        <f t="shared" ref="G88:G104" si="14">E88*F88</f>
-        <v>0</v>
-      </c>
-      <c r="H88" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I88" s="14">
-        <v>45</v>
-      </c>
-      <c r="J88" s="52" t="s">
-        <v>171</v>
-      </c>
-      <c r="L88" s="120"/>
-    </row>
-    <row r="89" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>6807</v>
-      </c>
-      <c r="B89" s="54" t="s">
-        <v>75</v>
       </c>
       <c r="C89" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D89" s="57">
-        <v>1001300366807</v>
+        <v>1001303637603</v>
       </c>
       <c r="E89" s="24"/>
       <c r="F89" s="23">
         <v>0.33</v>
       </c>
       <c r="G89" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="G89:G106" si="14">E89*F89</f>
         <v>0</v>
       </c>
       <c r="H89" s="14">
@@ -10840,22 +10841,24 @@
       <c r="I89" s="14">
         <v>45</v>
       </c>
-      <c r="J89" s="29"/>
+      <c r="J89" s="52" t="s">
+        <v>171</v>
+      </c>
       <c r="L89" s="120"/>
     </row>
     <row r="90" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>6787</v>
+        <v>6807</v>
       </c>
       <c r="B90" s="54" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C90" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D90" s="57">
-        <v>1001300456787</v>
+        <v>1001300366807</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
@@ -10877,27 +10880,27 @@
     <row r="91" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>6697</v>
-      </c>
-      <c r="B91" s="114" t="s">
-        <v>66</v>
+        <v>6787</v>
+      </c>
+      <c r="B91" s="54" t="s">
+        <v>65</v>
       </c>
       <c r="C91" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D91" s="57">
-        <v>1001301876697</v>
+        <v>1001300456787</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="G91" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H91" s="14">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="I91" s="14">
         <v>45</v>
@@ -10908,58 +10911,54 @@
     <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7169</v>
-      </c>
-      <c r="B92" s="114" t="s">
-        <v>70</v>
+        <v>7489</v>
+      </c>
+      <c r="B92" s="54" t="s">
+        <v>215</v>
       </c>
       <c r="C92" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="57">
-        <v>1001303987169</v>
+        <v>1001307357489</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="G92" si="15">E92*F92</f>
         <v>0</v>
       </c>
-      <c r="H92" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I92" s="14">
-        <v>50</v>
-      </c>
+      <c r="H92" s="14"/>
+      <c r="I92" s="14"/>
       <c r="J92" s="29"/>
       <c r="L92" s="120"/>
     </row>
-    <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7233</v>
-      </c>
-      <c r="B93" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="C93" s="50" t="s">
+        <v>6697</v>
+      </c>
+      <c r="B93" s="114" t="s">
+        <v>66</v>
+      </c>
+      <c r="C93" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="D93" s="51">
-        <v>1001303637233</v>
+      <c r="D93" s="57">
+        <v>1001301876697</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G93" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H93" s="14">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="I93" s="14">
         <v>45</v>
@@ -10967,81 +10966,81 @@
       <c r="J93" s="29"/>
       <c r="L93" s="120"/>
     </row>
-    <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7236</v>
-      </c>
-      <c r="B94" s="53" t="s">
-        <v>68</v>
-      </c>
-      <c r="C94" s="50" t="s">
+        <v>7169</v>
+      </c>
+      <c r="B94" s="114" t="s">
+        <v>70</v>
+      </c>
+      <c r="C94" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="D94" s="51">
-        <v>1001304507236</v>
+      <c r="D94" s="57">
+        <v>1001303987169</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G94" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H94" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I94" s="14">
-        <v>45</v>
-      </c>
-      <c r="J94" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J94" s="29"/>
       <c r="L94" s="120"/>
     </row>
     <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7177</v>
+        <v>7233</v>
       </c>
       <c r="B95" s="53" t="s">
-        <v>124</v>
+        <v>181</v>
       </c>
       <c r="C95" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D95" s="51">
-        <v>1001302347177</v>
+        <v>1001303637233</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="G95" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H95" s="14">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="I95" s="14">
-        <v>50</v>
-      </c>
-      <c r="J95" s="49"/>
+        <v>45</v>
+      </c>
+      <c r="J95" s="29"/>
       <c r="L95" s="120"/>
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7232</v>
+        <v>7236</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C96" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D96" s="51">
-        <v>1001302277232</v>
+        <v>1001304507236</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
@@ -11055,7 +11054,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="I96" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J96" s="49"/>
       <c r="L96" s="120"/>
@@ -11063,16 +11062,16 @@
     <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7154</v>
+        <v>7177</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="51">
-        <v>1001300387154</v>
+        <v>1001302347177</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
@@ -11094,30 +11093,30 @@
     <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7238</v>
+        <v>7232</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>123</v>
+        <v>61</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="51">
-        <v>1001305197238</v>
+        <v>1001302277232</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G98" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.48</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I98" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J98" s="49"/>
       <c r="L98" s="120"/>
@@ -11125,30 +11124,30 @@
     <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7237</v>
+        <v>7154</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="51">
-        <v>1001304497237</v>
+        <v>1001300387154</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G99" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I99" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J99" s="49"/>
       <c r="L99" s="120"/>
@@ -11156,27 +11155,27 @@
     <row r="100" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7241</v>
+        <v>7238</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D100" s="51">
-        <v>1001303107241</v>
+        <v>1001305197238</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G100" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I100" s="14">
         <v>45</v>
@@ -11187,16 +11186,16 @@
     <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7332</v>
+        <v>7237</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D101" s="51">
-        <v>1001301777332</v>
+        <v>1001304497237</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
@@ -11210,7 +11209,7 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="I101" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J101" s="49"/>
       <c r="L101" s="120"/>
@@ -11218,16 +11217,16 @@
     <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="56" t="str">
         <f t="shared" si="11"/>
-        <v>7333</v>
+        <v>7241</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="51">
-        <v>1001303987333</v>
+        <v>1001303107241</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="23">
@@ -11241,264 +11240,152 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="I102" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J102" s="49"/>
       <c r="L102" s="120"/>
     </row>
     <row r="103" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="143">
-        <v>7608</v>
+      <c r="A103" s="56" t="str">
+        <f t="shared" si="11"/>
+        <v>7332</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
       <c r="C103" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D103" s="51">
-        <v>1001304197608</v>
+        <v>1001301777332</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G103" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H103" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I103" s="14">
-        <v>45</v>
-      </c>
-      <c r="J103" s="52" t="s">
-        <v>210</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J103" s="49"/>
       <c r="L103" s="120"/>
     </row>
-    <row r="104" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="143">
-        <v>7610</v>
+    <row r="104" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="56" t="str">
+        <f t="shared" si="11"/>
+        <v>7333</v>
       </c>
       <c r="B104" s="53" t="s">
-        <v>211</v>
+        <v>69</v>
       </c>
       <c r="C104" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D104" s="51">
-        <v>1001306717610</v>
+        <v>1001303987333</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G104" s="23">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H104" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I104" s="14">
+        <v>50</v>
+      </c>
+      <c r="J104" s="49"/>
+      <c r="L104" s="120"/>
+    </row>
+    <row r="105" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="143">
+        <v>7608</v>
+      </c>
+      <c r="B105" s="53" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D105" s="51">
+        <v>1001304197608</v>
+      </c>
+      <c r="E105" s="24"/>
+      <c r="F105" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G105" s="23">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H105" s="14">
         <v>1</v>
       </c>
-      <c r="I104" s="14">
+      <c r="I105" s="14">
         <v>45</v>
       </c>
-      <c r="J104" s="52" t="s">
-        <v>212</v>
-      </c>
-      <c r="L104" s="120"/>
-    </row>
-    <row r="105" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="47" t="s">
+      <c r="J105" s="52" t="s">
+        <v>209</v>
+      </c>
+      <c r="L105" s="120"/>
+    </row>
+    <row r="106" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="143">
+        <v>7610</v>
+      </c>
+      <c r="B106" s="53" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D106" s="51">
+        <v>1001306717610</v>
+      </c>
+      <c r="E106" s="24"/>
+      <c r="F106" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G106" s="23">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="H106" s="14">
+        <v>1</v>
+      </c>
+      <c r="I106" s="14">
+        <v>45</v>
+      </c>
+      <c r="J106" s="52" t="s">
+        <v>211</v>
+      </c>
+      <c r="L106" s="120"/>
+    </row>
+    <row r="107" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B105" s="42" t="s">
+      <c r="B107" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="C105" s="42"/>
-      <c r="D105" s="42"/>
-      <c r="E105" s="42"/>
-      <c r="F105" s="41"/>
-      <c r="G105" s="42"/>
-      <c r="H105" s="42"/>
-      <c r="I105" s="42"/>
-      <c r="J105" s="43"/>
-      <c r="K105" s="60"/>
-      <c r="L105" s="120"/>
-      <c r="M105" s="120"/>
-      <c r="N105" s="120"/>
-      <c r="O105" s="120"/>
-      <c r="P105" s="120"/>
-      <c r="Q105" s="120"/>
-      <c r="R105" s="120"/>
-      <c r="S105" s="120"/>
-      <c r="T105" s="120"/>
-      <c r="U105" s="120"/>
-      <c r="V105" s="120"/>
-      <c r="W105" s="120"/>
-      <c r="X105" s="120"/>
-      <c r="Y105" s="120"/>
-      <c r="Z105" s="120"/>
-      <c r="AA105" s="120"/>
-      <c r="AB105" s="120"/>
-      <c r="AC105" s="120"/>
-      <c r="AD105" s="120"/>
-      <c r="AE105" s="120"/>
-      <c r="AF105" s="120"/>
-      <c r="AG105" s="120"/>
-      <c r="AH105" s="120"/>
-      <c r="AI105" s="120"/>
-      <c r="AJ105" s="120"/>
-      <c r="AK105" s="120"/>
-      <c r="AL105" s="120"/>
-      <c r="AM105" s="120"/>
-      <c r="AN105" s="120"/>
-      <c r="AO105" s="120"/>
-      <c r="AP105" s="120"/>
-      <c r="AQ105" s="120"/>
-      <c r="AR105" s="120"/>
-      <c r="AS105" s="120"/>
-      <c r="AT105" s="120"/>
-      <c r="AU105" s="120"/>
-      <c r="AV105" s="120"/>
-      <c r="AW105" s="120"/>
-      <c r="AX105" s="120"/>
-      <c r="AY105" s="120"/>
-      <c r="AZ105" s="120"/>
-      <c r="BA105" s="120"/>
-      <c r="BB105" s="120"/>
-      <c r="BC105" s="120"/>
-      <c r="BD105" s="120"/>
-      <c r="BE105" s="120"/>
-      <c r="BF105" s="120"/>
-      <c r="BG105" s="120"/>
-      <c r="BH105" s="120"/>
-      <c r="BI105" s="120"/>
-      <c r="BJ105" s="120"/>
-      <c r="BK105" s="120"/>
-      <c r="BL105" s="120"/>
-      <c r="BM105" s="120"/>
-      <c r="BN105" s="120"/>
-      <c r="BO105" s="120"/>
-    </row>
-    <row r="106" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="56" t="str">
-        <f t="shared" ref="A106:A135" si="15">RIGHT(D106,4)</f>
-        <v>0614</v>
-      </c>
-      <c r="B106" s="54" t="s">
-        <v>140</v>
-      </c>
-      <c r="C106" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D106" s="57">
-        <v>1001060720614</v>
-      </c>
-      <c r="E106" s="24"/>
-      <c r="F106" s="58">
-        <v>0.52</v>
-      </c>
-      <c r="G106" s="23">
-        <f t="shared" ref="G106:G109" si="16">E106</f>
-        <v>0</v>
-      </c>
-      <c r="H106" s="108">
-        <v>3.64</v>
-      </c>
-      <c r="I106" s="107">
-        <v>120</v>
-      </c>
-      <c r="J106" s="59"/>
-      <c r="K106" s="60"/>
-      <c r="L106" s="120"/>
-      <c r="M106" s="120"/>
-      <c r="N106" s="120"/>
-      <c r="O106" s="120"/>
-      <c r="P106" s="120"/>
-      <c r="Q106" s="120"/>
-      <c r="R106" s="120"/>
-      <c r="S106" s="120"/>
-      <c r="T106" s="120"/>
-      <c r="U106" s="120"/>
-      <c r="V106" s="120"/>
-      <c r="W106" s="120"/>
-      <c r="X106" s="120"/>
-      <c r="Y106" s="120"/>
-      <c r="Z106" s="120"/>
-      <c r="AA106" s="120"/>
-      <c r="AB106" s="120"/>
-      <c r="AC106" s="120"/>
-      <c r="AD106" s="120"/>
-      <c r="AE106" s="120"/>
-      <c r="AF106" s="120"/>
-      <c r="AG106" s="120"/>
-      <c r="AH106" s="120"/>
-      <c r="AI106" s="120"/>
-      <c r="AJ106" s="120"/>
-      <c r="AK106" s="120"/>
-      <c r="AL106" s="120"/>
-      <c r="AM106" s="120"/>
-      <c r="AN106" s="120"/>
-      <c r="AO106" s="120"/>
-      <c r="AP106" s="120"/>
-      <c r="AQ106" s="120"/>
-      <c r="AR106" s="120"/>
-      <c r="AS106" s="120"/>
-      <c r="AT106" s="120"/>
-      <c r="AU106" s="120"/>
-      <c r="AV106" s="120"/>
-      <c r="AW106" s="120"/>
-      <c r="AX106" s="120"/>
-      <c r="AY106" s="120"/>
-      <c r="AZ106" s="120"/>
-      <c r="BA106" s="120"/>
-      <c r="BB106" s="120"/>
-      <c r="BC106" s="120"/>
-      <c r="BD106" s="120"/>
-      <c r="BE106" s="120"/>
-      <c r="BF106" s="120"/>
-      <c r="BG106" s="120"/>
-      <c r="BH106" s="120"/>
-      <c r="BI106" s="120"/>
-      <c r="BJ106" s="120"/>
-      <c r="BK106" s="120"/>
-      <c r="BL106" s="120"/>
-      <c r="BM106" s="120"/>
-      <c r="BN106" s="120"/>
-      <c r="BO106" s="120"/>
-    </row>
-    <row r="107" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>3287</v>
-      </c>
-      <c r="B107" s="54" t="s">
-        <v>90</v>
-      </c>
-      <c r="C107" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D107" s="57">
-        <v>1001060763287</v>
-      </c>
-      <c r="E107" s="24"/>
-      <c r="F107" s="58">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="G107" s="23">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H107" s="108">
-        <v>3.9</v>
-      </c>
-      <c r="I107" s="107">
-        <v>120</v>
-      </c>
-      <c r="J107" s="59"/>
+      <c r="C107" s="42"/>
+      <c r="D107" s="42"/>
+      <c r="E107" s="42"/>
+      <c r="F107" s="41"/>
+      <c r="G107" s="42"/>
+      <c r="H107" s="42"/>
+      <c r="I107" s="42"/>
+      <c r="J107" s="43"/>
       <c r="K107" s="60"/>
       <c r="L107" s="120"/>
       <c r="M107" s="120"/>
@@ -11557,92 +11444,204 @@
       <c r="BN107" s="120"/>
       <c r="BO107" s="120"/>
     </row>
-    <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A108" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>5708</v>
-      </c>
-      <c r="B108" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C108" s="50" t="s">
+        <f t="shared" ref="A108:A137" si="16">RIGHT(D108,4)</f>
+        <v>0614</v>
+      </c>
+      <c r="B108" s="54" t="s">
+        <v>140</v>
+      </c>
+      <c r="C108" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="D108" s="51">
-        <v>1001063145708</v>
+      <c r="D108" s="57">
+        <v>1001060720614</v>
       </c>
       <c r="E108" s="24"/>
-      <c r="F108" s="23">
-        <v>0.5</v>
+      <c r="F108" s="58">
+        <v>0.52</v>
       </c>
       <c r="G108" s="23">
+        <f t="shared" ref="G108:G111" si="17">E108</f>
+        <v>0</v>
+      </c>
+      <c r="H108" s="108">
+        <v>3.64</v>
+      </c>
+      <c r="I108" s="107">
+        <v>120</v>
+      </c>
+      <c r="J108" s="59"/>
+      <c r="K108" s="60"/>
+      <c r="L108" s="120"/>
+      <c r="M108" s="120"/>
+      <c r="N108" s="120"/>
+      <c r="O108" s="120"/>
+      <c r="P108" s="120"/>
+      <c r="Q108" s="120"/>
+      <c r="R108" s="120"/>
+      <c r="S108" s="120"/>
+      <c r="T108" s="120"/>
+      <c r="U108" s="120"/>
+      <c r="V108" s="120"/>
+      <c r="W108" s="120"/>
+      <c r="X108" s="120"/>
+      <c r="Y108" s="120"/>
+      <c r="Z108" s="120"/>
+      <c r="AA108" s="120"/>
+      <c r="AB108" s="120"/>
+      <c r="AC108" s="120"/>
+      <c r="AD108" s="120"/>
+      <c r="AE108" s="120"/>
+      <c r="AF108" s="120"/>
+      <c r="AG108" s="120"/>
+      <c r="AH108" s="120"/>
+      <c r="AI108" s="120"/>
+      <c r="AJ108" s="120"/>
+      <c r="AK108" s="120"/>
+      <c r="AL108" s="120"/>
+      <c r="AM108" s="120"/>
+      <c r="AN108" s="120"/>
+      <c r="AO108" s="120"/>
+      <c r="AP108" s="120"/>
+      <c r="AQ108" s="120"/>
+      <c r="AR108" s="120"/>
+      <c r="AS108" s="120"/>
+      <c r="AT108" s="120"/>
+      <c r="AU108" s="120"/>
+      <c r="AV108" s="120"/>
+      <c r="AW108" s="120"/>
+      <c r="AX108" s="120"/>
+      <c r="AY108" s="120"/>
+      <c r="AZ108" s="120"/>
+      <c r="BA108" s="120"/>
+      <c r="BB108" s="120"/>
+      <c r="BC108" s="120"/>
+      <c r="BD108" s="120"/>
+      <c r="BE108" s="120"/>
+      <c r="BF108" s="120"/>
+      <c r="BG108" s="120"/>
+      <c r="BH108" s="120"/>
+      <c r="BI108" s="120"/>
+      <c r="BJ108" s="120"/>
+      <c r="BK108" s="120"/>
+      <c r="BL108" s="120"/>
+      <c r="BM108" s="120"/>
+      <c r="BN108" s="120"/>
+      <c r="BO108" s="120"/>
+    </row>
+    <row r="109" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="56" t="str">
         <f t="shared" si="16"/>
+        <v>3287</v>
+      </c>
+      <c r="B109" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C109" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D109" s="57">
+        <v>1001060763287</v>
+      </c>
+      <c r="E109" s="24"/>
+      <c r="F109" s="58">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="G109" s="23">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H108" s="106">
-        <v>4</v>
-      </c>
-      <c r="I108" s="14">
+      <c r="H109" s="108">
+        <v>3.9</v>
+      </c>
+      <c r="I109" s="107">
         <v>120</v>
       </c>
-      <c r="J108" s="29"/>
-      <c r="L108" s="120"/>
-    </row>
-    <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>4117</v>
-      </c>
-      <c r="B109" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="C109" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D109" s="51">
-        <v>1001062504117</v>
-      </c>
-      <c r="E109" s="24"/>
-      <c r="F109" s="23">
-        <v>0.49399999999999999</v>
-      </c>
-      <c r="G109" s="23">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="H109" s="14">
-        <v>3.95</v>
-      </c>
-      <c r="I109" s="14">
-        <v>120</v>
-      </c>
-      <c r="J109" s="29"/>
+      <c r="J109" s="59"/>
+      <c r="K109" s="60"/>
       <c r="L109" s="120"/>
+      <c r="M109" s="120"/>
+      <c r="N109" s="120"/>
+      <c r="O109" s="120"/>
+      <c r="P109" s="120"/>
+      <c r="Q109" s="120"/>
+      <c r="R109" s="120"/>
+      <c r="S109" s="120"/>
+      <c r="T109" s="120"/>
+      <c r="U109" s="120"/>
+      <c r="V109" s="120"/>
+      <c r="W109" s="120"/>
+      <c r="X109" s="120"/>
+      <c r="Y109" s="120"/>
+      <c r="Z109" s="120"/>
+      <c r="AA109" s="120"/>
+      <c r="AB109" s="120"/>
+      <c r="AC109" s="120"/>
+      <c r="AD109" s="120"/>
+      <c r="AE109" s="120"/>
+      <c r="AF109" s="120"/>
+      <c r="AG109" s="120"/>
+      <c r="AH109" s="120"/>
+      <c r="AI109" s="120"/>
+      <c r="AJ109" s="120"/>
+      <c r="AK109" s="120"/>
+      <c r="AL109" s="120"/>
+      <c r="AM109" s="120"/>
+      <c r="AN109" s="120"/>
+      <c r="AO109" s="120"/>
+      <c r="AP109" s="120"/>
+      <c r="AQ109" s="120"/>
+      <c r="AR109" s="120"/>
+      <c r="AS109" s="120"/>
+      <c r="AT109" s="120"/>
+      <c r="AU109" s="120"/>
+      <c r="AV109" s="120"/>
+      <c r="AW109" s="120"/>
+      <c r="AX109" s="120"/>
+      <c r="AY109" s="120"/>
+      <c r="AZ109" s="120"/>
+      <c r="BA109" s="120"/>
+      <c r="BB109" s="120"/>
+      <c r="BC109" s="120"/>
+      <c r="BD109" s="120"/>
+      <c r="BE109" s="120"/>
+      <c r="BF109" s="120"/>
+      <c r="BG109" s="120"/>
+      <c r="BH109" s="120"/>
+      <c r="BI109" s="120"/>
+      <c r="BJ109" s="120"/>
+      <c r="BK109" s="120"/>
+      <c r="BL109" s="120"/>
+      <c r="BM109" s="120"/>
+      <c r="BN109" s="120"/>
+      <c r="BO109" s="120"/>
     </row>
     <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7316</v>
+        <f t="shared" si="16"/>
+        <v>5708</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>148</v>
+        <v>80</v>
       </c>
       <c r="C110" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D110" s="51">
-        <v>1001060727316</v>
+        <v>1001063145708</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" ref="G110:G123" si="17">E110*F110</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H110" s="14">
-        <v>3.78</v>
+      <c r="H110" s="106">
+        <v>4</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -11652,28 +11651,28 @@
     </row>
     <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7317</v>
+        <f t="shared" si="16"/>
+        <v>4117</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="C111" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D111" s="51">
-        <v>1001066567317</v>
+        <v>1001062504117</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.54</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G111" s="23">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="I111" s="14">
         <v>120</v>
@@ -11683,28 +11682,28 @@
     </row>
     <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7143</v>
+        <f t="shared" si="16"/>
+        <v>7316</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C112" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="51">
-        <v>1001060717143</v>
+        <v>1001060727316</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
-        <v>0.22</v>
+        <v>0.54</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="G112:G125" si="18">E112*F112</f>
         <v>0</v>
       </c>
       <c r="H112" s="14">
-        <v>1.76</v>
+        <v>3.78</v>
       </c>
       <c r="I112" s="14">
         <v>120</v>
@@ -11714,28 +11713,28 @@
     </row>
     <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7147</v>
+        <f t="shared" si="16"/>
+        <v>7317</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="C113" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="51">
-        <v>1001063237147</v>
+        <v>1001066567317</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.22</v>
+        <v>0.54</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>1.76</v>
+        <v>3.78</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -11745,59 +11744,59 @@
     </row>
     <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7456</v>
+        <f t="shared" si="16"/>
+        <v>7143</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D114" s="51">
-        <v>1001063097456</v>
+        <v>1001060717143</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I114" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J114" s="29"/>
       <c r="L114" s="120"/>
     </row>
     <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7318</v>
+        <f t="shared" si="16"/>
+        <v>7147</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="C115" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D115" s="51">
-        <v>1001060727318</v>
+        <v>1001063237147</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="I115" s="14">
         <v>120</v>
@@ -11807,179 +11806,179 @@
     </row>
     <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>3986</v>
+        <f t="shared" si="16"/>
+        <v>7456</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D116" s="51">
-        <v>1001061973986</v>
+        <v>1001063097456</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I116" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J116" s="29"/>
       <c r="L116" s="120"/>
     </row>
     <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7364</v>
+        <f t="shared" si="16"/>
+        <v>7318</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D117" s="51">
-        <v>1001063217364</v>
+        <v>1001060727318</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="I117" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J117" s="29"/>
       <c r="L117" s="120"/>
     </row>
     <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7383</v>
+        <f t="shared" si="16"/>
+        <v>3986</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D118" s="51">
-        <v>1001065467383</v>
+        <v>1001061973986</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I118" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J118" s="29"/>
       <c r="L118" s="120"/>
     </row>
     <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>6967</v>
+        <f t="shared" si="16"/>
+        <v>7364</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>83</v>
+        <v>144</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="51">
-        <v>1001063656967</v>
+        <v>1001063217364</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="I119" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J119" s="29"/>
       <c r="L119" s="120"/>
     </row>
     <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>4993</v>
+        <f t="shared" si="16"/>
+        <v>7383</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D120" s="51">
-        <v>1001060764993</v>
+        <v>1001065467383</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="I120" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J120" s="29"/>
       <c r="L120" s="120"/>
     </row>
     <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>6937</v>
+        <f t="shared" si="16"/>
+        <v>6967</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D121" s="51">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
         <v>0.25</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
@@ -11993,24 +11992,24 @@
     </row>
     <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>5483</v>
+        <f t="shared" si="16"/>
+        <v>4993</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D122" s="51">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
         <v>0.25</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
@@ -12024,28 +12023,28 @@
     </row>
     <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>5931</v>
+        <f t="shared" si="16"/>
+        <v>6937</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D123" s="51">
-        <v>1001060755931</v>
+        <v>1001063106937</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I123" s="14">
         <v>120</v>
@@ -12055,342 +12054,340 @@
     </row>
     <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>6832</v>
+        <f t="shared" si="16"/>
+        <v>5483</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C124" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D124" s="51">
-        <v>1001065616832</v>
+        <v>1001062505483</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.215</v>
+        <v>0.25</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" ref="G124:G125" si="18">E124</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="I124" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J124" s="29"/>
       <c r="L124" s="120"/>
     </row>
     <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7299</v>
+        <f t="shared" si="16"/>
+        <v>5931</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C125" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D125" s="51">
-        <v>1001060677299</v>
+        <v>1001060755931</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.215</v>
+        <v>0.22</v>
       </c>
       <c r="G125" s="23">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="I125" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J125" s="29"/>
       <c r="L125" s="120"/>
     </row>
     <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7386</v>
+        <f t="shared" si="16"/>
+        <v>6832</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>150</v>
+        <v>81</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D126" s="51">
-        <v>1001067017386</v>
+        <v>1001065616832</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" ref="G126:G136" si="19">E126*F126</f>
+        <f t="shared" ref="G126:G127" si="19">E126</f>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I126" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J126" s="29"/>
       <c r="L126" s="120"/>
     </row>
     <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>5679</v>
+        <f t="shared" si="16"/>
+        <v>7299</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="C127" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D127" s="51">
-        <v>1001190765679</v>
+        <v>1001060677299</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G127" s="23">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H127" s="14">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="I127" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J127" s="29"/>
       <c r="L127" s="120"/>
     </row>
     <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>7382</v>
+        <f t="shared" si="16"/>
+        <v>7386</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D128" s="51">
-        <v>1001203117382</v>
+        <v>1001067017386</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G128" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G128:G138" si="20">E128*F128</f>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <v>0.96</v>
+        <v>1.35</v>
       </c>
       <c r="I128" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J128" s="29"/>
       <c r="L128" s="120"/>
     </row>
     <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="143">
-        <v>7613</v>
+      <c r="A129" s="56" t="str">
+        <f t="shared" si="16"/>
+        <v>5679</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>205</v>
+        <v>136</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D129" s="51">
-        <v>1001061977613</v>
+        <v>1001190765679</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H129" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I129" s="14">
         <v>60</v>
       </c>
-      <c r="J129" s="52" t="s">
-        <v>206</v>
-      </c>
+      <c r="J129" s="29"/>
       <c r="L129" s="120"/>
     </row>
     <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="143">
-        <v>7616</v>
+      <c r="A130" s="56" t="str">
+        <f t="shared" si="16"/>
+        <v>7382</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>207</v>
+        <v>84</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D130" s="51">
-        <v>1001062507616</v>
+        <v>1001203117382</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G130" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I130" s="14">
         <v>60</v>
       </c>
-      <c r="J130" s="52" t="s">
-        <v>208</v>
-      </c>
+      <c r="J130" s="29"/>
       <c r="L130" s="120"/>
     </row>
     <row r="131" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>6221</v>
+      <c r="A131" s="143">
+        <v>7613</v>
       </c>
       <c r="B131" s="53" t="s">
-        <v>86</v>
+        <v>216</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D131" s="51">
-        <v>1001205376221</v>
+        <v>1001061977613</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G131" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H131" s="14">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="I131" s="14">
         <v>60</v>
       </c>
-      <c r="J131" s="29"/>
+      <c r="J131" s="52" t="s">
+        <v>205</v>
+      </c>
       <c r="L131" s="120"/>
     </row>
     <row r="132" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>6222</v>
+      <c r="A132" s="143">
+        <v>7616</v>
       </c>
       <c r="B132" s="53" t="s">
-        <v>133</v>
+        <v>206</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D132" s="51">
-        <v>1001205386222</v>
+        <v>1001062507616</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I132" s="14">
         <v>60</v>
       </c>
-      <c r="J132" s="29"/>
+      <c r="J132" s="52" t="s">
+        <v>207</v>
+      </c>
       <c r="L132" s="120"/>
     </row>
     <row r="133" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="145" t="str">
-        <f t="shared" si="15"/>
-        <v>6834</v>
-      </c>
-      <c r="B133" s="146" t="s">
-        <v>132</v>
-      </c>
-      <c r="C133" s="147" t="s">
+      <c r="A133" s="56" t="str">
+        <f t="shared" si="16"/>
+        <v>6221</v>
+      </c>
+      <c r="B133" s="53" t="s">
+        <v>86</v>
+      </c>
+      <c r="C133" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D133" s="148">
-        <v>1001203146834</v>
-      </c>
-      <c r="E133" s="149"/>
-      <c r="F133" s="150">
-        <v>0.1</v>
-      </c>
-      <c r="G133" s="150">
-        <f t="shared" si="19"/>
+      <c r="D133" s="51">
+        <v>1001205376221</v>
+      </c>
+      <c r="E133" s="24"/>
+      <c r="F133" s="23">
+        <v>0.09</v>
+      </c>
+      <c r="G133" s="23">
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H133" s="151">
-        <v>1</v>
-      </c>
-      <c r="I133" s="151">
+      <c r="H133" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="I133" s="14">
         <v>60</v>
       </c>
-      <c r="J133" s="151" t="s">
-        <v>204</v>
-      </c>
+      <c r="J133" s="29"/>
       <c r="L133" s="120"/>
     </row>
     <row r="134" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>6965</v>
+        <f t="shared" si="16"/>
+        <v>6222</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D134" s="51">
-        <v>1001206356965</v>
+        <v>1001205386222</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="23">
-        <v>7.0000000000000007E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H134" s="14">
-        <v>0.98</v>
+        <v>0.9</v>
       </c>
       <c r="I134" s="14">
         <v>60</v>
@@ -12399,317 +12396,207 @@
       <c r="L134" s="120"/>
     </row>
     <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v>6557</v>
-      </c>
-      <c r="B135" s="53" t="s">
-        <v>135</v>
-      </c>
-      <c r="C135" s="50" t="s">
+      <c r="A135" s="145" t="str">
+        <f t="shared" si="16"/>
+        <v>6834</v>
+      </c>
+      <c r="B135" s="146" t="s">
+        <v>132</v>
+      </c>
+      <c r="C135" s="147" t="s">
         <v>20</v>
       </c>
-      <c r="D135" s="51">
-        <v>1001200756557</v>
-      </c>
-      <c r="E135" s="24"/>
-      <c r="F135" s="23">
+      <c r="D135" s="148">
+        <v>1001203146834</v>
+      </c>
+      <c r="E135" s="149"/>
+      <c r="F135" s="150">
         <v>0.1</v>
       </c>
-      <c r="G135" s="23">
-        <f t="shared" si="19"/>
+      <c r="G135" s="150">
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="H135" s="14">
+      <c r="H135" s="151">
         <v>1</v>
       </c>
-      <c r="I135" s="14">
+      <c r="I135" s="151">
         <v>60</v>
       </c>
-      <c r="J135" s="29"/>
+      <c r="J135" s="151" t="s">
+        <v>204</v>
+      </c>
       <c r="L135" s="120"/>
     </row>
-    <row r="136" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="143">
-        <v>7626</v>
+    <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="56" t="str">
+        <f t="shared" si="16"/>
+        <v>6965</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>202</v>
+        <v>134</v>
       </c>
       <c r="C136" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D136" s="51">
-        <v>1001066607626</v>
+        <v>1001206356965</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="23">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G136" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H136" s="14">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I136" s="14">
         <v>60</v>
       </c>
-      <c r="J136" s="52" t="s">
-        <v>203</v>
-      </c>
+      <c r="J136" s="29"/>
       <c r="L136" s="120"/>
     </row>
-    <row r="137" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B137" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C137" s="42"/>
-      <c r="D137" s="42"/>
-      <c r="E137" s="42"/>
-      <c r="F137" s="41"/>
-      <c r="G137" s="42"/>
-      <c r="H137" s="42"/>
-      <c r="I137" s="42"/>
-      <c r="J137" s="43"/>
+    <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="56" t="str">
+        <f t="shared" si="16"/>
+        <v>6557</v>
+      </c>
+      <c r="B137" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="C137" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D137" s="51">
+        <v>1001200756557</v>
+      </c>
+      <c r="E137" s="24"/>
+      <c r="F137" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G137" s="23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H137" s="14">
+        <v>1</v>
+      </c>
+      <c r="I137" s="14">
+        <v>60</v>
+      </c>
+      <c r="J137" s="29"/>
       <c r="L137" s="120"/>
     </row>
-    <row r="138" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="56" t="str">
-        <f t="shared" ref="A138:A147" si="20">RIGHT(D138,4)</f>
-        <v>6470</v>
-      </c>
-      <c r="B138" s="112" t="s">
-        <v>116</v>
+    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="143">
+        <v>7626</v>
+      </c>
+      <c r="B138" s="53" t="s">
+        <v>202</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D138" s="111">
-        <v>1001092436470</v>
+        <v>20</v>
+      </c>
+      <c r="D138" s="51">
+        <v>1001066607626</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G138" s="23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="H138" s="14">
+        <v>1</v>
+      </c>
+      <c r="I138" s="14">
+        <v>60</v>
+      </c>
+      <c r="J138" s="52" t="s">
+        <v>203</v>
+      </c>
+      <c r="L138" s="120"/>
+    </row>
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B139" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C139" s="42"/>
+      <c r="D139" s="42"/>
+      <c r="E139" s="42"/>
+      <c r="F139" s="41"/>
+      <c r="G139" s="42"/>
+      <c r="H139" s="42"/>
+      <c r="I139" s="42"/>
+      <c r="J139" s="43"/>
+      <c r="L139" s="120"/>
+    </row>
+    <row r="140" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="56" t="str">
+        <f t="shared" ref="A140:A149" si="21">RIGHT(D140,4)</f>
+        <v>6470</v>
+      </c>
+      <c r="B140" s="112" t="s">
+        <v>116</v>
+      </c>
+      <c r="C140" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D140" s="111">
+        <v>1001092436470</v>
+      </c>
+      <c r="E140" s="24"/>
+      <c r="F140" s="23">
         <v>1.2</v>
       </c>
-      <c r="G138" s="23">
-        <f>E138</f>
+      <c r="G140" s="23">
+        <f>E140</f>
         <v>0</v>
       </c>
-      <c r="H138" s="14">
+      <c r="H140" s="14">
         <v>4.8</v>
       </c>
-      <c r="I138" s="14">
+      <c r="I140" s="14">
         <v>45</v>
       </c>
-      <c r="J138" s="29"/>
-      <c r="L138" s="120"/>
-    </row>
-    <row r="139" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="56" t="str">
-        <f t="shared" si="20"/>
-        <v>6495</v>
-      </c>
-      <c r="B139" s="113" t="s">
-        <v>95</v>
-      </c>
-      <c r="C139" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="D139" s="70">
-        <v>1001092436495</v>
-      </c>
-      <c r="E139" s="24"/>
-      <c r="F139" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="G139" s="23">
-        <f>E139*F139</f>
-        <v>0</v>
-      </c>
-      <c r="H139" s="59">
-        <v>1.8</v>
-      </c>
-      <c r="I139" s="59">
-        <v>45</v>
-      </c>
-      <c r="J139" s="59"/>
-      <c r="K139" s="60"/>
-      <c r="L139" s="120"/>
-      <c r="M139" s="120"/>
-      <c r="N139" s="120"/>
-      <c r="O139" s="120"/>
-      <c r="P139" s="120"/>
-      <c r="Q139" s="120"/>
-      <c r="R139" s="120"/>
-      <c r="S139" s="120"/>
-      <c r="T139" s="120"/>
-      <c r="U139" s="120"/>
-      <c r="V139" s="120"/>
-      <c r="W139" s="120"/>
-      <c r="X139" s="120"/>
-      <c r="Y139" s="120"/>
-      <c r="Z139" s="120"/>
-      <c r="AA139" s="120"/>
-      <c r="AB139" s="120"/>
-      <c r="AC139" s="120"/>
-      <c r="AD139" s="120"/>
-      <c r="AE139" s="120"/>
-      <c r="AF139" s="120"/>
-      <c r="AG139" s="120"/>
-      <c r="AH139" s="120"/>
-      <c r="AI139" s="120"/>
-      <c r="AJ139" s="120"/>
-      <c r="AK139" s="120"/>
-      <c r="AL139" s="120"/>
-      <c r="AM139" s="120"/>
-      <c r="AN139" s="120"/>
-      <c r="AO139" s="120"/>
-      <c r="AP139" s="120"/>
-      <c r="AQ139" s="120"/>
-      <c r="AR139" s="120"/>
-      <c r="AS139" s="120"/>
-      <c r="AT139" s="120"/>
-      <c r="AU139" s="120"/>
-      <c r="AV139" s="120"/>
-      <c r="AW139" s="120"/>
-      <c r="AX139" s="120"/>
-      <c r="AY139" s="120"/>
-      <c r="AZ139" s="120"/>
-      <c r="BA139" s="120"/>
-      <c r="BB139" s="120"/>
-      <c r="BC139" s="120"/>
-      <c r="BD139" s="120"/>
-      <c r="BE139" s="120"/>
-      <c r="BF139" s="120"/>
-      <c r="BG139" s="120"/>
-      <c r="BH139" s="120"/>
-      <c r="BI139" s="120"/>
-      <c r="BJ139" s="120"/>
-      <c r="BK139" s="120"/>
-      <c r="BL139" s="120"/>
-      <c r="BM139" s="120"/>
-      <c r="BN139" s="120"/>
-      <c r="BO139" s="120"/>
-    </row>
-    <row r="140" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="56" t="str">
-        <f t="shared" si="20"/>
-        <v>5452</v>
-      </c>
-      <c r="B140" s="109" t="s">
-        <v>93</v>
-      </c>
-      <c r="C140" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D140" s="70">
-        <v>1001092485452</v>
-      </c>
-      <c r="E140" s="24"/>
-      <c r="F140" s="58">
-        <v>1.35</v>
-      </c>
-      <c r="G140" s="23">
-        <f t="shared" ref="G140:G143" si="21">E140</f>
-        <v>0</v>
-      </c>
-      <c r="H140" s="59">
-        <v>4.05</v>
-      </c>
-      <c r="I140" s="59">
-        <v>60</v>
-      </c>
-      <c r="J140" s="59"/>
-      <c r="K140" s="60"/>
+      <c r="J140" s="29"/>
       <c r="L140" s="120"/>
-      <c r="M140" s="120"/>
-      <c r="N140" s="120"/>
-      <c r="O140" s="120"/>
-      <c r="P140" s="120"/>
-      <c r="Q140" s="120"/>
-      <c r="R140" s="120"/>
-      <c r="S140" s="120"/>
-      <c r="T140" s="120"/>
-      <c r="U140" s="120"/>
-      <c r="V140" s="120"/>
-      <c r="W140" s="120"/>
-      <c r="X140" s="120"/>
-      <c r="Y140" s="120"/>
-      <c r="Z140" s="120"/>
-      <c r="AA140" s="120"/>
-      <c r="AB140" s="120"/>
-      <c r="AC140" s="120"/>
-      <c r="AD140" s="120"/>
-      <c r="AE140" s="120"/>
-      <c r="AF140" s="120"/>
-      <c r="AG140" s="120"/>
-      <c r="AH140" s="120"/>
-      <c r="AI140" s="120"/>
-      <c r="AJ140" s="120"/>
-      <c r="AK140" s="120"/>
-      <c r="AL140" s="120"/>
-      <c r="AM140" s="120"/>
-      <c r="AN140" s="120"/>
-      <c r="AO140" s="120"/>
-      <c r="AP140" s="120"/>
-      <c r="AQ140" s="120"/>
-      <c r="AR140" s="120"/>
-      <c r="AS140" s="120"/>
-      <c r="AT140" s="120"/>
-      <c r="AU140" s="120"/>
-      <c r="AV140" s="120"/>
-      <c r="AW140" s="120"/>
-      <c r="AX140" s="120"/>
-      <c r="AY140" s="120"/>
-      <c r="AZ140" s="120"/>
-      <c r="BA140" s="120"/>
-      <c r="BB140" s="120"/>
-      <c r="BC140" s="120"/>
-      <c r="BD140" s="120"/>
-      <c r="BE140" s="120"/>
-      <c r="BF140" s="120"/>
-      <c r="BG140" s="120"/>
-      <c r="BH140" s="120"/>
-      <c r="BI140" s="120"/>
-      <c r="BJ140" s="120"/>
-      <c r="BK140" s="120"/>
-      <c r="BL140" s="120"/>
-      <c r="BM140" s="120"/>
-      <c r="BN140" s="120"/>
-      <c r="BO140" s="120"/>
     </row>
     <row r="141" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="56" t="str">
-        <f t="shared" si="20"/>
-        <v>6866</v>
-      </c>
-      <c r="B141" s="109" t="s">
-        <v>92</v>
+        <f t="shared" si="21"/>
+        <v>6495</v>
+      </c>
+      <c r="B141" s="113" t="s">
+        <v>95</v>
       </c>
       <c r="C141" s="55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D141" s="70">
-        <v>1001095716866</v>
+        <v>1001092436495</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="58">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="G141" s="23">
-        <f t="shared" si="21"/>
+        <f>E141*F141</f>
         <v>0</v>
       </c>
       <c r="H141" s="59">
-        <v>6</v>
+        <v>1.8</v>
       </c>
       <c r="I141" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J141" s="59"/>
       <c r="K141" s="60"/>
@@ -12772,28 +12659,28 @@
     </row>
     <row r="142" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="56" t="str">
-        <f t="shared" si="20"/>
-        <v>6025</v>
+        <f t="shared" si="21"/>
+        <v>5452</v>
       </c>
       <c r="B142" s="109" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="C142" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D142" s="70">
-        <v>1001094966025</v>
+        <v>1001092485452</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="58">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="G142" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G142:G145" si="22">E142</f>
         <v>0</v>
       </c>
       <c r="H142" s="59">
-        <v>6</v>
+        <v>4.05</v>
       </c>
       <c r="I142" s="59">
         <v>60</v>
@@ -12859,28 +12746,28 @@
     </row>
     <row r="143" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="56" t="str">
-        <f t="shared" si="20"/>
-        <v>4584</v>
+        <f t="shared" si="21"/>
+        <v>6866</v>
       </c>
       <c r="B143" s="109" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="C143" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D143" s="70">
-        <v>1001092674584</v>
+        <v>1001095716866</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="58">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G143" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H143" s="59">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I143" s="59">
         <v>60</v>
@@ -12944,30 +12831,30 @@
       <c r="BN143" s="120"/>
       <c r="BO143" s="120"/>
     </row>
-    <row r="144" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="56" t="str">
-        <f t="shared" si="20"/>
-        <v>3215</v>
-      </c>
-      <c r="B144" s="54" t="s">
-        <v>176</v>
+        <f t="shared" si="21"/>
+        <v>6025</v>
+      </c>
+      <c r="B144" s="109" t="s">
+        <v>118</v>
       </c>
       <c r="C144" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="D144" s="110">
-        <v>1001094053215</v>
+        <v>22</v>
+      </c>
+      <c r="D144" s="70">
+        <v>1001094966025</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="58">
-        <v>0.4</v>
+        <v>3</v>
       </c>
       <c r="G144" s="23">
-        <f t="shared" ref="G144:G147" si="22">E144*F144</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H144" s="59">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="I144" s="59">
         <v>60</v>
@@ -13031,30 +12918,30 @@
       <c r="BN144" s="120"/>
       <c r="BO144" s="120"/>
     </row>
-    <row r="145" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="56" t="str">
-        <f t="shared" si="20"/>
-        <v>5495</v>
-      </c>
-      <c r="B145" s="54" t="s">
-        <v>94</v>
+        <f t="shared" si="21"/>
+        <v>4584</v>
+      </c>
+      <c r="B145" s="109" t="s">
+        <v>175</v>
       </c>
       <c r="C145" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="D145" s="110">
-        <v>1001093345495</v>
+        <v>22</v>
+      </c>
+      <c r="D145" s="70">
+        <v>1001092674584</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="58">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="G145" s="23">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H145" s="59">
-        <v>2.4</v>
+        <v>7.5</v>
       </c>
       <c r="I145" s="59">
         <v>60</v>
@@ -13120,31 +13007,31 @@
     </row>
     <row r="146" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="56" t="str">
-        <f t="shared" si="20"/>
-        <v>7377</v>
+        <f t="shared" si="21"/>
+        <v>3215</v>
       </c>
       <c r="B146" s="54" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="C146" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D146" s="110">
-        <v>1001095027377</v>
+        <v>1001094053215</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="58">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G146" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G146:G149" si="23">E146*F146</f>
         <v>0</v>
       </c>
       <c r="H146" s="59">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="I146" s="59">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J146" s="59"/>
       <c r="K146" s="60"/>
@@ -13205,33 +13092,33 @@
       <c r="BN146" s="120"/>
       <c r="BO146" s="120"/>
     </row>
-    <row r="147" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="56" t="str">
-        <f t="shared" si="20"/>
-        <v>6925</v>
+        <f t="shared" si="21"/>
+        <v>5495</v>
       </c>
       <c r="B147" s="54" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C147" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D147" s="110">
-        <v>1001095226925</v>
+        <v>1001093345495</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="58">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H147" s="59">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I147" s="59">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J147" s="59"/>
       <c r="K147" s="60"/>
@@ -13292,36 +13179,35 @@
       <c r="BN147" s="120"/>
       <c r="BO147" s="120"/>
     </row>
-    <row r="148" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="143">
-        <v>7647</v>
+    <row r="148" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>7377</v>
       </c>
       <c r="B148" s="54" t="s">
-        <v>196</v>
+        <v>117</v>
       </c>
       <c r="C148" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D148" s="110">
-        <v>1001097747647</v>
+        <v>1001095027377</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="58">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G148" s="23">
-        <f>E148*F148</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H148" s="59">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I148" s="59">
-        <v>30</v>
-      </c>
-      <c r="J148" s="144" t="s">
-        <v>197</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J148" s="59"/>
       <c r="K148" s="60"/>
       <c r="L148" s="120"/>
       <c r="M148" s="120"/>
@@ -13380,36 +13266,35 @@
       <c r="BN148" s="120"/>
       <c r="BO148" s="120"/>
     </row>
-    <row r="149" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="143">
-        <v>7651</v>
+    <row r="149" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="56" t="str">
+        <f t="shared" si="21"/>
+        <v>6925</v>
       </c>
       <c r="B149" s="54" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="C149" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D149" s="110">
-        <v>1001097767651</v>
+        <v>1001095226925</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="58">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G149" s="23">
-        <f>E149*F149</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H149" s="59">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="I149" s="59">
-        <v>30</v>
-      </c>
-      <c r="J149" s="144" t="s">
-        <v>197</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J149" s="59"/>
       <c r="K149" s="60"/>
       <c r="L149" s="120"/>
       <c r="M149" s="120"/>
@@ -13468,137 +13353,250 @@
       <c r="BN149" s="120"/>
       <c r="BO149" s="120"/>
     </row>
-    <row r="150" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="47" t="s">
+    <row r="150" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="143">
+        <v>7647</v>
+      </c>
+      <c r="B150" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C150" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D150" s="110">
+        <v>1001097747647</v>
+      </c>
+      <c r="E150" s="24"/>
+      <c r="F150" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G150" s="23">
+        <f>E150*F150</f>
+        <v>0</v>
+      </c>
+      <c r="H150" s="59">
+        <v>1</v>
+      </c>
+      <c r="I150" s="59">
+        <v>30</v>
+      </c>
+      <c r="J150" s="144" t="s">
+        <v>197</v>
+      </c>
+      <c r="K150" s="60"/>
+      <c r="L150" s="120"/>
+      <c r="M150" s="120"/>
+      <c r="N150" s="120"/>
+      <c r="O150" s="120"/>
+      <c r="P150" s="120"/>
+      <c r="Q150" s="120"/>
+      <c r="R150" s="120"/>
+      <c r="S150" s="120"/>
+      <c r="T150" s="120"/>
+      <c r="U150" s="120"/>
+      <c r="V150" s="120"/>
+      <c r="W150" s="120"/>
+      <c r="X150" s="120"/>
+      <c r="Y150" s="120"/>
+      <c r="Z150" s="120"/>
+      <c r="AA150" s="120"/>
+      <c r="AB150" s="120"/>
+      <c r="AC150" s="120"/>
+      <c r="AD150" s="120"/>
+      <c r="AE150" s="120"/>
+      <c r="AF150" s="120"/>
+      <c r="AG150" s="120"/>
+      <c r="AH150" s="120"/>
+      <c r="AI150" s="120"/>
+      <c r="AJ150" s="120"/>
+      <c r="AK150" s="120"/>
+      <c r="AL150" s="120"/>
+      <c r="AM150" s="120"/>
+      <c r="AN150" s="120"/>
+      <c r="AO150" s="120"/>
+      <c r="AP150" s="120"/>
+      <c r="AQ150" s="120"/>
+      <c r="AR150" s="120"/>
+      <c r="AS150" s="120"/>
+      <c r="AT150" s="120"/>
+      <c r="AU150" s="120"/>
+      <c r="AV150" s="120"/>
+      <c r="AW150" s="120"/>
+      <c r="AX150" s="120"/>
+      <c r="AY150" s="120"/>
+      <c r="AZ150" s="120"/>
+      <c r="BA150" s="120"/>
+      <c r="BB150" s="120"/>
+      <c r="BC150" s="120"/>
+      <c r="BD150" s="120"/>
+      <c r="BE150" s="120"/>
+      <c r="BF150" s="120"/>
+      <c r="BG150" s="120"/>
+      <c r="BH150" s="120"/>
+      <c r="BI150" s="120"/>
+      <c r="BJ150" s="120"/>
+      <c r="BK150" s="120"/>
+      <c r="BL150" s="120"/>
+      <c r="BM150" s="120"/>
+      <c r="BN150" s="120"/>
+      <c r="BO150" s="120"/>
+    </row>
+    <row r="151" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="143">
+        <v>7651</v>
+      </c>
+      <c r="B151" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="C151" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D151" s="110">
+        <v>1001097767651</v>
+      </c>
+      <c r="E151" s="24"/>
+      <c r="F151" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G151" s="23">
+        <f>E151*F151</f>
+        <v>0</v>
+      </c>
+      <c r="H151" s="59">
+        <v>1</v>
+      </c>
+      <c r="I151" s="59">
+        <v>30</v>
+      </c>
+      <c r="J151" s="144" t="s">
+        <v>197</v>
+      </c>
+      <c r="K151" s="60"/>
+      <c r="L151" s="120"/>
+      <c r="M151" s="120"/>
+      <c r="N151" s="120"/>
+      <c r="O151" s="120"/>
+      <c r="P151" s="120"/>
+      <c r="Q151" s="120"/>
+      <c r="R151" s="120"/>
+      <c r="S151" s="120"/>
+      <c r="T151" s="120"/>
+      <c r="U151" s="120"/>
+      <c r="V151" s="120"/>
+      <c r="W151" s="120"/>
+      <c r="X151" s="120"/>
+      <c r="Y151" s="120"/>
+      <c r="Z151" s="120"/>
+      <c r="AA151" s="120"/>
+      <c r="AB151" s="120"/>
+      <c r="AC151" s="120"/>
+      <c r="AD151" s="120"/>
+      <c r="AE151" s="120"/>
+      <c r="AF151" s="120"/>
+      <c r="AG151" s="120"/>
+      <c r="AH151" s="120"/>
+      <c r="AI151" s="120"/>
+      <c r="AJ151" s="120"/>
+      <c r="AK151" s="120"/>
+      <c r="AL151" s="120"/>
+      <c r="AM151" s="120"/>
+      <c r="AN151" s="120"/>
+      <c r="AO151" s="120"/>
+      <c r="AP151" s="120"/>
+      <c r="AQ151" s="120"/>
+      <c r="AR151" s="120"/>
+      <c r="AS151" s="120"/>
+      <c r="AT151" s="120"/>
+      <c r="AU151" s="120"/>
+      <c r="AV151" s="120"/>
+      <c r="AW151" s="120"/>
+      <c r="AX151" s="120"/>
+      <c r="AY151" s="120"/>
+      <c r="AZ151" s="120"/>
+      <c r="BA151" s="120"/>
+      <c r="BB151" s="120"/>
+      <c r="BC151" s="120"/>
+      <c r="BD151" s="120"/>
+      <c r="BE151" s="120"/>
+      <c r="BF151" s="120"/>
+      <c r="BG151" s="120"/>
+      <c r="BH151" s="120"/>
+      <c r="BI151" s="120"/>
+      <c r="BJ151" s="120"/>
+      <c r="BK151" s="120"/>
+      <c r="BL151" s="120"/>
+      <c r="BM151" s="120"/>
+      <c r="BN151" s="120"/>
+      <c r="BO151" s="120"/>
+    </row>
+    <row r="152" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B150" s="42" t="s">
+      <c r="B152" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="C150" s="42"/>
-      <c r="D150" s="42"/>
-      <c r="E150" s="42"/>
-      <c r="F150" s="41"/>
-      <c r="G150" s="42"/>
-      <c r="H150" s="42"/>
-      <c r="I150" s="42"/>
-      <c r="J150" s="43"/>
-      <c r="L150" s="120"/>
-    </row>
-    <row r="151" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="56" t="str">
-        <f t="shared" ref="A151:A161" si="23">RIGHT(D151,4)</f>
+      <c r="C152" s="42"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="42"/>
+      <c r="F152" s="41"/>
+      <c r="G152" s="42"/>
+      <c r="H152" s="42"/>
+      <c r="I152" s="42"/>
+      <c r="J152" s="43"/>
+      <c r="L152" s="120"/>
+    </row>
+    <row r="153" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="56" t="str">
+        <f t="shared" ref="A153:A163" si="24">RIGHT(D153,4)</f>
         <v>6620</v>
       </c>
-      <c r="B151" s="35" t="s">
+      <c r="B153" s="35" t="s">
         <v>97</v>
-      </c>
-      <c r="C151" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D151" s="51">
-        <v>1001081596620</v>
-      </c>
-      <c r="E151" s="24"/>
-      <c r="F151" s="23">
-        <v>1.05</v>
-      </c>
-      <c r="G151" s="23">
-        <f>E151</f>
-        <v>0</v>
-      </c>
-      <c r="H151" s="14">
-        <v>3.15</v>
-      </c>
-      <c r="I151" s="14">
-        <v>30</v>
-      </c>
-      <c r="J151" s="29"/>
-      <c r="L151" s="120"/>
-    </row>
-    <row r="152" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="56" t="str">
-        <f t="shared" si="23"/>
-        <v>7187</v>
-      </c>
-      <c r="B152" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C152" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D152" s="51">
-        <v>1001085637187</v>
-      </c>
-      <c r="E152" s="24"/>
-      <c r="F152" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G152" s="23">
-        <f t="shared" ref="G152:G162" si="24">E152*F152</f>
-        <v>0</v>
-      </c>
-      <c r="H152" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I152" s="14">
-        <v>50</v>
-      </c>
-      <c r="J152" s="29"/>
-      <c r="L152" s="120"/>
-    </row>
-    <row r="153" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="143">
-        <v>6008</v>
-      </c>
-      <c r="B153" s="35" t="s">
-        <v>199</v>
       </c>
       <c r="C153" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D153" s="51">
-        <v>1001084856008</v>
+        <v>1001081596620</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="G153" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G153" si="25">E153</f>
         <v>0</v>
       </c>
       <c r="H153" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I153" s="14">
-        <v>40</v>
-      </c>
-      <c r="J153" s="144" t="s">
-        <v>197</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J153" s="29"/>
       <c r="L153" s="120"/>
     </row>
     <row r="154" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="56" t="str">
-        <f t="shared" si="23"/>
-        <v>7090</v>
+        <f t="shared" si="24"/>
+        <v>7187</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C154" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D154" s="51">
-        <v>1001084217090</v>
+        <v>1001085637187</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
         <v>0.3</v>
       </c>
       <c r="G154" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G154:G164" si="26">E154*F154</f>
         <v>0</v>
       </c>
       <c r="H154" s="14">
@@ -13611,91 +13609,92 @@
       <c r="L154" s="120"/>
     </row>
     <row r="155" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="56" t="str">
-        <f t="shared" si="23"/>
-        <v>7103</v>
+      <c r="A155" s="143">
+        <v>6008</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C155" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D155" s="51">
-        <v>1001223297103</v>
+        <v>1001084856008</v>
       </c>
       <c r="E155" s="24"/>
       <c r="F155" s="23">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="G155" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H155" s="14">
         <v>1.8</v>
       </c>
       <c r="I155" s="14">
-        <v>50</v>
-      </c>
-      <c r="J155" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J155" s="144" t="s">
+        <v>197</v>
+      </c>
       <c r="L155" s="120"/>
     </row>
     <row r="156" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="56" t="str">
-        <f>RIGHT(D156,4)</f>
-        <v>6279</v>
+        <f t="shared" si="24"/>
+        <v>7090</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D156" s="51">
-        <v>1001220286279</v>
+        <v>1001084217090</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="G156" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H156" s="14">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="I156" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J156" s="29"/>
       <c r="L156" s="120"/>
     </row>
     <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="56" t="str">
-        <f t="shared" si="23"/>
-        <v>7092</v>
+        <f t="shared" si="24"/>
+        <v>7103</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D157" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I157" s="14">
         <v>50</v>
@@ -13705,28 +13704,28 @@
     </row>
     <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="56" t="str">
-        <f t="shared" si="23"/>
-        <v>6448</v>
+        <f>RIGHT(D158,4)</f>
+        <v>6279</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D158" s="51">
-        <v>1001234146448</v>
+        <v>1001220286279</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G158" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I158" s="14">
         <v>45</v>
@@ -13736,59 +13735,59 @@
     </row>
     <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="56" t="str">
-        <f t="shared" si="23"/>
-        <v>6754</v>
+        <f t="shared" si="24"/>
+        <v>7092</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D159" s="51">
-        <v>1001225406754</v>
+        <v>1001223297092</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G159" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>0.72</v>
+        <v>1.4</v>
       </c>
       <c r="I159" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J159" s="29"/>
       <c r="L159" s="120"/>
     </row>
     <row r="160" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="56" t="str">
-        <f t="shared" si="23"/>
-        <v>6208</v>
+        <f t="shared" si="24"/>
+        <v>6448</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D160" s="51">
-        <v>1001220226208</v>
+        <v>1001234146448</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G160" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
@@ -13798,108 +13797,150 @@
     </row>
     <row r="161" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="56" t="str">
-        <f t="shared" si="23"/>
-        <v>6228</v>
+        <f t="shared" si="24"/>
+        <v>6754</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D161" s="51">
-        <v>1001225416228</v>
+        <v>1001225406754</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
         <v>0.09</v>
       </c>
       <c r="G161" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="I161" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J161" s="29"/>
       <c r="L161" s="120"/>
     </row>
-    <row r="162" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="143">
-        <v>7612</v>
+    <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="56" t="str">
+        <f t="shared" si="24"/>
+        <v>6208</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="C162" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D162" s="51">
-        <v>1001453907612</v>
+        <v>1001220226208</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G162" s="23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H162" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="I162" s="14">
+        <v>45</v>
+      </c>
+      <c r="J162" s="29"/>
+      <c r="L162" s="120"/>
+    </row>
+    <row r="163" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="56" t="str">
+        <f t="shared" si="24"/>
+        <v>6228</v>
+      </c>
+      <c r="B163" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C163" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D163" s="51">
+        <v>1001225416228</v>
+      </c>
+      <c r="E163" s="24"/>
+      <c r="F163" s="23">
+        <v>0.09</v>
+      </c>
+      <c r="G163" s="23">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H163" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="I163" s="14">
+        <v>45</v>
+      </c>
+      <c r="J163" s="29"/>
+      <c r="L163" s="120"/>
+    </row>
+    <row r="164" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="143">
+        <v>7612</v>
+      </c>
+      <c r="B164" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="C164" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D164" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E164" s="24"/>
+      <c r="F164" s="23">
         <v>0.1</v>
       </c>
-      <c r="G162" s="23">
-        <f t="shared" si="24"/>
+      <c r="G164" s="23">
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H162" s="14">
+      <c r="H164" s="14">
         <v>1</v>
       </c>
-      <c r="I162" s="14">
+      <c r="I164" s="14">
         <v>60</v>
       </c>
-      <c r="J162" s="52" t="s">
+      <c r="J164" s="52" t="s">
         <v>201</v>
       </c>
-      <c r="L162" s="120"/>
-    </row>
-    <row r="163" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="48"/>
-      <c r="B163" s="45" t="s">
+      <c r="L164" s="120"/>
+    </row>
+    <row r="165" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="48"/>
+      <c r="B165" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C163" s="16"/>
-      <c r="D163" s="36"/>
-      <c r="E163" s="17">
-        <f>SUM(E10:E162)</f>
+      <c r="C165" s="16"/>
+      <c r="D165" s="36"/>
+      <c r="E165" s="17">
+        <f>SUM(E10:E164)</f>
         <v>0</v>
       </c>
-      <c r="F163" s="17"/>
-      <c r="G163" s="17">
-        <f>SUM(G11:G162)</f>
+      <c r="F165" s="17"/>
+      <c r="G165" s="17">
+        <f>SUM(G11:G164)</f>
         <v>0</v>
       </c>
-      <c r="H163" s="17"/>
-      <c r="I163" s="17"/>
-      <c r="J163" s="17"/>
-    </row>
-    <row r="164" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="37"/>
-      <c r="C164" s="18"/>
-      <c r="D164" s="40"/>
-      <c r="F164" s="19"/>
-      <c r="G164" s="19"/>
-      <c r="H164" s="20"/>
-      <c r="I164" s="20"/>
-      <c r="J164" s="21"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B165" s="37"/>
-      <c r="C165" s="18"/>
-      <c r="D165" s="40"/>
-      <c r="F165" s="19"/>
-      <c r="G165" s="19"/>
-      <c r="H165" s="20"/>
-      <c r="I165" s="20"/>
-      <c r="J165" s="21"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H165" s="17"/>
+      <c r="I165" s="17"/>
+      <c r="J165" s="17"/>
+    </row>
+    <row r="166" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B166" s="37"/>
       <c r="C166" s="18"/>
       <c r="D166" s="40"/>
@@ -13941,55 +13982,55 @@
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B170" s="37"/>
-      <c r="C170" s="62"/>
-      <c r="D170" s="63"/>
-      <c r="E170" s="64"/>
-      <c r="F170" s="65"/>
-      <c r="G170" s="65"/>
-      <c r="H170" s="66"/>
-      <c r="I170" s="66"/>
+      <c r="C170" s="18"/>
+      <c r="D170" s="40"/>
+      <c r="F170" s="19"/>
+      <c r="G170" s="19"/>
+      <c r="H170" s="20"/>
+      <c r="I170" s="20"/>
       <c r="J170" s="21"/>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B171" s="37"/>
-      <c r="C171" s="62"/>
-      <c r="D171" s="63"/>
-      <c r="E171" s="64"/>
-      <c r="F171" s="65"/>
-      <c r="G171" s="65"/>
-      <c r="H171" s="66"/>
-      <c r="I171" s="66"/>
+      <c r="C171" s="18"/>
+      <c r="D171" s="40"/>
+      <c r="F171" s="19"/>
+      <c r="G171" s="19"/>
+      <c r="H171" s="20"/>
+      <c r="I171" s="20"/>
       <c r="J171" s="21"/>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B172" s="37"/>
       <c r="C172" s="62"/>
-      <c r="D172" s="67"/>
-      <c r="E172" s="68"/>
-      <c r="F172" s="67"/>
-      <c r="G172" s="69"/>
-      <c r="H172" s="70"/>
-      <c r="I172" s="71"/>
+      <c r="D172" s="63"/>
+      <c r="E172" s="64"/>
+      <c r="F172" s="65"/>
+      <c r="G172" s="65"/>
+      <c r="H172" s="66"/>
+      <c r="I172" s="66"/>
       <c r="J172" s="21"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
-      <c r="C173" s="18"/>
-      <c r="D173" s="40"/>
-      <c r="F173" s="19"/>
-      <c r="G173" s="19"/>
-      <c r="H173" s="20"/>
-      <c r="I173" s="20"/>
+      <c r="C173" s="62"/>
+      <c r="D173" s="63"/>
+      <c r="E173" s="64"/>
+      <c r="F173" s="65"/>
+      <c r="G173" s="65"/>
+      <c r="H173" s="66"/>
+      <c r="I173" s="66"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
-      <c r="C174" s="18"/>
-      <c r="D174" s="40"/>
-      <c r="F174" s="19"/>
-      <c r="G174" s="19"/>
-      <c r="H174" s="20"/>
-      <c r="I174" s="20"/>
+      <c r="C174" s="62"/>
+      <c r="D174" s="67"/>
+      <c r="E174" s="68"/>
+      <c r="F174" s="67"/>
+      <c r="G174" s="69"/>
+      <c r="H174" s="70"/>
+      <c r="I174" s="71"/>
       <c r="J174" s="21"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -29122,13 +29163,33 @@
       <c r="I1687" s="20"/>
       <c r="J1687" s="21"/>
     </row>
+    <row r="1688" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1688" s="37"/>
+      <c r="C1688" s="18"/>
+      <c r="D1688" s="40"/>
+      <c r="F1688" s="19"/>
+      <c r="G1688" s="19"/>
+      <c r="H1688" s="20"/>
+      <c r="I1688" s="20"/>
+      <c r="J1688" s="21"/>
+    </row>
+    <row r="1689" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1689" s="37"/>
+      <c r="C1689" s="18"/>
+      <c r="D1689" s="40"/>
+      <c r="F1689" s="19"/>
+      <c r="G1689" s="19"/>
+      <c r="H1689" s="20"/>
+      <c r="I1689" s="20"/>
+      <c r="J1689" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J163" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J165" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D172">
+  <conditionalFormatting sqref="D174">
     <cfRule type="duplicateValues" dxfId="384" priority="1"/>
     <cfRule type="duplicateValues" dxfId="383" priority="2"/>
     <cfRule type="duplicateValues" dxfId="382" priority="3"/>
@@ -29140,7 +29201,7 @@
     <cfRule type="duplicateValues" dxfId="376" priority="10"/>
     <cfRule type="duplicateValues" dxfId="375" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D172">
+  <conditionalFormatting sqref="D174">
     <cfRule type="duplicateValues" dxfId="374" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29AC705-3B40-402D-9B89-4BE3482D9A50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF83CAA-212C-4A54-9297-23C9DCADB15D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$165</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$601</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$601</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$167</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$603</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$603</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="222">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -958,9 +958,6 @@
     <t>Ротация кода 6453</t>
   </si>
   <si>
-    <t xml:space="preserve">СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11 </t>
-  </si>
-  <si>
     <t>Ротация кода 6459</t>
   </si>
   <si>
@@ -983,6 +980,24 @@
   </si>
   <si>
     <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10 (7613)</t>
+  </si>
+  <si>
+    <t>С ИНДЕЙКОЙ ПМ сос ц/о в/у 1/270 8шт.</t>
+  </si>
+  <si>
+    <t>ВЕТЧ.РУБЛЕНАЯ ПМ в/у срез 0.3кг 6шт.</t>
+  </si>
+  <si>
+    <t>ВЕТЧ.МЯСНАЯ Папа может п/о 0.4кг 8шт.</t>
+  </si>
+  <si>
+    <t>БЕКОН Останкино с/к с/н в/у 1/180_50с</t>
+  </si>
+  <si>
+    <t>БРЕСТСКИЕ сос п/о в/у 0.3кг 8шт.</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
   </si>
 </sst>
 </file>
@@ -1543,7 +1558,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1949,13 +1964,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -6250,7 +6259,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1689"/>
+  <dimension ref="A1:BO1691"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -6272,17 +6281,17 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="153">
+      <c r="D1" s="151">
         <v>130438644</v>
       </c>
-      <c r="E1" s="154" t="s">
-        <v>212</v>
-      </c>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-      <c r="H1" s="155"/>
-      <c r="I1" s="155"/>
-      <c r="J1" s="156"/>
+      <c r="E1" s="152" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1" s="153"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="154"/>
       <c r="K1" s="121">
         <v>130438384</v>
       </c>
@@ -6303,22 +6312,22 @@
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="152">
+      <c r="D3" s="150">
         <v>46209</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="152">
+      <c r="F3" s="150">
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="157" t="s">
-        <v>213</v>
-      </c>
-      <c r="H3" s="155"/>
-      <c r="I3" s="155"/>
-      <c r="J3" s="156"/>
+      <c r="G3" s="155" t="s">
+        <v>212</v>
+      </c>
+      <c r="H3" s="153"/>
+      <c r="I3" s="153"/>
+      <c r="J3" s="154"/>
       <c r="K3" s="121">
         <v>130439106</v>
       </c>
@@ -6334,7 +6343,7 @@
         <v>193</v>
       </c>
       <c r="O4" s="117" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:67" x14ac:dyDescent="0.25">
@@ -6578,8 +6587,8 @@
       <c r="BO11" s="119"/>
     </row>
     <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="143" t="str">
-        <f t="shared" ref="A12:A74" si="1">RIGHT(D12,4)</f>
+      <c r="A12" s="56" t="str">
+        <f t="shared" ref="A12:A33" si="1">RIGHT(D12,4)</f>
         <v>7536</v>
       </c>
       <c r="B12" s="53" t="s">
@@ -7121,7 +7130,7 @@
       <c r="L20" s="120"/>
     </row>
     <row r="21" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="143" t="str">
+      <c r="A21" s="56" t="str">
         <f t="shared" si="1"/>
         <v>7539</v>
       </c>
@@ -7303,7 +7312,8 @@
       <c r="BO24" s="120"/>
     </row>
     <row r="25" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="143">
+      <c r="A25" s="56" t="str">
+        <f t="shared" si="1"/>
         <v>7632</v>
       </c>
       <c r="B25" s="54" t="s">
@@ -7391,7 +7401,7 @@
       <c r="BO25" s="120"/>
     </row>
     <row r="26" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="143" t="str">
+      <c r="A26" s="56" t="str">
         <f t="shared" si="1"/>
         <v>7523</v>
       </c>
@@ -7827,7 +7837,7 @@
     </row>
     <row r="35" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A35:A71" si="6">RIGHT(D35,4)</f>
         <v>6767</v>
       </c>
       <c r="B35" s="54" t="s">
@@ -7844,7 +7854,7 @@
         <v>1.04</v>
       </c>
       <c r="G35" s="23">
-        <f t="shared" ref="G35:G46" si="6">E35</f>
+        <f t="shared" ref="G35:G46" si="7">E35</f>
         <v>0</v>
       </c>
       <c r="H35" s="59">
@@ -7914,7 +7924,7 @@
     </row>
     <row r="36" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6761</v>
       </c>
       <c r="B36" s="54" t="s">
@@ -7931,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H36" s="59">
@@ -8001,7 +8011,7 @@
     </row>
     <row r="37" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6764</v>
       </c>
       <c r="B37" s="54" t="s">
@@ -8018,7 +8028,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H37" s="59">
@@ -8088,7 +8098,7 @@
     </row>
     <row r="38" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6254</v>
       </c>
       <c r="B38" s="54" t="s">
@@ -8105,7 +8115,7 @@
         <v>1.5</v>
       </c>
       <c r="G38" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H38" s="59">
@@ -8175,7 +8185,7 @@
     </row>
     <row r="39" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>7075</v>
       </c>
       <c r="B39" s="54" t="s">
@@ -8192,7 +8202,7 @@
         <v>1.5</v>
       </c>
       <c r="G39" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H39" s="59">
@@ -8262,7 +8272,7 @@
     </row>
     <row r="40" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>7083</v>
       </c>
       <c r="B40" s="54" t="s">
@@ -8279,7 +8289,7 @@
         <v>1.5</v>
       </c>
       <c r="G40" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H40" s="59">
@@ -8349,7 +8359,7 @@
     </row>
     <row r="41" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6829</v>
       </c>
       <c r="B41" s="54" t="s">
@@ -8366,7 +8376,7 @@
         <v>2.1</v>
       </c>
       <c r="G41" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H41" s="59">
@@ -8436,7 +8446,7 @@
     </row>
     <row r="42" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>7070</v>
       </c>
       <c r="B42" s="54" t="s">
@@ -8453,7 +8463,7 @@
         <v>1.5</v>
       </c>
       <c r="G42" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H42" s="59">
@@ -8523,7 +8533,7 @@
     </row>
     <row r="43" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>7076</v>
       </c>
       <c r="B43" s="54" t="s">
@@ -8540,7 +8550,7 @@
         <v>1.5</v>
       </c>
       <c r="G43" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H43" s="59">
@@ -8610,7 +8620,7 @@
     </row>
     <row r="44" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>7271</v>
       </c>
       <c r="B44" s="54" t="s">
@@ -8627,7 +8637,7 @@
         <v>1.5</v>
       </c>
       <c r="G44" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H44" s="59">
@@ -8697,7 +8707,7 @@
     </row>
     <row r="45" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6303</v>
       </c>
       <c r="B45" s="54" t="s">
@@ -8714,7 +8724,7 @@
         <v>1.5</v>
       </c>
       <c r="G45" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H45" s="59">
@@ -8784,7 +8794,7 @@
     </row>
     <row r="46" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6661</v>
       </c>
       <c r="B46" s="54" t="s">
@@ -8801,7 +8811,7 @@
         <v>1.5</v>
       </c>
       <c r="G46" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H46" s="59">
@@ -8871,7 +8881,7 @@
     </row>
     <row r="47" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6759</v>
       </c>
       <c r="B47" s="54" t="s">
@@ -8888,7 +8898,7 @@
         <v>0.4</v>
       </c>
       <c r="G47" s="23">
-        <f t="shared" ref="G47:G70" si="7">E47*F47</f>
+        <f t="shared" ref="G47:G71" si="8">E47*F47</f>
         <v>0</v>
       </c>
       <c r="H47" s="59">
@@ -8958,7 +8968,7 @@
     </row>
     <row r="48" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6762</v>
       </c>
       <c r="B48" s="54" t="s">
@@ -8975,7 +8985,7 @@
         <v>0.41</v>
       </c>
       <c r="G48" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H48" s="59">
@@ -9045,7 +9055,7 @@
     </row>
     <row r="49" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6765</v>
       </c>
       <c r="B49" s="54" t="s">
@@ -9062,7 +9072,7 @@
         <v>0.36</v>
       </c>
       <c r="G49" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H49" s="59">
@@ -9132,7 +9142,7 @@
     </row>
     <row r="50" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>7074</v>
       </c>
       <c r="B50" s="54" t="s">
@@ -9149,7 +9159,7 @@
         <v>0.6</v>
       </c>
       <c r="G50" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H50" s="59">
@@ -9219,7 +9229,7 @@
     </row>
     <row r="51" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="56" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>7123</v>
       </c>
       <c r="B51" s="54" t="s">
@@ -9236,7 +9246,7 @@
         <v>0.3</v>
       </c>
       <c r="G51" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H51" s="59">
@@ -9306,32 +9316,28 @@
     </row>
     <row r="52" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>5819</v>
+        <f t="shared" si="6"/>
+        <v>7040</v>
       </c>
       <c r="B52" s="54" t="s">
-        <v>38</v>
+        <v>216</v>
       </c>
       <c r="C52" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D52" s="70">
-        <v>1001022725819</v>
+        <v>1001025027040</v>
       </c>
       <c r="E52" s="24"/>
       <c r="F52" s="58">
-        <v>0.4</v>
+        <v>0.27</v>
       </c>
       <c r="G52" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H52" s="59">
-        <v>3.2</v>
-      </c>
-      <c r="I52" s="59">
-        <v>45</v>
-      </c>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
       <c r="J52" s="59"/>
       <c r="K52" s="60"/>
       <c r="L52" s="120"/>
@@ -9393,28 +9399,28 @@
     </row>
     <row r="53" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>6475</v>
+        <f t="shared" si="6"/>
+        <v>5819</v>
       </c>
       <c r="B53" s="54" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C53" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="70">
-        <v>1001025176475</v>
+        <v>1001022725819</v>
       </c>
       <c r="E53" s="24"/>
       <c r="F53" s="58">
         <v>0.4</v>
       </c>
       <c r="G53" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H53" s="59">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="I53" s="59">
         <v>45</v>
@@ -9480,31 +9486,31 @@
     </row>
     <row r="54" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7284</v>
+        <f t="shared" si="6"/>
+        <v>6475</v>
       </c>
       <c r="B54" s="54" t="s">
-        <v>188</v>
+        <v>45</v>
       </c>
       <c r="C54" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D54" s="70">
-        <v>1001025767284</v>
+        <v>1001025176475</v>
       </c>
       <c r="E54" s="24"/>
       <c r="F54" s="58">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="G54" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H54" s="59">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="I54" s="59">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J54" s="59"/>
       <c r="K54" s="60"/>
@@ -9567,28 +9573,28 @@
     </row>
     <row r="55" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7601</v>
+        <f t="shared" si="6"/>
+        <v>7284</v>
       </c>
       <c r="B55" s="54" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C55" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="70">
-        <v>1001025767601</v>
+        <v>1001025767284</v>
       </c>
       <c r="E55" s="24"/>
       <c r="F55" s="58">
-        <v>0.26400000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="G55" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H55" s="59">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="I55" s="59">
         <v>30</v>
@@ -9654,35 +9660,33 @@
     </row>
     <row r="56" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7461</v>
+        <f t="shared" si="6"/>
+        <v>7601</v>
       </c>
       <c r="B56" s="54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C56" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D56" s="70">
-        <v>1001025767461</v>
+        <v>1001025767601</v>
       </c>
       <c r="E56" s="24"/>
       <c r="F56" s="58">
-        <v>0.33</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="G56" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H56" s="59">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="I56" s="59">
         <v>30</v>
       </c>
-      <c r="J56" s="52" t="s">
-        <v>169</v>
-      </c>
+      <c r="J56" s="59"/>
       <c r="K56" s="60"/>
       <c r="L56" s="120"/>
       <c r="M56" s="120"/>
@@ -9743,33 +9747,35 @@
     </row>
     <row r="57" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7371</v>
+        <f t="shared" si="6"/>
+        <v>7461</v>
       </c>
       <c r="B57" s="54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C57" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D57" s="70">
-        <v>1001026947371</v>
+        <v>1001025767461</v>
       </c>
       <c r="E57" s="24"/>
       <c r="F57" s="58">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="G57" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H57" s="59">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="I57" s="59">
-        <v>45</v>
-      </c>
-      <c r="J57" s="59"/>
+        <v>30</v>
+      </c>
+      <c r="J57" s="52" t="s">
+        <v>169</v>
+      </c>
       <c r="K57" s="60"/>
       <c r="L57" s="120"/>
       <c r="M57" s="120"/>
@@ -9830,24 +9836,24 @@
     </row>
     <row r="58" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>6837</v>
+        <f t="shared" si="6"/>
+        <v>7371</v>
       </c>
       <c r="B58" s="54" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C58" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D58" s="70">
-        <v>1001022556837</v>
+        <v>1001026947371</v>
       </c>
       <c r="E58" s="24"/>
       <c r="F58" s="58">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G58" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H58" s="59">
@@ -9915,247 +9921,303 @@
       <c r="BN58" s="120"/>
       <c r="BO58" s="120"/>
     </row>
-    <row r="59" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7080</v>
+        <f t="shared" si="6"/>
+        <v>6837</v>
       </c>
       <c r="B59" s="54" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C59" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D59" s="70">
-        <v>1001022467080</v>
+        <v>1001022556837</v>
       </c>
       <c r="E59" s="24"/>
-      <c r="F59" s="23">
-        <v>0.41</v>
+      <c r="F59" s="58">
+        <v>0.4</v>
       </c>
       <c r="G59" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H59" s="14">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="I59" s="14">
-        <v>50</v>
-      </c>
-      <c r="J59" s="29"/>
+      <c r="H59" s="59">
+        <v>2.4</v>
+      </c>
+      <c r="I59" s="59">
+        <v>45</v>
+      </c>
+      <c r="J59" s="59"/>
+      <c r="K59" s="60"/>
       <c r="L59" s="120"/>
+      <c r="M59" s="120"/>
+      <c r="N59" s="120"/>
+      <c r="O59" s="120"/>
+      <c r="P59" s="120"/>
+      <c r="Q59" s="120"/>
+      <c r="R59" s="120"/>
+      <c r="S59" s="120"/>
+      <c r="T59" s="120"/>
+      <c r="U59" s="120"/>
+      <c r="V59" s="120"/>
+      <c r="W59" s="120"/>
+      <c r="X59" s="120"/>
+      <c r="Y59" s="120"/>
+      <c r="Z59" s="120"/>
+      <c r="AA59" s="120"/>
+      <c r="AB59" s="120"/>
+      <c r="AC59" s="120"/>
+      <c r="AD59" s="120"/>
+      <c r="AE59" s="120"/>
+      <c r="AF59" s="120"/>
+      <c r="AG59" s="120"/>
+      <c r="AH59" s="120"/>
+      <c r="AI59" s="120"/>
+      <c r="AJ59" s="120"/>
+      <c r="AK59" s="120"/>
+      <c r="AL59" s="120"/>
+      <c r="AM59" s="120"/>
+      <c r="AN59" s="120"/>
+      <c r="AO59" s="120"/>
+      <c r="AP59" s="120"/>
+      <c r="AQ59" s="120"/>
+      <c r="AR59" s="120"/>
+      <c r="AS59" s="120"/>
+      <c r="AT59" s="120"/>
+      <c r="AU59" s="120"/>
+      <c r="AV59" s="120"/>
+      <c r="AW59" s="120"/>
+      <c r="AX59" s="120"/>
+      <c r="AY59" s="120"/>
+      <c r="AZ59" s="120"/>
+      <c r="BA59" s="120"/>
+      <c r="BB59" s="120"/>
+      <c r="BC59" s="120"/>
+      <c r="BD59" s="120"/>
+      <c r="BE59" s="120"/>
+      <c r="BF59" s="120"/>
+      <c r="BG59" s="120"/>
+      <c r="BH59" s="120"/>
+      <c r="BI59" s="120"/>
+      <c r="BJ59" s="120"/>
+      <c r="BK59" s="120"/>
+      <c r="BL59" s="120"/>
+      <c r="BM59" s="120"/>
+      <c r="BN59" s="120"/>
+      <c r="BO59" s="120"/>
     </row>
     <row r="60" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>6724</v>
+        <f t="shared" si="6"/>
+        <v>7080</v>
       </c>
       <c r="B60" s="54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C60" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D60" s="70">
-        <v>1001020836724</v>
+        <v>1001022467080</v>
       </c>
       <c r="E60" s="24"/>
       <c r="F60" s="23">
         <v>0.41</v>
       </c>
       <c r="G60" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H60" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="I60" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J60" s="29"/>
       <c r="L60" s="120"/>
     </row>
     <row r="61" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7066</v>
+        <f t="shared" si="6"/>
+        <v>6724</v>
       </c>
       <c r="B61" s="54" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C61" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D61" s="70">
-        <v>1001022377066</v>
+        <v>1001020836724</v>
       </c>
       <c r="E61" s="24"/>
       <c r="F61" s="23">
         <v>0.41</v>
       </c>
       <c r="G61" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H61" s="14">
         <v>4.0999999999999996</v>
       </c>
       <c r="I61" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J61" s="29"/>
       <c r="L61" s="120"/>
     </row>
     <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>6713</v>
+        <f t="shared" si="6"/>
+        <v>7066</v>
       </c>
       <c r="B62" s="54" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C62" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D62" s="70">
-        <v>1001022246713</v>
+        <v>1001022377066</v>
       </c>
       <c r="E62" s="24"/>
       <c r="F62" s="23">
         <v>0.41</v>
       </c>
       <c r="G62" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H62" s="14">
-        <v>3.28</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I62" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J62" s="29"/>
       <c r="L62" s="120"/>
     </row>
     <row r="63" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7255</v>
+        <f t="shared" si="6"/>
+        <v>6713</v>
       </c>
       <c r="B63" s="54" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C63" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D63" s="70">
-        <v>1001025507255</v>
+        <v>1001022246713</v>
       </c>
       <c r="E63" s="24"/>
       <c r="F63" s="23">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G63" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H63" s="14">
-        <v>2.4</v>
+        <v>3.28</v>
       </c>
       <c r="I63" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J63" s="29"/>
       <c r="L63" s="120"/>
     </row>
     <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>6602</v>
+        <f t="shared" si="6"/>
+        <v>7255</v>
       </c>
       <c r="B64" s="54" t="s">
-        <v>155</v>
+        <v>37</v>
       </c>
       <c r="C64" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D64" s="70">
-        <v>1001021966602</v>
+        <v>1001025507255</v>
       </c>
       <c r="E64" s="24"/>
       <c r="F64" s="23">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="G64" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H64" s="14">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="I64" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J64" s="29"/>
       <c r="L64" s="120"/>
     </row>
     <row r="65" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7073</v>
+        <f t="shared" si="6"/>
+        <v>6602</v>
       </c>
       <c r="B65" s="54" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="C65" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D65" s="70">
-        <v>1001022657073</v>
+        <v>1001021966602</v>
       </c>
       <c r="E65" s="24"/>
       <c r="F65" s="23">
         <v>0.35</v>
       </c>
       <c r="G65" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H65" s="14">
         <v>2.8</v>
       </c>
       <c r="I65" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J65" s="29"/>
       <c r="L65" s="120"/>
     </row>
     <row r="66" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7276</v>
+        <f t="shared" si="6"/>
+        <v>7073</v>
       </c>
       <c r="B66" s="54" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C66" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D66" s="70">
-        <v>1001022467276</v>
+        <v>1001022657073</v>
       </c>
       <c r="E66" s="24"/>
       <c r="F66" s="23">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="G66" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H66" s="14">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="I66" s="14">
         <v>50</v>
@@ -10165,59 +10227,59 @@
     </row>
     <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>6616</v>
+        <f t="shared" si="6"/>
+        <v>7276</v>
       </c>
       <c r="B67" s="54" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C67" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D67" s="70">
-        <v>1001024976616</v>
+        <v>1001022467276</v>
       </c>
       <c r="E67" s="24"/>
       <c r="F67" s="23">
         <v>0.3</v>
       </c>
       <c r="G67" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H67" s="14">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="I67" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J67" s="29"/>
       <c r="L67" s="120"/>
     </row>
     <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7385</v>
+        <f t="shared" si="6"/>
+        <v>6616</v>
       </c>
       <c r="B68" s="54" t="s">
-        <v>163</v>
+        <v>42</v>
       </c>
       <c r="C68" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D68" s="70">
-        <v>1001027067385</v>
+        <v>1001024976616</v>
       </c>
       <c r="E68" s="24"/>
       <c r="F68" s="23">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="G68" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H68" s="14">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="I68" s="14">
         <v>45</v>
@@ -10227,28 +10289,28 @@
     </row>
     <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7044</v>
+        <f t="shared" si="6"/>
+        <v>7385</v>
       </c>
       <c r="B69" s="54" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C69" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D69" s="70">
-        <v>1001025167044</v>
+        <v>1001027067385</v>
       </c>
       <c r="E69" s="24"/>
       <c r="F69" s="23">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="G69" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H69" s="14">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="I69" s="14">
         <v>45</v>
@@ -10256,30 +10318,30 @@
       <c r="J69" s="29"/>
       <c r="L69" s="120"/>
     </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>7460</v>
+        <f t="shared" si="6"/>
+        <v>7044</v>
       </c>
       <c r="B70" s="54" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C70" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D70" s="70">
-        <v>1001027247460</v>
+        <v>1001025167044</v>
       </c>
       <c r="E70" s="24"/>
       <c r="F70" s="23">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="G70" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H70" s="14">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="I70" s="14">
         <v>45</v>
@@ -10287,105 +10349,105 @@
       <c r="J70" s="29"/>
       <c r="L70" s="120"/>
     </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B71" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C71" s="42"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="42"/>
-      <c r="H71" s="42"/>
-      <c r="I71" s="42"/>
-      <c r="J71" s="43"/>
-      <c r="L71" s="120"/>
-    </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>6527</v>
-      </c>
-      <c r="B72" s="115" t="s">
-        <v>152</v>
-      </c>
-      <c r="C72" s="116" t="s">
-        <v>22</v>
-      </c>
-      <c r="D72" s="57">
-        <v>1001031076527</v>
-      </c>
-      <c r="E72" s="24"/>
-      <c r="F72" s="58">
-        <v>1</v>
-      </c>
-      <c r="G72" s="23">
-        <f t="shared" ref="G72:G76" si="8">E72</f>
-        <v>0</v>
-      </c>
-      <c r="H72" s="59">
-        <v>3</v>
-      </c>
-      <c r="I72" s="59">
-        <v>45</v>
-      </c>
-      <c r="J72" s="59"/>
-      <c r="L72" s="120"/>
-    </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>6550</v>
-      </c>
-      <c r="B73" s="115" t="s">
-        <v>151</v>
-      </c>
-      <c r="C73" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D73" s="51">
-        <v>1001032736550</v>
-      </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="23">
-        <v>1</v>
-      </c>
-      <c r="G73" s="23">
+    <row r="71" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>7460</v>
+      </c>
+      <c r="B71" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="C71" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="70">
+        <v>1001027247460</v>
+      </c>
+      <c r="E71" s="24"/>
+      <c r="F71" s="23">
+        <v>0.33</v>
+      </c>
+      <c r="G71" s="23">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="H73" s="14">
+      <c r="H71" s="14">
+        <v>2.64</v>
+      </c>
+      <c r="I71" s="14">
+        <v>45</v>
+      </c>
+      <c r="J71" s="29"/>
+      <c r="L71" s="120"/>
+    </row>
+    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="C72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+      <c r="I72" s="42"/>
+      <c r="J72" s="43"/>
+      <c r="L72" s="120"/>
+    </row>
+    <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="56" t="str">
+        <f t="shared" ref="A73:A79" si="9">RIGHT(D73,4)</f>
+        <v>6527</v>
+      </c>
+      <c r="B73" s="115" t="s">
+        <v>152</v>
+      </c>
+      <c r="C73" s="116" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="57">
+        <v>1001031076527</v>
+      </c>
+      <c r="E73" s="24"/>
+      <c r="F73" s="58">
+        <v>1</v>
+      </c>
+      <c r="G73" s="23">
+        <f t="shared" ref="G73:G77" si="10">E73</f>
+        <v>0</v>
+      </c>
+      <c r="H73" s="59">
         <v>3</v>
       </c>
-      <c r="I73" s="14">
+      <c r="I73" s="59">
         <v>45</v>
       </c>
-      <c r="J73" s="29"/>
+      <c r="J73" s="59"/>
       <c r="L73" s="120"/>
     </row>
     <row r="74" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="56" t="str">
-        <f t="shared" si="1"/>
-        <v>6549</v>
+        <f t="shared" si="9"/>
+        <v>6550</v>
       </c>
       <c r="B74" s="115" t="s">
-        <v>184</v>
+        <v>151</v>
       </c>
       <c r="C74" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D74" s="51">
-        <v>1001032736549</v>
+        <v>1001032736550</v>
       </c>
       <c r="E74" s="24"/>
       <c r="F74" s="23">
         <v>1</v>
       </c>
       <c r="G74" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H74" s="14">
@@ -10399,24 +10461,24 @@
     </row>
     <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="56" t="str">
-        <f t="shared" ref="A75:A78" si="9">RIGHT(D75,4)</f>
-        <v>7001</v>
+        <f t="shared" si="9"/>
+        <v>6549</v>
       </c>
       <c r="B75" s="115" t="s">
-        <v>57</v>
+        <v>184</v>
       </c>
       <c r="C75" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D75" s="51">
-        <v>1001035937001</v>
+        <v>1001032736549</v>
       </c>
       <c r="E75" s="24"/>
       <c r="F75" s="23">
         <v>1</v>
       </c>
       <c r="G75" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H75" s="14">
@@ -10431,23 +10493,23 @@
     <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="56" t="str">
         <f t="shared" si="9"/>
-        <v>6608</v>
-      </c>
-      <c r="B76" s="105" t="s">
-        <v>58</v>
+        <v>7001</v>
+      </c>
+      <c r="B76" s="115" t="s">
+        <v>57</v>
       </c>
       <c r="C76" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D76" s="51">
-        <v>1001033856608</v>
+        <v>1001035937001</v>
       </c>
       <c r="E76" s="24"/>
       <c r="F76" s="23">
         <v>1</v>
       </c>
       <c r="G76" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H76" s="14">
@@ -10462,135 +10524,133 @@
     <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="56" t="str">
         <f t="shared" si="9"/>
-        <v>7059</v>
+        <v>6608</v>
       </c>
       <c r="B77" s="105" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="C77" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D77" s="51">
-        <v>1001035277059</v>
+        <v>1001033856608</v>
       </c>
       <c r="E77" s="24"/>
       <c r="F77" s="23">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G77" s="23">
-        <f t="shared" ref="G77:G78" si="10">E77*F77</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H77" s="14">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="I77" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J77" s="29"/>
       <c r="L77" s="120"/>
     </row>
-    <row r="78" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="56" t="str">
         <f t="shared" si="9"/>
-        <v>6609</v>
+        <v>7059</v>
       </c>
       <c r="B78" s="105" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C78" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D78" s="51">
-        <v>1001033856609</v>
+        <v>1001035277059</v>
       </c>
       <c r="E78" s="24"/>
       <c r="F78" s="23">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G78" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="G78:G79" si="11">E78*F78</f>
         <v>0</v>
       </c>
       <c r="H78" s="14">
         <v>2.4</v>
       </c>
       <c r="I78" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J78" s="29"/>
       <c r="L78" s="120"/>
     </row>
-    <row r="79" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="47" t="s">
+    <row r="79" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="56" t="str">
+        <f t="shared" si="9"/>
+        <v>6609</v>
+      </c>
+      <c r="B79" s="105" t="s">
+        <v>153</v>
+      </c>
+      <c r="C79" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D79" s="51">
+        <v>1001033856609</v>
+      </c>
+      <c r="E79" s="24"/>
+      <c r="F79" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="G79" s="23">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H79" s="14">
+        <v>2.4</v>
+      </c>
+      <c r="I79" s="14">
+        <v>45</v>
+      </c>
+      <c r="J79" s="29"/>
+      <c r="L79" s="120"/>
+    </row>
+    <row r="80" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B79" s="42" t="s">
+      <c r="B80" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="C79" s="42"/>
-      <c r="D79" s="42"/>
-      <c r="E79" s="42"/>
-      <c r="F79" s="41"/>
-      <c r="G79" s="42"/>
-      <c r="H79" s="42"/>
-      <c r="I79" s="42"/>
-      <c r="J79" s="43"/>
-      <c r="L79" s="120"/>
-    </row>
-    <row r="80" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="143" t="str">
-        <f t="shared" ref="A80:A104" si="11">RIGHT(D80,4)</f>
+      <c r="C80" s="42"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="42"/>
+      <c r="I80" s="42"/>
+      <c r="J80" s="43"/>
+      <c r="L80" s="120"/>
+    </row>
+    <row r="81" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="56" t="str">
+        <f t="shared" ref="A81:A107" si="12">RIGHT(D81,4)</f>
         <v>7564</v>
       </c>
-      <c r="B80" s="53" t="s">
+      <c r="B81" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="C80" s="50" t="s">
+      <c r="C81" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D80" s="51">
+      <c r="D81" s="51">
         <v>1001303637564</v>
-      </c>
-      <c r="E80" s="24"/>
-      <c r="F80" s="23">
-        <v>0.84</v>
-      </c>
-      <c r="G80" s="23">
-        <f t="shared" ref="G80:G85" si="12">E80</f>
-        <v>0</v>
-      </c>
-      <c r="H80" s="14">
-        <v>5.04</v>
-      </c>
-      <c r="I80" s="14">
-        <v>45</v>
-      </c>
-      <c r="J80" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="L80" s="120"/>
-    </row>
-    <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7133</v>
-      </c>
-      <c r="B81" s="54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C81" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D81" s="57">
-        <v>1001300367133</v>
       </c>
       <c r="E81" s="24"/>
       <c r="F81" s="23">
         <v>0.84</v>
       </c>
       <c r="G81" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="G81:G86" si="13">E81</f>
         <v>0</v>
       </c>
       <c r="H81" s="14">
@@ -10599,29 +10659,31 @@
       <c r="I81" s="14">
         <v>45</v>
       </c>
-      <c r="J81" s="59"/>
+      <c r="J81" s="52" t="s">
+        <v>170</v>
+      </c>
       <c r="L81" s="120"/>
     </row>
     <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>6946</v>
+        <f t="shared" si="12"/>
+        <v>7133</v>
       </c>
       <c r="B82" s="54" t="s">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="C82" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D82" s="57">
-        <v>1001300456946</v>
+        <v>1001300367133</v>
       </c>
       <c r="E82" s="24"/>
       <c r="F82" s="23">
         <v>0.84</v>
       </c>
       <c r="G82" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H82" s="14">
@@ -10630,64 +10692,64 @@
       <c r="I82" s="14">
         <v>45</v>
       </c>
-      <c r="J82" s="29"/>
+      <c r="J82" s="59"/>
       <c r="L82" s="120"/>
     </row>
     <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7132</v>
+        <f t="shared" si="12"/>
+        <v>6946</v>
       </c>
       <c r="B83" s="54" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C83" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D83" s="57">
-        <v>1001300517132</v>
+        <v>1001300456946</v>
       </c>
       <c r="E83" s="24"/>
-      <c r="F83" s="58">
+      <c r="F83" s="23">
         <v>0.84</v>
       </c>
       <c r="G83" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H83" s="59">
+      <c r="H83" s="14">
         <v>5.04</v>
       </c>
-      <c r="I83" s="59">
+      <c r="I83" s="14">
         <v>45</v>
       </c>
-      <c r="J83" s="59"/>
+      <c r="J83" s="29"/>
       <c r="L83" s="120"/>
     </row>
     <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>5544</v>
+        <f t="shared" si="12"/>
+        <v>7132</v>
       </c>
       <c r="B84" s="54" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="C84" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D84" s="57">
-        <v>1001051875544</v>
+        <v>1001300517132</v>
       </c>
       <c r="E84" s="24"/>
       <c r="F84" s="58">
-        <v>0.81</v>
+        <v>0.84</v>
       </c>
       <c r="G84" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H84" s="59">
-        <v>4.8600000000000003</v>
+        <v>5.04</v>
       </c>
       <c r="I84" s="59">
         <v>45</v>
@@ -10697,80 +10759,80 @@
     </row>
     <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>6946</v>
+        <f t="shared" si="12"/>
+        <v>5544</v>
       </c>
       <c r="B85" s="54" t="s">
-        <v>179</v>
+        <v>72</v>
       </c>
       <c r="C85" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D85" s="57">
-        <v>1001300456946</v>
+        <v>1001051875544</v>
       </c>
       <c r="E85" s="24"/>
-      <c r="F85" s="58"/>
+      <c r="F85" s="58">
+        <v>0.81</v>
+      </c>
       <c r="G85" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H85" s="59"/>
-      <c r="I85" s="59"/>
+      <c r="H85" s="59">
+        <v>4.8600000000000003</v>
+      </c>
+      <c r="I85" s="59">
+        <v>45</v>
+      </c>
       <c r="J85" s="59"/>
       <c r="L85" s="120"/>
     </row>
     <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7149</v>
+        <f t="shared" si="12"/>
+        <v>6946</v>
       </c>
       <c r="B86" s="54" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="C86" s="55" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D86" s="57">
-        <v>1001303637149</v>
+        <v>1001300456946</v>
       </c>
       <c r="E86" s="24"/>
-      <c r="F86" s="58">
-        <v>0.84</v>
-      </c>
+      <c r="F86" s="58"/>
       <c r="G86" s="23">
-        <f>E86*F86</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="H86" s="59">
-        <v>5.04</v>
-      </c>
-      <c r="I86" s="59">
-        <v>50</v>
-      </c>
+      <c r="H86" s="59"/>
+      <c r="I86" s="59"/>
       <c r="J86" s="59"/>
       <c r="L86" s="120"/>
     </row>
     <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7157</v>
+        <f t="shared" si="12"/>
+        <v>7149</v>
       </c>
       <c r="B87" s="54" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="C87" s="55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D87" s="57">
-        <v>1001300387157</v>
+        <v>1001303637149</v>
       </c>
       <c r="E87" s="24"/>
       <c r="F87" s="58">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="G87" s="23">
-        <f t="shared" ref="G87:G88" si="13">E87</f>
+        <f>E87*F87</f>
         <v>0</v>
       </c>
       <c r="H87" s="59">
@@ -10784,28 +10846,28 @@
     </row>
     <row r="88" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7166</v>
+        <f t="shared" si="12"/>
+        <v>7157</v>
       </c>
       <c r="B88" s="54" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C88" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D88" s="57">
-        <v>1001303987166</v>
+        <v>1001300387157</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="58">
-        <v>0.7</v>
+        <v>0.63</v>
       </c>
       <c r="G88" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="G88:G89" si="14">E88</f>
         <v>0</v>
       </c>
       <c r="H88" s="59">
-        <v>5.6</v>
+        <v>5.04</v>
       </c>
       <c r="I88" s="59">
         <v>50</v>
@@ -10814,58 +10876,56 @@
       <c r="L88" s="120"/>
     </row>
     <row r="89" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="143" t="str">
-        <f t="shared" si="11"/>
-        <v>7603</v>
+      <c r="A89" s="56" t="str">
+        <f t="shared" si="12"/>
+        <v>7166</v>
       </c>
       <c r="B89" s="54" t="s">
-        <v>122</v>
+        <v>71</v>
       </c>
       <c r="C89" s="55" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D89" s="57">
-        <v>1001303637603</v>
+        <v>1001303987166</v>
       </c>
       <c r="E89" s="24"/>
-      <c r="F89" s="23">
-        <v>0.33</v>
+      <c r="F89" s="58">
+        <v>0.7</v>
       </c>
       <c r="G89" s="23">
-        <f t="shared" ref="G89:G106" si="14">E89*F89</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="H89" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I89" s="14">
-        <v>45</v>
-      </c>
-      <c r="J89" s="52" t="s">
-        <v>171</v>
-      </c>
+      <c r="H89" s="59">
+        <v>5.6</v>
+      </c>
+      <c r="I89" s="59">
+        <v>50</v>
+      </c>
+      <c r="J89" s="59"/>
       <c r="L89" s="120"/>
     </row>
     <row r="90" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>6807</v>
+        <f t="shared" si="12"/>
+        <v>7603</v>
       </c>
       <c r="B90" s="54" t="s">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="C90" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D90" s="57">
-        <v>1001300366807</v>
+        <v>1001303637603</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
         <v>0.33</v>
       </c>
       <c r="G90" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="G90:G107" si="15">E90*F90</f>
         <v>0</v>
       </c>
       <c r="H90" s="14">
@@ -10874,29 +10934,31 @@
       <c r="I90" s="14">
         <v>45</v>
       </c>
-      <c r="J90" s="29"/>
+      <c r="J90" s="52" t="s">
+        <v>171</v>
+      </c>
       <c r="L90" s="120"/>
     </row>
     <row r="91" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>6787</v>
+        <f t="shared" si="12"/>
+        <v>6807</v>
       </c>
       <c r="B91" s="54" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C91" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D91" s="57">
-        <v>1001300456787</v>
+        <v>1001300366807</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
         <v>0.33</v>
       </c>
       <c r="G91" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H91" s="14">
@@ -10910,210 +10972,210 @@
     </row>
     <row r="92" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7489</v>
+        <f t="shared" si="12"/>
+        <v>6787</v>
       </c>
       <c r="B92" s="54" t="s">
-        <v>215</v>
+        <v>65</v>
       </c>
       <c r="C92" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="57">
-        <v>1001307357489</v>
+        <v>1001300456787</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.33</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" ref="G92" si="15">E92*F92</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H92" s="14"/>
-      <c r="I92" s="14"/>
+      <c r="H92" s="14">
+        <v>2.64</v>
+      </c>
+      <c r="I92" s="14">
+        <v>45</v>
+      </c>
       <c r="J92" s="29"/>
       <c r="L92" s="120"/>
     </row>
     <row r="93" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>6697</v>
-      </c>
-      <c r="B93" s="114" t="s">
-        <v>66</v>
+        <f t="shared" si="12"/>
+        <v>7489</v>
+      </c>
+      <c r="B93" s="54" t="s">
+        <v>214</v>
       </c>
       <c r="C93" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D93" s="57">
-        <v>1001301876697</v>
+        <v>1001307357489</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G93" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="G93" si="16">E93*F93</f>
         <v>0</v>
       </c>
-      <c r="H93" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I93" s="14">
-        <v>45</v>
-      </c>
+      <c r="H93" s="14"/>
+      <c r="I93" s="14"/>
       <c r="J93" s="29"/>
       <c r="L93" s="120"/>
     </row>
     <row r="94" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7169</v>
+        <f t="shared" si="12"/>
+        <v>6697</v>
       </c>
       <c r="B94" s="114" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C94" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D94" s="57">
-        <v>1001303987169</v>
+        <v>1001301876697</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
         <v>0.35</v>
       </c>
       <c r="G94" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H94" s="14">
         <v>2.8</v>
       </c>
       <c r="I94" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J94" s="29"/>
       <c r="L94" s="120"/>
     </row>
-    <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7233</v>
-      </c>
-      <c r="B95" s="53" t="s">
-        <v>181</v>
-      </c>
-      <c r="C95" s="50" t="s">
+        <f t="shared" si="12"/>
+        <v>7169</v>
+      </c>
+      <c r="B95" s="114" t="s">
+        <v>70</v>
+      </c>
+      <c r="C95" s="55" t="s">
         <v>20</v>
       </c>
-      <c r="D95" s="51">
-        <v>1001303637233</v>
+      <c r="D95" s="57">
+        <v>1001303987169</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G95" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H95" s="14">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="I95" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J95" s="29"/>
       <c r="L95" s="120"/>
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7236</v>
+        <f t="shared" si="12"/>
+        <v>7233</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="C96" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D96" s="51">
-        <v>1001304507236</v>
+        <v>1001303637233</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G96" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H96" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I96" s="14">
         <v>45</v>
       </c>
-      <c r="J96" s="49"/>
+      <c r="J96" s="29"/>
       <c r="L96" s="120"/>
     </row>
     <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7177</v>
+        <f t="shared" si="12"/>
+        <v>7236</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="51">
-        <v>1001302347177</v>
+        <v>1001304507236</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G97" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>2.8</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I97" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J97" s="49"/>
       <c r="L97" s="120"/>
     </row>
     <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7232</v>
+        <f t="shared" si="12"/>
+        <v>7177</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="51">
-        <v>1001302277232</v>
+        <v>1001302347177</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G98" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I98" s="14">
         <v>50</v>
@@ -11123,28 +11185,28 @@
     </row>
     <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7154</v>
+        <f t="shared" si="12"/>
+        <v>7232</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="51">
-        <v>1001300387154</v>
+        <v>1001302277232</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.35</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G99" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>2.8</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I99" s="14">
         <v>50</v>
@@ -11154,59 +11216,59 @@
     </row>
     <row r="100" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7238</v>
+        <f t="shared" si="12"/>
+        <v>7154</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>123</v>
+        <v>64</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D100" s="51">
-        <v>1001305197238</v>
+        <v>1001300387154</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G100" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="I100" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J100" s="49"/>
       <c r="L100" s="120"/>
     </row>
     <row r="101" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7237</v>
+        <f t="shared" si="12"/>
+        <v>7238</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>67</v>
+        <v>123</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D101" s="51">
-        <v>1001304497237</v>
+        <v>1001305197238</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G101" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H101" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I101" s="14">
         <v>45</v>
@@ -11216,24 +11278,24 @@
     </row>
     <row r="102" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7241</v>
+        <f t="shared" si="12"/>
+        <v>7237</v>
       </c>
       <c r="B102" s="53" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="51">
-        <v>1001303107241</v>
+        <v>1001304497237</v>
       </c>
       <c r="E102" s="24"/>
       <c r="F102" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G102" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H102" s="14">
@@ -11247,55 +11309,55 @@
     </row>
     <row r="103" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7332</v>
+        <f t="shared" si="12"/>
+        <v>7241</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C103" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D103" s="51">
-        <v>1001301777332</v>
+        <v>1001303107241</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G103" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H103" s="14">
         <v>2.2400000000000002</v>
       </c>
       <c r="I103" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J103" s="49"/>
       <c r="L103" s="120"/>
     </row>
     <row r="104" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="56" t="str">
-        <f t="shared" si="11"/>
-        <v>7333</v>
+        <f t="shared" si="12"/>
+        <v>7332</v>
       </c>
       <c r="B104" s="53" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C104" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D104" s="51">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G104" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H104" s="14">
@@ -11308,56 +11370,56 @@
       <c r="L104" s="120"/>
     </row>
     <row r="105" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="143">
-        <v>7608</v>
+      <c r="A105" s="56" t="str">
+        <f t="shared" si="12"/>
+        <v>7333</v>
       </c>
       <c r="B105" s="53" t="s">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="C105" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D105" s="51">
-        <v>1001304197608</v>
+        <v>1001303987333</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G105" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H105" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I105" s="14">
-        <v>45</v>
-      </c>
-      <c r="J105" s="52" t="s">
-        <v>209</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J105" s="49"/>
       <c r="L105" s="120"/>
     </row>
-    <row r="106" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="143">
-        <v>7610</v>
+    <row r="106" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="56" t="str">
+        <f t="shared" si="12"/>
+        <v>7608</v>
       </c>
       <c r="B106" s="53" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C106" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D106" s="51">
-        <v>1001306717610</v>
+        <v>1001304197608</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="23">
         <v>0.1</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H106" s="14">
@@ -11367,112 +11429,58 @@
         <v>45</v>
       </c>
       <c r="J106" s="52" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="L106" s="120"/>
     </row>
-    <row r="107" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="47" t="s">
+    <row r="107" spans="1:67" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="56" t="str">
+        <f t="shared" si="12"/>
+        <v>7610</v>
+      </c>
+      <c r="B107" s="53" t="s">
+        <v>209</v>
+      </c>
+      <c r="C107" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D107" s="51">
+        <v>1001306717610</v>
+      </c>
+      <c r="E107" s="24"/>
+      <c r="F107" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G107" s="23">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="H107" s="14">
+        <v>1</v>
+      </c>
+      <c r="I107" s="14">
+        <v>45</v>
+      </c>
+      <c r="J107" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="L107" s="120"/>
+    </row>
+    <row r="108" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B107" s="42" t="s">
+      <c r="B108" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="C107" s="42"/>
-      <c r="D107" s="42"/>
-      <c r="E107" s="42"/>
-      <c r="F107" s="41"/>
-      <c r="G107" s="42"/>
-      <c r="H107" s="42"/>
-      <c r="I107" s="42"/>
-      <c r="J107" s="43"/>
-      <c r="K107" s="60"/>
-      <c r="L107" s="120"/>
-      <c r="M107" s="120"/>
-      <c r="N107" s="120"/>
-      <c r="O107" s="120"/>
-      <c r="P107" s="120"/>
-      <c r="Q107" s="120"/>
-      <c r="R107" s="120"/>
-      <c r="S107" s="120"/>
-      <c r="T107" s="120"/>
-      <c r="U107" s="120"/>
-      <c r="V107" s="120"/>
-      <c r="W107" s="120"/>
-      <c r="X107" s="120"/>
-      <c r="Y107" s="120"/>
-      <c r="Z107" s="120"/>
-      <c r="AA107" s="120"/>
-      <c r="AB107" s="120"/>
-      <c r="AC107" s="120"/>
-      <c r="AD107" s="120"/>
-      <c r="AE107" s="120"/>
-      <c r="AF107" s="120"/>
-      <c r="AG107" s="120"/>
-      <c r="AH107" s="120"/>
-      <c r="AI107" s="120"/>
-      <c r="AJ107" s="120"/>
-      <c r="AK107" s="120"/>
-      <c r="AL107" s="120"/>
-      <c r="AM107" s="120"/>
-      <c r="AN107" s="120"/>
-      <c r="AO107" s="120"/>
-      <c r="AP107" s="120"/>
-      <c r="AQ107" s="120"/>
-      <c r="AR107" s="120"/>
-      <c r="AS107" s="120"/>
-      <c r="AT107" s="120"/>
-      <c r="AU107" s="120"/>
-      <c r="AV107" s="120"/>
-      <c r="AW107" s="120"/>
-      <c r="AX107" s="120"/>
-      <c r="AY107" s="120"/>
-      <c r="AZ107" s="120"/>
-      <c r="BA107" s="120"/>
-      <c r="BB107" s="120"/>
-      <c r="BC107" s="120"/>
-      <c r="BD107" s="120"/>
-      <c r="BE107" s="120"/>
-      <c r="BF107" s="120"/>
-      <c r="BG107" s="120"/>
-      <c r="BH107" s="120"/>
-      <c r="BI107" s="120"/>
-      <c r="BJ107" s="120"/>
-      <c r="BK107" s="120"/>
-      <c r="BL107" s="120"/>
-      <c r="BM107" s="120"/>
-      <c r="BN107" s="120"/>
-      <c r="BO107" s="120"/>
-    </row>
-    <row r="108" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="56" t="str">
-        <f t="shared" ref="A108:A137" si="16">RIGHT(D108,4)</f>
-        <v>0614</v>
-      </c>
-      <c r="B108" s="54" t="s">
-        <v>140</v>
-      </c>
-      <c r="C108" s="55" t="s">
-        <v>22</v>
-      </c>
-      <c r="D108" s="57">
-        <v>1001060720614</v>
-      </c>
-      <c r="E108" s="24"/>
-      <c r="F108" s="58">
-        <v>0.52</v>
-      </c>
-      <c r="G108" s="23">
-        <f t="shared" ref="G108:G111" si="17">E108</f>
-        <v>0</v>
-      </c>
-      <c r="H108" s="108">
-        <v>3.64</v>
-      </c>
-      <c r="I108" s="107">
-        <v>120</v>
-      </c>
-      <c r="J108" s="59"/>
+      <c r="C108" s="42"/>
+      <c r="D108" s="42"/>
+      <c r="E108" s="42"/>
+      <c r="F108" s="41"/>
+      <c r="G108" s="42"/>
+      <c r="H108" s="42"/>
+      <c r="I108" s="42"/>
+      <c r="J108" s="43"/>
       <c r="K108" s="60"/>
       <c r="L108" s="120"/>
       <c r="M108" s="120"/>
@@ -11531,30 +11539,30 @@
       <c r="BN108" s="120"/>
       <c r="BO108" s="120"/>
     </row>
-    <row r="109" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A109" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>3287</v>
+        <f t="shared" ref="A109:A139" si="17">RIGHT(D109,4)</f>
+        <v>0614</v>
       </c>
       <c r="B109" s="54" t="s">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="C109" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D109" s="57">
-        <v>1001060763287</v>
+        <v>1001060720614</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="58">
-        <v>0.48799999999999999</v>
+        <v>0.52</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="G109:G112" si="18">E109</f>
         <v>0</v>
       </c>
       <c r="H109" s="108">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="I109" s="107">
         <v>120</v>
@@ -11618,61 +11626,117 @@
       <c r="BN109" s="120"/>
       <c r="BO109" s="120"/>
     </row>
-    <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>5708</v>
-      </c>
-      <c r="B110" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C110" s="50" t="s">
+        <f t="shared" si="17"/>
+        <v>3287</v>
+      </c>
+      <c r="B110" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="C110" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="D110" s="51">
-        <v>1001063145708</v>
+      <c r="D110" s="57">
+        <v>1001060763287</v>
       </c>
       <c r="E110" s="24"/>
-      <c r="F110" s="23">
-        <v>0.5</v>
+      <c r="F110" s="58">
+        <v>0.48799999999999999</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H110" s="106">
-        <v>4</v>
-      </c>
-      <c r="I110" s="14">
+      <c r="H110" s="108">
+        <v>3.9</v>
+      </c>
+      <c r="I110" s="107">
         <v>120</v>
       </c>
-      <c r="J110" s="29"/>
+      <c r="J110" s="59"/>
+      <c r="K110" s="60"/>
       <c r="L110" s="120"/>
+      <c r="M110" s="120"/>
+      <c r="N110" s="120"/>
+      <c r="O110" s="120"/>
+      <c r="P110" s="120"/>
+      <c r="Q110" s="120"/>
+      <c r="R110" s="120"/>
+      <c r="S110" s="120"/>
+      <c r="T110" s="120"/>
+      <c r="U110" s="120"/>
+      <c r="V110" s="120"/>
+      <c r="W110" s="120"/>
+      <c r="X110" s="120"/>
+      <c r="Y110" s="120"/>
+      <c r="Z110" s="120"/>
+      <c r="AA110" s="120"/>
+      <c r="AB110" s="120"/>
+      <c r="AC110" s="120"/>
+      <c r="AD110" s="120"/>
+      <c r="AE110" s="120"/>
+      <c r="AF110" s="120"/>
+      <c r="AG110" s="120"/>
+      <c r="AH110" s="120"/>
+      <c r="AI110" s="120"/>
+      <c r="AJ110" s="120"/>
+      <c r="AK110" s="120"/>
+      <c r="AL110" s="120"/>
+      <c r="AM110" s="120"/>
+      <c r="AN110" s="120"/>
+      <c r="AO110" s="120"/>
+      <c r="AP110" s="120"/>
+      <c r="AQ110" s="120"/>
+      <c r="AR110" s="120"/>
+      <c r="AS110" s="120"/>
+      <c r="AT110" s="120"/>
+      <c r="AU110" s="120"/>
+      <c r="AV110" s="120"/>
+      <c r="AW110" s="120"/>
+      <c r="AX110" s="120"/>
+      <c r="AY110" s="120"/>
+      <c r="AZ110" s="120"/>
+      <c r="BA110" s="120"/>
+      <c r="BB110" s="120"/>
+      <c r="BC110" s="120"/>
+      <c r="BD110" s="120"/>
+      <c r="BE110" s="120"/>
+      <c r="BF110" s="120"/>
+      <c r="BG110" s="120"/>
+      <c r="BH110" s="120"/>
+      <c r="BI110" s="120"/>
+      <c r="BJ110" s="120"/>
+      <c r="BK110" s="120"/>
+      <c r="BL110" s="120"/>
+      <c r="BM110" s="120"/>
+      <c r="BN110" s="120"/>
+      <c r="BO110" s="120"/>
     </row>
     <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>4117</v>
+        <f t="shared" si="17"/>
+        <v>5708</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C111" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D111" s="51">
-        <v>1001062504117</v>
+        <v>1001063145708</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H111" s="14">
-        <v>3.95</v>
+      <c r="H111" s="106">
+        <v>4</v>
       </c>
       <c r="I111" s="14">
         <v>120</v>
@@ -11682,28 +11746,28 @@
     </row>
     <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7316</v>
+        <f t="shared" si="17"/>
+        <v>4117</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="C112" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D112" s="51">
-        <v>1001060727316</v>
+        <v>1001062504117</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
-        <v>0.54</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" ref="G112:G125" si="18">E112*F112</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H112" s="14">
-        <v>3.78</v>
+        <v>3.95</v>
       </c>
       <c r="I112" s="14">
         <v>120</v>
@@ -11713,24 +11777,24 @@
     </row>
     <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7317</v>
+        <f t="shared" si="17"/>
+        <v>7316</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C113" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="51">
-        <v>1001066567317</v>
+        <v>1001060727316</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
         <v>0.54</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G113:G126" si="19">E113*F113</f>
         <v>0</v>
       </c>
       <c r="H113" s="14">
@@ -11744,28 +11808,28 @@
     </row>
     <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7143</v>
+        <f t="shared" si="17"/>
+        <v>7317</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D114" s="51">
-        <v>1001060717143</v>
+        <v>1001066567317</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.22</v>
+        <v>0.54</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>1.76</v>
+        <v>3.78</v>
       </c>
       <c r="I114" s="14">
         <v>120</v>
@@ -11775,24 +11839,24 @@
     </row>
     <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7147</v>
+        <f t="shared" si="17"/>
+        <v>7143</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C115" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D115" s="51">
-        <v>1001063237147</v>
+        <v>1001060717143</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
         <v>0.22</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
@@ -11806,90 +11870,90 @@
     </row>
     <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7456</v>
+        <f t="shared" si="17"/>
+        <v>7147</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D116" s="51">
-        <v>1001063097456</v>
+        <v>1001063237147</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I116" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J116" s="29"/>
       <c r="L116" s="120"/>
     </row>
     <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7318</v>
+        <f t="shared" si="17"/>
+        <v>7456</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D117" s="51">
-        <v>1001060727318</v>
+        <v>1001063097456</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="I117" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J117" s="29"/>
       <c r="L117" s="120"/>
     </row>
     <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>3986</v>
+        <f t="shared" si="17"/>
+        <v>7318</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D118" s="51">
-        <v>1001061973986</v>
+        <v>1001060727318</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="I118" s="14">
         <v>120</v>
@@ -11899,55 +11963,55 @@
     </row>
     <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7364</v>
+        <f t="shared" si="17"/>
+        <v>3986</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="51">
-        <v>1001063217364</v>
+        <v>1001061973986</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I119" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J119" s="29"/>
       <c r="L119" s="120"/>
     </row>
     <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7383</v>
+        <f t="shared" si="17"/>
+        <v>7364</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D120" s="51">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
         <v>0.22</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
@@ -11961,55 +12025,55 @@
     </row>
     <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>6967</v>
+        <f t="shared" si="17"/>
+        <v>7383</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D121" s="51">
-        <v>1001063656967</v>
+        <v>1001065467383</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="I121" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J121" s="29"/>
       <c r="L121" s="120"/>
     </row>
     <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>4993</v>
+        <f t="shared" si="17"/>
+        <v>6967</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D122" s="51">
-        <v>1001060764993</v>
+        <v>1001063656967</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
         <v>0.25</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
@@ -12023,24 +12087,24 @@
     </row>
     <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>6937</v>
+        <f t="shared" si="17"/>
+        <v>4993</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D123" s="51">
-        <v>1001063106937</v>
+        <v>1001060764993</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
         <v>0.25</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
@@ -12054,24 +12118,24 @@
     </row>
     <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>5483</v>
+        <f t="shared" si="17"/>
+        <v>6937</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D124" s="51">
-        <v>1001062505483</v>
+        <v>1001063106937</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
         <v>0.25</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
@@ -12085,28 +12149,28 @@
     </row>
     <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>5931</v>
+        <f t="shared" si="17"/>
+        <v>5483</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C125" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D125" s="51">
-        <v>1001060755931</v>
+        <v>1001062505483</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G125" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I125" s="14">
         <v>120</v>
@@ -12116,55 +12180,55 @@
     </row>
     <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>6832</v>
+        <f t="shared" si="17"/>
+        <v>5931</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D126" s="51">
-        <v>1001065616832</v>
+        <v>1001060755931</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.215</v>
+        <v>0.22</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" ref="G126:G127" si="19">E126</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="I126" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J126" s="29"/>
       <c r="L126" s="120"/>
     </row>
     <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7299</v>
+        <f t="shared" si="17"/>
+        <v>6832</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C127" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D127" s="51">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
         <v>0.215</v>
       </c>
       <c r="G127" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G127:G128" si="20">E127</f>
         <v>0</v>
       </c>
       <c r="H127" s="14">
@@ -12178,90 +12242,90 @@
     </row>
     <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7386</v>
+        <f t="shared" si="17"/>
+        <v>7299</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D128" s="51">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G128" s="23">
-        <f t="shared" ref="G128:G138" si="20">E128*F128</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I128" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J128" s="29"/>
       <c r="L128" s="120"/>
     </row>
     <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>5679</v>
+        <f t="shared" si="17"/>
+        <v>7386</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D129" s="51">
-        <v>1001190765679</v>
+        <v>1001067017386</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
         <v>0.15</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G129:G139" si="21">E129*F129</f>
         <v>0</v>
       </c>
       <c r="H129" s="14">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="I129" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J129" s="29"/>
       <c r="L129" s="120"/>
     </row>
     <row r="130" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>7382</v>
+        <f t="shared" si="17"/>
+        <v>5679</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D130" s="51">
-        <v>1001203117382</v>
+        <v>1001190765679</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G130" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <v>0.96</v>
+        <v>1.2</v>
       </c>
       <c r="I130" s="14">
         <v>60</v>
@@ -12270,120 +12334,122 @@
       <c r="L130" s="120"/>
     </row>
     <row r="131" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="143">
-        <v>7613</v>
+      <c r="A131" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7382</v>
       </c>
       <c r="B131" s="53" t="s">
-        <v>216</v>
+        <v>84</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D131" s="51">
-        <v>1001061977613</v>
+        <v>1001203117382</v>
       </c>
       <c r="E131" s="24"/>
       <c r="F131" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G131" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H131" s="14">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="I131" s="14">
         <v>60</v>
       </c>
-      <c r="J131" s="52" t="s">
-        <v>205</v>
-      </c>
+      <c r="J131" s="29"/>
       <c r="L131" s="120"/>
     </row>
     <row r="132" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="143">
-        <v>7616</v>
+      <c r="A132" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7613</v>
       </c>
       <c r="B132" s="53" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D132" s="51">
-        <v>1001062507616</v>
+        <v>1001061977613</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="23">
         <v>0.1</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H132" s="14">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="I132" s="14">
         <v>60</v>
       </c>
       <c r="J132" s="52" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L132" s="120"/>
     </row>
     <row r="133" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>6221</v>
+        <f t="shared" si="17"/>
+        <v>7616</v>
       </c>
       <c r="B133" s="53" t="s">
-        <v>86</v>
+        <v>206</v>
       </c>
       <c r="C133" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D133" s="51">
-        <v>1001205376221</v>
+        <v>1001062507616</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H133" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I133" s="14">
         <v>60</v>
       </c>
-      <c r="J133" s="29"/>
+      <c r="J133" s="52" t="s">
+        <v>207</v>
+      </c>
       <c r="L133" s="120"/>
     </row>
     <row r="134" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>6222</v>
+        <f t="shared" si="17"/>
+        <v>6221</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D134" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="23">
         <v>0.09</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H134" s="14">
@@ -12396,93 +12462,93 @@
       <c r="L134" s="120"/>
     </row>
     <row r="135" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="145" t="str">
-        <f t="shared" si="16"/>
-        <v>6834</v>
-      </c>
-      <c r="B135" s="146" t="s">
-        <v>132</v>
-      </c>
-      <c r="C135" s="147" t="s">
+      <c r="A135" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>6222</v>
+      </c>
+      <c r="B135" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="C135" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D135" s="148">
-        <v>1001203146834</v>
-      </c>
-      <c r="E135" s="149"/>
-      <c r="F135" s="150">
-        <v>0.1</v>
-      </c>
-      <c r="G135" s="150">
-        <f t="shared" si="20"/>
+      <c r="D135" s="51">
+        <v>1001205386222</v>
+      </c>
+      <c r="E135" s="24"/>
+      <c r="F135" s="23">
+        <v>0.09</v>
+      </c>
+      <c r="G135" s="23">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H135" s="151">
-        <v>1</v>
-      </c>
-      <c r="I135" s="151">
+      <c r="H135" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="I135" s="14">
         <v>60</v>
       </c>
-      <c r="J135" s="151" t="s">
-        <v>204</v>
-      </c>
+      <c r="J135" s="29"/>
       <c r="L135" s="120"/>
     </row>
     <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>6965</v>
-      </c>
-      <c r="B136" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="C136" s="50" t="s">
+        <f t="shared" si="17"/>
+        <v>6834</v>
+      </c>
+      <c r="B136" s="144" t="s">
+        <v>132</v>
+      </c>
+      <c r="C136" s="145" t="s">
         <v>20</v>
       </c>
-      <c r="D136" s="51">
-        <v>1001206356965</v>
-      </c>
-      <c r="E136" s="24"/>
-      <c r="F136" s="23">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G136" s="23">
-        <f t="shared" si="20"/>
+      <c r="D136" s="146">
+        <v>1001203146834</v>
+      </c>
+      <c r="E136" s="147"/>
+      <c r="F136" s="148">
+        <v>0.1</v>
+      </c>
+      <c r="G136" s="148">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="H136" s="14">
-        <v>0.98</v>
-      </c>
-      <c r="I136" s="14">
+      <c r="H136" s="149">
+        <v>1</v>
+      </c>
+      <c r="I136" s="149">
         <v>60</v>
       </c>
-      <c r="J136" s="29"/>
+      <c r="J136" s="149" t="s">
+        <v>204</v>
+      </c>
       <c r="L136" s="120"/>
     </row>
     <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="56" t="str">
-        <f t="shared" si="16"/>
-        <v>6557</v>
+        <f t="shared" si="17"/>
+        <v>6965</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D137" s="51">
-        <v>1001200756557</v>
+        <v>1001206356965</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="23">
-        <v>0.1</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="G137" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H137" s="14">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="I137" s="14">
         <v>60</v>
@@ -12490,25 +12556,26 @@
       <c r="J137" s="29"/>
       <c r="L137" s="120"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="143">
-        <v>7626</v>
+    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>6557</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>202</v>
+        <v>135</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D138" s="51">
-        <v>1001066607626</v>
+        <v>1001200756557</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="23">
         <v>0.1</v>
       </c>
       <c r="G138" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H138" s="14">
@@ -12517,173 +12584,117 @@
       <c r="I138" s="14">
         <v>60</v>
       </c>
-      <c r="J138" s="52" t="s">
+      <c r="J138" s="29"/>
+      <c r="L138" s="120"/>
+    </row>
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="56" t="str">
+        <f t="shared" si="17"/>
+        <v>7626</v>
+      </c>
+      <c r="B139" s="53" t="s">
+        <v>202</v>
+      </c>
+      <c r="C139" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D139" s="51">
+        <v>1001066607626</v>
+      </c>
+      <c r="E139" s="24"/>
+      <c r="F139" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G139" s="23">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="H139" s="14">
+        <v>1</v>
+      </c>
+      <c r="I139" s="14">
+        <v>60</v>
+      </c>
+      <c r="J139" s="52" t="s">
         <v>203</v>
       </c>
-      <c r="L138" s="120"/>
-    </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="47" t="s">
+      <c r="L139" s="120"/>
+    </row>
+    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B139" s="42" t="s">
+      <c r="B140" s="42" t="s">
         <v>91</v>
       </c>
-      <c r="C139" s="42"/>
-      <c r="D139" s="42"/>
-      <c r="E139" s="42"/>
-      <c r="F139" s="41"/>
-      <c r="G139" s="42"/>
-      <c r="H139" s="42"/>
-      <c r="I139" s="42"/>
-      <c r="J139" s="43"/>
-      <c r="L139" s="120"/>
-    </row>
-    <row r="140" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="56" t="str">
-        <f t="shared" ref="A140:A149" si="21">RIGHT(D140,4)</f>
+      <c r="C140" s="42"/>
+      <c r="D140" s="42"/>
+      <c r="E140" s="42"/>
+      <c r="F140" s="41"/>
+      <c r="G140" s="42"/>
+      <c r="H140" s="42"/>
+      <c r="I140" s="42"/>
+      <c r="J140" s="43"/>
+      <c r="L140" s="120"/>
+    </row>
+    <row r="141" spans="1:67" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="56" t="str">
+        <f t="shared" ref="A141:A153" si="22">RIGHT(D141,4)</f>
         <v>6470</v>
       </c>
-      <c r="B140" s="112" t="s">
+      <c r="B141" s="112" t="s">
         <v>116</v>
       </c>
-      <c r="C140" s="50" t="s">
+      <c r="C141" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D140" s="111">
+      <c r="D141" s="111">
         <v>1001092436470</v>
       </c>
-      <c r="E140" s="24"/>
-      <c r="F140" s="23">
+      <c r="E141" s="24"/>
+      <c r="F141" s="23">
         <v>1.2</v>
       </c>
-      <c r="G140" s="23">
-        <f>E140</f>
+      <c r="G141" s="23">
+        <f>E141</f>
         <v>0</v>
       </c>
-      <c r="H140" s="14">
+      <c r="H141" s="14">
         <v>4.8</v>
       </c>
-      <c r="I140" s="14">
+      <c r="I141" s="14">
         <v>45</v>
       </c>
-      <c r="J140" s="29"/>
-      <c r="L140" s="120"/>
-    </row>
-    <row r="141" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6495</v>
-      </c>
-      <c r="B141" s="113" t="s">
-        <v>95</v>
-      </c>
-      <c r="C141" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="D141" s="70">
-        <v>1001092436495</v>
-      </c>
-      <c r="E141" s="24"/>
-      <c r="F141" s="58">
-        <v>0.3</v>
-      </c>
-      <c r="G141" s="23">
-        <f>E141*F141</f>
-        <v>0</v>
-      </c>
-      <c r="H141" s="59">
-        <v>1.8</v>
-      </c>
-      <c r="I141" s="59">
-        <v>45</v>
-      </c>
-      <c r="J141" s="59"/>
-      <c r="K141" s="60"/>
+      <c r="J141" s="29"/>
       <c r="L141" s="120"/>
-      <c r="M141" s="120"/>
-      <c r="N141" s="120"/>
-      <c r="O141" s="120"/>
-      <c r="P141" s="120"/>
-      <c r="Q141" s="120"/>
-      <c r="R141" s="120"/>
-      <c r="S141" s="120"/>
-      <c r="T141" s="120"/>
-      <c r="U141" s="120"/>
-      <c r="V141" s="120"/>
-      <c r="W141" s="120"/>
-      <c r="X141" s="120"/>
-      <c r="Y141" s="120"/>
-      <c r="Z141" s="120"/>
-      <c r="AA141" s="120"/>
-      <c r="AB141" s="120"/>
-      <c r="AC141" s="120"/>
-      <c r="AD141" s="120"/>
-      <c r="AE141" s="120"/>
-      <c r="AF141" s="120"/>
-      <c r="AG141" s="120"/>
-      <c r="AH141" s="120"/>
-      <c r="AI141" s="120"/>
-      <c r="AJ141" s="120"/>
-      <c r="AK141" s="120"/>
-      <c r="AL141" s="120"/>
-      <c r="AM141" s="120"/>
-      <c r="AN141" s="120"/>
-      <c r="AO141" s="120"/>
-      <c r="AP141" s="120"/>
-      <c r="AQ141" s="120"/>
-      <c r="AR141" s="120"/>
-      <c r="AS141" s="120"/>
-      <c r="AT141" s="120"/>
-      <c r="AU141" s="120"/>
-      <c r="AV141" s="120"/>
-      <c r="AW141" s="120"/>
-      <c r="AX141" s="120"/>
-      <c r="AY141" s="120"/>
-      <c r="AZ141" s="120"/>
-      <c r="BA141" s="120"/>
-      <c r="BB141" s="120"/>
-      <c r="BC141" s="120"/>
-      <c r="BD141" s="120"/>
-      <c r="BE141" s="120"/>
-      <c r="BF141" s="120"/>
-      <c r="BG141" s="120"/>
-      <c r="BH141" s="120"/>
-      <c r="BI141" s="120"/>
-      <c r="BJ141" s="120"/>
-      <c r="BK141" s="120"/>
-      <c r="BL141" s="120"/>
-      <c r="BM141" s="120"/>
-      <c r="BN141" s="120"/>
-      <c r="BO141" s="120"/>
     </row>
     <row r="142" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>5452</v>
-      </c>
-      <c r="B142" s="109" t="s">
-        <v>93</v>
+        <f t="shared" si="22"/>
+        <v>6495</v>
+      </c>
+      <c r="B142" s="113" t="s">
+        <v>95</v>
       </c>
       <c r="C142" s="55" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D142" s="70">
-        <v>1001092485452</v>
+        <v>1001092436495</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="58">
-        <v>1.35</v>
+        <v>0.3</v>
       </c>
       <c r="G142" s="23">
-        <f t="shared" ref="G142:G145" si="22">E142</f>
+        <f>E142*F142</f>
         <v>0</v>
       </c>
       <c r="H142" s="59">
-        <v>4.05</v>
+        <v>1.8</v>
       </c>
       <c r="I142" s="59">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J142" s="59"/>
       <c r="K142" s="60"/>
@@ -12746,28 +12757,28 @@
     </row>
     <row r="143" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6866</v>
+        <f t="shared" si="22"/>
+        <v>5452</v>
       </c>
       <c r="B143" s="109" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C143" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D143" s="70">
-        <v>1001095716866</v>
+        <v>1001092485452</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="58">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="G143" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G143:G146" si="23">E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="59">
-        <v>6</v>
+        <v>4.05</v>
       </c>
       <c r="I143" s="59">
         <v>60</v>
@@ -12833,24 +12844,24 @@
     </row>
     <row r="144" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6025</v>
+        <f t="shared" si="22"/>
+        <v>6866</v>
       </c>
       <c r="B144" s="109" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="C144" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D144" s="70">
-        <v>1001094966025</v>
+        <v>1001095716866</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="58">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G144" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H144" s="59">
@@ -12920,28 +12931,28 @@
     </row>
     <row r="145" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>4584</v>
+        <f t="shared" si="22"/>
+        <v>6025</v>
       </c>
       <c r="B145" s="109" t="s">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="C145" s="55" t="s">
         <v>22</v>
       </c>
       <c r="D145" s="70">
-        <v>1001092674584</v>
+        <v>1001094966025</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="58">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G145" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H145" s="59">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="I145" s="59">
         <v>60</v>
@@ -13005,30 +13016,30 @@
       <c r="BN145" s="120"/>
       <c r="BO145" s="120"/>
     </row>
-    <row r="146" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:67" s="61" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>3215</v>
-      </c>
-      <c r="B146" s="54" t="s">
-        <v>176</v>
+        <f t="shared" si="22"/>
+        <v>4584</v>
+      </c>
+      <c r="B146" s="109" t="s">
+        <v>175</v>
       </c>
       <c r="C146" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="D146" s="110">
-        <v>1001094053215</v>
+        <v>22</v>
+      </c>
+      <c r="D146" s="70">
+        <v>1001092674584</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="58">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="G146" s="23">
-        <f t="shared" ref="G146:G149" si="23">E146*F146</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H146" s="59">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="I146" s="59">
         <v>60</v>
@@ -13094,28 +13105,28 @@
     </row>
     <row r="147" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>5495</v>
+        <f t="shared" si="22"/>
+        <v>3215</v>
       </c>
       <c r="B147" s="54" t="s">
-        <v>94</v>
+        <v>218</v>
       </c>
       <c r="C147" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D147" s="110">
-        <v>1001093345495</v>
+        <v>1001094053215</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="58">
         <v>0.4</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G147:G151" si="24">E147*F147</f>
         <v>0</v>
       </c>
       <c r="H147" s="59">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="I147" s="59">
         <v>60</v>
@@ -13181,31 +13192,31 @@
     </row>
     <row r="148" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>7377</v>
+        <f t="shared" si="22"/>
+        <v>5495</v>
       </c>
       <c r="B148" s="54" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C148" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D148" s="110">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="58">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H148" s="59">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I148" s="59">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J148" s="59"/>
       <c r="K148" s="60"/>
@@ -13266,30 +13277,30 @@
       <c r="BN148" s="120"/>
       <c r="BO148" s="120"/>
     </row>
-    <row r="149" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="56" t="str">
-        <f t="shared" si="21"/>
-        <v>6925</v>
+        <f t="shared" si="22"/>
+        <v>7377</v>
       </c>
       <c r="B149" s="54" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C149" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D149" s="110">
-        <v>1001095226925</v>
+        <v>1001095027377</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="58">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G149" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H149" s="59">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I149" s="59">
         <v>45</v>
@@ -13353,36 +13364,31 @@
       <c r="BN149" s="120"/>
       <c r="BO149" s="120"/>
     </row>
-    <row r="150" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="143">
-        <v>7647</v>
+    <row r="150" spans="1:67" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="56" t="str">
+        <f t="shared" si="22"/>
+        <v>6411</v>
       </c>
       <c r="B150" s="54" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C150" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D150" s="110">
-        <v>1001097747647</v>
+        <v>1001093316411</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="58">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G150" s="23">
-        <f>E150*F150</f>
+        <f t="shared" ref="G150" si="25">E150*F150</f>
         <v>0</v>
       </c>
-      <c r="H150" s="59">
-        <v>1</v>
-      </c>
-      <c r="I150" s="59">
-        <v>30</v>
-      </c>
-      <c r="J150" s="144" t="s">
-        <v>197</v>
-      </c>
+      <c r="H150" s="59"/>
+      <c r="I150" s="59"/>
+      <c r="J150" s="59"/>
       <c r="K150" s="60"/>
       <c r="L150" s="120"/>
       <c r="M150" s="120"/>
@@ -13441,36 +13447,35 @@
       <c r="BN150" s="120"/>
       <c r="BO150" s="120"/>
     </row>
-    <row r="151" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="143">
-        <v>7651</v>
+    <row r="151" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="56" t="str">
+        <f t="shared" si="22"/>
+        <v>6925</v>
       </c>
       <c r="B151" s="54" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="C151" s="55" t="s">
         <v>20</v>
       </c>
       <c r="D151" s="110">
-        <v>1001097767651</v>
+        <v>1001095226925</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="58">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="G151" s="23">
-        <f>E151*F151</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H151" s="59">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="I151" s="59">
-        <v>30</v>
-      </c>
-      <c r="J151" s="144" t="s">
-        <v>197</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J151" s="59"/>
       <c r="K151" s="60"/>
       <c r="L151" s="120"/>
       <c r="M151" s="120"/>
@@ -13529,137 +13534,252 @@
       <c r="BN151" s="120"/>
       <c r="BO151" s="120"/>
     </row>
-    <row r="152" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="47" t="s">
+    <row r="152" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="56" t="str">
+        <f t="shared" si="22"/>
+        <v>7647</v>
+      </c>
+      <c r="B152" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C152" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152" s="110">
+        <v>1001097747647</v>
+      </c>
+      <c r="E152" s="24"/>
+      <c r="F152" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G152" s="23">
+        <f>E152*F152</f>
+        <v>0</v>
+      </c>
+      <c r="H152" s="59">
+        <v>1</v>
+      </c>
+      <c r="I152" s="59">
+        <v>30</v>
+      </c>
+      <c r="J152" s="143" t="s">
+        <v>197</v>
+      </c>
+      <c r="K152" s="60"/>
+      <c r="L152" s="120"/>
+      <c r="M152" s="120"/>
+      <c r="N152" s="120"/>
+      <c r="O152" s="120"/>
+      <c r="P152" s="120"/>
+      <c r="Q152" s="120"/>
+      <c r="R152" s="120"/>
+      <c r="S152" s="120"/>
+      <c r="T152" s="120"/>
+      <c r="U152" s="120"/>
+      <c r="V152" s="120"/>
+      <c r="W152" s="120"/>
+      <c r="X152" s="120"/>
+      <c r="Y152" s="120"/>
+      <c r="Z152" s="120"/>
+      <c r="AA152" s="120"/>
+      <c r="AB152" s="120"/>
+      <c r="AC152" s="120"/>
+      <c r="AD152" s="120"/>
+      <c r="AE152" s="120"/>
+      <c r="AF152" s="120"/>
+      <c r="AG152" s="120"/>
+      <c r="AH152" s="120"/>
+      <c r="AI152" s="120"/>
+      <c r="AJ152" s="120"/>
+      <c r="AK152" s="120"/>
+      <c r="AL152" s="120"/>
+      <c r="AM152" s="120"/>
+      <c r="AN152" s="120"/>
+      <c r="AO152" s="120"/>
+      <c r="AP152" s="120"/>
+      <c r="AQ152" s="120"/>
+      <c r="AR152" s="120"/>
+      <c r="AS152" s="120"/>
+      <c r="AT152" s="120"/>
+      <c r="AU152" s="120"/>
+      <c r="AV152" s="120"/>
+      <c r="AW152" s="120"/>
+      <c r="AX152" s="120"/>
+      <c r="AY152" s="120"/>
+      <c r="AZ152" s="120"/>
+      <c r="BA152" s="120"/>
+      <c r="BB152" s="120"/>
+      <c r="BC152" s="120"/>
+      <c r="BD152" s="120"/>
+      <c r="BE152" s="120"/>
+      <c r="BF152" s="120"/>
+      <c r="BG152" s="120"/>
+      <c r="BH152" s="120"/>
+      <c r="BI152" s="120"/>
+      <c r="BJ152" s="120"/>
+      <c r="BK152" s="120"/>
+      <c r="BL152" s="120"/>
+      <c r="BM152" s="120"/>
+      <c r="BN152" s="120"/>
+      <c r="BO152" s="120"/>
+    </row>
+    <row r="153" spans="1:67" s="61" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="56" t="str">
+        <f t="shared" si="22"/>
+        <v>7651</v>
+      </c>
+      <c r="B153" s="54" t="s">
+        <v>198</v>
+      </c>
+      <c r="C153" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" s="110">
+        <v>1001097767651</v>
+      </c>
+      <c r="E153" s="24"/>
+      <c r="F153" s="58">
+        <v>0.1</v>
+      </c>
+      <c r="G153" s="23">
+        <f>E153*F153</f>
+        <v>0</v>
+      </c>
+      <c r="H153" s="59">
+        <v>1</v>
+      </c>
+      <c r="I153" s="59">
+        <v>30</v>
+      </c>
+      <c r="J153" s="143" t="s">
+        <v>197</v>
+      </c>
+      <c r="K153" s="60"/>
+      <c r="L153" s="120"/>
+      <c r="M153" s="120"/>
+      <c r="N153" s="120"/>
+      <c r="O153" s="120"/>
+      <c r="P153" s="120"/>
+      <c r="Q153" s="120"/>
+      <c r="R153" s="120"/>
+      <c r="S153" s="120"/>
+      <c r="T153" s="120"/>
+      <c r="U153" s="120"/>
+      <c r="V153" s="120"/>
+      <c r="W153" s="120"/>
+      <c r="X153" s="120"/>
+      <c r="Y153" s="120"/>
+      <c r="Z153" s="120"/>
+      <c r="AA153" s="120"/>
+      <c r="AB153" s="120"/>
+      <c r="AC153" s="120"/>
+      <c r="AD153" s="120"/>
+      <c r="AE153" s="120"/>
+      <c r="AF153" s="120"/>
+      <c r="AG153" s="120"/>
+      <c r="AH153" s="120"/>
+      <c r="AI153" s="120"/>
+      <c r="AJ153" s="120"/>
+      <c r="AK153" s="120"/>
+      <c r="AL153" s="120"/>
+      <c r="AM153" s="120"/>
+      <c r="AN153" s="120"/>
+      <c r="AO153" s="120"/>
+      <c r="AP153" s="120"/>
+      <c r="AQ153" s="120"/>
+      <c r="AR153" s="120"/>
+      <c r="AS153" s="120"/>
+      <c r="AT153" s="120"/>
+      <c r="AU153" s="120"/>
+      <c r="AV153" s="120"/>
+      <c r="AW153" s="120"/>
+      <c r="AX153" s="120"/>
+      <c r="AY153" s="120"/>
+      <c r="AZ153" s="120"/>
+      <c r="BA153" s="120"/>
+      <c r="BB153" s="120"/>
+      <c r="BC153" s="120"/>
+      <c r="BD153" s="120"/>
+      <c r="BE153" s="120"/>
+      <c r="BF153" s="120"/>
+      <c r="BG153" s="120"/>
+      <c r="BH153" s="120"/>
+      <c r="BI153" s="120"/>
+      <c r="BJ153" s="120"/>
+      <c r="BK153" s="120"/>
+      <c r="BL153" s="120"/>
+      <c r="BM153" s="120"/>
+      <c r="BN153" s="120"/>
+      <c r="BO153" s="120"/>
+    </row>
+    <row r="154" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B152" s="42" t="s">
+      <c r="B154" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="C152" s="42"/>
-      <c r="D152" s="42"/>
-      <c r="E152" s="42"/>
-      <c r="F152" s="41"/>
-      <c r="G152" s="42"/>
-      <c r="H152" s="42"/>
-      <c r="I152" s="42"/>
-      <c r="J152" s="43"/>
-      <c r="L152" s="120"/>
-    </row>
-    <row r="153" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="56" t="str">
-        <f t="shared" ref="A153:A163" si="24">RIGHT(D153,4)</f>
+      <c r="C154" s="42"/>
+      <c r="D154" s="42"/>
+      <c r="E154" s="42"/>
+      <c r="F154" s="41"/>
+      <c r="G154" s="42"/>
+      <c r="H154" s="42"/>
+      <c r="I154" s="42"/>
+      <c r="J154" s="43"/>
+      <c r="L154" s="120"/>
+    </row>
+    <row r="155" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="56" t="str">
+        <f t="shared" ref="A155:A166" si="26">RIGHT(D155,4)</f>
         <v>6620</v>
       </c>
-      <c r="B153" s="35" t="s">
+      <c r="B155" s="35" t="s">
         <v>97</v>
-      </c>
-      <c r="C153" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D153" s="51">
-        <v>1001081596620</v>
-      </c>
-      <c r="E153" s="24"/>
-      <c r="F153" s="23">
-        <v>1.05</v>
-      </c>
-      <c r="G153" s="23">
-        <f t="shared" ref="G153" si="25">E153</f>
-        <v>0</v>
-      </c>
-      <c r="H153" s="14">
-        <v>3.15</v>
-      </c>
-      <c r="I153" s="14">
-        <v>30</v>
-      </c>
-      <c r="J153" s="29"/>
-      <c r="L153" s="120"/>
-    </row>
-    <row r="154" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="56" t="str">
-        <f t="shared" si="24"/>
-        <v>7187</v>
-      </c>
-      <c r="B154" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="C154" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D154" s="51">
-        <v>1001085637187</v>
-      </c>
-      <c r="E154" s="24"/>
-      <c r="F154" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G154" s="23">
-        <f t="shared" ref="G154:G164" si="26">E154*F154</f>
-        <v>0</v>
-      </c>
-      <c r="H154" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I154" s="14">
-        <v>50</v>
-      </c>
-      <c r="J154" s="29"/>
-      <c r="L154" s="120"/>
-    </row>
-    <row r="155" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="143">
-        <v>6008</v>
-      </c>
-      <c r="B155" s="35" t="s">
-        <v>199</v>
       </c>
       <c r="C155" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D155" s="51">
-        <v>1001084856008</v>
+        <v>1001081596620</v>
       </c>
       <c r="E155" s="24"/>
       <c r="F155" s="23">
-        <v>0.3</v>
+        <v>1.05</v>
       </c>
       <c r="G155" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G155" si="27">E155</f>
         <v>0</v>
       </c>
       <c r="H155" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I155" s="14">
-        <v>40</v>
-      </c>
-      <c r="J155" s="144" t="s">
-        <v>197</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J155" s="29"/>
       <c r="L155" s="120"/>
     </row>
     <row r="156" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="56" t="str">
-        <f t="shared" si="24"/>
-        <v>7090</v>
+        <f t="shared" si="26"/>
+        <v>7187</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D156" s="51">
-        <v>1001084217090</v>
+        <v>1001085637187</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
         <v>0.3</v>
       </c>
       <c r="G156" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G156:G166" si="28">E156*F156</f>
         <v>0</v>
       </c>
       <c r="H156" s="14">
@@ -13673,90 +13793,92 @@
     </row>
     <row r="157" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="56" t="str">
-        <f t="shared" si="24"/>
-        <v>7103</v>
+        <f t="shared" si="26"/>
+        <v>6008</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C157" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D157" s="51">
-        <v>1001223297103</v>
+        <v>1001084856008</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
         <v>1.8</v>
       </c>
       <c r="I157" s="14">
-        <v>50</v>
-      </c>
-      <c r="J157" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J157" s="143" t="s">
+        <v>197</v>
+      </c>
       <c r="L157" s="120"/>
     </row>
     <row r="158" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="56" t="str">
-        <f>RIGHT(D158,4)</f>
-        <v>6279</v>
+        <f t="shared" si="26"/>
+        <v>7090</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D158" s="51">
-        <v>1001220286279</v>
+        <v>1001084217090</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="G158" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="I158" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J158" s="29"/>
       <c r="L158" s="120"/>
     </row>
     <row r="159" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="56" t="str">
-        <f t="shared" si="24"/>
-        <v>7092</v>
+        <f t="shared" si="26"/>
+        <v>7103</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>78</v>
+        <v>219</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D159" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G159" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H159" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I159" s="14">
         <v>50</v>
@@ -13766,28 +13888,28 @@
     </row>
     <row r="160" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="56" t="str">
-        <f t="shared" si="24"/>
-        <v>6448</v>
+        <f t="shared" si="26"/>
+        <v>6279</v>
       </c>
       <c r="B160" s="35" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="C160" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D160" s="51">
-        <v>1001234146448</v>
+        <v>1001220286279</v>
       </c>
       <c r="E160" s="24"/>
       <c r="F160" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G160" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H160" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I160" s="14">
         <v>45</v>
@@ -13797,59 +13919,59 @@
     </row>
     <row r="161" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="56" t="str">
-        <f t="shared" si="24"/>
-        <v>6754</v>
+        <f t="shared" si="26"/>
+        <v>7092</v>
       </c>
       <c r="B161" s="35" t="s">
-        <v>178</v>
+        <v>78</v>
       </c>
       <c r="C161" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D161" s="51">
-        <v>1001225406754</v>
+        <v>1001223297092</v>
       </c>
       <c r="E161" s="24"/>
       <c r="F161" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G161" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H161" s="14">
-        <v>0.72</v>
+        <v>1.4</v>
       </c>
       <c r="I161" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J161" s="29"/>
       <c r="L161" s="120"/>
     </row>
     <row r="162" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="56" t="str">
-        <f t="shared" si="24"/>
-        <v>6208</v>
+        <f t="shared" si="26"/>
+        <v>6448</v>
       </c>
       <c r="B162" s="35" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C162" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D162" s="51">
-        <v>1001220226208</v>
+        <v>1001234146448</v>
       </c>
       <c r="E162" s="24"/>
       <c r="F162" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G162" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H162" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I162" s="14">
         <v>45</v>
@@ -13859,108 +13981,151 @@
     </row>
     <row r="163" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="56" t="str">
-        <f t="shared" si="24"/>
-        <v>6228</v>
+        <f t="shared" si="26"/>
+        <v>6754</v>
       </c>
       <c r="B163" s="35" t="s">
-        <v>89</v>
+        <v>178</v>
       </c>
       <c r="C163" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D163" s="51">
-        <v>1001225416228</v>
+        <v>1001225406754</v>
       </c>
       <c r="E163" s="24"/>
       <c r="F163" s="23">
         <v>0.09</v>
       </c>
       <c r="G163" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H163" s="14">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="I163" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J163" s="29"/>
       <c r="L163" s="120"/>
     </row>
-    <row r="164" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="143">
-        <v>7612</v>
+    <row r="164" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="56" t="str">
+        <f t="shared" si="26"/>
+        <v>6208</v>
       </c>
       <c r="B164" s="35" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="C164" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D164" s="51">
-        <v>1001453907612</v>
+        <v>1001220226208</v>
       </c>
       <c r="E164" s="24"/>
       <c r="F164" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G164" s="23">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H164" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="I164" s="14">
+        <v>45</v>
+      </c>
+      <c r="J164" s="29"/>
+      <c r="L164" s="120"/>
+    </row>
+    <row r="165" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="56" t="str">
+        <f t="shared" si="26"/>
+        <v>6228</v>
+      </c>
+      <c r="B165" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C165" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D165" s="51">
+        <v>1001225416228</v>
+      </c>
+      <c r="E165" s="24"/>
+      <c r="F165" s="23">
+        <v>0.09</v>
+      </c>
+      <c r="G165" s="23">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H165" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="I165" s="14">
+        <v>45</v>
+      </c>
+      <c r="J165" s="29"/>
+      <c r="L165" s="120"/>
+    </row>
+    <row r="166" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="56" t="str">
+        <f t="shared" si="26"/>
+        <v>7612</v>
+      </c>
+      <c r="B166" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="C166" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D166" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E166" s="24"/>
+      <c r="F166" s="23">
         <v>0.1</v>
       </c>
-      <c r="G164" s="23">
-        <f t="shared" si="26"/>
+      <c r="G166" s="23">
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H164" s="14">
+      <c r="H166" s="14">
         <v>1</v>
       </c>
-      <c r="I164" s="14">
+      <c r="I166" s="14">
         <v>60</v>
       </c>
-      <c r="J164" s="52" t="s">
+      <c r="J166" s="52" t="s">
         <v>201</v>
       </c>
-      <c r="L164" s="120"/>
-    </row>
-    <row r="165" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="48"/>
-      <c r="B165" s="45" t="s">
+      <c r="L166" s="120"/>
+    </row>
+    <row r="167" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="48"/>
+      <c r="B167" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C165" s="16"/>
-      <c r="D165" s="36"/>
-      <c r="E165" s="17">
-        <f>SUM(E10:E164)</f>
+      <c r="C167" s="16"/>
+      <c r="D167" s="36"/>
+      <c r="E167" s="17">
+        <f>SUM(E10:E166)</f>
         <v>0</v>
       </c>
-      <c r="F165" s="17"/>
-      <c r="G165" s="17">
-        <f>SUM(G11:G164)</f>
+      <c r="F167" s="17"/>
+      <c r="G167" s="17">
+        <f>SUM(G11:G166)</f>
         <v>0</v>
       </c>
-      <c r="H165" s="17"/>
-      <c r="I165" s="17"/>
-      <c r="J165" s="17"/>
-    </row>
-    <row r="166" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="37"/>
-      <c r="C166" s="18"/>
-      <c r="D166" s="40"/>
-      <c r="F166" s="19"/>
-      <c r="G166" s="19"/>
-      <c r="H166" s="20"/>
-      <c r="I166" s="20"/>
-      <c r="J166" s="21"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B167" s="37"/>
-      <c r="C167" s="18"/>
-      <c r="D167" s="40"/>
-      <c r="F167" s="19"/>
-      <c r="G167" s="19"/>
-      <c r="H167" s="20"/>
-      <c r="I167" s="20"/>
-      <c r="J167" s="21"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H167" s="17"/>
+      <c r="I167" s="17"/>
+      <c r="J167" s="17"/>
+    </row>
+    <row r="168" spans="1:12" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B168" s="37"/>
       <c r="C168" s="18"/>
       <c r="D168" s="40"/>
@@ -14002,55 +14167,55 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B172" s="37"/>
-      <c r="C172" s="62"/>
-      <c r="D172" s="63"/>
-      <c r="E172" s="64"/>
-      <c r="F172" s="65"/>
-      <c r="G172" s="65"/>
-      <c r="H172" s="66"/>
-      <c r="I172" s="66"/>
+      <c r="C172" s="18"/>
+      <c r="D172" s="40"/>
+      <c r="F172" s="19"/>
+      <c r="G172" s="19"/>
+      <c r="H172" s="20"/>
+      <c r="I172" s="20"/>
       <c r="J172" s="21"/>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
-      <c r="C173" s="62"/>
-      <c r="D173" s="63"/>
-      <c r="E173" s="64"/>
-      <c r="F173" s="65"/>
-      <c r="G173" s="65"/>
-      <c r="H173" s="66"/>
-      <c r="I173" s="66"/>
+      <c r="C173" s="18"/>
+      <c r="D173" s="40"/>
+      <c r="F173" s="19"/>
+      <c r="G173" s="19"/>
+      <c r="H173" s="20"/>
+      <c r="I173" s="20"/>
       <c r="J173" s="21"/>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
       <c r="C174" s="62"/>
-      <c r="D174" s="67"/>
-      <c r="E174" s="68"/>
-      <c r="F174" s="67"/>
-      <c r="G174" s="69"/>
-      <c r="H174" s="70"/>
-      <c r="I174" s="71"/>
+      <c r="D174" s="63"/>
+      <c r="E174" s="64"/>
+      <c r="F174" s="65"/>
+      <c r="G174" s="65"/>
+      <c r="H174" s="66"/>
+      <c r="I174" s="66"/>
       <c r="J174" s="21"/>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B175" s="37"/>
-      <c r="C175" s="18"/>
-      <c r="D175" s="40"/>
-      <c r="F175" s="19"/>
-      <c r="G175" s="19"/>
-      <c r="H175" s="20"/>
-      <c r="I175" s="20"/>
+      <c r="C175" s="62"/>
+      <c r="D175" s="63"/>
+      <c r="E175" s="64"/>
+      <c r="F175" s="65"/>
+      <c r="G175" s="65"/>
+      <c r="H175" s="66"/>
+      <c r="I175" s="66"/>
       <c r="J175" s="21"/>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B176" s="37"/>
-      <c r="C176" s="18"/>
-      <c r="D176" s="40"/>
-      <c r="F176" s="19"/>
-      <c r="G176" s="19"/>
-      <c r="H176" s="20"/>
-      <c r="I176" s="20"/>
+      <c r="C176" s="62"/>
+      <c r="D176" s="67"/>
+      <c r="E176" s="68"/>
+      <c r="F176" s="67"/>
+      <c r="G176" s="69"/>
+      <c r="H176" s="70"/>
+      <c r="I176" s="71"/>
       <c r="J176" s="21"/>
     </row>
     <row r="177" spans="2:10" x14ac:dyDescent="0.25">
@@ -29183,13 +29348,33 @@
       <c r="I1689" s="20"/>
       <c r="J1689" s="21"/>
     </row>
+    <row r="1690" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1690" s="37"/>
+      <c r="C1690" s="18"/>
+      <c r="D1690" s="40"/>
+      <c r="F1690" s="19"/>
+      <c r="G1690" s="19"/>
+      <c r="H1690" s="20"/>
+      <c r="I1690" s="20"/>
+      <c r="J1690" s="21"/>
+    </row>
+    <row r="1691" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1691" s="37"/>
+      <c r="C1691" s="18"/>
+      <c r="D1691" s="40"/>
+      <c r="F1691" s="19"/>
+      <c r="G1691" s="19"/>
+      <c r="H1691" s="20"/>
+      <c r="I1691" s="20"/>
+      <c r="J1691" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J165" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J167" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D174">
+  <conditionalFormatting sqref="D176">
     <cfRule type="duplicateValues" dxfId="384" priority="1"/>
     <cfRule type="duplicateValues" dxfId="383" priority="2"/>
     <cfRule type="duplicateValues" dxfId="382" priority="3"/>
@@ -29201,7 +29386,7 @@
     <cfRule type="duplicateValues" dxfId="376" priority="10"/>
     <cfRule type="duplicateValues" dxfId="375" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D174">
+  <conditionalFormatting sqref="D176">
     <cfRule type="duplicateValues" dxfId="374" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Uaer4\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C99AF9-696A-4926-9CCA-D602215E51AF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EEB01C-B147-43AD-9F31-AD961064C341}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$152</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$585</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$585</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$153</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$586</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$586</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="225">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1004,6 +1004,9 @@
   </si>
   <si>
     <t>Ротация кода 7284</t>
+  </si>
+  <si>
+    <t>ВЕТЧ.РУБЛЕНАЯ ПМ в/у срез 0.3кг 6шт.</t>
   </si>
 </sst>
 </file>
@@ -6213,7 +6216,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1673"/>
+  <dimension ref="A1:BO1674"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -11962,7 +11965,7 @@
     </row>
     <row r="126" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A126" s="137" t="str">
-        <f t="shared" ref="A126:A138" si="26">RIGHT(D126,4)</f>
+        <f t="shared" ref="A126:A139" si="26">RIGHT(D126,4)</f>
         <v>4584</v>
       </c>
       <c r="B126" s="98" t="s">
@@ -12501,7 +12504,7 @@
         <v>0.4</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" ref="G132:G134" si="28">E132*F132</f>
+        <f t="shared" ref="G132:G135" si="28">E132*F132</f>
         <v>0</v>
       </c>
       <c r="H132" s="29">
@@ -12656,34 +12659,30 @@
       <c r="BN133" s="102"/>
       <c r="BO133" s="102"/>
     </row>
-    <row r="134" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="137" t="str">
         <f t="shared" si="26"/>
-        <v>6925</v>
+        <v>6411</v>
       </c>
       <c r="B134" s="53" t="s">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D134" s="136">
-        <v>1001095226925</v>
+        <v>1001093316411</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="128">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G134" si="29">E134*F134</f>
         <v>0</v>
       </c>
-      <c r="H134" s="29">
-        <v>4.8</v>
-      </c>
-      <c r="I134" s="29">
-        <v>45</v>
-      </c>
+      <c r="H134" s="29"/>
+      <c r="I134" s="29"/>
       <c r="J134" s="29"/>
       <c r="K134" s="27"/>
       <c r="L134" s="102"/>
@@ -12746,30 +12745,30 @@
     <row r="135" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="137" t="str">
         <f t="shared" si="26"/>
-        <v>6025</v>
+        <v>6925</v>
       </c>
       <c r="B135" s="53" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D135" s="136">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="128">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G135" s="23">
-        <f>E135</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H135" s="29">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I135" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J135" s="29"/>
       <c r="K135" s="27"/>
@@ -12830,81 +12829,135 @@
       <c r="BN135" s="102"/>
       <c r="BO135" s="102"/>
     </row>
-    <row r="136" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="137" t="str">
         <f t="shared" si="26"/>
-        <v>7485</v>
+        <v>6025</v>
       </c>
       <c r="B136" s="53" t="s">
-        <v>221</v>
+        <v>118</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D136" s="136">
-        <v>1001107397485</v>
+        <v>1001094966025</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="128">
-        <v>0.15</v>
+        <v>3</v>
       </c>
       <c r="G136" s="23">
-        <f>F136*E136</f>
+        <f>E136</f>
         <v>0</v>
       </c>
-      <c r="H136" s="29"/>
-      <c r="I136" s="29"/>
-      <c r="J136" s="125" t="s">
-        <v>196</v>
-      </c>
+      <c r="H136" s="29">
+        <v>6</v>
+      </c>
+      <c r="I136" s="29">
+        <v>60</v>
+      </c>
+      <c r="J136" s="29"/>
+      <c r="K136" s="27"/>
       <c r="L136" s="102"/>
+      <c r="M136" s="102"/>
+      <c r="N136" s="102"/>
+      <c r="O136" s="102"/>
+      <c r="P136" s="102"/>
+      <c r="Q136" s="102"/>
+      <c r="R136" s="102"/>
+      <c r="S136" s="102"/>
+      <c r="T136" s="102"/>
+      <c r="U136" s="102"/>
+      <c r="V136" s="102"/>
+      <c r="W136" s="102"/>
+      <c r="X136" s="102"/>
+      <c r="Y136" s="102"/>
+      <c r="Z136" s="102"/>
+      <c r="AA136" s="102"/>
+      <c r="AB136" s="102"/>
+      <c r="AC136" s="102"/>
+      <c r="AD136" s="102"/>
+      <c r="AE136" s="102"/>
+      <c r="AF136" s="102"/>
+      <c r="AG136" s="102"/>
+      <c r="AH136" s="102"/>
+      <c r="AI136" s="102"/>
+      <c r="AJ136" s="102"/>
+      <c r="AK136" s="102"/>
+      <c r="AL136" s="102"/>
+      <c r="AM136" s="102"/>
+      <c r="AN136" s="102"/>
+      <c r="AO136" s="102"/>
+      <c r="AP136" s="102"/>
+      <c r="AQ136" s="102"/>
+      <c r="AR136" s="102"/>
+      <c r="AS136" s="102"/>
+      <c r="AT136" s="102"/>
+      <c r="AU136" s="102"/>
+      <c r="AV136" s="102"/>
+      <c r="AW136" s="102"/>
+      <c r="AX136" s="102"/>
+      <c r="AY136" s="102"/>
+      <c r="AZ136" s="102"/>
+      <c r="BA136" s="102"/>
+      <c r="BB136" s="102"/>
+      <c r="BC136" s="102"/>
+      <c r="BD136" s="102"/>
+      <c r="BE136" s="102"/>
+      <c r="BF136" s="102"/>
+      <c r="BG136" s="102"/>
+      <c r="BH136" s="102"/>
+      <c r="BI136" s="102"/>
+      <c r="BJ136" s="102"/>
+      <c r="BK136" s="102"/>
+      <c r="BL136" s="102"/>
+      <c r="BM136" s="102"/>
+      <c r="BN136" s="102"/>
+      <c r="BO136" s="102"/>
     </row>
     <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="137" t="str">
         <f t="shared" si="26"/>
-        <v>7647</v>
+        <v>7485</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D137" s="136">
-        <v>1001097747647</v>
+        <v>1001107397485</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="128">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G137" s="23">
-        <f>E137*F137</f>
+        <f>F137*E137</f>
         <v>0</v>
       </c>
-      <c r="H137" s="29">
-        <v>1</v>
-      </c>
-      <c r="I137" s="29">
-        <v>30</v>
-      </c>
+      <c r="H137" s="29"/>
+      <c r="I137" s="29"/>
       <c r="J137" s="125" t="s">
         <v>196</v>
       </c>
       <c r="L137" s="102"/>
     </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="137" t="str">
         <f t="shared" si="26"/>
-        <v>7651</v>
+        <v>7647</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D138" s="136">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="128">
@@ -12925,74 +12978,76 @@
       </c>
       <c r="L138" s="102"/>
     </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="47" t="s">
+    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="137" t="str">
+        <f t="shared" si="26"/>
+        <v>7651</v>
+      </c>
+      <c r="B139" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="C139" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D139" s="136">
+        <v>1001097767651</v>
+      </c>
+      <c r="E139" s="24"/>
+      <c r="F139" s="128">
+        <v>0.1</v>
+      </c>
+      <c r="G139" s="23">
+        <f>E139*F139</f>
+        <v>0</v>
+      </c>
+      <c r="H139" s="29">
+        <v>1</v>
+      </c>
+      <c r="I139" s="29">
+        <v>30</v>
+      </c>
+      <c r="J139" s="125" t="s">
+        <v>196</v>
+      </c>
+      <c r="L139" s="102"/>
+    </row>
+    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B139" s="42" t="s">
+      <c r="B140" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="C139" s="42"/>
-      <c r="D139" s="42"/>
-      <c r="E139" s="42"/>
-      <c r="F139" s="41"/>
-      <c r="G139" s="42"/>
-      <c r="H139" s="42"/>
-      <c r="I139" s="42"/>
-      <c r="J139" s="43"/>
-      <c r="L139" s="102"/>
-    </row>
-    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="137" t="str">
-        <f t="shared" ref="A140:A151" si="29">RIGHT(D140,4)</f>
+      <c r="C140" s="42"/>
+      <c r="D140" s="42"/>
+      <c r="E140" s="42"/>
+      <c r="F140" s="41"/>
+      <c r="G140" s="42"/>
+      <c r="H140" s="42"/>
+      <c r="I140" s="42"/>
+      <c r="J140" s="43"/>
+      <c r="L140" s="102"/>
+    </row>
+    <row r="141" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="137" t="str">
+        <f t="shared" ref="A141:A152" si="30">RIGHT(D141,4)</f>
         <v>7090</v>
       </c>
-      <c r="B140" s="35" t="s">
+      <c r="B141" s="35" t="s">
         <v>100</v>
-      </c>
-      <c r="C140" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D140" s="51">
-        <v>1001084217090</v>
-      </c>
-      <c r="E140" s="24"/>
-      <c r="F140" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G140" s="23">
-        <f t="shared" ref="G140:G141" si="30">E140*F140</f>
-        <v>0</v>
-      </c>
-      <c r="H140" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I140" s="14">
-        <v>50</v>
-      </c>
-      <c r="J140" s="29"/>
-      <c r="L140" s="102"/>
-    </row>
-    <row r="141" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>7187</v>
-      </c>
-      <c r="B141" s="35" t="s">
-        <v>101</v>
       </c>
       <c r="C141" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D141" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="23">
         <v>0.3</v>
       </c>
       <c r="G141" s="23">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="G141:G142" si="31">E141*F141</f>
         <v>0</v>
       </c>
       <c r="H141" s="14">
@@ -13006,123 +13061,123 @@
     </row>
     <row r="142" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>6008</v>
+        <f t="shared" si="30"/>
+        <v>7187</v>
       </c>
       <c r="B142" s="35" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D142" s="51">
-        <v>1001084856008</v>
+        <v>1001085637187</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="23">
         <v>0.3</v>
       </c>
       <c r="G142" s="23">
-        <f>E142</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H142" s="14">
         <v>1.8</v>
       </c>
       <c r="I142" s="14">
-        <v>40</v>
-      </c>
-      <c r="J142" s="125" t="s">
-        <v>196</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J142" s="29"/>
       <c r="L142" s="102"/>
     </row>
     <row r="143" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>6620</v>
+        <f t="shared" si="30"/>
+        <v>6008</v>
       </c>
       <c r="B143" s="35" t="s">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="C143" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D143" s="51">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E143" s="24"/>
       <c r="F143" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G143" s="23">
         <f>E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I143" s="14">
-        <v>30</v>
-      </c>
-      <c r="J143" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J143" s="125" t="s">
+        <v>196</v>
+      </c>
       <c r="L143" s="102"/>
     </row>
     <row r="144" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>7103</v>
+        <f t="shared" si="30"/>
+        <v>6620</v>
       </c>
       <c r="B144" s="35" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D144" s="51">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="23">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G144" s="23">
-        <f t="shared" ref="G144:G151" si="31">E144*F144</f>
+        <f>E144</f>
         <v>0</v>
       </c>
       <c r="H144" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I144" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J144" s="29"/>
       <c r="L144" s="102"/>
     </row>
     <row r="145" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>7092</v>
+        <f t="shared" si="30"/>
+        <v>7103</v>
       </c>
       <c r="B145" s="35" t="s">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="C145" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D145" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G145" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" ref="G145:G152" si="32">E145*F145</f>
         <v>0</v>
       </c>
       <c r="H145" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I145" s="14">
         <v>50</v>
@@ -13132,59 +13187,59 @@
     </row>
     <row r="146" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>6228</v>
+        <f t="shared" si="30"/>
+        <v>7092</v>
       </c>
       <c r="B146" s="35" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C146" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D146" s="51">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G146" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H146" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I146" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J146" s="29"/>
       <c r="L146" s="102"/>
     </row>
     <row r="147" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>6448</v>
+        <f t="shared" si="30"/>
+        <v>6228</v>
       </c>
       <c r="B147" s="35" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="C147" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D147" s="51">
-        <v>1001234146448</v>
+        <v>1001225416228</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H147" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I147" s="14">
         <v>45</v>
@@ -13194,28 +13249,28 @@
     </row>
     <row r="148" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>6208</v>
+        <f t="shared" si="30"/>
+        <v>6448</v>
       </c>
       <c r="B148" s="35" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D148" s="51">
-        <v>1001220226208</v>
+        <v>1001234146448</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H148" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I148" s="14">
         <v>45</v>
@@ -13225,127 +13280,148 @@
     </row>
     <row r="149" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>6754</v>
+        <f t="shared" si="30"/>
+        <v>6208</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="C149" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D149" s="51">
-        <v>1001225406754</v>
+        <v>1001220226208</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G149" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H149" s="14">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="I149" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J149" s="29"/>
-    </row>
-    <row r="150" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L149" s="102"/>
+    </row>
+    <row r="150" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>6279</v>
+        <f t="shared" si="30"/>
+        <v>6754</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>98</v>
+        <v>222</v>
       </c>
       <c r="C150" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D150" s="51">
-        <v>1001220286279</v>
+        <v>1001225406754</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G150" s="23">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="H150" s="14">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="I150" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J150" s="29"/>
     </row>
-    <row r="151" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="137" t="str">
-        <f t="shared" si="29"/>
-        <v>7612</v>
+        <f t="shared" si="30"/>
+        <v>6279</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="C151" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D151" s="51">
-        <v>1001453907612</v>
+        <v>1001220286279</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G151" s="23">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H151" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I151" s="14">
+        <v>45</v>
+      </c>
+      <c r="J151" s="29"/>
+    </row>
+    <row r="152" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A152" s="137" t="str">
+        <f t="shared" si="30"/>
+        <v>7612</v>
+      </c>
+      <c r="B152" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="C152" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D152" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E152" s="24"/>
+      <c r="F152" s="23">
         <v>0.1</v>
       </c>
-      <c r="G151" s="23">
-        <f t="shared" si="31"/>
+      <c r="G152" s="23">
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="H151" s="14">
+      <c r="H152" s="14">
         <v>1</v>
       </c>
-      <c r="I151" s="14">
+      <c r="I152" s="14">
         <v>60</v>
       </c>
-      <c r="J151" s="52" t="s">
+      <c r="J152" s="52" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="48"/>
-      <c r="B152" s="45" t="s">
+    <row r="153" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A153" s="48"/>
+      <c r="B153" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C152" s="16"/>
-      <c r="D152" s="36"/>
-      <c r="E152" s="17">
-        <f>SUM(E10:E151)</f>
+      <c r="C153" s="16"/>
+      <c r="D153" s="36"/>
+      <c r="E153" s="17">
+        <f>SUM(E10:E152)</f>
         <v>0</v>
       </c>
-      <c r="F152" s="17"/>
-      <c r="G152" s="17">
-        <f>SUM(G11:G151)</f>
+      <c r="F153" s="17"/>
+      <c r="G153" s="17">
+        <f>SUM(G11:G152)</f>
         <v>0</v>
       </c>
-      <c r="H152" s="17"/>
-      <c r="I152" s="17"/>
-      <c r="J152" s="17"/>
-    </row>
-    <row r="153" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="37"/>
-      <c r="C153" s="18"/>
-      <c r="D153" s="40"/>
-      <c r="F153" s="19"/>
-      <c r="G153" s="19"/>
-      <c r="H153" s="20"/>
-      <c r="I153" s="20"/>
-      <c r="J153" s="21"/>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H153" s="17"/>
+      <c r="I153" s="17"/>
+      <c r="J153" s="17"/>
+    </row>
+    <row r="154" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B154" s="37"/>
       <c r="C154" s="18"/>
       <c r="D154" s="40"/>
@@ -13367,13 +13443,12 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B156" s="37"/>
-      <c r="C156" s="55"/>
-      <c r="D156" s="56"/>
-      <c r="E156" s="57"/>
-      <c r="F156" s="58"/>
-      <c r="G156" s="58"/>
-      <c r="H156" s="59"/>
-      <c r="I156" s="59"/>
+      <c r="C156" s="18"/>
+      <c r="D156" s="40"/>
+      <c r="F156" s="19"/>
+      <c r="G156" s="19"/>
+      <c r="H156" s="20"/>
+      <c r="I156" s="20"/>
       <c r="J156" s="21"/>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -13390,22 +13465,23 @@
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B158" s="37"/>
       <c r="C158" s="55"/>
-      <c r="D158" s="60"/>
-      <c r="E158" s="61"/>
-      <c r="F158" s="60"/>
-      <c r="G158" s="62"/>
-      <c r="H158" s="63"/>
-      <c r="I158" s="64"/>
+      <c r="D158" s="56"/>
+      <c r="E158" s="57"/>
+      <c r="F158" s="58"/>
+      <c r="G158" s="58"/>
+      <c r="H158" s="59"/>
+      <c r="I158" s="59"/>
       <c r="J158" s="21"/>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B159" s="37"/>
-      <c r="C159" s="18"/>
-      <c r="D159" s="40"/>
-      <c r="F159" s="19"/>
-      <c r="G159" s="19"/>
-      <c r="H159" s="20"/>
-      <c r="I159" s="20"/>
+      <c r="C159" s="55"/>
+      <c r="D159" s="60"/>
+      <c r="E159" s="61"/>
+      <c r="F159" s="60"/>
+      <c r="G159" s="62"/>
+      <c r="H159" s="63"/>
+      <c r="I159" s="64"/>
       <c r="J159" s="21"/>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -28548,13 +28624,23 @@
       <c r="I1673" s="20"/>
       <c r="J1673" s="21"/>
     </row>
+    <row r="1674" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1674" s="37"/>
+      <c r="C1674" s="18"/>
+      <c r="D1674" s="40"/>
+      <c r="F1674" s="19"/>
+      <c r="G1674" s="19"/>
+      <c r="H1674" s="20"/>
+      <c r="I1674" s="20"/>
+      <c r="J1674" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J152" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J153" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D158">
+  <conditionalFormatting sqref="D159">
     <cfRule type="duplicateValues" dxfId="384" priority="1"/>
     <cfRule type="duplicateValues" dxfId="383" priority="2"/>
     <cfRule type="duplicateValues" dxfId="382" priority="3"/>
@@ -28566,7 +28652,7 @@
     <cfRule type="duplicateValues" dxfId="376" priority="10"/>
     <cfRule type="duplicateValues" dxfId="375" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D158">
+  <conditionalFormatting sqref="D159">
     <cfRule type="duplicateValues" dxfId="374" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5EEB01C-B147-43AD-9F31-AD961064C341}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF143D1-23E7-4172-A6BC-EA201124AFFC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$153</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$586</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$586</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$159</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$592</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$592</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="232">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1007,6 +1007,27 @@
   </si>
   <si>
     <t>ВЕТЧ.РУБЛЕНАЯ ПМ в/у срез 0.3кг 6шт.</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ КОПЧ.НА БУКЕ в/к в/у 0.35кг_50с</t>
+  </si>
+  <si>
+    <t>ДОКТОРСКАЯ ПРЕМИУМ п/о(п)</t>
+  </si>
+  <si>
+    <t>ЛЮБИТЕЛЬСКАЯ ОСТАНКИНСКАЯ вар ц/о в/у</t>
+  </si>
+  <si>
+    <t>ТЕЛЯЧЬЯ ГОСТ Останкино вар н/о в/у</t>
+  </si>
+  <si>
+    <t>КАРБОНAД ДОМАШНИЙ ПМ к/в кр/к в/у</t>
+  </si>
+  <si>
+    <t>ВОСКРЕСЕНСКАЯ ВЯЛЕНАЯ в/к в/у срез 1/260</t>
+  </si>
+  <si>
+    <t>НОВОМОСКОВСКАЯ в/к в/у срез 0.31кг</t>
   </si>
 </sst>
 </file>
@@ -6216,7 +6237,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1674"/>
+  <dimension ref="A1:BO1680"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -6547,7 +6568,7 @@
     </row>
     <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="137" t="str">
-        <f t="shared" ref="A12:A67" si="1">RIGHT(D12,4)</f>
+        <f t="shared" ref="A12:A69" si="1">RIGHT(D12,4)</f>
         <v>6220</v>
       </c>
       <c r="B12" s="53" t="s">
@@ -7427,7 +7448,7 @@
         <v>8014</v>
       </c>
       <c r="B28" s="53" t="s">
-        <v>113</v>
+        <v>226</v>
       </c>
       <c r="C28" s="50" t="s">
         <v>22</v>
@@ -7511,31 +7532,25 @@
     <row r="29" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7343</v>
+        <v>7514</v>
       </c>
       <c r="B29" s="53" t="s">
-        <v>31</v>
+        <v>227</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D29" s="51">
-        <v>1001016747343</v>
+        <v>1001017557514</v>
       </c>
       <c r="E29" s="24"/>
-      <c r="F29" s="128">
-        <v>0.4</v>
-      </c>
+      <c r="F29" s="128"/>
       <c r="G29" s="23">
-        <f t="shared" ref="G29:G31" si="6">E29*F29</f>
+        <f>E29</f>
         <v>0</v>
       </c>
-      <c r="H29" s="29">
-        <v>3.2</v>
-      </c>
-      <c r="I29" s="29">
-        <v>60</v>
-      </c>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
       <c r="J29" s="29"/>
       <c r="K29" s="27"/>
       <c r="L29" s="102"/>
@@ -7595,61 +7610,111 @@
       <c r="BN29" s="102"/>
       <c r="BO29" s="102"/>
     </row>
-    <row r="30" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6797</v>
+        <v>7518</v>
       </c>
       <c r="B30" s="53" t="s">
-        <v>114</v>
+        <v>228</v>
       </c>
       <c r="C30" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D30" s="51">
-        <v>1001015026797</v>
+        <v>1001017567518</v>
       </c>
       <c r="E30" s="24"/>
-      <c r="F30" s="128">
-        <v>0.4</v>
-      </c>
+      <c r="F30" s="128"/>
       <c r="G30" s="23">
-        <f t="shared" si="6"/>
+        <f>E30</f>
         <v>0</v>
       </c>
-      <c r="H30" s="29">
-        <v>3.2</v>
-      </c>
-      <c r="I30" s="29">
-        <v>60</v>
-      </c>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
       <c r="J30" s="29"/>
+      <c r="K30" s="27"/>
       <c r="L30" s="102"/>
-    </row>
-    <row r="31" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M30" s="102"/>
+      <c r="N30" s="102"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="102"/>
+      <c r="Q30" s="102"/>
+      <c r="R30" s="102"/>
+      <c r="S30" s="102"/>
+      <c r="T30" s="102"/>
+      <c r="U30" s="102"/>
+      <c r="V30" s="102"/>
+      <c r="W30" s="102"/>
+      <c r="X30" s="102"/>
+      <c r="Y30" s="102"/>
+      <c r="Z30" s="102"/>
+      <c r="AA30" s="102"/>
+      <c r="AB30" s="102"/>
+      <c r="AC30" s="102"/>
+      <c r="AD30" s="102"/>
+      <c r="AE30" s="102"/>
+      <c r="AF30" s="102"/>
+      <c r="AG30" s="102"/>
+      <c r="AH30" s="102"/>
+      <c r="AI30" s="102"/>
+      <c r="AJ30" s="102"/>
+      <c r="AK30" s="102"/>
+      <c r="AL30" s="102"/>
+      <c r="AM30" s="102"/>
+      <c r="AN30" s="102"/>
+      <c r="AO30" s="102"/>
+      <c r="AP30" s="102"/>
+      <c r="AQ30" s="102"/>
+      <c r="AR30" s="102"/>
+      <c r="AS30" s="102"/>
+      <c r="AT30" s="102"/>
+      <c r="AU30" s="102"/>
+      <c r="AV30" s="102"/>
+      <c r="AW30" s="102"/>
+      <c r="AX30" s="102"/>
+      <c r="AY30" s="102"/>
+      <c r="AZ30" s="102"/>
+      <c r="BA30" s="102"/>
+      <c r="BB30" s="102"/>
+      <c r="BC30" s="102"/>
+      <c r="BD30" s="102"/>
+      <c r="BE30" s="102"/>
+      <c r="BF30" s="102"/>
+      <c r="BG30" s="102"/>
+      <c r="BH30" s="102"/>
+      <c r="BI30" s="102"/>
+      <c r="BJ30" s="102"/>
+      <c r="BK30" s="102"/>
+      <c r="BL30" s="102"/>
+      <c r="BM30" s="102"/>
+      <c r="BN30" s="102"/>
+      <c r="BO30" s="102"/>
+    </row>
+    <row r="31" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7231</v>
+        <v>7343</v>
       </c>
       <c r="B31" s="53" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C31" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="51">
-        <v>1001013957231</v>
+        <v>1001016747343</v>
       </c>
       <c r="E31" s="24"/>
       <c r="F31" s="128">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G31" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G31:G33" si="6">E31*F31</f>
         <v>0</v>
       </c>
       <c r="H31" s="29">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="I31" s="29">
         <v>60</v>
@@ -7713,106 +7778,64 @@
       <c r="BN31" s="102"/>
       <c r="BO31" s="102"/>
     </row>
-    <row r="32" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="42" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="27"/>
+    <row r="32" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="137" t="str">
+        <f t="shared" si="1"/>
+        <v>6797</v>
+      </c>
+      <c r="B32" s="53" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D32" s="51">
+        <v>1001015026797</v>
+      </c>
+      <c r="E32" s="24"/>
+      <c r="F32" s="128">
+        <v>0.4</v>
+      </c>
+      <c r="G32" s="23">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="29">
+        <v>3.2</v>
+      </c>
+      <c r="I32" s="29">
+        <v>60</v>
+      </c>
+      <c r="J32" s="29"/>
       <c r="L32" s="102"/>
-      <c r="M32" s="102"/>
-      <c r="N32" s="102"/>
-      <c r="O32" s="102"/>
-      <c r="P32" s="102"/>
-      <c r="Q32" s="102"/>
-      <c r="R32" s="102"/>
-      <c r="S32" s="102"/>
-      <c r="T32" s="102"/>
-      <c r="U32" s="102"/>
-      <c r="V32" s="102"/>
-      <c r="W32" s="102"/>
-      <c r="X32" s="102"/>
-      <c r="Y32" s="102"/>
-      <c r="Z32" s="102"/>
-      <c r="AA32" s="102"/>
-      <c r="AB32" s="102"/>
-      <c r="AC32" s="102"/>
-      <c r="AD32" s="102"/>
-      <c r="AE32" s="102"/>
-      <c r="AF32" s="102"/>
-      <c r="AG32" s="102"/>
-      <c r="AH32" s="102"/>
-      <c r="AI32" s="102"/>
-      <c r="AJ32" s="102"/>
-      <c r="AK32" s="102"/>
-      <c r="AL32" s="102"/>
-      <c r="AM32" s="102"/>
-      <c r="AN32" s="102"/>
-      <c r="AO32" s="102"/>
-      <c r="AP32" s="102"/>
-      <c r="AQ32" s="102"/>
-      <c r="AR32" s="102"/>
-      <c r="AS32" s="102"/>
-      <c r="AT32" s="102"/>
-      <c r="AU32" s="102"/>
-      <c r="AV32" s="102"/>
-      <c r="AW32" s="102"/>
-      <c r="AX32" s="102"/>
-      <c r="AY32" s="102"/>
-      <c r="AZ32" s="102"/>
-      <c r="BA32" s="102"/>
-      <c r="BB32" s="102"/>
-      <c r="BC32" s="102"/>
-      <c r="BD32" s="102"/>
-      <c r="BE32" s="102"/>
-      <c r="BF32" s="102"/>
-      <c r="BG32" s="102"/>
-      <c r="BH32" s="102"/>
-      <c r="BI32" s="102"/>
-      <c r="BJ32" s="102"/>
-      <c r="BK32" s="102"/>
-      <c r="BL32" s="102"/>
-      <c r="BM32" s="102"/>
-      <c r="BN32" s="102"/>
-      <c r="BO32" s="102"/>
-    </row>
-    <row r="33" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6602</v>
+        <v>7231</v>
       </c>
       <c r="B33" s="53" t="s">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="C33" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="51">
-        <v>1001021966602</v>
+        <v>1001013957231</v>
       </c>
       <c r="E33" s="24"/>
       <c r="F33" s="128">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="G33" s="23">
-        <f t="shared" ref="G33:G37" si="7">E33*F33</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H33" s="29">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="I33" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J33" s="29"/>
       <c r="K33" s="27"/>
@@ -7873,35 +7896,21 @@
       <c r="BN33" s="102"/>
       <c r="BO33" s="102"/>
     </row>
-    <row r="34" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v>7601</v>
-      </c>
-      <c r="B34" s="53" t="s">
-        <v>218</v>
-      </c>
-      <c r="C34" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="51">
-        <v>1001025767601</v>
-      </c>
-      <c r="E34" s="24"/>
-      <c r="F34" s="128">
-        <v>0.26400000000000001</v>
-      </c>
-      <c r="G34" s="23">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H34" s="29">
-        <v>1.58</v>
-      </c>
-      <c r="I34" s="29">
-        <v>30</v>
-      </c>
-      <c r="J34" s="29"/>
+    <row r="34" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="43"/>
       <c r="K34" s="27"/>
       <c r="L34" s="102"/>
       <c r="M34" s="102"/>
@@ -7960,37 +7969,35 @@
       <c r="BN34" s="102"/>
       <c r="BO34" s="102"/>
     </row>
-    <row r="35" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A35" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7461</v>
+        <v>6602</v>
       </c>
       <c r="B35" s="53" t="s">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="C35" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="51">
-        <v>1001025767461</v>
+        <v>1001021966602</v>
       </c>
       <c r="E35" s="24"/>
       <c r="F35" s="128">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="G35" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="G35:G39" si="7">E35*F35</f>
         <v>0</v>
       </c>
       <c r="H35" s="29">
-        <v>1.98</v>
+        <v>2.8</v>
       </c>
       <c r="I35" s="29">
-        <v>30</v>
-      </c>
-      <c r="J35" s="52" t="s">
-        <v>223</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J35" s="29"/>
       <c r="K35" s="27"/>
       <c r="L35" s="102"/>
       <c r="M35" s="102"/>
@@ -8052,30 +8059,32 @@
     <row r="36" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7040</v>
+        <v>7601</v>
       </c>
       <c r="B36" s="53" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C36" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D36" s="51">
-        <v>1001025027040</v>
+        <v>1001025767601</v>
       </c>
       <c r="E36" s="24"/>
       <c r="F36" s="128">
-        <v>0.27</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="G36" s="23">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="125" t="s">
-        <v>196</v>
-      </c>
+      <c r="H36" s="29">
+        <v>1.58</v>
+      </c>
+      <c r="I36" s="29">
+        <v>30</v>
+      </c>
+      <c r="J36" s="29"/>
       <c r="K36" s="27"/>
       <c r="L36" s="102"/>
       <c r="M36" s="102"/>
@@ -8137,32 +8146,34 @@
     <row r="37" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6759</v>
+        <v>7461</v>
       </c>
       <c r="B37" s="53" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="C37" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D37" s="51">
-        <v>1001020836759</v>
+        <v>1001025767461</v>
       </c>
       <c r="E37" s="24"/>
       <c r="F37" s="128">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="G37" s="23">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H37" s="29">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="I37" s="29">
         <v>30</v>
       </c>
-      <c r="J37" s="29"/>
+      <c r="J37" s="52" t="s">
+        <v>223</v>
+      </c>
       <c r="K37" s="27"/>
       <c r="L37" s="102"/>
       <c r="M37" s="102"/>
@@ -8224,32 +8235,30 @@
     <row r="38" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6761</v>
+        <v>7040</v>
       </c>
       <c r="B38" s="53" t="s">
-        <v>52</v>
+        <v>214</v>
       </c>
       <c r="C38" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D38" s="51">
-        <v>1001020836761</v>
+        <v>1001025027040</v>
       </c>
       <c r="E38" s="24"/>
       <c r="F38" s="128">
-        <v>1</v>
+        <v>0.27</v>
       </c>
       <c r="G38" s="23">
-        <f t="shared" ref="G38:G39" si="8">E38</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="H38" s="29">
-        <v>4</v>
-      </c>
-      <c r="I38" s="29">
-        <v>30</v>
-      </c>
-      <c r="J38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="125" t="s">
+        <v>196</v>
+      </c>
       <c r="K38" s="27"/>
       <c r="L38" s="102"/>
       <c r="M38" s="102"/>
@@ -8311,30 +8320,30 @@
     <row r="39" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6829</v>
+        <v>6759</v>
       </c>
       <c r="B39" s="53" t="s">
-        <v>156</v>
+        <v>41</v>
       </c>
       <c r="C39" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D39" s="51">
-        <v>1001024976829</v>
+        <v>1001020836759</v>
       </c>
       <c r="E39" s="24"/>
       <c r="F39" s="128">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="G39" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H39" s="29">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="I39" s="29">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J39" s="29"/>
       <c r="K39" s="27"/>
@@ -8398,30 +8407,30 @@
     <row r="40" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6616</v>
+        <v>6761</v>
       </c>
       <c r="B40" s="53" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C40" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D40" s="51">
-        <v>1001024976616</v>
+        <v>1001020836761</v>
       </c>
       <c r="E40" s="24"/>
       <c r="F40" s="128">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G40" s="23">
-        <f>E40*F40</f>
+        <f t="shared" ref="G40:G41" si="8">E40</f>
         <v>0</v>
       </c>
       <c r="H40" s="29">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="I40" s="29">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="J40" s="29"/>
       <c r="K40" s="27"/>
@@ -8485,30 +8494,30 @@
     <row r="41" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7075</v>
+        <v>6829</v>
       </c>
       <c r="B41" s="53" t="s">
-        <v>49</v>
+        <v>156</v>
       </c>
       <c r="C41" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D41" s="51">
-        <v>1001022657075</v>
+        <v>1001024976829</v>
       </c>
       <c r="E41" s="24"/>
       <c r="F41" s="128">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="G41" s="23">
-        <f>E41</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H41" s="29">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="I41" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J41" s="29"/>
       <c r="K41" s="27"/>
@@ -8572,30 +8581,30 @@
     <row r="42" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7074</v>
+        <v>6616</v>
       </c>
       <c r="B42" s="53" t="s">
-        <v>157</v>
+        <v>42</v>
       </c>
       <c r="C42" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="51">
-        <v>1001022657074</v>
+        <v>1001024976616</v>
       </c>
       <c r="E42" s="24"/>
       <c r="F42" s="128">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G42" s="23">
-        <f t="shared" ref="G42:G45" si="9">E42*F42</f>
+        <f>E42*F42</f>
         <v>0</v>
       </c>
       <c r="H42" s="29">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="I42" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J42" s="29"/>
       <c r="K42" s="27"/>
@@ -8659,27 +8668,27 @@
     <row r="43" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7073</v>
+        <v>7075</v>
       </c>
       <c r="B43" s="53" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D43" s="51">
-        <v>1001022657073</v>
+        <v>1001022657075</v>
       </c>
       <c r="E43" s="24"/>
       <c r="F43" s="128">
-        <v>0.35</v>
+        <v>1.5</v>
       </c>
       <c r="G43" s="23">
-        <f t="shared" si="9"/>
+        <f>E43</f>
         <v>0</v>
       </c>
       <c r="H43" s="29">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="I43" s="29">
         <v>50</v>
@@ -8746,30 +8755,30 @@
     <row r="44" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6724</v>
+        <v>7074</v>
       </c>
       <c r="B44" s="53" t="s">
-        <v>51</v>
+        <v>157</v>
       </c>
       <c r="C44" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D44" s="51">
-        <v>1001020836724</v>
+        <v>1001022657074</v>
       </c>
       <c r="E44" s="24"/>
       <c r="F44" s="128">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="G44" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="G44:G47" si="9">E44*F44</f>
         <v>0</v>
       </c>
       <c r="H44" s="29">
-        <v>4.0999999999999996</v>
+        <v>4.8</v>
       </c>
       <c r="I44" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J44" s="29"/>
       <c r="K44" s="27"/>
@@ -8833,30 +8842,30 @@
     <row r="45" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>5819</v>
+        <v>7073</v>
       </c>
       <c r="B45" s="53" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C45" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D45" s="51">
-        <v>1001022725819</v>
+        <v>1001022657073</v>
       </c>
       <c r="E45" s="24"/>
       <c r="F45" s="128">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="G45" s="23">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H45" s="29">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="I45" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J45" s="29"/>
       <c r="K45" s="27"/>
@@ -8920,27 +8929,27 @@
     <row r="46" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6303</v>
+        <v>6724</v>
       </c>
       <c r="B46" s="53" t="s">
-        <v>158</v>
+        <v>51</v>
       </c>
       <c r="C46" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D46" s="51">
-        <v>1001022726303</v>
+        <v>1001020836724</v>
       </c>
       <c r="E46" s="24"/>
       <c r="F46" s="128">
-        <v>1.5</v>
+        <v>0.41</v>
       </c>
       <c r="G46" s="23">
-        <f>E46</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H46" s="29">
-        <v>4.5</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I46" s="29">
         <v>45</v>
@@ -9007,30 +9016,30 @@
     <row r="47" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7255</v>
+        <v>5819</v>
       </c>
       <c r="B47" s="53" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C47" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D47" s="51">
-        <v>1001025507255</v>
+        <v>1001022725819</v>
       </c>
       <c r="E47" s="24"/>
       <c r="F47" s="128">
         <v>0.4</v>
       </c>
       <c r="G47" s="23">
-        <f>E47*F47</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H47" s="29">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="I47" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J47" s="29"/>
       <c r="K47" s="27"/>
@@ -9094,16 +9103,16 @@
     <row r="48" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7271</v>
+        <v>6303</v>
       </c>
       <c r="B48" s="53" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C48" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D48" s="51">
-        <v>1001025507271</v>
+        <v>1001022726303</v>
       </c>
       <c r="E48" s="24"/>
       <c r="F48" s="128">
@@ -9114,10 +9123,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="29">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="I48" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J48" s="29"/>
       <c r="K48" s="27"/>
@@ -9181,30 +9190,30 @@
     <row r="49" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6765</v>
+        <v>7255</v>
       </c>
       <c r="B49" s="53" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C49" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D49" s="51">
-        <v>1001023696765</v>
+        <v>1001025507255</v>
       </c>
       <c r="E49" s="24"/>
       <c r="F49" s="128">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="G49" s="23">
         <f>E49*F49</f>
         <v>0</v>
       </c>
       <c r="H49" s="29">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="I49" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J49" s="29"/>
       <c r="K49" s="27"/>
@@ -9268,30 +9277,30 @@
     <row r="50" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6767</v>
+        <v>7271</v>
       </c>
       <c r="B50" s="53" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="C50" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D50" s="51">
-        <v>1001023696767</v>
+        <v>1001025507271</v>
       </c>
       <c r="E50" s="24"/>
       <c r="F50" s="128">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G50" s="23">
         <f>E50</f>
         <v>0</v>
       </c>
       <c r="H50" s="29">
-        <v>4.16</v>
+        <v>6</v>
       </c>
       <c r="I50" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J50" s="29"/>
       <c r="K50" s="27"/>
@@ -9355,27 +9364,27 @@
     <row r="51" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6475</v>
+        <v>6765</v>
       </c>
       <c r="B51" s="53" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C51" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D51" s="51">
-        <v>1001025176475</v>
+        <v>1001023696765</v>
       </c>
       <c r="E51" s="24"/>
       <c r="F51" s="128">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="G51" s="23">
         <f>E51*F51</f>
         <v>0</v>
       </c>
       <c r="H51" s="29">
-        <v>2.4</v>
+        <v>2.16</v>
       </c>
       <c r="I51" s="29">
         <v>45</v>
@@ -9442,30 +9451,30 @@
     <row r="52" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7083</v>
+        <v>6767</v>
       </c>
       <c r="B52" s="53" t="s">
-        <v>160</v>
+        <v>43</v>
       </c>
       <c r="C52" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D52" s="51">
-        <v>1001022467083</v>
+        <v>1001023696767</v>
       </c>
       <c r="E52" s="24"/>
       <c r="F52" s="128">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="G52" s="23">
         <f>E52</f>
         <v>0</v>
       </c>
       <c r="H52" s="29">
-        <v>6</v>
+        <v>4.16</v>
       </c>
       <c r="I52" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J52" s="29"/>
       <c r="K52" s="27"/>
@@ -9529,30 +9538,30 @@
     <row r="53" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7080</v>
+        <v>6475</v>
       </c>
       <c r="B53" s="53" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C53" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D53" s="51">
-        <v>1001022467080</v>
+        <v>1001025176475</v>
       </c>
       <c r="E53" s="24"/>
       <c r="F53" s="128">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="G53" s="23">
-        <f t="shared" ref="G53:G55" si="10">E53*F53</f>
+        <f>E53*F53</f>
         <v>0</v>
       </c>
       <c r="H53" s="29">
-        <v>4.0999999999999996</v>
+        <v>2.4</v>
       </c>
       <c r="I53" s="29">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J53" s="29"/>
       <c r="K53" s="27"/>
@@ -9613,95 +9622,207 @@
       <c r="BN53" s="102"/>
       <c r="BO53" s="102"/>
     </row>
-    <row r="54" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7276</v>
+        <v>7083</v>
       </c>
       <c r="B54" s="53" t="s">
-        <v>54</v>
+        <v>160</v>
       </c>
       <c r="C54" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D54" s="51">
-        <v>1001022467276</v>
+        <v>1001022467083</v>
       </c>
       <c r="E54" s="24"/>
       <c r="F54" s="128">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="G54" s="23">
-        <f t="shared" si="10"/>
+        <f>E54</f>
         <v>0</v>
       </c>
       <c r="H54" s="29">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="I54" s="29">
         <v>50</v>
       </c>
       <c r="J54" s="29"/>
+      <c r="K54" s="27"/>
       <c r="L54" s="102"/>
-    </row>
-    <row r="55" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M54" s="102"/>
+      <c r="N54" s="102"/>
+      <c r="O54" s="102"/>
+      <c r="P54" s="102"/>
+      <c r="Q54" s="102"/>
+      <c r="R54" s="102"/>
+      <c r="S54" s="102"/>
+      <c r="T54" s="102"/>
+      <c r="U54" s="102"/>
+      <c r="V54" s="102"/>
+      <c r="W54" s="102"/>
+      <c r="X54" s="102"/>
+      <c r="Y54" s="102"/>
+      <c r="Z54" s="102"/>
+      <c r="AA54" s="102"/>
+      <c r="AB54" s="102"/>
+      <c r="AC54" s="102"/>
+      <c r="AD54" s="102"/>
+      <c r="AE54" s="102"/>
+      <c r="AF54" s="102"/>
+      <c r="AG54" s="102"/>
+      <c r="AH54" s="102"/>
+      <c r="AI54" s="102"/>
+      <c r="AJ54" s="102"/>
+      <c r="AK54" s="102"/>
+      <c r="AL54" s="102"/>
+      <c r="AM54" s="102"/>
+      <c r="AN54" s="102"/>
+      <c r="AO54" s="102"/>
+      <c r="AP54" s="102"/>
+      <c r="AQ54" s="102"/>
+      <c r="AR54" s="102"/>
+      <c r="AS54" s="102"/>
+      <c r="AT54" s="102"/>
+      <c r="AU54" s="102"/>
+      <c r="AV54" s="102"/>
+      <c r="AW54" s="102"/>
+      <c r="AX54" s="102"/>
+      <c r="AY54" s="102"/>
+      <c r="AZ54" s="102"/>
+      <c r="BA54" s="102"/>
+      <c r="BB54" s="102"/>
+      <c r="BC54" s="102"/>
+      <c r="BD54" s="102"/>
+      <c r="BE54" s="102"/>
+      <c r="BF54" s="102"/>
+      <c r="BG54" s="102"/>
+      <c r="BH54" s="102"/>
+      <c r="BI54" s="102"/>
+      <c r="BJ54" s="102"/>
+      <c r="BK54" s="102"/>
+      <c r="BL54" s="102"/>
+      <c r="BM54" s="102"/>
+      <c r="BN54" s="102"/>
+      <c r="BO54" s="102"/>
+    </row>
+    <row r="55" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6762</v>
+        <v>7080</v>
       </c>
       <c r="B55" s="53" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C55" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D55" s="51">
-        <v>1001020846762</v>
+        <v>1001022467080</v>
       </c>
       <c r="E55" s="24"/>
       <c r="F55" s="128">
         <v>0.41</v>
       </c>
       <c r="G55" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="G55:G57" si="10">E55*F55</f>
         <v>0</v>
       </c>
       <c r="H55" s="29">
-        <v>3.28</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I55" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J55" s="29"/>
+      <c r="K55" s="27"/>
       <c r="L55" s="102"/>
+      <c r="M55" s="102"/>
+      <c r="N55" s="102"/>
+      <c r="O55" s="102"/>
+      <c r="P55" s="102"/>
+      <c r="Q55" s="102"/>
+      <c r="R55" s="102"/>
+      <c r="S55" s="102"/>
+      <c r="T55" s="102"/>
+      <c r="U55" s="102"/>
+      <c r="V55" s="102"/>
+      <c r="W55" s="102"/>
+      <c r="X55" s="102"/>
+      <c r="Y55" s="102"/>
+      <c r="Z55" s="102"/>
+      <c r="AA55" s="102"/>
+      <c r="AB55" s="102"/>
+      <c r="AC55" s="102"/>
+      <c r="AD55" s="102"/>
+      <c r="AE55" s="102"/>
+      <c r="AF55" s="102"/>
+      <c r="AG55" s="102"/>
+      <c r="AH55" s="102"/>
+      <c r="AI55" s="102"/>
+      <c r="AJ55" s="102"/>
+      <c r="AK55" s="102"/>
+      <c r="AL55" s="102"/>
+      <c r="AM55" s="102"/>
+      <c r="AN55" s="102"/>
+      <c r="AO55" s="102"/>
+      <c r="AP55" s="102"/>
+      <c r="AQ55" s="102"/>
+      <c r="AR55" s="102"/>
+      <c r="AS55" s="102"/>
+      <c r="AT55" s="102"/>
+      <c r="AU55" s="102"/>
+      <c r="AV55" s="102"/>
+      <c r="AW55" s="102"/>
+      <c r="AX55" s="102"/>
+      <c r="AY55" s="102"/>
+      <c r="AZ55" s="102"/>
+      <c r="BA55" s="102"/>
+      <c r="BB55" s="102"/>
+      <c r="BC55" s="102"/>
+      <c r="BD55" s="102"/>
+      <c r="BE55" s="102"/>
+      <c r="BF55" s="102"/>
+      <c r="BG55" s="102"/>
+      <c r="BH55" s="102"/>
+      <c r="BI55" s="102"/>
+      <c r="BJ55" s="102"/>
+      <c r="BK55" s="102"/>
+      <c r="BL55" s="102"/>
+      <c r="BM55" s="102"/>
+      <c r="BN55" s="102"/>
+      <c r="BO55" s="102"/>
     </row>
     <row r="56" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6764</v>
+        <v>7276</v>
       </c>
       <c r="B56" s="53" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="C56" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D56" s="51">
-        <v>1001020846764</v>
+        <v>1001022467276</v>
       </c>
       <c r="E56" s="24"/>
-      <c r="F56" s="23">
-        <v>1</v>
+      <c r="F56" s="128">
+        <v>0.3</v>
       </c>
       <c r="G56" s="23">
-        <f>E56</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H56" s="14">
-        <v>4</v>
-      </c>
-      <c r="I56" s="14">
-        <v>45</v>
+      <c r="H56" s="29">
+        <v>2.1</v>
+      </c>
+      <c r="I56" s="29">
+        <v>50</v>
       </c>
       <c r="J56" s="29"/>
       <c r="L56" s="102"/>
@@ -9709,30 +9830,30 @@
     <row r="57" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7066</v>
+        <v>6762</v>
       </c>
       <c r="B57" s="53" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C57" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D57" s="51">
-        <v>1001022377066</v>
+        <v>1001020846762</v>
       </c>
       <c r="E57" s="24"/>
-      <c r="F57" s="23">
+      <c r="F57" s="128">
         <v>0.41</v>
       </c>
       <c r="G57" s="23">
-        <f>E57*F57</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="H57" s="14">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="I57" s="14">
-        <v>50</v>
+      <c r="H57" s="29">
+        <v>3.28</v>
+      </c>
+      <c r="I57" s="29">
+        <v>45</v>
       </c>
       <c r="J57" s="29"/>
       <c r="L57" s="102"/>
@@ -9740,30 +9861,30 @@
     <row r="58" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7070</v>
+        <v>6764</v>
       </c>
       <c r="B58" s="53" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C58" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D58" s="51">
-        <v>1001022377070</v>
+        <v>1001020846764</v>
       </c>
       <c r="E58" s="24"/>
       <c r="F58" s="23">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G58" s="23">
         <f>E58</f>
         <v>0</v>
       </c>
       <c r="H58" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I58" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J58" s="29"/>
       <c r="L58" s="102"/>
@@ -9771,16 +9892,16 @@
     <row r="59" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6713</v>
+        <v>7066</v>
       </c>
       <c r="B59" s="53" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C59" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D59" s="51">
-        <v>1001022246713</v>
+        <v>1001022377066</v>
       </c>
       <c r="E59" s="24"/>
       <c r="F59" s="23">
@@ -9791,10 +9912,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="14">
-        <v>3.28</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="I59" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J59" s="29"/>
       <c r="L59" s="102"/>
@@ -9802,30 +9923,30 @@
     <row r="60" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6661</v>
+        <v>7070</v>
       </c>
       <c r="B60" s="53" t="s">
-        <v>161</v>
+        <v>44</v>
       </c>
       <c r="C60" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D60" s="51">
-        <v>1001022246661</v>
+        <v>1001022377070</v>
       </c>
       <c r="E60" s="24"/>
       <c r="F60" s="23">
         <v>1.5</v>
       </c>
       <c r="G60" s="23">
-        <f t="shared" ref="G60:G61" si="11">E60</f>
+        <f>E60</f>
         <v>0</v>
       </c>
       <c r="H60" s="14">
         <v>6</v>
       </c>
       <c r="I60" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J60" s="29"/>
       <c r="L60" s="102"/>
@@ -9833,27 +9954,27 @@
     <row r="61" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6254</v>
+        <v>6713</v>
       </c>
       <c r="B61" s="53" t="s">
-        <v>162</v>
+        <v>46</v>
       </c>
       <c r="C61" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D61" s="51">
-        <v>1001022556254</v>
+        <v>1001022246713</v>
       </c>
       <c r="E61" s="24"/>
       <c r="F61" s="23">
-        <v>1.5</v>
+        <v>0.41</v>
       </c>
       <c r="G61" s="23">
-        <f t="shared" si="11"/>
+        <f>E61*F61</f>
         <v>0</v>
       </c>
       <c r="H61" s="14">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="I61" s="14">
         <v>45</v>
@@ -9864,27 +9985,27 @@
     <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>6837</v>
+        <v>6661</v>
       </c>
       <c r="B62" s="53" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="C62" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D62" s="51">
-        <v>1001022556837</v>
+        <v>1001022246661</v>
       </c>
       <c r="E62" s="24"/>
       <c r="F62" s="23">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G62" s="23">
-        <f t="shared" ref="G62:G63" si="12">E62*F62</f>
+        <f t="shared" ref="G62:G63" si="11">E62</f>
         <v>0</v>
       </c>
       <c r="H62" s="14">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I62" s="14">
         <v>45</v>
@@ -9892,160 +10013,160 @@
       <c r="J62" s="29"/>
       <c r="L62" s="102"/>
     </row>
-    <row r="63" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="137" t="str">
         <f t="shared" si="1"/>
-        <v>7044</v>
+        <v>6254</v>
       </c>
       <c r="B63" s="53" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C63" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D63" s="51">
-        <v>1001025167044</v>
+        <v>1001022556254</v>
       </c>
       <c r="E63" s="24"/>
       <c r="F63" s="23">
+        <v>1.5</v>
+      </c>
+      <c r="G63" s="23">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>3</v>
+      </c>
+      <c r="I63" s="14">
+        <v>45</v>
+      </c>
+      <c r="J63" s="29"/>
+      <c r="L63" s="102"/>
+    </row>
+    <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="137" t="str">
+        <f t="shared" si="1"/>
+        <v>6837</v>
+      </c>
+      <c r="B64" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C64" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="51">
+        <v>1001022556837</v>
+      </c>
+      <c r="E64" s="24"/>
+      <c r="F64" s="23">
+        <v>0.4</v>
+      </c>
+      <c r="G64" s="23">
+        <f t="shared" ref="G64:G65" si="12">E64*F64</f>
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>2.4</v>
+      </c>
+      <c r="I64" s="14">
+        <v>45</v>
+      </c>
+      <c r="J64" s="29"/>
+      <c r="L64" s="102"/>
+    </row>
+    <row r="65" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="137" t="str">
+        <f t="shared" si="1"/>
+        <v>7044</v>
+      </c>
+      <c r="B65" s="53" t="s">
+        <v>164</v>
+      </c>
+      <c r="C65" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="51">
+        <v>1001025167044</v>
+      </c>
+      <c r="E65" s="24"/>
+      <c r="F65" s="23">
         <v>0.32</v>
       </c>
-      <c r="G63" s="23">
+      <c r="G65" s="23">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="H63" s="14">
+      <c r="H65" s="14">
         <v>2.56</v>
       </c>
-      <c r="I63" s="14">
+      <c r="I65" s="14">
         <v>45</v>
       </c>
-      <c r="J63" s="29"/>
-      <c r="L63" s="102"/>
-    </row>
-    <row r="64" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="47" t="s">
+      <c r="J65" s="29"/>
+      <c r="L65" s="102"/>
+    </row>
+    <row r="66" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B64" s="42" t="s">
+      <c r="B66" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="42"/>
-      <c r="H64" s="42"/>
-      <c r="I64" s="42"/>
-      <c r="J64" s="43"/>
-      <c r="L64" s="102"/>
-    </row>
-    <row r="65" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="137" t="str">
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="41"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+      <c r="I66" s="42"/>
+      <c r="J66" s="43"/>
+      <c r="L66" s="102"/>
+    </row>
+    <row r="67" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6550</v>
       </c>
-      <c r="B65" s="129" t="s">
+      <c r="B67" s="129" t="s">
         <v>151</v>
       </c>
-      <c r="C65" s="130" t="s">
+      <c r="C67" s="130" t="s">
         <v>22</v>
       </c>
-      <c r="D65" s="51">
+      <c r="D67" s="51">
         <v>1001032736550</v>
       </c>
-      <c r="E65" s="24"/>
-      <c r="F65" s="128">
+      <c r="E67" s="24"/>
+      <c r="F67" s="128">
         <v>1</v>
       </c>
-      <c r="G65" s="23">
-        <f t="shared" ref="G65:G68" si="13">E65</f>
+      <c r="G67" s="23">
+        <f t="shared" ref="G67:G70" si="13">E67</f>
         <v>0</v>
       </c>
-      <c r="H65" s="29">
+      <c r="H67" s="29">
         <v>3</v>
       </c>
-      <c r="I65" s="29">
+      <c r="I67" s="29">
         <v>45</v>
       </c>
-      <c r="J65" s="29"/>
-      <c r="L65" s="102"/>
-    </row>
-    <row r="66" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="137" t="str">
+      <c r="J67" s="29"/>
+      <c r="L67" s="102"/>
+    </row>
+    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6608</v>
       </c>
-      <c r="B66" s="129" t="s">
+      <c r="B68" s="129" t="s">
         <v>58</v>
-      </c>
-      <c r="C66" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D66" s="51">
-        <v>1001033856608</v>
-      </c>
-      <c r="E66" s="24"/>
-      <c r="F66" s="23">
-        <v>1</v>
-      </c>
-      <c r="G66" s="23">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H66" s="14">
-        <v>3</v>
-      </c>
-      <c r="I66" s="14">
-        <v>45</v>
-      </c>
-      <c r="J66" s="29"/>
-      <c r="L66" s="102"/>
-    </row>
-    <row r="67" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="137" t="str">
-        <f t="shared" si="1"/>
-        <v>7001</v>
-      </c>
-      <c r="B67" s="129" t="s">
-        <v>57</v>
-      </c>
-      <c r="C67" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D67" s="51">
-        <v>1001035937001</v>
-      </c>
-      <c r="E67" s="24"/>
-      <c r="F67" s="23">
-        <v>1</v>
-      </c>
-      <c r="G67" s="23">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="H67" s="14">
-        <v>3</v>
-      </c>
-      <c r="I67" s="14">
-        <v>45</v>
-      </c>
-      <c r="J67" s="29"/>
-      <c r="L67" s="102"/>
-    </row>
-    <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="137" t="str">
-        <f t="shared" ref="A68:A70" si="14">RIGHT(D68,4)</f>
-        <v>6527</v>
-      </c>
-      <c r="B68" s="129" t="s">
-        <v>152</v>
       </c>
       <c r="C68" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D68" s="51">
-        <v>1001031076527</v>
+        <v>1001033856608</v>
       </c>
       <c r="E68" s="24"/>
       <c r="F68" s="23">
@@ -10066,237 +10187,237 @@
     </row>
     <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="137" t="str">
+        <f t="shared" si="1"/>
+        <v>7001</v>
+      </c>
+      <c r="B69" s="129" t="s">
+        <v>57</v>
+      </c>
+      <c r="C69" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D69" s="51">
+        <v>1001035937001</v>
+      </c>
+      <c r="E69" s="24"/>
+      <c r="F69" s="23">
+        <v>1</v>
+      </c>
+      <c r="G69" s="23">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H69" s="14">
+        <v>3</v>
+      </c>
+      <c r="I69" s="14">
+        <v>45</v>
+      </c>
+      <c r="J69" s="29"/>
+      <c r="L69" s="102"/>
+    </row>
+    <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="137" t="str">
+        <f t="shared" ref="A70:A72" si="14">RIGHT(D70,4)</f>
+        <v>6527</v>
+      </c>
+      <c r="B70" s="129" t="s">
+        <v>152</v>
+      </c>
+      <c r="C70" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D70" s="51">
+        <v>1001031076527</v>
+      </c>
+      <c r="E70" s="24"/>
+      <c r="F70" s="23">
+        <v>1</v>
+      </c>
+      <c r="G70" s="23">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="H70" s="14">
+        <v>3</v>
+      </c>
+      <c r="I70" s="14">
+        <v>45</v>
+      </c>
+      <c r="J70" s="29"/>
+      <c r="L70" s="102"/>
+    </row>
+    <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="137" t="str">
         <f t="shared" si="14"/>
         <v>6609</v>
       </c>
-      <c r="B69" s="129" t="s">
+      <c r="B71" s="129" t="s">
         <v>153</v>
       </c>
-      <c r="C69" s="50" t="s">
+      <c r="C71" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D69" s="51">
+      <c r="D71" s="51">
         <v>1001033856609</v>
       </c>
-      <c r="E69" s="24"/>
-      <c r="F69" s="23">
+      <c r="E71" s="24"/>
+      <c r="F71" s="23">
         <v>0.4</v>
       </c>
-      <c r="G69" s="23">
-        <f t="shared" ref="G69:G70" si="15">E69*F69</f>
+      <c r="G71" s="23">
+        <f t="shared" ref="G71:G72" si="15">E71*F71</f>
         <v>0</v>
       </c>
-      <c r="H69" s="14">
+      <c r="H71" s="14">
         <v>2.4</v>
       </c>
-      <c r="I69" s="14">
+      <c r="I71" s="14">
         <v>45</v>
       </c>
-      <c r="J69" s="29"/>
-      <c r="L69" s="102"/>
-    </row>
-    <row r="70" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="137" t="str">
+      <c r="J71" s="29"/>
+      <c r="L71" s="102"/>
+    </row>
+    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7059</v>
       </c>
-      <c r="B70" s="129" t="s">
+      <c r="B72" s="129" t="s">
         <v>154</v>
       </c>
-      <c r="C70" s="50" t="s">
+      <c r="C72" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D70" s="51">
+      <c r="D72" s="51">
         <v>1001035277059</v>
       </c>
-      <c r="E70" s="24"/>
-      <c r="F70" s="23">
+      <c r="E72" s="24"/>
+      <c r="F72" s="23">
         <v>0.3</v>
       </c>
-      <c r="G70" s="23">
+      <c r="G72" s="23">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H70" s="14">
+      <c r="H72" s="14">
         <v>2.4</v>
       </c>
-      <c r="I70" s="14">
+      <c r="I72" s="14">
         <v>60</v>
       </c>
-      <c r="J70" s="29"/>
-      <c r="L70" s="102"/>
-    </row>
-    <row r="71" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="47" t="s">
+      <c r="J72" s="29"/>
+      <c r="L72" s="102"/>
+    </row>
+    <row r="73" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B71" s="42" t="s">
+      <c r="B73" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="C71" s="42"/>
-      <c r="D71" s="42"/>
-      <c r="E71" s="42"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="42"/>
-      <c r="H71" s="42"/>
-      <c r="I71" s="42"/>
-      <c r="J71" s="43"/>
-      <c r="L71" s="102"/>
-    </row>
-    <row r="72" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="137" t="str">
-        <f t="shared" ref="A72:A95" si="16">RIGHT(D72,4)</f>
+      <c r="C73" s="42"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="41"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="42"/>
+      <c r="I73" s="42"/>
+      <c r="J73" s="43"/>
+      <c r="L73" s="102"/>
+    </row>
+    <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="137" t="str">
+        <f t="shared" ref="A74:A100" si="16">RIGHT(D74,4)</f>
         <v>7564</v>
       </c>
-      <c r="B72" s="53" t="s">
+      <c r="B74" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="C72" s="50" t="s">
+      <c r="C74" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="51">
+      <c r="D74" s="51">
         <v>1001303637564</v>
-      </c>
-      <c r="E72" s="24"/>
-      <c r="F72" s="23">
-        <v>0.84</v>
-      </c>
-      <c r="G72" s="23">
-        <f>E72</f>
-        <v>0</v>
-      </c>
-      <c r="H72" s="14">
-        <v>5.04</v>
-      </c>
-      <c r="I72" s="14">
-        <v>45</v>
-      </c>
-      <c r="J72" s="52" t="s">
-        <v>169</v>
-      </c>
-      <c r="L72" s="102"/>
-    </row>
-    <row r="73" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7603</v>
-      </c>
-      <c r="B73" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="C73" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="51">
-        <v>1001303637603</v>
-      </c>
-      <c r="E73" s="24"/>
-      <c r="F73" s="23">
-        <v>0.33</v>
-      </c>
-      <c r="G73" s="23">
-        <f t="shared" ref="G73:G85" si="17">E73*F73</f>
-        <v>0</v>
-      </c>
-      <c r="H73" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I73" s="14">
-        <v>45</v>
-      </c>
-      <c r="J73" s="52" t="s">
-        <v>170</v>
-      </c>
-      <c r="L73" s="102"/>
-    </row>
-    <row r="74" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7149</v>
-      </c>
-      <c r="B74" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="C74" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D74" s="51">
-        <v>1001303637149</v>
       </c>
       <c r="E74" s="24"/>
       <c r="F74" s="23">
         <v>0.84</v>
       </c>
       <c r="G74" s="23">
-        <f t="shared" si="17"/>
+        <f>E74</f>
         <v>0</v>
       </c>
       <c r="H74" s="14">
         <v>5.04</v>
       </c>
       <c r="I74" s="14">
-        <v>50</v>
-      </c>
-      <c r="J74" s="29"/>
+        <v>45</v>
+      </c>
+      <c r="J74" s="52" t="s">
+        <v>169</v>
+      </c>
       <c r="L74" s="102"/>
     </row>
     <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7233</v>
+        <v>7603</v>
       </c>
       <c r="B75" s="53" t="s">
-        <v>219</v>
+        <v>122</v>
       </c>
       <c r="C75" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D75" s="51">
-        <v>1001303637233</v>
+        <v>1001303637603</v>
       </c>
       <c r="E75" s="24"/>
-      <c r="F75" s="128">
-        <v>0.31</v>
+      <c r="F75" s="23">
+        <v>0.33</v>
       </c>
       <c r="G75" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" ref="G75:G87" si="17">E75*F75</f>
         <v>0</v>
       </c>
-      <c r="H75" s="29">
-        <v>2.48</v>
-      </c>
-      <c r="I75" s="29">
+      <c r="H75" s="14">
+        <v>2.64</v>
+      </c>
+      <c r="I75" s="14">
         <v>45</v>
       </c>
-      <c r="J75" s="29"/>
+      <c r="J75" s="52" t="s">
+        <v>170</v>
+      </c>
       <c r="L75" s="102"/>
     </row>
     <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7232</v>
+        <v>7149</v>
       </c>
       <c r="B76" s="53" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="C76" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D76" s="51">
-        <v>1001302277232</v>
+        <v>1001303637149</v>
       </c>
       <c r="E76" s="24"/>
-      <c r="F76" s="128">
-        <v>0.28000000000000003</v>
+      <c r="F76" s="23">
+        <v>0.84</v>
       </c>
       <c r="G76" s="23">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H76" s="29">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I76" s="29">
+      <c r="H76" s="14">
+        <v>5.04</v>
+      </c>
+      <c r="I76" s="14">
         <v>50</v>
       </c>
       <c r="J76" s="29"/>
@@ -10305,27 +10426,27 @@
     <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7241</v>
+        <v>7233</v>
       </c>
       <c r="B77" s="53" t="s">
-        <v>63</v>
+        <v>219</v>
       </c>
       <c r="C77" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D77" s="51">
-        <v>1001303107241</v>
+        <v>1001303637233</v>
       </c>
       <c r="E77" s="24"/>
       <c r="F77" s="128">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G77" s="23">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H77" s="29">
-        <v>2.2400000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I77" s="29">
         <v>45</v>
@@ -10336,30 +10457,30 @@
     <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7133</v>
+        <v>7232</v>
       </c>
       <c r="B78" s="53" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="C78" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D78" s="51">
-        <v>1001300367133</v>
+        <v>1001302277232</v>
       </c>
       <c r="E78" s="24"/>
       <c r="F78" s="128">
-        <v>0.84</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G78" s="23">
-        <f>E78</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H78" s="29">
-        <v>5.04</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I78" s="29">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J78" s="29"/>
       <c r="L78" s="102"/>
@@ -10367,205 +10488,207 @@
     <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>6946</v>
+        <v>7241</v>
       </c>
       <c r="B79" s="53" t="s">
-        <v>178</v>
+        <v>63</v>
       </c>
       <c r="C79" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D79" s="51">
-        <v>1001300456946</v>
+        <v>1001303107241</v>
       </c>
       <c r="E79" s="24"/>
-      <c r="F79" s="128"/>
+      <c r="F79" s="128">
+        <v>0.28000000000000003</v>
+      </c>
       <c r="G79" s="23">
-        <f>E79</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H79" s="29"/>
-      <c r="I79" s="29"/>
+      <c r="H79" s="29">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I79" s="29">
+        <v>45</v>
+      </c>
       <c r="J79" s="29"/>
       <c r="L79" s="102"/>
     </row>
     <row r="80" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>6807</v>
+        <v>7133</v>
       </c>
       <c r="B80" s="53" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C80" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D80" s="51">
-        <v>1001300366807</v>
+        <v>1001300367133</v>
       </c>
       <c r="E80" s="24"/>
       <c r="F80" s="128">
+        <v>0.84</v>
+      </c>
+      <c r="G80" s="23">
+        <f>E80</f>
+        <v>0</v>
+      </c>
+      <c r="H80" s="29">
+        <v>5.04</v>
+      </c>
+      <c r="I80" s="29">
+        <v>45</v>
+      </c>
+      <c r="J80" s="29"/>
+      <c r="L80" s="102"/>
+    </row>
+    <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="137" t="str">
+        <f t="shared" si="16"/>
+        <v>6946</v>
+      </c>
+      <c r="B81" s="53" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D81" s="51">
+        <v>1001300456946</v>
+      </c>
+      <c r="E81" s="24"/>
+      <c r="F81" s="128"/>
+      <c r="G81" s="23">
+        <f>E81</f>
+        <v>0</v>
+      </c>
+      <c r="H81" s="29"/>
+      <c r="I81" s="29"/>
+      <c r="J81" s="29"/>
+      <c r="L81" s="102"/>
+    </row>
+    <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="137" t="str">
+        <f t="shared" si="16"/>
+        <v>6807</v>
+      </c>
+      <c r="B82" s="53" t="s">
+        <v>75</v>
+      </c>
+      <c r="C82" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D82" s="51">
+        <v>1001300366807</v>
+      </c>
+      <c r="E82" s="24"/>
+      <c r="F82" s="128">
         <v>0.33</v>
       </c>
-      <c r="G80" s="23">
+      <c r="G82" s="23">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H80" s="29">
+      <c r="H82" s="29">
         <v>2.64</v>
       </c>
-      <c r="I80" s="29">
+      <c r="I82" s="29">
         <v>45</v>
       </c>
-      <c r="J80" s="29"/>
-      <c r="L80" s="102"/>
-    </row>
-    <row r="81" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="137" t="str">
+      <c r="J82" s="29"/>
+      <c r="L82" s="102"/>
+    </row>
+    <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="137" t="str">
         <f t="shared" si="16"/>
         <v>7154</v>
       </c>
-      <c r="B81" s="53" t="s">
+      <c r="B83" s="53" t="s">
         <v>64</v>
-      </c>
-      <c r="C81" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D81" s="51">
-        <v>1001300387154</v>
-      </c>
-      <c r="E81" s="24"/>
-      <c r="F81" s="23">
-        <v>0.35</v>
-      </c>
-      <c r="G81" s="23">
-        <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="H81" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I81" s="14">
-        <v>50</v>
-      </c>
-      <c r="J81" s="29"/>
-      <c r="L81" s="102"/>
-    </row>
-    <row r="82" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7157</v>
-      </c>
-      <c r="B82" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="C82" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" s="51">
-        <v>1001300387157</v>
-      </c>
-      <c r="E82" s="24"/>
-      <c r="F82" s="23">
-        <v>0.63</v>
-      </c>
-      <c r="G82" s="23">
-        <f>E82</f>
-        <v>0</v>
-      </c>
-      <c r="H82" s="14">
-        <v>5.04</v>
-      </c>
-      <c r="I82" s="14">
-        <v>50</v>
-      </c>
-      <c r="J82" s="29"/>
-      <c r="L82" s="102"/>
-    </row>
-    <row r="83" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7236</v>
-      </c>
-      <c r="B83" s="53" t="s">
-        <v>68</v>
       </c>
       <c r="C83" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D83" s="51">
-        <v>1001304507236</v>
+        <v>1001300387154</v>
       </c>
       <c r="E83" s="24"/>
       <c r="F83" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G83" s="23">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H83" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I83" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J83" s="29"/>
       <c r="L83" s="102"/>
     </row>
-    <row r="84" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7489</v>
+        <v>7157</v>
       </c>
       <c r="B84" s="53" t="s">
-        <v>212</v>
+        <v>74</v>
       </c>
       <c r="C84" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D84" s="51">
-        <v>1001307357489</v>
+        <v>1001300387157</v>
       </c>
       <c r="E84" s="24"/>
       <c r="F84" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.63</v>
       </c>
       <c r="G84" s="23">
-        <f t="shared" si="17"/>
+        <f>E84</f>
         <v>0</v>
       </c>
-      <c r="H84" s="14"/>
-      <c r="I84" s="14"/>
-      <c r="J84" s="125" t="s">
-        <v>196</v>
-      </c>
+      <c r="H84" s="14">
+        <v>5.04</v>
+      </c>
+      <c r="I84" s="14">
+        <v>50</v>
+      </c>
+      <c r="J84" s="29"/>
       <c r="L84" s="102"/>
     </row>
-    <row r="85" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>6787</v>
-      </c>
-      <c r="B85" s="131" t="s">
-        <v>65</v>
+        <v>7236</v>
+      </c>
+      <c r="B85" s="53" t="s">
+        <v>68</v>
       </c>
       <c r="C85" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D85" s="51">
-        <v>1001300456787</v>
+        <v>1001304507236</v>
       </c>
       <c r="E85" s="24"/>
       <c r="F85" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G85" s="23">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H85" s="14">
-        <v>2.64</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I85" s="14">
         <v>45</v>
@@ -10573,659 +10696,645 @@
       <c r="J85" s="29"/>
       <c r="L85" s="102"/>
     </row>
-    <row r="86" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7166</v>
-      </c>
-      <c r="B86" s="131" t="s">
-        <v>71</v>
+        <v>7489</v>
+      </c>
+      <c r="B86" s="53" t="s">
+        <v>212</v>
       </c>
       <c r="C86" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D86" s="51">
-        <v>1001303987166</v>
+        <v>1001307357489</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="23">
-        <v>0.7</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G86" s="23">
-        <f>E86</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="H86" s="14">
-        <v>5.6</v>
-      </c>
-      <c r="I86" s="14">
-        <v>50</v>
-      </c>
-      <c r="J86" s="29"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="125" t="s">
+        <v>196</v>
+      </c>
       <c r="L86" s="102"/>
     </row>
-    <row r="87" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7169</v>
-      </c>
-      <c r="B87" s="53" t="s">
-        <v>70</v>
+        <v>6787</v>
+      </c>
+      <c r="B87" s="131" t="s">
+        <v>65</v>
       </c>
       <c r="C87" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D87" s="51">
-        <v>1001303987169</v>
+        <v>1001300456787</v>
       </c>
       <c r="E87" s="24"/>
       <c r="F87" s="23">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="G87" s="23">
-        <f>E87*F87</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H87" s="14">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="I87" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J87" s="29"/>
       <c r="L87" s="102"/>
     </row>
-    <row r="88" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>5544</v>
-      </c>
-      <c r="B88" s="53" t="s">
-        <v>72</v>
+        <v>7166</v>
+      </c>
+      <c r="B88" s="131" t="s">
+        <v>71</v>
       </c>
       <c r="C88" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D88" s="51">
-        <v>1001051875544</v>
+        <v>1001303987166</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="23">
-        <v>0.81</v>
+        <v>0.7</v>
       </c>
       <c r="G88" s="23">
         <f>E88</f>
         <v>0</v>
       </c>
       <c r="H88" s="14">
-        <v>4.8600000000000003</v>
+        <v>5.6</v>
       </c>
       <c r="I88" s="14">
-        <v>45</v>
-      </c>
-      <c r="J88" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J88" s="29"/>
       <c r="L88" s="102"/>
     </row>
-    <row r="89" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>6697</v>
+        <v>7169</v>
       </c>
       <c r="B89" s="53" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C89" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D89" s="51">
-        <v>1001301876697</v>
+        <v>1001303987169</v>
       </c>
       <c r="E89" s="24"/>
       <c r="F89" s="23">
         <v>0.35</v>
       </c>
       <c r="G89" s="23">
-        <f t="shared" ref="G89:G95" si="18">E89*F89</f>
+        <f>E89*F89</f>
         <v>0</v>
       </c>
       <c r="H89" s="14">
         <v>2.8</v>
       </c>
       <c r="I89" s="14">
-        <v>45</v>
-      </c>
-      <c r="J89" s="49"/>
+        <v>50</v>
+      </c>
+      <c r="J89" s="29"/>
       <c r="L89" s="102"/>
     </row>
-    <row r="90" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7238</v>
+        <v>7156</v>
       </c>
       <c r="B90" s="53" t="s">
-        <v>123</v>
+        <v>225</v>
       </c>
       <c r="C90" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D90" s="51">
-        <v>1001305197238</v>
+        <v>1001304237156</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G90" s="23">
-        <f t="shared" si="18"/>
+        <f>E90*F90</f>
         <v>0</v>
       </c>
-      <c r="H90" s="14">
-        <v>2.48</v>
-      </c>
-      <c r="I90" s="14">
-        <v>45</v>
-      </c>
+      <c r="H90" s="14"/>
+      <c r="I90" s="14"/>
       <c r="J90" s="49"/>
       <c r="L90" s="102"/>
     </row>
-    <row r="91" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7177</v>
+        <v>5544</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D91" s="51">
-        <v>1001302347177</v>
+        <v>1001051875544</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G91" s="23">
-        <f t="shared" si="18"/>
+        <f>E91</f>
         <v>0</v>
       </c>
       <c r="H91" s="14">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I91" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J91" s="49"/>
       <c r="L91" s="102"/>
     </row>
-    <row r="92" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7332</v>
+        <v>6697</v>
       </c>
       <c r="B92" s="53" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C92" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D92" s="51">
-        <v>1001301777332</v>
+        <v>1001301876697</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G92:G100" si="18">E92*F92</f>
         <v>0</v>
       </c>
       <c r="H92" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I92" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J92" s="49"/>
       <c r="L92" s="102"/>
     </row>
-    <row r="93" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7333</v>
+        <v>7238</v>
       </c>
       <c r="B93" s="53" t="s">
-        <v>69</v>
+        <v>123</v>
       </c>
       <c r="C93" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D93" s="51">
-        <v>1001303987333</v>
+        <v>1001305197238</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="G93" s="23">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H93" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.48</v>
       </c>
       <c r="I93" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J93" s="49"/>
       <c r="L93" s="102"/>
     </row>
-    <row r="94" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="137" t="str">
         <f t="shared" si="16"/>
-        <v>7608</v>
+        <v>7516</v>
       </c>
       <c r="B94" s="53" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="C94" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D94" s="51">
-        <v>1001304197608</v>
+        <v>1001307107516</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="G94" s="23">
+        <f t="shared" ref="G94" si="19">E94*F94</f>
+        <v>0</v>
+      </c>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="49"/>
+      <c r="L94" s="102"/>
+    </row>
+    <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="137" t="str">
+        <f t="shared" si="16"/>
+        <v>7513</v>
+      </c>
+      <c r="B95" s="53" t="s">
+        <v>230</v>
+      </c>
+      <c r="C95" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D95" s="51">
+        <v>1001307077513</v>
+      </c>
+      <c r="E95" s="24"/>
+      <c r="F95" s="23">
+        <v>0.26</v>
+      </c>
+      <c r="G95" s="23">
+        <f t="shared" ref="G95" si="20">E95*F95</f>
+        <v>0</v>
+      </c>
+      <c r="H95" s="14"/>
+      <c r="I95" s="14"/>
+      <c r="J95" s="49"/>
+      <c r="L95" s="102"/>
+    </row>
+    <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="137" t="str">
+        <f t="shared" si="16"/>
+        <v>7177</v>
+      </c>
+      <c r="B96" s="53" t="s">
+        <v>124</v>
+      </c>
+      <c r="C96" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D96" s="51">
+        <v>1001302347177</v>
+      </c>
+      <c r="E96" s="24"/>
+      <c r="F96" s="23">
+        <v>0.35</v>
+      </c>
+      <c r="G96" s="23">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H94" s="14">
+      <c r="H96" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="I96" s="14">
+        <v>50</v>
+      </c>
+      <c r="J96" s="49"/>
+      <c r="L96" s="102"/>
+    </row>
+    <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="137" t="str">
+        <f t="shared" si="16"/>
+        <v>7332</v>
+      </c>
+      <c r="B97" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C97" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D97" s="51">
+        <v>1001301777332</v>
+      </c>
+      <c r="E97" s="24"/>
+      <c r="F97" s="23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G97" s="23">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H97" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I97" s="14">
+        <v>50</v>
+      </c>
+      <c r="J97" s="49"/>
+      <c r="L97" s="102"/>
+    </row>
+    <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="137" t="str">
+        <f t="shared" si="16"/>
+        <v>7333</v>
+      </c>
+      <c r="B98" s="53" t="s">
+        <v>69</v>
+      </c>
+      <c r="C98" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D98" s="51">
+        <v>1001303987333</v>
+      </c>
+      <c r="E98" s="24"/>
+      <c r="F98" s="23">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G98" s="23">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H98" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I98" s="14">
+        <v>50</v>
+      </c>
+      <c r="J98" s="49"/>
+      <c r="L98" s="102"/>
+    </row>
+    <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="137" t="str">
+        <f t="shared" si="16"/>
+        <v>7608</v>
+      </c>
+      <c r="B99" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="C99" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D99" s="51">
+        <v>1001304197608</v>
+      </c>
+      <c r="E99" s="24"/>
+      <c r="F99" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G99" s="23">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="H99" s="14">
         <v>1</v>
       </c>
-      <c r="I94" s="14">
+      <c r="I99" s="14">
         <v>45</v>
       </c>
-      <c r="J94" s="52" t="s">
+      <c r="J99" s="52" t="s">
         <v>206</v>
       </c>
-      <c r="L94" s="102"/>
-    </row>
-    <row r="95" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="137" t="str">
+      <c r="L99" s="102"/>
+    </row>
+    <row r="100" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="137" t="str">
         <f t="shared" si="16"/>
         <v>7610</v>
       </c>
-      <c r="B95" s="53" t="s">
+      <c r="B100" s="53" t="s">
         <v>207</v>
       </c>
-      <c r="C95" s="50" t="s">
+      <c r="C100" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D95" s="51">
+      <c r="D100" s="51">
         <v>1001306717610</v>
       </c>
-      <c r="E95" s="24"/>
-      <c r="F95" s="23">
+      <c r="E100" s="24"/>
+      <c r="F100" s="23">
         <v>0.1</v>
       </c>
-      <c r="G95" s="23">
+      <c r="G100" s="23">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H95" s="14">
+      <c r="H100" s="14">
         <v>1</v>
       </c>
-      <c r="I95" s="14">
+      <c r="I100" s="14">
         <v>45</v>
       </c>
-      <c r="J95" s="52" t="s">
+      <c r="J100" s="52" t="s">
         <v>208</v>
       </c>
-      <c r="K95" s="27"/>
-      <c r="L95" s="102"/>
-      <c r="M95" s="102"/>
-      <c r="N95" s="102"/>
-      <c r="O95" s="102"/>
-      <c r="P95" s="102"/>
-      <c r="Q95" s="102"/>
-      <c r="R95" s="102"/>
-      <c r="S95" s="102"/>
-      <c r="T95" s="102"/>
-      <c r="U95" s="102"/>
-      <c r="V95" s="102"/>
-      <c r="W95" s="102"/>
-      <c r="X95" s="102"/>
-      <c r="Y95" s="102"/>
-      <c r="Z95" s="102"/>
-      <c r="AA95" s="102"/>
-      <c r="AB95" s="102"/>
-      <c r="AC95" s="102"/>
-      <c r="AD95" s="102"/>
-      <c r="AE95" s="102"/>
-      <c r="AF95" s="102"/>
-      <c r="AG95" s="102"/>
-      <c r="AH95" s="102"/>
-      <c r="AI95" s="102"/>
-      <c r="AJ95" s="102"/>
-      <c r="AK95" s="102"/>
-      <c r="AL95" s="102"/>
-      <c r="AM95" s="102"/>
-      <c r="AN95" s="102"/>
-      <c r="AO95" s="102"/>
-      <c r="AP95" s="102"/>
-      <c r="AQ95" s="102"/>
-      <c r="AR95" s="102"/>
-      <c r="AS95" s="102"/>
-      <c r="AT95" s="102"/>
-      <c r="AU95" s="102"/>
-      <c r="AV95" s="102"/>
-      <c r="AW95" s="102"/>
-      <c r="AX95" s="102"/>
-      <c r="AY95" s="102"/>
-      <c r="AZ95" s="102"/>
-      <c r="BA95" s="102"/>
-      <c r="BB95" s="102"/>
-      <c r="BC95" s="102"/>
-      <c r="BD95" s="102"/>
-      <c r="BE95" s="102"/>
-      <c r="BF95" s="102"/>
-      <c r="BG95" s="102"/>
-      <c r="BH95" s="102"/>
-      <c r="BI95" s="102"/>
-      <c r="BJ95" s="102"/>
-      <c r="BK95" s="102"/>
-      <c r="BL95" s="102"/>
-      <c r="BM95" s="102"/>
-      <c r="BN95" s="102"/>
-      <c r="BO95" s="102"/>
-    </row>
-    <row r="96" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="47" t="s">
+      <c r="K100" s="27"/>
+      <c r="L100" s="102"/>
+      <c r="M100" s="102"/>
+      <c r="N100" s="102"/>
+      <c r="O100" s="102"/>
+      <c r="P100" s="102"/>
+      <c r="Q100" s="102"/>
+      <c r="R100" s="102"/>
+      <c r="S100" s="102"/>
+      <c r="T100" s="102"/>
+      <c r="U100" s="102"/>
+      <c r="V100" s="102"/>
+      <c r="W100" s="102"/>
+      <c r="X100" s="102"/>
+      <c r="Y100" s="102"/>
+      <c r="Z100" s="102"/>
+      <c r="AA100" s="102"/>
+      <c r="AB100" s="102"/>
+      <c r="AC100" s="102"/>
+      <c r="AD100" s="102"/>
+      <c r="AE100" s="102"/>
+      <c r="AF100" s="102"/>
+      <c r="AG100" s="102"/>
+      <c r="AH100" s="102"/>
+      <c r="AI100" s="102"/>
+      <c r="AJ100" s="102"/>
+      <c r="AK100" s="102"/>
+      <c r="AL100" s="102"/>
+      <c r="AM100" s="102"/>
+      <c r="AN100" s="102"/>
+      <c r="AO100" s="102"/>
+      <c r="AP100" s="102"/>
+      <c r="AQ100" s="102"/>
+      <c r="AR100" s="102"/>
+      <c r="AS100" s="102"/>
+      <c r="AT100" s="102"/>
+      <c r="AU100" s="102"/>
+      <c r="AV100" s="102"/>
+      <c r="AW100" s="102"/>
+      <c r="AX100" s="102"/>
+      <c r="AY100" s="102"/>
+      <c r="AZ100" s="102"/>
+      <c r="BA100" s="102"/>
+      <c r="BB100" s="102"/>
+      <c r="BC100" s="102"/>
+      <c r="BD100" s="102"/>
+      <c r="BE100" s="102"/>
+      <c r="BF100" s="102"/>
+      <c r="BG100" s="102"/>
+      <c r="BH100" s="102"/>
+      <c r="BI100" s="102"/>
+      <c r="BJ100" s="102"/>
+      <c r="BK100" s="102"/>
+      <c r="BL100" s="102"/>
+      <c r="BM100" s="102"/>
+      <c r="BN100" s="102"/>
+      <c r="BO100" s="102"/>
+    </row>
+    <row r="101" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B96" s="42" t="s">
+      <c r="B101" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="C96" s="42"/>
-      <c r="D96" s="42"/>
-      <c r="E96" s="42"/>
-      <c r="F96" s="41"/>
-      <c r="G96" s="42"/>
-      <c r="H96" s="42"/>
-      <c r="I96" s="42"/>
-      <c r="J96" s="43"/>
-      <c r="K96" s="27"/>
-      <c r="L96" s="102"/>
-      <c r="M96" s="102"/>
-      <c r="N96" s="102"/>
-      <c r="O96" s="102"/>
-      <c r="P96" s="102"/>
-      <c r="Q96" s="102"/>
-      <c r="R96" s="102"/>
-      <c r="S96" s="102"/>
-      <c r="T96" s="102"/>
-      <c r="U96" s="102"/>
-      <c r="V96" s="102"/>
-      <c r="W96" s="102"/>
-      <c r="X96" s="102"/>
-      <c r="Y96" s="102"/>
-      <c r="Z96" s="102"/>
-      <c r="AA96" s="102"/>
-      <c r="AB96" s="102"/>
-      <c r="AC96" s="102"/>
-      <c r="AD96" s="102"/>
-      <c r="AE96" s="102"/>
-      <c r="AF96" s="102"/>
-      <c r="AG96" s="102"/>
-      <c r="AH96" s="102"/>
-      <c r="AI96" s="102"/>
-      <c r="AJ96" s="102"/>
-      <c r="AK96" s="102"/>
-      <c r="AL96" s="102"/>
-      <c r="AM96" s="102"/>
-      <c r="AN96" s="102"/>
-      <c r="AO96" s="102"/>
-      <c r="AP96" s="102"/>
-      <c r="AQ96" s="102"/>
-      <c r="AR96" s="102"/>
-      <c r="AS96" s="102"/>
-      <c r="AT96" s="102"/>
-      <c r="AU96" s="102"/>
-      <c r="AV96" s="102"/>
-      <c r="AW96" s="102"/>
-      <c r="AX96" s="102"/>
-      <c r="AY96" s="102"/>
-      <c r="AZ96" s="102"/>
-      <c r="BA96" s="102"/>
-      <c r="BB96" s="102"/>
-      <c r="BC96" s="102"/>
-      <c r="BD96" s="102"/>
-      <c r="BE96" s="102"/>
-      <c r="BF96" s="102"/>
-      <c r="BG96" s="102"/>
-      <c r="BH96" s="102"/>
-      <c r="BI96" s="102"/>
-      <c r="BJ96" s="102"/>
-      <c r="BK96" s="102"/>
-      <c r="BL96" s="102"/>
-      <c r="BM96" s="102"/>
-      <c r="BN96" s="102"/>
-      <c r="BO96" s="102"/>
-    </row>
-    <row r="97" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="137" t="str">
-        <f t="shared" ref="A97:A124" si="19">RIGHT(D97,4)</f>
+      <c r="C101" s="42"/>
+      <c r="D101" s="42"/>
+      <c r="E101" s="42"/>
+      <c r="F101" s="41"/>
+      <c r="G101" s="42"/>
+      <c r="H101" s="42"/>
+      <c r="I101" s="42"/>
+      <c r="J101" s="43"/>
+      <c r="K101" s="27"/>
+      <c r="L101" s="102"/>
+      <c r="M101" s="102"/>
+      <c r="N101" s="102"/>
+      <c r="O101" s="102"/>
+      <c r="P101" s="102"/>
+      <c r="Q101" s="102"/>
+      <c r="R101" s="102"/>
+      <c r="S101" s="102"/>
+      <c r="T101" s="102"/>
+      <c r="U101" s="102"/>
+      <c r="V101" s="102"/>
+      <c r="W101" s="102"/>
+      <c r="X101" s="102"/>
+      <c r="Y101" s="102"/>
+      <c r="Z101" s="102"/>
+      <c r="AA101" s="102"/>
+      <c r="AB101" s="102"/>
+      <c r="AC101" s="102"/>
+      <c r="AD101" s="102"/>
+      <c r="AE101" s="102"/>
+      <c r="AF101" s="102"/>
+      <c r="AG101" s="102"/>
+      <c r="AH101" s="102"/>
+      <c r="AI101" s="102"/>
+      <c r="AJ101" s="102"/>
+      <c r="AK101" s="102"/>
+      <c r="AL101" s="102"/>
+      <c r="AM101" s="102"/>
+      <c r="AN101" s="102"/>
+      <c r="AO101" s="102"/>
+      <c r="AP101" s="102"/>
+      <c r="AQ101" s="102"/>
+      <c r="AR101" s="102"/>
+      <c r="AS101" s="102"/>
+      <c r="AT101" s="102"/>
+      <c r="AU101" s="102"/>
+      <c r="AV101" s="102"/>
+      <c r="AW101" s="102"/>
+      <c r="AX101" s="102"/>
+      <c r="AY101" s="102"/>
+      <c r="AZ101" s="102"/>
+      <c r="BA101" s="102"/>
+      <c r="BB101" s="102"/>
+      <c r="BC101" s="102"/>
+      <c r="BD101" s="102"/>
+      <c r="BE101" s="102"/>
+      <c r="BF101" s="102"/>
+      <c r="BG101" s="102"/>
+      <c r="BH101" s="102"/>
+      <c r="BI101" s="102"/>
+      <c r="BJ101" s="102"/>
+      <c r="BK101" s="102"/>
+      <c r="BL101" s="102"/>
+      <c r="BM101" s="102"/>
+      <c r="BN101" s="102"/>
+      <c r="BO101" s="102"/>
+    </row>
+    <row r="102" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="137" t="str">
+        <f t="shared" ref="A102:A129" si="21">RIGHT(D102,4)</f>
         <v>3986</v>
       </c>
-      <c r="B97" s="53" t="s">
+      <c r="B102" s="53" t="s">
         <v>79</v>
-      </c>
-      <c r="C97" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D97" s="51">
-        <v>1001061973986</v>
-      </c>
-      <c r="E97" s="24"/>
-      <c r="F97" s="128">
-        <v>0.25</v>
-      </c>
-      <c r="G97" s="23">
-        <f t="shared" ref="G97:G102" si="20">E97*F97</f>
-        <v>0</v>
-      </c>
-      <c r="H97" s="132">
-        <v>2</v>
-      </c>
-      <c r="I97" s="133">
-        <v>120</v>
-      </c>
-      <c r="J97" s="29"/>
-      <c r="L97" s="102"/>
-    </row>
-    <row r="98" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>5931</v>
-      </c>
-      <c r="B98" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="C98" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D98" s="51">
-        <v>1001060755931</v>
-      </c>
-      <c r="E98" s="24"/>
-      <c r="F98" s="23">
-        <v>0.22</v>
-      </c>
-      <c r="G98" s="23">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="H98" s="97">
-        <v>1.76</v>
-      </c>
-      <c r="I98" s="14">
-        <v>120</v>
-      </c>
-      <c r="J98" s="29"/>
-      <c r="L98" s="102"/>
-    </row>
-    <row r="99" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>5708</v>
-      </c>
-      <c r="B99" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="C99" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D99" s="51">
-        <v>1001063145708</v>
-      </c>
-      <c r="E99" s="24"/>
-      <c r="F99" s="23">
-        <v>0.5</v>
-      </c>
-      <c r="G99" s="23">
-        <f t="shared" ref="G99:G100" si="21">E99</f>
-        <v>0</v>
-      </c>
-      <c r="H99" s="14">
-        <v>4</v>
-      </c>
-      <c r="I99" s="14">
-        <v>120</v>
-      </c>
-      <c r="J99" s="29"/>
-      <c r="L99" s="102"/>
-    </row>
-    <row r="100" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>3287</v>
-      </c>
-      <c r="B100" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="C100" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D100" s="51">
-        <v>1001060763287</v>
-      </c>
-      <c r="E100" s="24"/>
-      <c r="F100" s="23">
-        <v>0.48799999999999999</v>
-      </c>
-      <c r="G100" s="23">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="H100" s="14">
-        <v>3.9</v>
-      </c>
-      <c r="I100" s="14">
-        <v>120</v>
-      </c>
-      <c r="J100" s="29"/>
-      <c r="L100" s="102"/>
-    </row>
-    <row r="101" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>4993</v>
-      </c>
-      <c r="B101" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="C101" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D101" s="51">
-        <v>1001060764993</v>
-      </c>
-      <c r="E101" s="24"/>
-      <c r="F101" s="23">
-        <v>0.25</v>
-      </c>
-      <c r="G101" s="23">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="H101" s="14">
-        <v>2</v>
-      </c>
-      <c r="I101" s="14">
-        <v>120</v>
-      </c>
-      <c r="J101" s="29"/>
-      <c r="L101" s="102"/>
-    </row>
-    <row r="102" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>5483</v>
-      </c>
-      <c r="B102" s="53" t="s">
-        <v>88</v>
       </c>
       <c r="C102" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D102" s="51">
-        <v>1001062505483</v>
+        <v>1001061973986</v>
       </c>
       <c r="E102" s="24"/>
-      <c r="F102" s="23">
+      <c r="F102" s="128">
         <v>0.25</v>
       </c>
       <c r="G102" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G102:G107" si="22">E102*F102</f>
         <v>0</v>
       </c>
-      <c r="H102" s="14">
+      <c r="H102" s="132">
         <v>2</v>
       </c>
-      <c r="I102" s="14">
+      <c r="I102" s="133">
         <v>120</v>
       </c>
       <c r="J102" s="29"/>
       <c r="L102" s="102"/>
     </row>
-    <row r="103" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>4117</v>
+        <f t="shared" si="21"/>
+        <v>5931</v>
       </c>
       <c r="B103" s="53" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="C103" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D103" s="51">
-        <v>1001062504117</v>
+        <v>1001060755931</v>
       </c>
       <c r="E103" s="24"/>
       <c r="F103" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.22</v>
       </c>
       <c r="G103" s="23">
-        <f t="shared" ref="G103:G104" si="22">E103</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H103" s="14">
-        <v>3.95</v>
+      <c r="H103" s="97">
+        <v>1.76</v>
       </c>
       <c r="I103" s="14">
         <v>120</v>
@@ -11233,30 +11342,30 @@
       <c r="J103" s="29"/>
       <c r="L103" s="102"/>
     </row>
-    <row r="104" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>0614</v>
+        <f t="shared" si="21"/>
+        <v>5708</v>
       </c>
       <c r="B104" s="53" t="s">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="C104" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D104" s="51">
-        <v>1001060720614</v>
+        <v>1001063145708</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="G104" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G104:G105" si="23">E104</f>
         <v>0</v>
       </c>
       <c r="H104" s="14">
-        <v>3.64</v>
+        <v>4</v>
       </c>
       <c r="I104" s="14">
         <v>120</v>
@@ -11264,30 +11373,30 @@
       <c r="J104" s="29"/>
       <c r="L104" s="102"/>
     </row>
-    <row r="105" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>6967</v>
+        <f t="shared" si="21"/>
+        <v>3287</v>
       </c>
       <c r="B105" s="53" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D105" s="51">
-        <v>1001063656967</v>
+        <v>1001060763287</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G105" s="23">
-        <f t="shared" ref="G105:G114" si="23">E105*F105</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H105" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I105" s="14">
         <v>120</v>
@@ -11295,26 +11404,26 @@
       <c r="J105" s="29"/>
       <c r="L105" s="102"/>
     </row>
-    <row r="106" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>6937</v>
+        <f t="shared" si="21"/>
+        <v>4993</v>
       </c>
       <c r="B106" s="53" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C106" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D106" s="51">
-        <v>1001063106937</v>
+        <v>1001060764993</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="23">
         <v>0.25</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H106" s="14">
@@ -11326,30 +11435,30 @@
       <c r="J106" s="29"/>
       <c r="L106" s="102"/>
     </row>
-    <row r="107" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7143</v>
+        <f t="shared" si="21"/>
+        <v>5483</v>
       </c>
       <c r="B107" s="53" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="C107" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D107" s="51">
-        <v>1001060717143</v>
+        <v>1001062505483</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H107" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I107" s="14">
         <v>120</v>
@@ -11357,30 +11466,30 @@
       <c r="J107" s="29"/>
       <c r="L107" s="102"/>
     </row>
-    <row r="108" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7147</v>
+        <f t="shared" si="21"/>
+        <v>4117</v>
       </c>
       <c r="B108" s="53" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D108" s="51">
-        <v>1001063237147</v>
+        <v>1001062504117</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
-        <v>0.22</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G108" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G108:G109" si="24">E108</f>
         <v>0</v>
       </c>
       <c r="H108" s="14">
-        <v>1.76</v>
+        <v>3.95</v>
       </c>
       <c r="I108" s="14">
         <v>120</v>
@@ -11388,123 +11497,123 @@
       <c r="J108" s="29"/>
       <c r="L108" s="102"/>
     </row>
-    <row r="109" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7456</v>
+        <f t="shared" si="21"/>
+        <v>0614</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C109" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D109" s="51">
-        <v>1001063097456</v>
+        <v>1001060720614</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.15</v>
+        <v>0.52</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>1.8</v>
+        <v>3.64</v>
       </c>
       <c r="I109" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J109" s="29"/>
       <c r="L109" s="102"/>
     </row>
-    <row r="110" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7364</v>
+        <f t="shared" si="21"/>
+        <v>6967</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
       <c r="C110" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D110" s="51">
-        <v>1001063217364</v>
+        <v>1001063656967</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G110:G119" si="25">E110*F110</f>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I110" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J110" s="29"/>
       <c r="L110" s="102"/>
     </row>
-    <row r="111" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7383</v>
+        <f t="shared" si="21"/>
+        <v>6937</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C111" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="51">
-        <v>1001065467383</v>
+        <v>1001063106937</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I111" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J111" s="29"/>
       <c r="L111" s="102"/>
     </row>
-    <row r="112" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7317</v>
+        <f t="shared" si="21"/>
+        <v>7143</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C112" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="51">
-        <v>1001066567317</v>
+        <v>1001060717143</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H112" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I112" s="14">
         <v>120</v>
@@ -11512,30 +11621,30 @@
       <c r="J112" s="29"/>
       <c r="L112" s="102"/>
     </row>
-    <row r="113" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7318</v>
+        <f t="shared" si="21"/>
+        <v>7147</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="C113" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="51">
-        <v>1001060727318</v>
+        <v>1001063237147</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>2.16</v>
+        <v>1.76</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -11543,803 +11652,523 @@
       <c r="J113" s="29"/>
       <c r="L113" s="102"/>
     </row>
-    <row r="114" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7316</v>
+        <f t="shared" si="21"/>
+        <v>7456</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D114" s="51">
-        <v>1001060727316</v>
+        <v>1001063097456</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.54</v>
+        <v>0.15</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>3.78</v>
+        <v>1.8</v>
       </c>
       <c r="I114" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J114" s="29"/>
       <c r="L114" s="102"/>
     </row>
-    <row r="115" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>6832</v>
+        <f t="shared" si="21"/>
+        <v>7364</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="C115" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D115" s="51">
-        <v>1001065616832</v>
+        <v>1001063217364</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.215</v>
+        <v>0.22</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" ref="G115:G116" si="24">E115</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="I115" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J115" s="29"/>
       <c r="L115" s="102"/>
     </row>
-    <row r="116" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7299</v>
+        <f t="shared" si="21"/>
+        <v>7383</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>82</v>
+        <v>145</v>
       </c>
       <c r="C116" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D116" s="51">
-        <v>1001060677299</v>
+        <v>1001065467383</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.215</v>
+        <v>0.22</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="I116" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="J116" s="29"/>
       <c r="L116" s="102"/>
     </row>
-    <row r="117" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7386</v>
+        <f t="shared" si="21"/>
+        <v>7317</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D117" s="51">
-        <v>1001067017386</v>
+        <v>1001066567317</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
-        <v>0.15</v>
+        <v>0.54</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" ref="G117:G124" si="25">E117*F117</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
-        <v>1.35</v>
+        <v>3.78</v>
       </c>
       <c r="I117" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J117" s="29"/>
       <c r="L117" s="102"/>
     </row>
-    <row r="118" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7613</v>
+        <f t="shared" si="21"/>
+        <v>7318</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D118" s="51">
-        <v>1001061977613</v>
+        <v>1001060727318</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.1</v>
+        <v>0.27</v>
       </c>
       <c r="G118" s="23">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>1</v>
+        <v>2.16</v>
       </c>
       <c r="I118" s="14">
-        <v>60</v>
-      </c>
-      <c r="J118" s="52" t="s">
-        <v>203</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="J118" s="29"/>
       <c r="L118" s="102"/>
     </row>
-    <row r="119" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7382</v>
+        <f t="shared" si="21"/>
+        <v>7316</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="51">
-        <v>1001203117382</v>
+        <v>1001060727316</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="G119" s="23">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>0.96</v>
+        <v>3.78</v>
       </c>
       <c r="I119" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="J119" s="29"/>
       <c r="L119" s="102"/>
     </row>
-    <row r="120" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7616</v>
+        <f t="shared" si="21"/>
+        <v>6832</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="C120" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D120" s="51">
-        <v>1001062507616</v>
+        <v>1001065616832</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.1</v>
+        <v>0.215</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G120:G121" si="26">E120</f>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="I120" s="14">
-        <v>60</v>
-      </c>
-      <c r="J120" s="52" t="s">
-        <v>205</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J120" s="29"/>
       <c r="L120" s="102"/>
     </row>
-    <row r="121" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>6221</v>
+        <f t="shared" si="21"/>
+        <v>7299</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C121" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D121" s="51">
-        <v>1001205376221</v>
+        <v>1001060677299</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
-        <v>0.09</v>
+        <v>0.215</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
-        <v>0.9</v>
+        <v>2.15</v>
       </c>
       <c r="I121" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J121" s="29"/>
       <c r="L121" s="102"/>
     </row>
-    <row r="122" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>6222</v>
+        <f t="shared" si="21"/>
+        <v>7386</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D122" s="51">
-        <v>1001205386222</v>
+        <v>1001067017386</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G122:G129" si="27">E122*F122</f>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <v>0.9</v>
+        <v>1.35</v>
       </c>
       <c r="I122" s="14">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J122" s="29"/>
       <c r="L122" s="102"/>
     </row>
-    <row r="123" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>5679</v>
+        <f t="shared" si="21"/>
+        <v>7613</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>136</v>
+        <v>213</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D123" s="51">
-        <v>1001190765679</v>
+        <v>1001061977613</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I123" s="14">
         <v>60</v>
       </c>
-      <c r="J123" s="29"/>
+      <c r="J123" s="52" t="s">
+        <v>203</v>
+      </c>
       <c r="L123" s="102"/>
     </row>
-    <row r="124" spans="1:67" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="137" t="str">
-        <f t="shared" si="19"/>
-        <v>7626</v>
+        <f t="shared" si="21"/>
+        <v>7382</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>201</v>
+        <v>84</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D124" s="51">
-        <v>1001066607626</v>
+        <v>1001203117382</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="I124" s="14">
         <v>60</v>
       </c>
-      <c r="J124" s="52" t="s">
-        <v>202</v>
-      </c>
+      <c r="J124" s="29"/>
       <c r="L124" s="102"/>
     </row>
-    <row r="125" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B125" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C125" s="42"/>
-      <c r="D125" s="42"/>
-      <c r="E125" s="42"/>
-      <c r="F125" s="41"/>
-      <c r="G125" s="42"/>
-      <c r="H125" s="42"/>
-      <c r="I125" s="42"/>
-      <c r="J125" s="43"/>
-      <c r="K125" s="27"/>
+    <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="137" t="str">
+        <f t="shared" si="21"/>
+        <v>7616</v>
+      </c>
+      <c r="B125" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="C125" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D125" s="51">
+        <v>1001062507616</v>
+      </c>
+      <c r="E125" s="24"/>
+      <c r="F125" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G125" s="23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="H125" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="I125" s="14">
+        <v>60</v>
+      </c>
+      <c r="J125" s="52" t="s">
+        <v>205</v>
+      </c>
       <c r="L125" s="102"/>
-      <c r="M125" s="102"/>
-      <c r="N125" s="102"/>
-      <c r="O125" s="102"/>
-      <c r="P125" s="102"/>
-      <c r="Q125" s="102"/>
-      <c r="R125" s="102"/>
-      <c r="S125" s="102"/>
-      <c r="T125" s="102"/>
-      <c r="U125" s="102"/>
-      <c r="V125" s="102"/>
-      <c r="W125" s="102"/>
-      <c r="X125" s="102"/>
-      <c r="Y125" s="102"/>
-      <c r="Z125" s="102"/>
-      <c r="AA125" s="102"/>
-      <c r="AB125" s="102"/>
-      <c r="AC125" s="102"/>
-      <c r="AD125" s="102"/>
-      <c r="AE125" s="102"/>
-      <c r="AF125" s="102"/>
-      <c r="AG125" s="102"/>
-      <c r="AH125" s="102"/>
-      <c r="AI125" s="102"/>
-      <c r="AJ125" s="102"/>
-      <c r="AK125" s="102"/>
-      <c r="AL125" s="102"/>
-      <c r="AM125" s="102"/>
-      <c r="AN125" s="102"/>
-      <c r="AO125" s="102"/>
-      <c r="AP125" s="102"/>
-      <c r="AQ125" s="102"/>
-      <c r="AR125" s="102"/>
-      <c r="AS125" s="102"/>
-      <c r="AT125" s="102"/>
-      <c r="AU125" s="102"/>
-      <c r="AV125" s="102"/>
-      <c r="AW125" s="102"/>
-      <c r="AX125" s="102"/>
-      <c r="AY125" s="102"/>
-      <c r="AZ125" s="102"/>
-      <c r="BA125" s="102"/>
-      <c r="BB125" s="102"/>
-      <c r="BC125" s="102"/>
-      <c r="BD125" s="102"/>
-      <c r="BE125" s="102"/>
-      <c r="BF125" s="102"/>
-      <c r="BG125" s="102"/>
-      <c r="BH125" s="102"/>
-      <c r="BI125" s="102"/>
-      <c r="BJ125" s="102"/>
-      <c r="BK125" s="102"/>
-      <c r="BL125" s="102"/>
-      <c r="BM125" s="102"/>
-      <c r="BN125" s="102"/>
-      <c r="BO125" s="102"/>
-    </row>
-    <row r="126" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="137" t="str">
-        <f t="shared" ref="A126:A139" si="26">RIGHT(D126,4)</f>
-        <v>4584</v>
-      </c>
-      <c r="B126" s="98" t="s">
-        <v>220</v>
+        <f t="shared" si="21"/>
+        <v>6221</v>
+      </c>
+      <c r="B126" s="53" t="s">
+        <v>86</v>
       </c>
       <c r="C126" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D126" s="134">
-        <v>1001092674584</v>
+        <v>20</v>
+      </c>
+      <c r="D126" s="51">
+        <v>1001205376221</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>2.5</v>
+        <v>0.09</v>
       </c>
       <c r="G126" s="23">
-        <f>E126</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>7.5</v>
+        <v>0.9</v>
       </c>
       <c r="I126" s="14">
         <v>60</v>
       </c>
       <c r="J126" s="29"/>
-      <c r="K126" s="27"/>
       <c r="L126" s="102"/>
-      <c r="M126" s="102"/>
-      <c r="N126" s="102"/>
-      <c r="O126" s="102"/>
-      <c r="P126" s="102"/>
-      <c r="Q126" s="102"/>
-      <c r="R126" s="102"/>
-      <c r="S126" s="102"/>
-      <c r="T126" s="102"/>
-      <c r="U126" s="102"/>
-      <c r="V126" s="102"/>
-      <c r="W126" s="102"/>
-      <c r="X126" s="102"/>
-      <c r="Y126" s="102"/>
-      <c r="Z126" s="102"/>
-      <c r="AA126" s="102"/>
-      <c r="AB126" s="102"/>
-      <c r="AC126" s="102"/>
-      <c r="AD126" s="102"/>
-      <c r="AE126" s="102"/>
-      <c r="AF126" s="102"/>
-      <c r="AG126" s="102"/>
-      <c r="AH126" s="102"/>
-      <c r="AI126" s="102"/>
-      <c r="AJ126" s="102"/>
-      <c r="AK126" s="102"/>
-      <c r="AL126" s="102"/>
-      <c r="AM126" s="102"/>
-      <c r="AN126" s="102"/>
-      <c r="AO126" s="102"/>
-      <c r="AP126" s="102"/>
-      <c r="AQ126" s="102"/>
-      <c r="AR126" s="102"/>
-      <c r="AS126" s="102"/>
-      <c r="AT126" s="102"/>
-      <c r="AU126" s="102"/>
-      <c r="AV126" s="102"/>
-      <c r="AW126" s="102"/>
-      <c r="AX126" s="102"/>
-      <c r="AY126" s="102"/>
-      <c r="AZ126" s="102"/>
-      <c r="BA126" s="102"/>
-      <c r="BB126" s="102"/>
-      <c r="BC126" s="102"/>
-      <c r="BD126" s="102"/>
-      <c r="BE126" s="102"/>
-      <c r="BF126" s="102"/>
-      <c r="BG126" s="102"/>
-      <c r="BH126" s="102"/>
-      <c r="BI126" s="102"/>
-      <c r="BJ126" s="102"/>
-      <c r="BK126" s="102"/>
-      <c r="BL126" s="102"/>
-      <c r="BM126" s="102"/>
-      <c r="BN126" s="102"/>
-      <c r="BO126" s="102"/>
-    </row>
-    <row r="127" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>6495</v>
-      </c>
-      <c r="B127" s="98" t="s">
-        <v>95</v>
+        <f t="shared" si="21"/>
+        <v>6222</v>
+      </c>
+      <c r="B127" s="53" t="s">
+        <v>133</v>
       </c>
       <c r="C127" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D127" s="51">
-        <v>1001092436495</v>
+        <v>1001205386222</v>
       </c>
       <c r="E127" s="24"/>
-      <c r="F127" s="128">
-        <v>0.3</v>
+      <c r="F127" s="23">
+        <v>0.09</v>
       </c>
       <c r="G127" s="23">
-        <f>E127*F127</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H127" s="29">
-        <v>1.8</v>
-      </c>
-      <c r="I127" s="29">
-        <v>45</v>
+      <c r="H127" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="I127" s="14">
+        <v>60</v>
       </c>
       <c r="J127" s="29"/>
-      <c r="K127" s="27"/>
       <c r="L127" s="102"/>
-      <c r="M127" s="102"/>
-      <c r="N127" s="102"/>
-      <c r="O127" s="102"/>
-      <c r="P127" s="102"/>
-      <c r="Q127" s="102"/>
-      <c r="R127" s="102"/>
-      <c r="S127" s="102"/>
-      <c r="T127" s="102"/>
-      <c r="U127" s="102"/>
-      <c r="V127" s="102"/>
-      <c r="W127" s="102"/>
-      <c r="X127" s="102"/>
-      <c r="Y127" s="102"/>
-      <c r="Z127" s="102"/>
-      <c r="AA127" s="102"/>
-      <c r="AB127" s="102"/>
-      <c r="AC127" s="102"/>
-      <c r="AD127" s="102"/>
-      <c r="AE127" s="102"/>
-      <c r="AF127" s="102"/>
-      <c r="AG127" s="102"/>
-      <c r="AH127" s="102"/>
-      <c r="AI127" s="102"/>
-      <c r="AJ127" s="102"/>
-      <c r="AK127" s="102"/>
-      <c r="AL127" s="102"/>
-      <c r="AM127" s="102"/>
-      <c r="AN127" s="102"/>
-      <c r="AO127" s="102"/>
-      <c r="AP127" s="102"/>
-      <c r="AQ127" s="102"/>
-      <c r="AR127" s="102"/>
-      <c r="AS127" s="102"/>
-      <c r="AT127" s="102"/>
-      <c r="AU127" s="102"/>
-      <c r="AV127" s="102"/>
-      <c r="AW127" s="102"/>
-      <c r="AX127" s="102"/>
-      <c r="AY127" s="102"/>
-      <c r="AZ127" s="102"/>
-      <c r="BA127" s="102"/>
-      <c r="BB127" s="102"/>
-      <c r="BC127" s="102"/>
-      <c r="BD127" s="102"/>
-      <c r="BE127" s="102"/>
-      <c r="BF127" s="102"/>
-      <c r="BG127" s="102"/>
-      <c r="BH127" s="102"/>
-      <c r="BI127" s="102"/>
-      <c r="BJ127" s="102"/>
-      <c r="BK127" s="102"/>
-      <c r="BL127" s="102"/>
-      <c r="BM127" s="102"/>
-      <c r="BN127" s="102"/>
-      <c r="BO127" s="102"/>
-    </row>
-    <row r="128" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>6470</v>
-      </c>
-      <c r="B128" s="135" t="s">
-        <v>116</v>
+        <f t="shared" si="21"/>
+        <v>5679</v>
+      </c>
+      <c r="B128" s="53" t="s">
+        <v>136</v>
       </c>
       <c r="C128" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D128" s="51">
-        <v>1001092436470</v>
+        <v>1001190765679</v>
       </c>
       <c r="E128" s="24"/>
-      <c r="F128" s="128">
+      <c r="F128" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G128" s="23">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="H128" s="14">
         <v>1.2</v>
       </c>
-      <c r="G128" s="23">
-        <f t="shared" ref="G128:G129" si="27">E128</f>
-        <v>0</v>
-      </c>
-      <c r="H128" s="29">
-        <v>4.8</v>
-      </c>
-      <c r="I128" s="29">
-        <v>45</v>
+      <c r="I128" s="14">
+        <v>60</v>
       </c>
       <c r="J128" s="29"/>
-      <c r="K128" s="27"/>
       <c r="L128" s="102"/>
-      <c r="M128" s="102"/>
-      <c r="N128" s="102"/>
-      <c r="O128" s="102"/>
-      <c r="P128" s="102"/>
-      <c r="Q128" s="102"/>
-      <c r="R128" s="102"/>
-      <c r="S128" s="102"/>
-      <c r="T128" s="102"/>
-      <c r="U128" s="102"/>
-      <c r="V128" s="102"/>
-      <c r="W128" s="102"/>
-      <c r="X128" s="102"/>
-      <c r="Y128" s="102"/>
-      <c r="Z128" s="102"/>
-      <c r="AA128" s="102"/>
-      <c r="AB128" s="102"/>
-      <c r="AC128" s="102"/>
-      <c r="AD128" s="102"/>
-      <c r="AE128" s="102"/>
-      <c r="AF128" s="102"/>
-      <c r="AG128" s="102"/>
-      <c r="AH128" s="102"/>
-      <c r="AI128" s="102"/>
-      <c r="AJ128" s="102"/>
-      <c r="AK128" s="102"/>
-      <c r="AL128" s="102"/>
-      <c r="AM128" s="102"/>
-      <c r="AN128" s="102"/>
-      <c r="AO128" s="102"/>
-      <c r="AP128" s="102"/>
-      <c r="AQ128" s="102"/>
-      <c r="AR128" s="102"/>
-      <c r="AS128" s="102"/>
-      <c r="AT128" s="102"/>
-      <c r="AU128" s="102"/>
-      <c r="AV128" s="102"/>
-      <c r="AW128" s="102"/>
-      <c r="AX128" s="102"/>
-      <c r="AY128" s="102"/>
-      <c r="AZ128" s="102"/>
-      <c r="BA128" s="102"/>
-      <c r="BB128" s="102"/>
-      <c r="BC128" s="102"/>
-      <c r="BD128" s="102"/>
-      <c r="BE128" s="102"/>
-      <c r="BF128" s="102"/>
-      <c r="BG128" s="102"/>
-      <c r="BH128" s="102"/>
-      <c r="BI128" s="102"/>
-      <c r="BJ128" s="102"/>
-      <c r="BK128" s="102"/>
-      <c r="BL128" s="102"/>
-      <c r="BM128" s="102"/>
-      <c r="BN128" s="102"/>
-      <c r="BO128" s="102"/>
-    </row>
-    <row r="129" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:67" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>5452</v>
-      </c>
-      <c r="B129" s="135" t="s">
-        <v>93</v>
+        <f t="shared" si="21"/>
+        <v>7626</v>
+      </c>
+      <c r="B129" s="53" t="s">
+        <v>201</v>
       </c>
       <c r="C129" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D129" s="51">
-        <v>1001092485452</v>
+        <v>1001066607626</v>
       </c>
       <c r="E129" s="24"/>
-      <c r="F129" s="128">
-        <v>1.35</v>
+      <c r="F129" s="23">
+        <v>0.1</v>
       </c>
       <c r="G129" s="23">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H129" s="29">
-        <v>4.05</v>
-      </c>
-      <c r="I129" s="29">
+      <c r="H129" s="14">
+        <v>1</v>
+      </c>
+      <c r="I129" s="14">
         <v>60</v>
       </c>
-      <c r="J129" s="29"/>
-      <c r="K129" s="27"/>
+      <c r="J129" s="52" t="s">
+        <v>202</v>
+      </c>
       <c r="L129" s="102"/>
-      <c r="M129" s="102"/>
-      <c r="N129" s="102"/>
-      <c r="O129" s="102"/>
-      <c r="P129" s="102"/>
-      <c r="Q129" s="102"/>
-      <c r="R129" s="102"/>
-      <c r="S129" s="102"/>
-      <c r="T129" s="102"/>
-      <c r="U129" s="102"/>
-      <c r="V129" s="102"/>
-      <c r="W129" s="102"/>
-      <c r="X129" s="102"/>
-      <c r="Y129" s="102"/>
-      <c r="Z129" s="102"/>
-      <c r="AA129" s="102"/>
-      <c r="AB129" s="102"/>
-      <c r="AC129" s="102"/>
-      <c r="AD129" s="102"/>
-      <c r="AE129" s="102"/>
-      <c r="AF129" s="102"/>
-      <c r="AG129" s="102"/>
-      <c r="AH129" s="102"/>
-      <c r="AI129" s="102"/>
-      <c r="AJ129" s="102"/>
-      <c r="AK129" s="102"/>
-      <c r="AL129" s="102"/>
-      <c r="AM129" s="102"/>
-      <c r="AN129" s="102"/>
-      <c r="AO129" s="102"/>
-      <c r="AP129" s="102"/>
-      <c r="AQ129" s="102"/>
-      <c r="AR129" s="102"/>
-      <c r="AS129" s="102"/>
-      <c r="AT129" s="102"/>
-      <c r="AU129" s="102"/>
-      <c r="AV129" s="102"/>
-      <c r="AW129" s="102"/>
-      <c r="AX129" s="102"/>
-      <c r="AY129" s="102"/>
-      <c r="AZ129" s="102"/>
-      <c r="BA129" s="102"/>
-      <c r="BB129" s="102"/>
-      <c r="BC129" s="102"/>
-      <c r="BD129" s="102"/>
-      <c r="BE129" s="102"/>
-      <c r="BF129" s="102"/>
-      <c r="BG129" s="102"/>
-      <c r="BH129" s="102"/>
-      <c r="BI129" s="102"/>
-      <c r="BJ129" s="102"/>
-      <c r="BK129" s="102"/>
-      <c r="BL129" s="102"/>
-      <c r="BM129" s="102"/>
-      <c r="BN129" s="102"/>
-      <c r="BO129" s="102"/>
-    </row>
-    <row r="130" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>3215</v>
-      </c>
-      <c r="B130" s="135" t="s">
-        <v>215</v>
-      </c>
-      <c r="C130" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D130" s="51">
-        <v>1001094053215</v>
-      </c>
-      <c r="E130" s="24"/>
-      <c r="F130" s="128">
-        <v>0.4</v>
-      </c>
-      <c r="G130" s="23">
-        <f>E130*F130</f>
-        <v>0</v>
-      </c>
-      <c r="H130" s="29">
-        <v>3.2</v>
-      </c>
-      <c r="I130" s="29">
-        <v>60</v>
-      </c>
-      <c r="J130" s="29"/>
+    </row>
+    <row r="130" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B130" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C130" s="42"/>
+      <c r="D130" s="42"/>
+      <c r="E130" s="42"/>
+      <c r="F130" s="41"/>
+      <c r="G130" s="42"/>
+      <c r="H130" s="42"/>
+      <c r="I130" s="42"/>
+      <c r="J130" s="43"/>
       <c r="K130" s="27"/>
       <c r="L130" s="102"/>
       <c r="M130" s="102"/>
@@ -12398,32 +12227,32 @@
       <c r="BN130" s="102"/>
       <c r="BO130" s="102"/>
     </row>
-    <row r="131" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A131" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>6866</v>
-      </c>
-      <c r="B131" s="135" t="s">
-        <v>92</v>
+        <f t="shared" ref="A131:A145" si="28">RIGHT(D131,4)</f>
+        <v>4584</v>
+      </c>
+      <c r="B131" s="98" t="s">
+        <v>220</v>
       </c>
       <c r="C131" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D131" s="51">
-        <v>1001095716866</v>
+      <c r="D131" s="134">
+        <v>1001092674584</v>
       </c>
       <c r="E131" s="24"/>
-      <c r="F131" s="128">
-        <v>1.5</v>
+      <c r="F131" s="23">
+        <v>2.5</v>
       </c>
       <c r="G131" s="23">
         <f>E131</f>
         <v>0</v>
       </c>
-      <c r="H131" s="29">
-        <v>6</v>
-      </c>
-      <c r="I131" s="29">
+      <c r="H131" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I131" s="14">
         <v>60</v>
       </c>
       <c r="J131" s="29"/>
@@ -12485,33 +12314,33 @@
       <c r="BN131" s="102"/>
       <c r="BO131" s="102"/>
     </row>
-    <row r="132" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>5495</v>
-      </c>
-      <c r="B132" s="53" t="s">
-        <v>94</v>
+        <f t="shared" si="28"/>
+        <v>6495</v>
+      </c>
+      <c r="B132" s="98" t="s">
+        <v>95</v>
       </c>
       <c r="C132" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D132" s="136">
-        <v>1001093345495</v>
+      <c r="D132" s="51">
+        <v>1001092436495</v>
       </c>
       <c r="E132" s="24"/>
       <c r="F132" s="128">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="G132" s="23">
-        <f t="shared" ref="G132:G135" si="28">E132*F132</f>
+        <f>E132*F132</f>
         <v>0</v>
       </c>
       <c r="H132" s="29">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="I132" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J132" s="29"/>
       <c r="K132" s="27"/>
@@ -12572,30 +12401,30 @@
       <c r="BN132" s="102"/>
       <c r="BO132" s="102"/>
     </row>
-    <row r="133" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>7377</v>
-      </c>
-      <c r="B133" s="53" t="s">
-        <v>117</v>
+        <f t="shared" si="28"/>
+        <v>6470</v>
+      </c>
+      <c r="B133" s="135" t="s">
+        <v>116</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D133" s="136">
-        <v>1001095027377</v>
+        <v>22</v>
+      </c>
+      <c r="D133" s="51">
+        <v>1001092436470</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="128">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G133:G134" si="29">E133</f>
         <v>0</v>
       </c>
       <c r="H133" s="29">
-        <v>1.8</v>
+        <v>4.8</v>
       </c>
       <c r="I133" s="29">
         <v>45</v>
@@ -12659,30 +12488,34 @@
       <c r="BN133" s="102"/>
       <c r="BO133" s="102"/>
     </row>
-    <row r="134" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>6411</v>
-      </c>
-      <c r="B134" s="53" t="s">
-        <v>224</v>
+        <f t="shared" si="28"/>
+        <v>5452</v>
+      </c>
+      <c r="B134" s="135" t="s">
+        <v>93</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D134" s="136">
-        <v>1001093316411</v>
+        <v>22</v>
+      </c>
+      <c r="D134" s="51">
+        <v>1001092485452</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="128">
-        <v>0.3</v>
+        <v>1.35</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" ref="G134" si="29">E134*F134</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H134" s="29"/>
-      <c r="I134" s="29"/>
+      <c r="H134" s="29">
+        <v>4.05</v>
+      </c>
+      <c r="I134" s="29">
+        <v>60</v>
+      </c>
       <c r="J134" s="29"/>
       <c r="K134" s="27"/>
       <c r="L134" s="102"/>
@@ -12742,33 +12575,33 @@
       <c r="BN134" s="102"/>
       <c r="BO134" s="102"/>
     </row>
-    <row r="135" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>6925</v>
-      </c>
-      <c r="B135" s="53" t="s">
-        <v>103</v>
+        <f t="shared" si="28"/>
+        <v>3215</v>
+      </c>
+      <c r="B135" s="135" t="s">
+        <v>215</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D135" s="136">
-        <v>1001095226925</v>
+      <c r="D135" s="51">
+        <v>1001094053215</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="128">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G135" s="23">
-        <f t="shared" si="28"/>
+        <f>E135*F135</f>
         <v>0</v>
       </c>
       <c r="H135" s="29">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="I135" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J135" s="29"/>
       <c r="K135" s="27"/>
@@ -12829,23 +12662,23 @@
       <c r="BN135" s="102"/>
       <c r="BO135" s="102"/>
     </row>
-    <row r="136" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>6025</v>
-      </c>
-      <c r="B136" s="53" t="s">
-        <v>118</v>
+        <f t="shared" si="28"/>
+        <v>6866</v>
+      </c>
+      <c r="B136" s="135" t="s">
+        <v>92</v>
       </c>
       <c r="C136" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D136" s="136">
-        <v>1001094966025</v>
+      <c r="D136" s="51">
+        <v>1001095716866</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="128">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G136" s="23">
         <f>E136</f>
@@ -12916,208 +12749,542 @@
       <c r="BN136" s="102"/>
       <c r="BO136" s="102"/>
     </row>
-    <row r="137" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>7485</v>
+        <f t="shared" si="28"/>
+        <v>5495</v>
       </c>
       <c r="B137" s="53" t="s">
-        <v>221</v>
+        <v>94</v>
       </c>
       <c r="C137" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D137" s="136">
-        <v>1001107397485</v>
+        <v>1001093345495</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="128">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="G137" s="23">
-        <f>F137*E137</f>
+        <f t="shared" ref="G137:G140" si="30">E137*F137</f>
         <v>0</v>
       </c>
-      <c r="H137" s="29"/>
-      <c r="I137" s="29"/>
-      <c r="J137" s="125" t="s">
-        <v>196</v>
-      </c>
+      <c r="H137" s="29">
+        <v>2.4</v>
+      </c>
+      <c r="I137" s="29">
+        <v>60</v>
+      </c>
+      <c r="J137" s="29"/>
+      <c r="K137" s="27"/>
       <c r="L137" s="102"/>
-    </row>
-    <row r="138" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M137" s="102"/>
+      <c r="N137" s="102"/>
+      <c r="O137" s="102"/>
+      <c r="P137" s="102"/>
+      <c r="Q137" s="102"/>
+      <c r="R137" s="102"/>
+      <c r="S137" s="102"/>
+      <c r="T137" s="102"/>
+      <c r="U137" s="102"/>
+      <c r="V137" s="102"/>
+      <c r="W137" s="102"/>
+      <c r="X137" s="102"/>
+      <c r="Y137" s="102"/>
+      <c r="Z137" s="102"/>
+      <c r="AA137" s="102"/>
+      <c r="AB137" s="102"/>
+      <c r="AC137" s="102"/>
+      <c r="AD137" s="102"/>
+      <c r="AE137" s="102"/>
+      <c r="AF137" s="102"/>
+      <c r="AG137" s="102"/>
+      <c r="AH137" s="102"/>
+      <c r="AI137" s="102"/>
+      <c r="AJ137" s="102"/>
+      <c r="AK137" s="102"/>
+      <c r="AL137" s="102"/>
+      <c r="AM137" s="102"/>
+      <c r="AN137" s="102"/>
+      <c r="AO137" s="102"/>
+      <c r="AP137" s="102"/>
+      <c r="AQ137" s="102"/>
+      <c r="AR137" s="102"/>
+      <c r="AS137" s="102"/>
+      <c r="AT137" s="102"/>
+      <c r="AU137" s="102"/>
+      <c r="AV137" s="102"/>
+      <c r="AW137" s="102"/>
+      <c r="AX137" s="102"/>
+      <c r="AY137" s="102"/>
+      <c r="AZ137" s="102"/>
+      <c r="BA137" s="102"/>
+      <c r="BB137" s="102"/>
+      <c r="BC137" s="102"/>
+      <c r="BD137" s="102"/>
+      <c r="BE137" s="102"/>
+      <c r="BF137" s="102"/>
+      <c r="BG137" s="102"/>
+      <c r="BH137" s="102"/>
+      <c r="BI137" s="102"/>
+      <c r="BJ137" s="102"/>
+      <c r="BK137" s="102"/>
+      <c r="BL137" s="102"/>
+      <c r="BM137" s="102"/>
+      <c r="BN137" s="102"/>
+      <c r="BO137" s="102"/>
+    </row>
+    <row r="138" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>7647</v>
+        <f t="shared" si="28"/>
+        <v>7377</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>195</v>
+        <v>117</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D138" s="136">
-        <v>1001097747647</v>
+        <v>1001095027377</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="128">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G138" s="23">
-        <f>E138*F138</f>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H138" s="29">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I138" s="29">
-        <v>30</v>
-      </c>
-      <c r="J138" s="125" t="s">
-        <v>196</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="J138" s="29"/>
+      <c r="K138" s="27"/>
       <c r="L138" s="102"/>
-    </row>
-    <row r="139" spans="1:67" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="M138" s="102"/>
+      <c r="N138" s="102"/>
+      <c r="O138" s="102"/>
+      <c r="P138" s="102"/>
+      <c r="Q138" s="102"/>
+      <c r="R138" s="102"/>
+      <c r="S138" s="102"/>
+      <c r="T138" s="102"/>
+      <c r="U138" s="102"/>
+      <c r="V138" s="102"/>
+      <c r="W138" s="102"/>
+      <c r="X138" s="102"/>
+      <c r="Y138" s="102"/>
+      <c r="Z138" s="102"/>
+      <c r="AA138" s="102"/>
+      <c r="AB138" s="102"/>
+      <c r="AC138" s="102"/>
+      <c r="AD138" s="102"/>
+      <c r="AE138" s="102"/>
+      <c r="AF138" s="102"/>
+      <c r="AG138" s="102"/>
+      <c r="AH138" s="102"/>
+      <c r="AI138" s="102"/>
+      <c r="AJ138" s="102"/>
+      <c r="AK138" s="102"/>
+      <c r="AL138" s="102"/>
+      <c r="AM138" s="102"/>
+      <c r="AN138" s="102"/>
+      <c r="AO138" s="102"/>
+      <c r="AP138" s="102"/>
+      <c r="AQ138" s="102"/>
+      <c r="AR138" s="102"/>
+      <c r="AS138" s="102"/>
+      <c r="AT138" s="102"/>
+      <c r="AU138" s="102"/>
+      <c r="AV138" s="102"/>
+      <c r="AW138" s="102"/>
+      <c r="AX138" s="102"/>
+      <c r="AY138" s="102"/>
+      <c r="AZ138" s="102"/>
+      <c r="BA138" s="102"/>
+      <c r="BB138" s="102"/>
+      <c r="BC138" s="102"/>
+      <c r="BD138" s="102"/>
+      <c r="BE138" s="102"/>
+      <c r="BF138" s="102"/>
+      <c r="BG138" s="102"/>
+      <c r="BH138" s="102"/>
+      <c r="BI138" s="102"/>
+      <c r="BJ138" s="102"/>
+      <c r="BK138" s="102"/>
+      <c r="BL138" s="102"/>
+      <c r="BM138" s="102"/>
+      <c r="BN138" s="102"/>
+      <c r="BO138" s="102"/>
+    </row>
+    <row r="139" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="137" t="str">
-        <f t="shared" si="26"/>
-        <v>7651</v>
+        <f t="shared" si="28"/>
+        <v>6411</v>
       </c>
       <c r="B139" s="53" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="C139" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D139" s="136">
-        <v>1001097767651</v>
+        <v>1001093316411</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="128">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G139" s="23">
-        <f>E139*F139</f>
+        <f t="shared" ref="G139" si="31">E139*F139</f>
         <v>0</v>
       </c>
-      <c r="H139" s="29">
-        <v>1</v>
-      </c>
-      <c r="I139" s="29">
-        <v>30</v>
-      </c>
-      <c r="J139" s="125" t="s">
-        <v>196</v>
-      </c>
+      <c r="H139" s="29"/>
+      <c r="I139" s="29"/>
+      <c r="J139" s="29"/>
+      <c r="K139" s="27"/>
       <c r="L139" s="102"/>
-    </row>
-    <row r="140" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B140" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C140" s="42"/>
-      <c r="D140" s="42"/>
-      <c r="E140" s="42"/>
-      <c r="F140" s="41"/>
-      <c r="G140" s="42"/>
-      <c r="H140" s="42"/>
-      <c r="I140" s="42"/>
-      <c r="J140" s="43"/>
+      <c r="M139" s="102"/>
+      <c r="N139" s="102"/>
+      <c r="O139" s="102"/>
+      <c r="P139" s="102"/>
+      <c r="Q139" s="102"/>
+      <c r="R139" s="102"/>
+      <c r="S139" s="102"/>
+      <c r="T139" s="102"/>
+      <c r="U139" s="102"/>
+      <c r="V139" s="102"/>
+      <c r="W139" s="102"/>
+      <c r="X139" s="102"/>
+      <c r="Y139" s="102"/>
+      <c r="Z139" s="102"/>
+      <c r="AA139" s="102"/>
+      <c r="AB139" s="102"/>
+      <c r="AC139" s="102"/>
+      <c r="AD139" s="102"/>
+      <c r="AE139" s="102"/>
+      <c r="AF139" s="102"/>
+      <c r="AG139" s="102"/>
+      <c r="AH139" s="102"/>
+      <c r="AI139" s="102"/>
+      <c r="AJ139" s="102"/>
+      <c r="AK139" s="102"/>
+      <c r="AL139" s="102"/>
+      <c r="AM139" s="102"/>
+      <c r="AN139" s="102"/>
+      <c r="AO139" s="102"/>
+      <c r="AP139" s="102"/>
+      <c r="AQ139" s="102"/>
+      <c r="AR139" s="102"/>
+      <c r="AS139" s="102"/>
+      <c r="AT139" s="102"/>
+      <c r="AU139" s="102"/>
+      <c r="AV139" s="102"/>
+      <c r="AW139" s="102"/>
+      <c r="AX139" s="102"/>
+      <c r="AY139" s="102"/>
+      <c r="AZ139" s="102"/>
+      <c r="BA139" s="102"/>
+      <c r="BB139" s="102"/>
+      <c r="BC139" s="102"/>
+      <c r="BD139" s="102"/>
+      <c r="BE139" s="102"/>
+      <c r="BF139" s="102"/>
+      <c r="BG139" s="102"/>
+      <c r="BH139" s="102"/>
+      <c r="BI139" s="102"/>
+      <c r="BJ139" s="102"/>
+      <c r="BK139" s="102"/>
+      <c r="BL139" s="102"/>
+      <c r="BM139" s="102"/>
+      <c r="BN139" s="102"/>
+      <c r="BO139" s="102"/>
+    </row>
+    <row r="140" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>6925</v>
+      </c>
+      <c r="B140" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="C140" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D140" s="136">
+        <v>1001095226925</v>
+      </c>
+      <c r="E140" s="24"/>
+      <c r="F140" s="128">
+        <v>0.6</v>
+      </c>
+      <c r="G140" s="23">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="H140" s="29">
+        <v>4.8</v>
+      </c>
+      <c r="I140" s="29">
+        <v>45</v>
+      </c>
+      <c r="J140" s="29"/>
+      <c r="K140" s="27"/>
       <c r="L140" s="102"/>
-    </row>
-    <row r="141" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M140" s="102"/>
+      <c r="N140" s="102"/>
+      <c r="O140" s="102"/>
+      <c r="P140" s="102"/>
+      <c r="Q140" s="102"/>
+      <c r="R140" s="102"/>
+      <c r="S140" s="102"/>
+      <c r="T140" s="102"/>
+      <c r="U140" s="102"/>
+      <c r="V140" s="102"/>
+      <c r="W140" s="102"/>
+      <c r="X140" s="102"/>
+      <c r="Y140" s="102"/>
+      <c r="Z140" s="102"/>
+      <c r="AA140" s="102"/>
+      <c r="AB140" s="102"/>
+      <c r="AC140" s="102"/>
+      <c r="AD140" s="102"/>
+      <c r="AE140" s="102"/>
+      <c r="AF140" s="102"/>
+      <c r="AG140" s="102"/>
+      <c r="AH140" s="102"/>
+      <c r="AI140" s="102"/>
+      <c r="AJ140" s="102"/>
+      <c r="AK140" s="102"/>
+      <c r="AL140" s="102"/>
+      <c r="AM140" s="102"/>
+      <c r="AN140" s="102"/>
+      <c r="AO140" s="102"/>
+      <c r="AP140" s="102"/>
+      <c r="AQ140" s="102"/>
+      <c r="AR140" s="102"/>
+      <c r="AS140" s="102"/>
+      <c r="AT140" s="102"/>
+      <c r="AU140" s="102"/>
+      <c r="AV140" s="102"/>
+      <c r="AW140" s="102"/>
+      <c r="AX140" s="102"/>
+      <c r="AY140" s="102"/>
+      <c r="AZ140" s="102"/>
+      <c r="BA140" s="102"/>
+      <c r="BB140" s="102"/>
+      <c r="BC140" s="102"/>
+      <c r="BD140" s="102"/>
+      <c r="BE140" s="102"/>
+      <c r="BF140" s="102"/>
+      <c r="BG140" s="102"/>
+      <c r="BH140" s="102"/>
+      <c r="BI140" s="102"/>
+      <c r="BJ140" s="102"/>
+      <c r="BK140" s="102"/>
+      <c r="BL140" s="102"/>
+      <c r="BM140" s="102"/>
+      <c r="BN140" s="102"/>
+      <c r="BO140" s="102"/>
+    </row>
+    <row r="141" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="137" t="str">
-        <f t="shared" ref="A141:A152" si="30">RIGHT(D141,4)</f>
-        <v>7090</v>
-      </c>
-      <c r="B141" s="35" t="s">
-        <v>100</v>
+        <f t="shared" si="28"/>
+        <v>6025</v>
+      </c>
+      <c r="B141" s="53" t="s">
+        <v>118</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D141" s="51">
-        <v>1001084217090</v>
+        <v>22</v>
+      </c>
+      <c r="D141" s="136">
+        <v>1001094966025</v>
       </c>
       <c r="E141" s="24"/>
-      <c r="F141" s="23">
-        <v>0.3</v>
+      <c r="F141" s="128">
+        <v>3</v>
       </c>
       <c r="G141" s="23">
-        <f t="shared" ref="G141:G142" si="31">E141*F141</f>
+        <f>E141</f>
         <v>0</v>
       </c>
-      <c r="H141" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I141" s="14">
-        <v>50</v>
+      <c r="H141" s="29">
+        <v>6</v>
+      </c>
+      <c r="I141" s="29">
+        <v>60</v>
       </c>
       <c r="J141" s="29"/>
+      <c r="K141" s="27"/>
       <c r="L141" s="102"/>
-    </row>
-    <row r="142" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M141" s="102"/>
+      <c r="N141" s="102"/>
+      <c r="O141" s="102"/>
+      <c r="P141" s="102"/>
+      <c r="Q141" s="102"/>
+      <c r="R141" s="102"/>
+      <c r="S141" s="102"/>
+      <c r="T141" s="102"/>
+      <c r="U141" s="102"/>
+      <c r="V141" s="102"/>
+      <c r="W141" s="102"/>
+      <c r="X141" s="102"/>
+      <c r="Y141" s="102"/>
+      <c r="Z141" s="102"/>
+      <c r="AA141" s="102"/>
+      <c r="AB141" s="102"/>
+      <c r="AC141" s="102"/>
+      <c r="AD141" s="102"/>
+      <c r="AE141" s="102"/>
+      <c r="AF141" s="102"/>
+      <c r="AG141" s="102"/>
+      <c r="AH141" s="102"/>
+      <c r="AI141" s="102"/>
+      <c r="AJ141" s="102"/>
+      <c r="AK141" s="102"/>
+      <c r="AL141" s="102"/>
+      <c r="AM141" s="102"/>
+      <c r="AN141" s="102"/>
+      <c r="AO141" s="102"/>
+      <c r="AP141" s="102"/>
+      <c r="AQ141" s="102"/>
+      <c r="AR141" s="102"/>
+      <c r="AS141" s="102"/>
+      <c r="AT141" s="102"/>
+      <c r="AU141" s="102"/>
+      <c r="AV141" s="102"/>
+      <c r="AW141" s="102"/>
+      <c r="AX141" s="102"/>
+      <c r="AY141" s="102"/>
+      <c r="AZ141" s="102"/>
+      <c r="BA141" s="102"/>
+      <c r="BB141" s="102"/>
+      <c r="BC141" s="102"/>
+      <c r="BD141" s="102"/>
+      <c r="BE141" s="102"/>
+      <c r="BF141" s="102"/>
+      <c r="BG141" s="102"/>
+      <c r="BH141" s="102"/>
+      <c r="BI141" s="102"/>
+      <c r="BJ141" s="102"/>
+      <c r="BK141" s="102"/>
+      <c r="BL141" s="102"/>
+      <c r="BM141" s="102"/>
+      <c r="BN141" s="102"/>
+      <c r="BO141" s="102"/>
+    </row>
+    <row r="142" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>7187</v>
-      </c>
-      <c r="B142" s="35" t="s">
-        <v>101</v>
+        <f t="shared" si="28"/>
+        <v>6929</v>
+      </c>
+      <c r="B142" s="53" t="s">
+        <v>229</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D142" s="51">
-        <v>1001085637187</v>
+        <v>22</v>
+      </c>
+      <c r="D142" s="136">
+        <v>1001085476929</v>
       </c>
       <c r="E142" s="24"/>
-      <c r="F142" s="23">
-        <v>0.3</v>
-      </c>
+      <c r="F142" s="128"/>
       <c r="G142" s="23">
-        <f t="shared" si="31"/>
+        <f>E142</f>
         <v>0</v>
       </c>
-      <c r="H142" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I142" s="14">
-        <v>50</v>
-      </c>
+      <c r="H142" s="29"/>
+      <c r="I142" s="29"/>
       <c r="J142" s="29"/>
+      <c r="K142" s="27"/>
       <c r="L142" s="102"/>
+      <c r="M142" s="102"/>
+      <c r="N142" s="102"/>
+      <c r="O142" s="102"/>
+      <c r="P142" s="102"/>
+      <c r="Q142" s="102"/>
+      <c r="R142" s="102"/>
+      <c r="S142" s="102"/>
+      <c r="T142" s="102"/>
+      <c r="U142" s="102"/>
+      <c r="V142" s="102"/>
+      <c r="W142" s="102"/>
+      <c r="X142" s="102"/>
+      <c r="Y142" s="102"/>
+      <c r="Z142" s="102"/>
+      <c r="AA142" s="102"/>
+      <c r="AB142" s="102"/>
+      <c r="AC142" s="102"/>
+      <c r="AD142" s="102"/>
+      <c r="AE142" s="102"/>
+      <c r="AF142" s="102"/>
+      <c r="AG142" s="102"/>
+      <c r="AH142" s="102"/>
+      <c r="AI142" s="102"/>
+      <c r="AJ142" s="102"/>
+      <c r="AK142" s="102"/>
+      <c r="AL142" s="102"/>
+      <c r="AM142" s="102"/>
+      <c r="AN142" s="102"/>
+      <c r="AO142" s="102"/>
+      <c r="AP142" s="102"/>
+      <c r="AQ142" s="102"/>
+      <c r="AR142" s="102"/>
+      <c r="AS142" s="102"/>
+      <c r="AT142" s="102"/>
+      <c r="AU142" s="102"/>
+      <c r="AV142" s="102"/>
+      <c r="AW142" s="102"/>
+      <c r="AX142" s="102"/>
+      <c r="AY142" s="102"/>
+      <c r="AZ142" s="102"/>
+      <c r="BA142" s="102"/>
+      <c r="BB142" s="102"/>
+      <c r="BC142" s="102"/>
+      <c r="BD142" s="102"/>
+      <c r="BE142" s="102"/>
+      <c r="BF142" s="102"/>
+      <c r="BG142" s="102"/>
+      <c r="BH142" s="102"/>
+      <c r="BI142" s="102"/>
+      <c r="BJ142" s="102"/>
+      <c r="BK142" s="102"/>
+      <c r="BL142" s="102"/>
+      <c r="BM142" s="102"/>
+      <c r="BN142" s="102"/>
+      <c r="BO142" s="102"/>
     </row>
     <row r="143" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>6008</v>
-      </c>
-      <c r="B143" s="35" t="s">
-        <v>198</v>
+        <f t="shared" si="28"/>
+        <v>7485</v>
+      </c>
+      <c r="B143" s="53" t="s">
+        <v>221</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D143" s="51">
-        <v>1001084856008</v>
+        <v>20</v>
+      </c>
+      <c r="D143" s="136">
+        <v>1001107397485</v>
       </c>
       <c r="E143" s="24"/>
-      <c r="F143" s="23">
-        <v>0.3</v>
+      <c r="F143" s="128">
+        <v>0.15</v>
       </c>
       <c r="G143" s="23">
-        <f>E143</f>
+        <f>F143*E143</f>
         <v>0</v>
       </c>
-      <c r="H143" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I143" s="14">
-        <v>40</v>
-      </c>
+      <c r="H143" s="29"/>
+      <c r="I143" s="29"/>
       <c r="J143" s="125" t="s">
         <v>196</v>
       </c>
@@ -13125,366 +13292,481 @@
     </row>
     <row r="144" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>6620</v>
-      </c>
-      <c r="B144" s="35" t="s">
-        <v>97</v>
+        <f t="shared" si="28"/>
+        <v>7647</v>
+      </c>
+      <c r="B144" s="53" t="s">
+        <v>195</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D144" s="51">
-        <v>1001081596620</v>
+        <v>20</v>
+      </c>
+      <c r="D144" s="136">
+        <v>1001097747647</v>
       </c>
       <c r="E144" s="24"/>
-      <c r="F144" s="23">
-        <v>1.05</v>
+      <c r="F144" s="128">
+        <v>0.1</v>
       </c>
       <c r="G144" s="23">
-        <f>E144</f>
+        <f>E144*F144</f>
         <v>0</v>
       </c>
-      <c r="H144" s="14">
-        <v>3.15</v>
-      </c>
-      <c r="I144" s="14">
+      <c r="H144" s="29">
+        <v>1</v>
+      </c>
+      <c r="I144" s="29">
         <v>30</v>
       </c>
-      <c r="J144" s="29"/>
+      <c r="J144" s="125" t="s">
+        <v>196</v>
+      </c>
       <c r="L144" s="102"/>
     </row>
-    <row r="145" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>7103</v>
-      </c>
-      <c r="B145" s="35" t="s">
-        <v>216</v>
+        <f t="shared" si="28"/>
+        <v>7651</v>
+      </c>
+      <c r="B145" s="53" t="s">
+        <v>197</v>
       </c>
       <c r="C145" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D145" s="51">
-        <v>1001223297103</v>
+      <c r="D145" s="136">
+        <v>1001097767651</v>
       </c>
       <c r="E145" s="24"/>
-      <c r="F145" s="23">
-        <v>0.18</v>
+      <c r="F145" s="128">
+        <v>0.1</v>
       </c>
       <c r="G145" s="23">
-        <f t="shared" ref="G145:G152" si="32">E145*F145</f>
+        <f>E145*F145</f>
         <v>0</v>
       </c>
-      <c r="H145" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I145" s="14">
-        <v>50</v>
-      </c>
-      <c r="J145" s="29"/>
+      <c r="H145" s="29">
+        <v>1</v>
+      </c>
+      <c r="I145" s="29">
+        <v>30</v>
+      </c>
+      <c r="J145" s="125" t="s">
+        <v>196</v>
+      </c>
       <c r="L145" s="102"/>
     </row>
-    <row r="146" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>7092</v>
-      </c>
-      <c r="B146" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="C146" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D146" s="51">
-        <v>1001223297092</v>
-      </c>
-      <c r="E146" s="24"/>
-      <c r="F146" s="23">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="G146" s="23">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="H146" s="14">
-        <v>1.4</v>
-      </c>
-      <c r="I146" s="14">
-        <v>50</v>
-      </c>
-      <c r="J146" s="29"/>
+    <row r="146" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B146" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C146" s="42"/>
+      <c r="D146" s="42"/>
+      <c r="E146" s="42"/>
+      <c r="F146" s="41"/>
+      <c r="G146" s="42"/>
+      <c r="H146" s="42"/>
+      <c r="I146" s="42"/>
+      <c r="J146" s="43"/>
       <c r="L146" s="102"/>
     </row>
-    <row r="147" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A147" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>6228</v>
+        <f t="shared" ref="A147:A158" si="32">RIGHT(D147,4)</f>
+        <v>7090</v>
       </c>
       <c r="B147" s="35" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C147" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D147" s="51">
-        <v>1001225416228</v>
+        <v>1001084217090</v>
       </c>
       <c r="E147" s="24"/>
       <c r="F147" s="23">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="G147" s="23">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="G147:G148" si="33">E147*F147</f>
         <v>0</v>
       </c>
       <c r="H147" s="14">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="I147" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J147" s="29"/>
       <c r="L147" s="102"/>
     </row>
     <row r="148" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>6448</v>
+        <f t="shared" si="32"/>
+        <v>7187</v>
       </c>
       <c r="B148" s="35" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D148" s="51">
-        <v>1001234146448</v>
+        <v>1001085637187</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="23">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="H148" s="14">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="I148" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J148" s="29"/>
       <c r="L148" s="102"/>
     </row>
     <row r="149" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>6208</v>
+        <f t="shared" si="32"/>
+        <v>6008</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>99</v>
+        <v>198</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D149" s="51">
-        <v>1001220226208</v>
+        <v>1001084856008</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="23">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="G149" s="23">
-        <f t="shared" si="32"/>
+        <f>E149</f>
         <v>0</v>
       </c>
       <c r="H149" s="14">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="I149" s="14">
-        <v>45</v>
-      </c>
-      <c r="J149" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J149" s="125" t="s">
+        <v>196</v>
+      </c>
       <c r="L149" s="102"/>
     </row>
     <row r="150" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>6754</v>
+        <f t="shared" si="32"/>
+        <v>6620</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>222</v>
+        <v>97</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D150" s="51">
-        <v>1001225406754</v>
+        <v>1001081596620</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="23">
-        <v>0.09</v>
+        <v>1.05</v>
       </c>
       <c r="G150" s="23">
+        <f>E150</f>
+        <v>0</v>
+      </c>
+      <c r="H150" s="14">
+        <v>3.15</v>
+      </c>
+      <c r="I150" s="14">
+        <v>30</v>
+      </c>
+      <c r="J150" s="29"/>
+      <c r="L150" s="102"/>
+    </row>
+    <row r="151" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="137" t="str">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="H150" s="14">
-        <v>0.72</v>
-      </c>
-      <c r="I150" s="14">
-        <v>60</v>
-      </c>
-      <c r="J150" s="29"/>
-    </row>
-    <row r="151" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>6279</v>
+        <v>7103</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>98</v>
+        <v>216</v>
       </c>
       <c r="C151" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D151" s="51">
-        <v>1001220286279</v>
+        <v>1001223297103</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="23">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="G151" s="23">
+        <f t="shared" ref="G151:G158" si="34">E151*F151</f>
+        <v>0</v>
+      </c>
+      <c r="H151" s="14">
+        <v>1.8</v>
+      </c>
+      <c r="I151" s="14">
+        <v>50</v>
+      </c>
+      <c r="J151" s="29"/>
+      <c r="L151" s="102"/>
+    </row>
+    <row r="152" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="137" t="str">
         <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="H151" s="14">
-        <v>1.2</v>
-      </c>
-      <c r="I151" s="14">
-        <v>45</v>
-      </c>
-      <c r="J151" s="29"/>
-    </row>
-    <row r="152" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="137" t="str">
-        <f t="shared" si="30"/>
-        <v>7612</v>
+        <v>7092</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>199</v>
+        <v>78</v>
       </c>
       <c r="C152" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D152" s="51">
-        <v>1001453907612</v>
+        <v>1001223297092</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="G152" s="23">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H152" s="14">
+        <v>1.4</v>
+      </c>
+      <c r="I152" s="14">
+        <v>50</v>
+      </c>
+      <c r="J152" s="29"/>
+      <c r="L152" s="102"/>
+    </row>
+    <row r="153" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="137" t="str">
+        <f t="shared" si="32"/>
+        <v>6228</v>
+      </c>
+      <c r="B153" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="C153" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D153" s="51">
+        <v>1001225416228</v>
+      </c>
+      <c r="E153" s="24"/>
+      <c r="F153" s="23">
+        <v>0.09</v>
+      </c>
+      <c r="G153" s="23">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H153" s="14">
+        <v>0.9</v>
+      </c>
+      <c r="I153" s="14">
+        <v>45</v>
+      </c>
+      <c r="J153" s="29"/>
+      <c r="L153" s="102"/>
+    </row>
+    <row r="154" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="137" t="str">
+        <f t="shared" si="32"/>
+        <v>6448</v>
+      </c>
+      <c r="B154" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C154" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D154" s="51">
+        <v>1001234146448</v>
+      </c>
+      <c r="E154" s="24"/>
+      <c r="F154" s="23">
         <v>0.1</v>
       </c>
-      <c r="G152" s="23">
+      <c r="G154" s="23">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H154" s="14">
+        <v>1</v>
+      </c>
+      <c r="I154" s="14">
+        <v>45</v>
+      </c>
+      <c r="J154" s="29"/>
+      <c r="L154" s="102"/>
+    </row>
+    <row r="155" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="137" t="str">
         <f t="shared" si="32"/>
+        <v>6208</v>
+      </c>
+      <c r="B155" s="35" t="s">
+        <v>99</v>
+      </c>
+      <c r="C155" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D155" s="51">
+        <v>1001220226208</v>
+      </c>
+      <c r="E155" s="24"/>
+      <c r="F155" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G155" s="23">
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="H152" s="14">
+      <c r="H155" s="14">
+        <v>1.5</v>
+      </c>
+      <c r="I155" s="14">
+        <v>45</v>
+      </c>
+      <c r="J155" s="29"/>
+      <c r="L155" s="102"/>
+    </row>
+    <row r="156" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="137" t="str">
+        <f t="shared" si="32"/>
+        <v>6754</v>
+      </c>
+      <c r="B156" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="C156" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D156" s="51">
+        <v>1001225406754</v>
+      </c>
+      <c r="E156" s="24"/>
+      <c r="F156" s="23">
+        <v>0.09</v>
+      </c>
+      <c r="G156" s="23">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H156" s="14">
+        <v>0.72</v>
+      </c>
+      <c r="I156" s="14">
+        <v>60</v>
+      </c>
+      <c r="J156" s="29"/>
+    </row>
+    <row r="157" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="137" t="str">
+        <f t="shared" si="32"/>
+        <v>6279</v>
+      </c>
+      <c r="B157" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C157" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D157" s="51">
+        <v>1001220286279</v>
+      </c>
+      <c r="E157" s="24"/>
+      <c r="F157" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G157" s="23">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H157" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I157" s="14">
+        <v>45</v>
+      </c>
+      <c r="J157" s="29"/>
+    </row>
+    <row r="158" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="137" t="str">
+        <f t="shared" si="32"/>
+        <v>7612</v>
+      </c>
+      <c r="B158" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="C158" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D158" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E158" s="24"/>
+      <c r="F158" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G158" s="23">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H158" s="14">
         <v>1</v>
       </c>
-      <c r="I152" s="14">
+      <c r="I158" s="14">
         <v>60</v>
       </c>
-      <c r="J152" s="52" t="s">
+      <c r="J158" s="52" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="48"/>
-      <c r="B153" s="45" t="s">
+    <row r="159" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="48"/>
+      <c r="B159" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C153" s="16"/>
-      <c r="D153" s="36"/>
-      <c r="E153" s="17">
-        <f>SUM(E10:E152)</f>
+      <c r="C159" s="16"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="17">
+        <f>SUM(E10:E158)</f>
         <v>0</v>
       </c>
-      <c r="F153" s="17"/>
-      <c r="G153" s="17">
-        <f>SUM(G11:G152)</f>
+      <c r="F159" s="17"/>
+      <c r="G159" s="17">
+        <f>SUM(G11:G158)</f>
         <v>0</v>
       </c>
-      <c r="H153" s="17"/>
-      <c r="I153" s="17"/>
-      <c r="J153" s="17"/>
-    </row>
-    <row r="154" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="37"/>
-      <c r="C154" s="18"/>
-      <c r="D154" s="40"/>
-      <c r="F154" s="19"/>
-      <c r="G154" s="19"/>
-      <c r="H154" s="20"/>
-      <c r="I154" s="20"/>
-      <c r="J154" s="21"/>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B155" s="37"/>
-      <c r="C155" s="18"/>
-      <c r="D155" s="40"/>
-      <c r="F155" s="19"/>
-      <c r="G155" s="19"/>
-      <c r="H155" s="20"/>
-      <c r="I155" s="20"/>
-      <c r="J155" s="21"/>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B156" s="37"/>
-      <c r="C156" s="18"/>
-      <c r="D156" s="40"/>
-      <c r="F156" s="19"/>
-      <c r="G156" s="19"/>
-      <c r="H156" s="20"/>
-      <c r="I156" s="20"/>
-      <c r="J156" s="21"/>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B157" s="37"/>
-      <c r="C157" s="55"/>
-      <c r="D157" s="56"/>
-      <c r="E157" s="57"/>
-      <c r="F157" s="58"/>
-      <c r="G157" s="58"/>
-      <c r="H157" s="59"/>
-      <c r="I157" s="59"/>
-      <c r="J157" s="21"/>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B158" s="37"/>
-      <c r="C158" s="55"/>
-      <c r="D158" s="56"/>
-      <c r="E158" s="57"/>
-      <c r="F158" s="58"/>
-      <c r="G158" s="58"/>
-      <c r="H158" s="59"/>
-      <c r="I158" s="59"/>
-      <c r="J158" s="21"/>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B159" s="37"/>
-      <c r="C159" s="55"/>
-      <c r="D159" s="60"/>
-      <c r="E159" s="61"/>
-      <c r="F159" s="60"/>
-      <c r="G159" s="62"/>
-      <c r="H159" s="63"/>
-      <c r="I159" s="64"/>
-      <c r="J159" s="21"/>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="H159" s="17"/>
+      <c r="I159" s="17"/>
+      <c r="J159" s="17"/>
+    </row>
+    <row r="160" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B160" s="37"/>
       <c r="C160" s="18"/>
       <c r="D160" s="40"/>
@@ -13516,32 +13798,35 @@
     </row>
     <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="37"/>
-      <c r="C163" s="18"/>
-      <c r="D163" s="40"/>
-      <c r="F163" s="19"/>
-      <c r="G163" s="19"/>
-      <c r="H163" s="20"/>
-      <c r="I163" s="20"/>
+      <c r="C163" s="55"/>
+      <c r="D163" s="56"/>
+      <c r="E163" s="57"/>
+      <c r="F163" s="58"/>
+      <c r="G163" s="58"/>
+      <c r="H163" s="59"/>
+      <c r="I163" s="59"/>
       <c r="J163" s="21"/>
     </row>
     <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="37"/>
-      <c r="C164" s="18"/>
-      <c r="D164" s="40"/>
-      <c r="F164" s="19"/>
-      <c r="G164" s="19"/>
-      <c r="H164" s="20"/>
-      <c r="I164" s="20"/>
+      <c r="C164" s="55"/>
+      <c r="D164" s="56"/>
+      <c r="E164" s="57"/>
+      <c r="F164" s="58"/>
+      <c r="G164" s="58"/>
+      <c r="H164" s="59"/>
+      <c r="I164" s="59"/>
       <c r="J164" s="21"/>
     </row>
     <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="37"/>
-      <c r="C165" s="18"/>
-      <c r="D165" s="40"/>
-      <c r="F165" s="19"/>
-      <c r="G165" s="19"/>
-      <c r="H165" s="20"/>
-      <c r="I165" s="20"/>
+      <c r="C165" s="55"/>
+      <c r="D165" s="60"/>
+      <c r="E165" s="61"/>
+      <c r="F165" s="60"/>
+      <c r="G165" s="62"/>
+      <c r="H165" s="63"/>
+      <c r="I165" s="64"/>
       <c r="J165" s="21"/>
     </row>
     <row r="166" spans="2:10" x14ac:dyDescent="0.25">
@@ -28634,13 +28919,73 @@
       <c r="I1674" s="20"/>
       <c r="J1674" s="21"/>
     </row>
+    <row r="1675" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1675" s="37"/>
+      <c r="C1675" s="18"/>
+      <c r="D1675" s="40"/>
+      <c r="F1675" s="19"/>
+      <c r="G1675" s="19"/>
+      <c r="H1675" s="20"/>
+      <c r="I1675" s="20"/>
+      <c r="J1675" s="21"/>
+    </row>
+    <row r="1676" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1676" s="37"/>
+      <c r="C1676" s="18"/>
+      <c r="D1676" s="40"/>
+      <c r="F1676" s="19"/>
+      <c r="G1676" s="19"/>
+      <c r="H1676" s="20"/>
+      <c r="I1676" s="20"/>
+      <c r="J1676" s="21"/>
+    </row>
+    <row r="1677" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1677" s="37"/>
+      <c r="C1677" s="18"/>
+      <c r="D1677" s="40"/>
+      <c r="F1677" s="19"/>
+      <c r="G1677" s="19"/>
+      <c r="H1677" s="20"/>
+      <c r="I1677" s="20"/>
+      <c r="J1677" s="21"/>
+    </row>
+    <row r="1678" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1678" s="37"/>
+      <c r="C1678" s="18"/>
+      <c r="D1678" s="40"/>
+      <c r="F1678" s="19"/>
+      <c r="G1678" s="19"/>
+      <c r="H1678" s="20"/>
+      <c r="I1678" s="20"/>
+      <c r="J1678" s="21"/>
+    </row>
+    <row r="1679" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1679" s="37"/>
+      <c r="C1679" s="18"/>
+      <c r="D1679" s="40"/>
+      <c r="F1679" s="19"/>
+      <c r="G1679" s="19"/>
+      <c r="H1679" s="20"/>
+      <c r="I1679" s="20"/>
+      <c r="J1679" s="21"/>
+    </row>
+    <row r="1680" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1680" s="37"/>
+      <c r="C1680" s="18"/>
+      <c r="D1680" s="40"/>
+      <c r="F1680" s="19"/>
+      <c r="G1680" s="19"/>
+      <c r="H1680" s="20"/>
+      <c r="I1680" s="20"/>
+      <c r="J1680" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J153" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J159" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D159">
+  <conditionalFormatting sqref="D165">
     <cfRule type="duplicateValues" dxfId="384" priority="1"/>
     <cfRule type="duplicateValues" dxfId="383" priority="2"/>
     <cfRule type="duplicateValues" dxfId="382" priority="3"/>
@@ -28652,7 +28997,7 @@
     <cfRule type="duplicateValues" dxfId="376" priority="10"/>
     <cfRule type="duplicateValues" dxfId="375" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D159">
+  <conditionalFormatting sqref="D165">
     <cfRule type="duplicateValues" dxfId="374" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF143D1-23E7-4172-A6BC-EA201124AFFC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7076BB99-B156-45AB-A732-9B896CB71E8B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="233">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1028,6 +1028,9 @@
   </si>
   <si>
     <t>НОВОМОСКОВСКАЯ в/к в/у срез 0.31кг</t>
+  </si>
+  <si>
+    <t>КРАКОВСКАЯ ГОСТ Останкино п/к н/о мгс</t>
   </si>
 </sst>
 </file>
@@ -1966,9 +1969,6 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1976,6 +1976,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6262,14 +6265,14 @@
       <c r="D1" s="127">
         <v>130438644</v>
       </c>
-      <c r="E1" s="138" t="s">
+      <c r="E1" s="137" t="s">
         <v>209</v>
       </c>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="140"/>
+      <c r="F1" s="138"/>
+      <c r="G1" s="138"/>
+      <c r="H1" s="138"/>
+      <c r="I1" s="138"/>
+      <c r="J1" s="139"/>
       <c r="K1" s="103">
         <v>130438384</v>
       </c>
@@ -6300,12 +6303,12 @@
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="141" t="s">
+      <c r="G3" s="140" t="s">
         <v>210</v>
       </c>
-      <c r="H3" s="139"/>
-      <c r="I3" s="139"/>
-      <c r="J3" s="140"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="139"/>
       <c r="K3" s="103">
         <v>130439106</v>
       </c>
@@ -6478,7 +6481,7 @@
       <c r="J10" s="43"/>
     </row>
     <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="137" t="str">
+      <c r="A11" s="141" t="str">
         <f>RIGHT(D11,4)</f>
         <v>7523</v>
       </c>
@@ -6567,8 +6570,8 @@
       <c r="BO11" s="101"/>
     </row>
     <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="137" t="str">
-        <f t="shared" ref="A12:A69" si="1">RIGHT(D12,4)</f>
+      <c r="A12" s="141" t="str">
+        <f t="shared" ref="A12:A72" si="1">RIGHT(D12,4)</f>
         <v>6220</v>
       </c>
       <c r="B12" s="53" t="s">
@@ -6654,7 +6657,7 @@
       <c r="BO12" s="101"/>
     </row>
     <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="137" t="str">
+      <c r="A13" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7539</v>
       </c>
@@ -6743,7 +6746,7 @@
       <c r="BO13" s="101"/>
     </row>
     <row r="14" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="137" t="str">
+      <c r="A14" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7536</v>
       </c>
@@ -6832,7 +6835,7 @@
       <c r="BO14" s="101"/>
     </row>
     <row r="15" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="137" t="str">
+      <c r="A15" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6861</v>
       </c>
@@ -6901,7 +6904,7 @@
       <c r="AX15" s="102"/>
     </row>
     <row r="16" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="137" t="str">
+      <c r="A16" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6862</v>
       </c>
@@ -6919,7 +6922,7 @@
         <v>1.95</v>
       </c>
       <c r="G16" s="23">
-        <f t="shared" ref="G16" si="2">E16</f>
+        <f t="shared" ref="G16:G18" si="2">E16</f>
         <v>0</v>
       </c>
       <c r="H16" s="14">
@@ -6932,7 +6935,7 @@
       <c r="L16" s="102"/>
     </row>
     <row r="17" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="137" t="str">
+      <c r="A17" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6498</v>
       </c>
@@ -6950,7 +6953,7 @@
         <v>1</v>
       </c>
       <c r="G17" s="23">
-        <f t="shared" ref="G17:G18" si="3">E17</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H17" s="14">
@@ -6963,7 +6966,7 @@
       <c r="L17" s="102"/>
     </row>
     <row r="18" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="137" t="str">
+      <c r="A18" s="141" t="str">
         <f t="shared" si="1"/>
         <v>4063</v>
       </c>
@@ -6981,7 +6984,7 @@
         <v>1.35</v>
       </c>
       <c r="G18" s="23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H18" s="14">
@@ -6994,7 +6997,7 @@
       <c r="L18" s="102"/>
     </row>
     <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="137" t="str">
+      <c r="A19" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6333</v>
       </c>
@@ -7025,7 +7028,7 @@
       <c r="L19" s="102"/>
     </row>
     <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="137" t="str">
+      <c r="A20" s="141" t="str">
         <f t="shared" si="1"/>
         <v>4574</v>
       </c>
@@ -7056,7 +7059,7 @@
       <c r="L20" s="102"/>
     </row>
     <row r="21" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="137" t="str">
+      <c r="A21" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7334</v>
       </c>
@@ -7087,7 +7090,7 @@
       <c r="L21" s="102"/>
     </row>
     <row r="22" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="137" t="str">
+      <c r="A22" s="141" t="str">
         <f t="shared" si="1"/>
         <v>4813</v>
       </c>
@@ -7174,7 +7177,7 @@
       <c r="BO22" s="102"/>
     </row>
     <row r="23" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="137" t="str">
+      <c r="A23" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6392</v>
       </c>
@@ -7261,7 +7264,7 @@
       <c r="BO23" s="102"/>
     </row>
     <row r="24" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="137" t="str">
+      <c r="A24" s="141" t="str">
         <f t="shared" si="1"/>
         <v>5851</v>
       </c>
@@ -7348,7 +7351,7 @@
       <c r="BO24" s="102"/>
     </row>
     <row r="25" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="137" t="str">
+      <c r="A25" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7632</v>
       </c>
@@ -7381,7 +7384,7 @@
       <c r="L25" s="102"/>
     </row>
     <row r="26" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="137" t="str">
+      <c r="A26" s="141" t="str">
         <f t="shared" si="1"/>
         <v>4561</v>
       </c>
@@ -7399,7 +7402,7 @@
         <v>1.35</v>
       </c>
       <c r="G26" s="23">
-        <f t="shared" ref="G26" si="4">E26</f>
+        <f t="shared" ref="G26" si="3">E26</f>
         <v>0</v>
       </c>
       <c r="H26" s="14">
@@ -7412,7 +7415,7 @@
       <c r="L26" s="102"/>
     </row>
     <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="137" t="str">
+      <c r="A27" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6325</v>
       </c>
@@ -7443,7 +7446,7 @@
       <c r="L27" s="102"/>
     </row>
     <row r="28" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="137" t="str">
+      <c r="A28" s="141" t="str">
         <f t="shared" si="1"/>
         <v>8014</v>
       </c>
@@ -7461,7 +7464,7 @@
         <v>1.35</v>
       </c>
       <c r="G28" s="23">
-        <f t="shared" ref="G28" si="5">E28</f>
+        <f t="shared" ref="G28" si="4">E28</f>
         <v>0</v>
       </c>
       <c r="H28" s="29">
@@ -7530,7 +7533,7 @@
       <c r="BO28" s="102"/>
     </row>
     <row r="29" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="137" t="str">
+      <c r="A29" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7514</v>
       </c>
@@ -7611,7 +7614,7 @@
       <c r="BO29" s="102"/>
     </row>
     <row r="30" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="137" t="str">
+      <c r="A30" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7518</v>
       </c>
@@ -7692,7 +7695,7 @@
       <c r="BO30" s="102"/>
     </row>
     <row r="31" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="137" t="str">
+      <c r="A31" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7343</v>
       </c>
@@ -7710,7 +7713,7 @@
         <v>0.4</v>
       </c>
       <c r="G31" s="23">
-        <f t="shared" ref="G31:G33" si="6">E31*F31</f>
+        <f t="shared" ref="G31:G33" si="5">E31*F31</f>
         <v>0</v>
       </c>
       <c r="H31" s="29">
@@ -7779,7 +7782,7 @@
       <c r="BO31" s="102"/>
     </row>
     <row r="32" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="137" t="str">
+      <c r="A32" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6797</v>
       </c>
@@ -7797,7 +7800,7 @@
         <v>0.4</v>
       </c>
       <c r="G32" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H32" s="29">
@@ -7810,7 +7813,7 @@
       <c r="L32" s="102"/>
     </row>
     <row r="33" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="137" t="str">
+      <c r="A33" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7231</v>
       </c>
@@ -7828,7 +7831,7 @@
         <v>0.3</v>
       </c>
       <c r="G33" s="23">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H33" s="29">
@@ -7970,7 +7973,7 @@
       <c r="BO34" s="102"/>
     </row>
     <row r="35" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="137" t="str">
+      <c r="A35" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6602</v>
       </c>
@@ -7988,7 +7991,7 @@
         <v>0.35</v>
       </c>
       <c r="G35" s="23">
-        <f t="shared" ref="G35:G39" si="7">E35*F35</f>
+        <f t="shared" ref="G35:G39" si="6">E35*F35</f>
         <v>0</v>
       </c>
       <c r="H35" s="29">
@@ -8057,7 +8060,7 @@
       <c r="BO35" s="102"/>
     </row>
     <row r="36" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="137" t="str">
+      <c r="A36" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7601</v>
       </c>
@@ -8075,7 +8078,7 @@
         <v>0.26400000000000001</v>
       </c>
       <c r="G36" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H36" s="29">
@@ -8144,7 +8147,7 @@
       <c r="BO36" s="102"/>
     </row>
     <row r="37" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="137" t="str">
+      <c r="A37" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7461</v>
       </c>
@@ -8162,7 +8165,7 @@
         <v>0.33</v>
       </c>
       <c r="G37" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H37" s="29">
@@ -8233,7 +8236,7 @@
       <c r="BO37" s="102"/>
     </row>
     <row r="38" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="137" t="str">
+      <c r="A38" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7040</v>
       </c>
@@ -8251,7 +8254,7 @@
         <v>0.27</v>
       </c>
       <c r="G38" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="29"/>
@@ -8318,7 +8321,7 @@
       <c r="BO38" s="102"/>
     </row>
     <row r="39" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="137" t="str">
+      <c r="A39" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6759</v>
       </c>
@@ -8336,7 +8339,7 @@
         <v>0.4</v>
       </c>
       <c r="G39" s="23">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H39" s="29">
@@ -8405,7 +8408,7 @@
       <c r="BO39" s="102"/>
     </row>
     <row r="40" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="137" t="str">
+      <c r="A40" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6761</v>
       </c>
@@ -8423,7 +8426,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="23">
-        <f t="shared" ref="G40:G41" si="8">E40</f>
+        <f t="shared" ref="G40:G41" si="7">E40</f>
         <v>0</v>
       </c>
       <c r="H40" s="29">
@@ -8492,7 +8495,7 @@
       <c r="BO40" s="102"/>
     </row>
     <row r="41" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="137" t="str">
+      <c r="A41" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6829</v>
       </c>
@@ -8510,7 +8513,7 @@
         <v>2.1</v>
       </c>
       <c r="G41" s="23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H41" s="29">
@@ -8579,7 +8582,7 @@
       <c r="BO41" s="102"/>
     </row>
     <row r="42" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="137" t="str">
+      <c r="A42" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6616</v>
       </c>
@@ -8666,7 +8669,7 @@
       <c r="BO42" s="102"/>
     </row>
     <row r="43" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="137" t="str">
+      <c r="A43" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7075</v>
       </c>
@@ -8753,7 +8756,7 @@
       <c r="BO43" s="102"/>
     </row>
     <row r="44" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="137" t="str">
+      <c r="A44" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7074</v>
       </c>
@@ -8771,7 +8774,7 @@
         <v>0.6</v>
       </c>
       <c r="G44" s="23">
-        <f t="shared" ref="G44:G47" si="9">E44*F44</f>
+        <f t="shared" ref="G44:G47" si="8">E44*F44</f>
         <v>0</v>
       </c>
       <c r="H44" s="29">
@@ -8840,7 +8843,7 @@
       <c r="BO44" s="102"/>
     </row>
     <row r="45" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="137" t="str">
+      <c r="A45" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7073</v>
       </c>
@@ -8858,7 +8861,7 @@
         <v>0.35</v>
       </c>
       <c r="G45" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H45" s="29">
@@ -8927,7 +8930,7 @@
       <c r="BO45" s="102"/>
     </row>
     <row r="46" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="137" t="str">
+      <c r="A46" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6724</v>
       </c>
@@ -8945,7 +8948,7 @@
         <v>0.41</v>
       </c>
       <c r="G46" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H46" s="29">
@@ -9014,7 +9017,7 @@
       <c r="BO46" s="102"/>
     </row>
     <row r="47" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="137" t="str">
+      <c r="A47" s="141" t="str">
         <f t="shared" si="1"/>
         <v>5819</v>
       </c>
@@ -9032,7 +9035,7 @@
         <v>0.4</v>
       </c>
       <c r="G47" s="23">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H47" s="29">
@@ -9101,7 +9104,7 @@
       <c r="BO47" s="102"/>
     </row>
     <row r="48" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="137" t="str">
+      <c r="A48" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6303</v>
       </c>
@@ -9188,7 +9191,7 @@
       <c r="BO48" s="102"/>
     </row>
     <row r="49" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="137" t="str">
+      <c r="A49" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7255</v>
       </c>
@@ -9275,7 +9278,7 @@
       <c r="BO49" s="102"/>
     </row>
     <row r="50" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="137" t="str">
+      <c r="A50" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7271</v>
       </c>
@@ -9362,7 +9365,7 @@
       <c r="BO50" s="102"/>
     </row>
     <row r="51" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="137" t="str">
+      <c r="A51" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6765</v>
       </c>
@@ -9449,7 +9452,7 @@
       <c r="BO51" s="102"/>
     </row>
     <row r="52" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="137" t="str">
+      <c r="A52" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6767</v>
       </c>
@@ -9536,7 +9539,7 @@
       <c r="BO52" s="102"/>
     </row>
     <row r="53" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="137" t="str">
+      <c r="A53" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6475</v>
       </c>
@@ -9623,7 +9626,7 @@
       <c r="BO53" s="102"/>
     </row>
     <row r="54" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="137" t="str">
+      <c r="A54" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7083</v>
       </c>
@@ -9710,7 +9713,7 @@
       <c r="BO54" s="102"/>
     </row>
     <row r="55" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="137" t="str">
+      <c r="A55" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7080</v>
       </c>
@@ -9728,7 +9731,7 @@
         <v>0.41</v>
       </c>
       <c r="G55" s="23">
-        <f t="shared" ref="G55:G57" si="10">E55*F55</f>
+        <f t="shared" ref="G55:G57" si="9">E55*F55</f>
         <v>0</v>
       </c>
       <c r="H55" s="29">
@@ -9797,7 +9800,7 @@
       <c r="BO55" s="102"/>
     </row>
     <row r="56" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="137" t="str">
+      <c r="A56" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7276</v>
       </c>
@@ -9815,7 +9818,7 @@
         <v>0.3</v>
       </c>
       <c r="G56" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H56" s="29">
@@ -9828,7 +9831,7 @@
       <c r="L56" s="102"/>
     </row>
     <row r="57" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="137" t="str">
+      <c r="A57" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6762</v>
       </c>
@@ -9846,7 +9849,7 @@
         <v>0.41</v>
       </c>
       <c r="G57" s="23">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="H57" s="29">
@@ -9859,7 +9862,7 @@
       <c r="L57" s="102"/>
     </row>
     <row r="58" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="137" t="str">
+      <c r="A58" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6764</v>
       </c>
@@ -9890,7 +9893,7 @@
       <c r="L58" s="102"/>
     </row>
     <row r="59" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="137" t="str">
+      <c r="A59" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7066</v>
       </c>
@@ -9921,7 +9924,7 @@
       <c r="L59" s="102"/>
     </row>
     <row r="60" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="137" t="str">
+      <c r="A60" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7070</v>
       </c>
@@ -9952,7 +9955,7 @@
       <c r="L60" s="102"/>
     </row>
     <row r="61" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="137" t="str">
+      <c r="A61" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6713</v>
       </c>
@@ -9983,7 +9986,7 @@
       <c r="L61" s="102"/>
     </row>
     <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="137" t="str">
+      <c r="A62" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6661</v>
       </c>
@@ -10001,7 +10004,7 @@
         <v>1.5</v>
       </c>
       <c r="G62" s="23">
-        <f t="shared" ref="G62:G63" si="11">E62</f>
+        <f t="shared" ref="G62:G63" si="10">E62</f>
         <v>0</v>
       </c>
       <c r="H62" s="14">
@@ -10014,7 +10017,7 @@
       <c r="L62" s="102"/>
     </row>
     <row r="63" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="137" t="str">
+      <c r="A63" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6254</v>
       </c>
@@ -10032,7 +10035,7 @@
         <v>1.5</v>
       </c>
       <c r="G63" s="23">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="H63" s="14">
@@ -10045,7 +10048,7 @@
       <c r="L63" s="102"/>
     </row>
     <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="137" t="str">
+      <c r="A64" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6837</v>
       </c>
@@ -10063,7 +10066,7 @@
         <v>0.4</v>
       </c>
       <c r="G64" s="23">
-        <f t="shared" ref="G64:G65" si="12">E64*F64</f>
+        <f t="shared" ref="G64:G65" si="11">E64*F64</f>
         <v>0</v>
       </c>
       <c r="H64" s="14">
@@ -10076,7 +10079,7 @@
       <c r="L64" s="102"/>
     </row>
     <row r="65" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="137" t="str">
+      <c r="A65" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7044</v>
       </c>
@@ -10094,7 +10097,7 @@
         <v>0.32</v>
       </c>
       <c r="G65" s="23">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H65" s="14">
@@ -10124,7 +10127,7 @@
       <c r="L66" s="102"/>
     </row>
     <row r="67" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="137" t="str">
+      <c r="A67" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6550</v>
       </c>
@@ -10142,7 +10145,7 @@
         <v>1</v>
       </c>
       <c r="G67" s="23">
-        <f t="shared" ref="G67:G70" si="13">E67</f>
+        <f t="shared" ref="G67:G70" si="12">E67</f>
         <v>0</v>
       </c>
       <c r="H67" s="29">
@@ -10155,7 +10158,7 @@
       <c r="L67" s="102"/>
     </row>
     <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="137" t="str">
+      <c r="A68" s="141" t="str">
         <f t="shared" si="1"/>
         <v>6608</v>
       </c>
@@ -10173,7 +10176,7 @@
         <v>1</v>
       </c>
       <c r="G68" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H68" s="14">
@@ -10186,7 +10189,7 @@
       <c r="L68" s="102"/>
     </row>
     <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="137" t="str">
+      <c r="A69" s="141" t="str">
         <f t="shared" si="1"/>
         <v>7001</v>
       </c>
@@ -10204,7 +10207,7 @@
         <v>1</v>
       </c>
       <c r="G69" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H69" s="14">
@@ -10217,8 +10220,8 @@
       <c r="L69" s="102"/>
     </row>
     <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="137" t="str">
-        <f t="shared" ref="A70:A72" si="14">RIGHT(D70,4)</f>
+      <c r="A70" s="141" t="str">
+        <f t="shared" si="1"/>
         <v>6527</v>
       </c>
       <c r="B70" s="129" t="s">
@@ -10235,7 +10238,7 @@
         <v>1</v>
       </c>
       <c r="G70" s="23">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H70" s="14">
@@ -10248,8 +10251,8 @@
       <c r="L70" s="102"/>
     </row>
     <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="137" t="str">
-        <f t="shared" si="14"/>
+      <c r="A71" s="141" t="str">
+        <f t="shared" si="1"/>
         <v>6609</v>
       </c>
       <c r="B71" s="129" t="s">
@@ -10266,7 +10269,7 @@
         <v>0.4</v>
       </c>
       <c r="G71" s="23">
-        <f t="shared" ref="G71:G72" si="15">E71*F71</f>
+        <f t="shared" ref="G71:G72" si="13">E71*F71</f>
         <v>0</v>
       </c>
       <c r="H71" s="14">
@@ -10279,8 +10282,8 @@
       <c r="L71" s="102"/>
     </row>
     <row r="72" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="137" t="str">
-        <f t="shared" si="14"/>
+      <c r="A72" s="141" t="str">
+        <f t="shared" si="1"/>
         <v>7059</v>
       </c>
       <c r="B72" s="129" t="s">
@@ -10297,7 +10300,7 @@
         <v>0.3</v>
       </c>
       <c r="G72" s="23">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="H72" s="14">
@@ -10327,8 +10330,8 @@
       <c r="L73" s="102"/>
     </row>
     <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="137" t="str">
-        <f t="shared" ref="A74:A100" si="16">RIGHT(D74,4)</f>
+      <c r="A74" s="141" t="str">
+        <f t="shared" ref="A74:A101" si="14">RIGHT(D74,4)</f>
         <v>7564</v>
       </c>
       <c r="B74" s="53" t="s">
@@ -10360,8 +10363,8 @@
       <c r="L74" s="102"/>
     </row>
     <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A75" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>7603</v>
       </c>
       <c r="B75" s="53" t="s">
@@ -10378,7 +10381,7 @@
         <v>0.33</v>
       </c>
       <c r="G75" s="23">
-        <f t="shared" ref="G75:G87" si="17">E75*F75</f>
+        <f t="shared" ref="G75:G88" si="15">E75*F75</f>
         <v>0</v>
       </c>
       <c r="H75" s="14">
@@ -10393,8 +10396,8 @@
       <c r="L75" s="102"/>
     </row>
     <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A76" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>7149</v>
       </c>
       <c r="B76" s="53" t="s">
@@ -10411,7 +10414,7 @@
         <v>0.84</v>
       </c>
       <c r="G76" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H76" s="14">
@@ -10424,8 +10427,8 @@
       <c r="L76" s="102"/>
     </row>
     <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A77" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>7233</v>
       </c>
       <c r="B77" s="53" t="s">
@@ -10442,7 +10445,7 @@
         <v>0.31</v>
       </c>
       <c r="G77" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H77" s="29">
@@ -10455,8 +10458,8 @@
       <c r="L77" s="102"/>
     </row>
     <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A78" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>7232</v>
       </c>
       <c r="B78" s="53" t="s">
@@ -10473,7 +10476,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G78" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H78" s="29">
@@ -10486,8 +10489,8 @@
       <c r="L78" s="102"/>
     </row>
     <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A79" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>7241</v>
       </c>
       <c r="B79" s="53" t="s">
@@ -10504,7 +10507,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G79" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H79" s="29">
@@ -10517,8 +10520,8 @@
       <c r="L79" s="102"/>
     </row>
     <row r="80" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A80" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>7133</v>
       </c>
       <c r="B80" s="53" t="s">
@@ -10548,8 +10551,8 @@
       <c r="L80" s="102"/>
     </row>
     <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A81" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>6946</v>
       </c>
       <c r="B81" s="53" t="s">
@@ -10573,8 +10576,8 @@
       <c r="L81" s="102"/>
     </row>
     <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A82" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>6807</v>
       </c>
       <c r="B82" s="53" t="s">
@@ -10591,7 +10594,7 @@
         <v>0.33</v>
       </c>
       <c r="G82" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H82" s="29">
@@ -10604,8 +10607,8 @@
       <c r="L82" s="102"/>
     </row>
     <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A83" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>7154</v>
       </c>
       <c r="B83" s="53" t="s">
@@ -10622,7 +10625,7 @@
         <v>0.35</v>
       </c>
       <c r="G83" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H83" s="14">
@@ -10635,8 +10638,8 @@
       <c r="L83" s="102"/>
     </row>
     <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="137" t="str">
-        <f t="shared" si="16"/>
+      <c r="A84" s="141" t="str">
+        <f t="shared" si="14"/>
         <v>7157</v>
       </c>
       <c r="B84" s="53" t="s">
@@ -10666,151 +10669,145 @@
       <c r="L84" s="102"/>
     </row>
     <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7236</v>
+      <c r="A85" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7562</v>
       </c>
       <c r="B85" s="53" t="s">
-        <v>68</v>
+        <v>232</v>
       </c>
       <c r="C85" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D85" s="51">
-        <v>1001304507236</v>
+        <v>1001307587562</v>
       </c>
       <c r="E85" s="24"/>
-      <c r="F85" s="23">
-        <v>0.28000000000000003</v>
-      </c>
+      <c r="F85" s="23"/>
       <c r="G85" s="23">
-        <f t="shared" si="17"/>
+        <f>E85</f>
         <v>0</v>
       </c>
-      <c r="H85" s="14">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="I85" s="14">
-        <v>45</v>
-      </c>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
       <c r="J85" s="29"/>
       <c r="L85" s="102"/>
     </row>
     <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7489</v>
+      <c r="A86" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7236</v>
       </c>
       <c r="B86" s="53" t="s">
-        <v>212</v>
+        <v>68</v>
       </c>
       <c r="C86" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D86" s="51">
-        <v>1001307357489</v>
+        <v>1001304507236</v>
       </c>
       <c r="E86" s="24"/>
       <c r="F86" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G86" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H86" s="14"/>
-      <c r="I86" s="14"/>
-      <c r="J86" s="125" t="s">
-        <v>196</v>
-      </c>
+      <c r="H86" s="14">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="I86" s="14">
+        <v>45</v>
+      </c>
+      <c r="J86" s="29"/>
       <c r="L86" s="102"/>
     </row>
     <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>6787</v>
-      </c>
-      <c r="B87" s="131" t="s">
-        <v>65</v>
+      <c r="A87" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7489</v>
+      </c>
+      <c r="B87" s="53" t="s">
+        <v>212</v>
       </c>
       <c r="C87" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D87" s="51">
-        <v>1001300456787</v>
+        <v>1001307357489</v>
       </c>
       <c r="E87" s="24"/>
       <c r="F87" s="23">
-        <v>0.33</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G87" s="23">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="H87" s="14">
-        <v>2.64</v>
-      </c>
-      <c r="I87" s="14">
-        <v>45</v>
-      </c>
-      <c r="J87" s="29"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="125" t="s">
+        <v>196</v>
+      </c>
       <c r="L87" s="102"/>
     </row>
     <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7166</v>
+      <c r="A88" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>6787</v>
       </c>
       <c r="B88" s="131" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C88" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D88" s="51">
-        <v>1001303987166</v>
+        <v>1001300456787</v>
       </c>
       <c r="E88" s="24"/>
       <c r="F88" s="23">
-        <v>0.7</v>
+        <v>0.33</v>
       </c>
       <c r="G88" s="23">
-        <f>E88</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="H88" s="14">
-        <v>5.6</v>
+        <v>2.64</v>
       </c>
       <c r="I88" s="14">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J88" s="29"/>
       <c r="L88" s="102"/>
     </row>
     <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7169</v>
-      </c>
-      <c r="B89" s="53" t="s">
-        <v>70</v>
+      <c r="A89" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7166</v>
+      </c>
+      <c r="B89" s="131" t="s">
+        <v>71</v>
       </c>
       <c r="C89" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D89" s="51">
-        <v>1001303987169</v>
+        <v>1001303987166</v>
       </c>
       <c r="E89" s="24"/>
       <c r="F89" s="23">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="G89" s="23">
-        <f>E89*F89</f>
+        <f>E89</f>
         <v>0</v>
       </c>
       <c r="H89" s="14">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="I89" s="14">
         <v>50</v>
@@ -10819,18 +10816,18 @@
       <c r="L89" s="102"/>
     </row>
     <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7156</v>
+      <c r="A90" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7169</v>
       </c>
       <c r="B90" s="53" t="s">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="C90" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D90" s="51">
-        <v>1001304237156</v>
+        <v>1001303987169</v>
       </c>
       <c r="E90" s="24"/>
       <c r="F90" s="23">
@@ -10840,66 +10837,66 @@
         <f>E90*F90</f>
         <v>0</v>
       </c>
-      <c r="H90" s="14"/>
-      <c r="I90" s="14"/>
-      <c r="J90" s="49"/>
+      <c r="H90" s="14">
+        <v>2.8</v>
+      </c>
+      <c r="I90" s="14">
+        <v>50</v>
+      </c>
+      <c r="J90" s="29"/>
       <c r="L90" s="102"/>
     </row>
     <row r="91" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>5544</v>
+      <c r="A91" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7156</v>
       </c>
       <c r="B91" s="53" t="s">
-        <v>72</v>
+        <v>225</v>
       </c>
       <c r="C91" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D91" s="51">
-        <v>1001051875544</v>
+        <v>1001304237156</v>
       </c>
       <c r="E91" s="24"/>
       <c r="F91" s="23">
-        <v>0.81</v>
+        <v>0.35</v>
       </c>
       <c r="G91" s="23">
-        <f>E91</f>
+        <f>E91*F91</f>
         <v>0</v>
       </c>
-      <c r="H91" s="14">
-        <v>4.8600000000000003</v>
-      </c>
-      <c r="I91" s="14">
-        <v>45</v>
-      </c>
+      <c r="H91" s="14"/>
+      <c r="I91" s="14"/>
       <c r="J91" s="49"/>
       <c r="L91" s="102"/>
     </row>
     <row r="92" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>6697</v>
+      <c r="A92" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>5544</v>
       </c>
       <c r="B92" s="53" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C92" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D92" s="51">
-        <v>1001301876697</v>
+        <v>1001051875544</v>
       </c>
       <c r="E92" s="24"/>
       <c r="F92" s="23">
-        <v>0.35</v>
+        <v>0.81</v>
       </c>
       <c r="G92" s="23">
-        <f t="shared" ref="G92:G100" si="18">E92*F92</f>
+        <f>E92</f>
         <v>0</v>
       </c>
       <c r="H92" s="14">
-        <v>2.8</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I92" s="14">
         <v>45</v>
@@ -10908,29 +10905,29 @@
       <c r="L92" s="102"/>
     </row>
     <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7238</v>
+      <c r="A93" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>6697</v>
       </c>
       <c r="B93" s="53" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="C93" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D93" s="51">
-        <v>1001305197238</v>
+        <v>1001301876697</v>
       </c>
       <c r="E93" s="24"/>
       <c r="F93" s="23">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="G93" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G93:G101" si="16">E93*F93</f>
         <v>0</v>
       </c>
       <c r="H93" s="14">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="I93" s="14">
         <v>45</v>
@@ -10939,52 +10936,56 @@
       <c r="L93" s="102"/>
     </row>
     <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7516</v>
+      <c r="A94" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7238</v>
       </c>
       <c r="B94" s="53" t="s">
-        <v>231</v>
+        <v>123</v>
       </c>
       <c r="C94" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D94" s="51">
-        <v>1001307107516</v>
+        <v>1001305197238</v>
       </c>
       <c r="E94" s="24"/>
       <c r="F94" s="23">
         <v>0.31</v>
       </c>
       <c r="G94" s="23">
-        <f t="shared" ref="G94" si="19">E94*F94</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H94" s="14"/>
-      <c r="I94" s="14"/>
+      <c r="H94" s="14">
+        <v>2.48</v>
+      </c>
+      <c r="I94" s="14">
+        <v>45</v>
+      </c>
       <c r="J94" s="49"/>
       <c r="L94" s="102"/>
     </row>
     <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7513</v>
+      <c r="A95" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7516</v>
       </c>
       <c r="B95" s="53" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C95" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D95" s="51">
-        <v>1001307077513</v>
+        <v>1001307107516</v>
       </c>
       <c r="E95" s="24"/>
       <c r="F95" s="23">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="G95" s="23">
-        <f t="shared" ref="G95" si="20">E95*F95</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H95" s="14"/>
@@ -10993,60 +10994,56 @@
       <c r="L95" s="102"/>
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7177</v>
+      <c r="A96" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7513</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="C96" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D96" s="51">
-        <v>1001302347177</v>
+        <v>1001307077513</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="G96" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H96" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I96" s="14">
-        <v>50</v>
-      </c>
+      <c r="H96" s="14"/>
+      <c r="I96" s="14"/>
       <c r="J96" s="49"/>
       <c r="L96" s="102"/>
     </row>
     <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7332</v>
+      <c r="A97" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7177</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="51">
-        <v>1001301777332</v>
+        <v>1001302347177</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G97" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H97" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I97" s="14">
         <v>50</v>
@@ -11055,25 +11052,25 @@
       <c r="L97" s="102"/>
     </row>
     <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7333</v>
+      <c r="A98" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7332</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="51">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
         <v>0.28000000000000003</v>
       </c>
       <c r="G98" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H98" s="14">
@@ -11086,58 +11083,56 @@
       <c r="L98" s="102"/>
     </row>
     <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7608</v>
+      <c r="A99" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7333</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="51">
-        <v>1001304197608</v>
+        <v>1001303987333</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G99" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H99" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I99" s="14">
-        <v>45</v>
-      </c>
-      <c r="J99" s="52" t="s">
-        <v>206</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J99" s="49"/>
       <c r="L99" s="102"/>
     </row>
-    <row r="100" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="137" t="str">
-        <f t="shared" si="16"/>
-        <v>7610</v>
+    <row r="100" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7608</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D100" s="51">
-        <v>1001306717610</v>
+        <v>1001304197608</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
         <v>0.1</v>
       </c>
       <c r="G100" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
@@ -11147,7 +11142,7 @@
         <v>45</v>
       </c>
       <c r="J100" s="52" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K100" s="27"/>
       <c r="L100" s="102"/>
@@ -11207,21 +11202,37 @@
       <c r="BN100" s="102"/>
       <c r="BO100" s="102"/>
     </row>
-    <row r="101" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B101" s="42" t="s">
-        <v>76</v>
-      </c>
-      <c r="C101" s="42"/>
-      <c r="D101" s="42"/>
-      <c r="E101" s="42"/>
-      <c r="F101" s="41"/>
-      <c r="G101" s="42"/>
-      <c r="H101" s="42"/>
-      <c r="I101" s="42"/>
-      <c r="J101" s="43"/>
+    <row r="101" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="141" t="str">
+        <f t="shared" si="14"/>
+        <v>7610</v>
+      </c>
+      <c r="B101" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C101" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101" s="51">
+        <v>1001306717610</v>
+      </c>
+      <c r="E101" s="24"/>
+      <c r="F101" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G101" s="23">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H101" s="14">
+        <v>1</v>
+      </c>
+      <c r="I101" s="14">
+        <v>45</v>
+      </c>
+      <c r="J101" s="52" t="s">
+        <v>208</v>
+      </c>
       <c r="K101" s="27"/>
       <c r="L101" s="102"/>
       <c r="M101" s="102"/>
@@ -11280,92 +11291,78 @@
       <c r="BN101" s="102"/>
       <c r="BO101" s="102"/>
     </row>
-    <row r="102" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="137" t="str">
-        <f t="shared" ref="A102:A129" si="21">RIGHT(D102,4)</f>
+    <row r="102" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B102" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="C102" s="42"/>
+      <c r="D102" s="42"/>
+      <c r="E102" s="42"/>
+      <c r="F102" s="41"/>
+      <c r="G102" s="42"/>
+      <c r="H102" s="42"/>
+      <c r="I102" s="42"/>
+      <c r="J102" s="43"/>
+      <c r="L102" s="102"/>
+    </row>
+    <row r="103" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="141" t="str">
+        <f t="shared" ref="A103:A130" si="17">RIGHT(D103,4)</f>
         <v>3986</v>
       </c>
-      <c r="B102" s="53" t="s">
+      <c r="B103" s="53" t="s">
         <v>79</v>
-      </c>
-      <c r="C102" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D102" s="51">
-        <v>1001061973986</v>
-      </c>
-      <c r="E102" s="24"/>
-      <c r="F102" s="128">
-        <v>0.25</v>
-      </c>
-      <c r="G102" s="23">
-        <f t="shared" ref="G102:G107" si="22">E102*F102</f>
-        <v>0</v>
-      </c>
-      <c r="H102" s="132">
-        <v>2</v>
-      </c>
-      <c r="I102" s="133">
-        <v>120</v>
-      </c>
-      <c r="J102" s="29"/>
-      <c r="L102" s="102"/>
-    </row>
-    <row r="103" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>5931</v>
-      </c>
-      <c r="B103" s="53" t="s">
-        <v>77</v>
       </c>
       <c r="C103" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D103" s="51">
-        <v>1001060755931</v>
+        <v>1001061973986</v>
       </c>
       <c r="E103" s="24"/>
-      <c r="F103" s="23">
-        <v>0.22</v>
+      <c r="F103" s="128">
+        <v>0.25</v>
       </c>
       <c r="G103" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G103:G108" si="18">E103*F103</f>
         <v>0</v>
       </c>
-      <c r="H103" s="97">
-        <v>1.76</v>
-      </c>
-      <c r="I103" s="14">
+      <c r="H103" s="132">
+        <v>2</v>
+      </c>
+      <c r="I103" s="133">
         <v>120</v>
       </c>
       <c r="J103" s="29"/>
       <c r="L103" s="102"/>
     </row>
     <row r="104" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>5708</v>
+      <c r="A104" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>5931</v>
       </c>
       <c r="B104" s="53" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C104" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D104" s="51">
-        <v>1001063145708</v>
+        <v>1001060755931</v>
       </c>
       <c r="E104" s="24"/>
       <c r="F104" s="23">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="G104" s="23">
-        <f t="shared" ref="G104:G105" si="23">E104</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="H104" s="14">
-        <v>4</v>
+      <c r="H104" s="97">
+        <v>1.76</v>
       </c>
       <c r="I104" s="14">
         <v>120</v>
@@ -11374,29 +11371,29 @@
       <c r="L104" s="102"/>
     </row>
     <row r="105" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>3287</v>
+      <c r="A105" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>5708</v>
       </c>
       <c r="B105" s="53" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C105" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D105" s="51">
-        <v>1001060763287</v>
+        <v>1001063145708</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G105" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G105:G106" si="19">E105</f>
         <v>0</v>
       </c>
       <c r="H105" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I105" s="14">
         <v>120</v>
@@ -11405,29 +11402,29 @@
       <c r="L105" s="102"/>
     </row>
     <row r="106" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>4993</v>
+      <c r="A106" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>3287</v>
       </c>
       <c r="B106" s="53" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="C106" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D106" s="51">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H106" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I106" s="14">
         <v>120</v>
@@ -11436,25 +11433,25 @@
       <c r="L106" s="102"/>
     </row>
     <row r="107" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>5483</v>
+      <c r="A107" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>4993</v>
       </c>
       <c r="B107" s="53" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="C107" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D107" s="51">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="23">
         <v>0.25</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H107" s="14">
@@ -11467,29 +11464,29 @@
       <c r="L107" s="102"/>
     </row>
     <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>4117</v>
+      <c r="A108" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>5483</v>
       </c>
       <c r="B108" s="53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C108" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D108" s="51">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G108" s="23">
-        <f t="shared" ref="G108:G109" si="24">E108</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H108" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I108" s="14">
         <v>120</v>
@@ -11498,29 +11495,29 @@
       <c r="L108" s="102"/>
     </row>
     <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>0614</v>
+      <c r="A109" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>4117</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="C109" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D109" s="51">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" si="24"/>
+        <f t="shared" ref="G109:G110" si="20">E109</f>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -11529,29 +11526,29 @@
       <c r="L109" s="102"/>
     </row>
     <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>6967</v>
+      <c r="A110" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>0614</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="C110" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D110" s="51">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" ref="G110:G119" si="25">E110*F110</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -11560,25 +11557,25 @@
       <c r="L110" s="102"/>
     </row>
     <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>6937</v>
+      <c r="A111" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>6967</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="C111" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D111" s="51">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
         <v>0.25</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G111:G120" si="21">E111*F111</f>
         <v>0</v>
       </c>
       <c r="H111" s="14">
@@ -11591,29 +11588,29 @@
       <c r="L111" s="102"/>
     </row>
     <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7143</v>
+      <c r="A112" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>6937</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C112" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="51">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H112" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I112" s="14">
         <v>120</v>
@@ -11622,25 +11619,25 @@
       <c r="L112" s="102"/>
     </row>
     <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7147</v>
+      <c r="A113" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7143</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C113" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="51">
-        <v>1001063237147</v>
+        <v>1001060717143</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
         <v>0.22</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
@@ -11653,60 +11650,60 @@
       <c r="L113" s="102"/>
     </row>
     <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7456</v>
+      <c r="A114" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7147</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D114" s="51">
-        <v>1001063097456</v>
+        <v>1001063237147</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I114" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J114" s="29"/>
       <c r="L114" s="102"/>
     </row>
     <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7364</v>
+      <c r="A115" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7456</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C115" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D115" s="51">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I115" s="14">
         <v>90</v>
@@ -11715,25 +11712,25 @@
       <c r="L115" s="102"/>
     </row>
     <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7383</v>
+      <c r="A116" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7364</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D116" s="51">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
         <v>0.22</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
@@ -11746,60 +11743,60 @@
       <c r="L116" s="102"/>
     </row>
     <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7317</v>
+      <c r="A117" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7383</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D117" s="51">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I117" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J117" s="29"/>
       <c r="L117" s="102"/>
     </row>
     <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7318</v>
+      <c r="A118" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7317</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D118" s="51">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I118" s="14">
         <v>120</v>
@@ -11808,29 +11805,29 @@
       <c r="L118" s="102"/>
     </row>
     <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7316</v>
+      <c r="A119" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7318</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="51">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I119" s="14">
         <v>120</v>
@@ -11839,56 +11836,56 @@
       <c r="L119" s="102"/>
     </row>
     <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>6832</v>
+      <c r="A120" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7316</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="C120" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D120" s="51">
-        <v>1001065616832</v>
+        <v>1001060727316</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.215</v>
+        <v>0.54</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" ref="G120:G121" si="26">E120</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="I120" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J120" s="29"/>
       <c r="L120" s="102"/>
     </row>
     <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7299</v>
+      <c r="A121" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>6832</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C121" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D121" s="51">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
         <v>0.215</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G121:G122" si="22">E121</f>
         <v>0</v>
       </c>
       <c r="H121" s="14">
@@ -11901,184 +11898,184 @@
       <c r="L121" s="102"/>
     </row>
     <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7386</v>
+      <c r="A122" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7299</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C122" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D122" s="51">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" ref="G122:G129" si="27">E122*F122</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H122" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I122" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J122" s="29"/>
       <c r="L122" s="102"/>
     </row>
     <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7613</v>
+      <c r="A123" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7386</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="C123" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D123" s="51">
-        <v>1001061977613</v>
+        <v>1001067017386</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" ref="G123:G130" si="23">E123*F123</f>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I123" s="14">
-        <v>60</v>
-      </c>
-      <c r="J123" s="52" t="s">
-        <v>203</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J123" s="29"/>
       <c r="L123" s="102"/>
     </row>
     <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7382</v>
+      <c r="A124" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7613</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D124" s="51">
-        <v>1001203117382</v>
+        <v>1001061977613</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I124" s="14">
         <v>60</v>
       </c>
-      <c r="J124" s="29"/>
+      <c r="J124" s="52" t="s">
+        <v>203</v>
+      </c>
       <c r="L124" s="102"/>
     </row>
     <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7616</v>
+      <c r="A125" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7382</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>204</v>
+        <v>84</v>
       </c>
       <c r="C125" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D125" s="51">
-        <v>1001062507616</v>
+        <v>1001203117382</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G125" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I125" s="14">
         <v>60</v>
       </c>
-      <c r="J125" s="52" t="s">
-        <v>205</v>
-      </c>
+      <c r="J125" s="29"/>
       <c r="L125" s="102"/>
     </row>
     <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>6221</v>
+      <c r="A126" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7616</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>86</v>
+        <v>204</v>
       </c>
       <c r="C126" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D126" s="51">
-        <v>1001205376221</v>
+        <v>1001062507616</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I126" s="14">
         <v>60</v>
       </c>
-      <c r="J126" s="29"/>
+      <c r="J126" s="52" t="s">
+        <v>205</v>
+      </c>
       <c r="L126" s="102"/>
     </row>
     <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>6222</v>
+      <c r="A127" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>6221</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="C127" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D127" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
         <v>0.09</v>
       </c>
       <c r="G127" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H127" s="14">
@@ -12091,29 +12088,29 @@
       <c r="L127" s="102"/>
     </row>
     <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>5679</v>
+      <c r="A128" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>6222</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D128" s="51">
-        <v>1001190765679</v>
+        <v>1001205386222</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G128" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I128" s="14">
         <v>60</v>
@@ -12121,54 +12118,68 @@
       <c r="J128" s="29"/>
       <c r="L128" s="102"/>
     </row>
-    <row r="129" spans="1:67" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="137" t="str">
-        <f t="shared" si="21"/>
-        <v>7626</v>
+    <row r="129" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>5679</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D129" s="51">
-        <v>1001066607626</v>
+        <v>1001190765679</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H129" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I129" s="14">
         <v>60</v>
       </c>
-      <c r="J129" s="52" t="s">
+      <c r="J129" s="29"/>
+      <c r="L129" s="102"/>
+    </row>
+    <row r="130" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="141" t="str">
+        <f t="shared" si="17"/>
+        <v>7626</v>
+      </c>
+      <c r="B130" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="C130" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D130" s="51">
+        <v>1001066607626</v>
+      </c>
+      <c r="E130" s="24"/>
+      <c r="F130" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G130" s="23">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="H130" s="14">
+        <v>1</v>
+      </c>
+      <c r="I130" s="14">
+        <v>60</v>
+      </c>
+      <c r="J130" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="L129" s="102"/>
-    </row>
-    <row r="130" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B130" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C130" s="42"/>
-      <c r="D130" s="42"/>
-      <c r="E130" s="42"/>
-      <c r="F130" s="41"/>
-      <c r="G130" s="42"/>
-      <c r="H130" s="42"/>
-      <c r="I130" s="42"/>
-      <c r="J130" s="43"/>
       <c r="K130" s="27"/>
       <c r="L130" s="102"/>
       <c r="M130" s="102"/>
@@ -12227,35 +12238,21 @@
       <c r="BN130" s="102"/>
       <c r="BO130" s="102"/>
     </row>
-    <row r="131" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="137" t="str">
-        <f t="shared" ref="A131:A145" si="28">RIGHT(D131,4)</f>
-        <v>4584</v>
-      </c>
-      <c r="B131" s="98" t="s">
-        <v>220</v>
-      </c>
-      <c r="C131" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D131" s="134">
-        <v>1001092674584</v>
-      </c>
-      <c r="E131" s="24"/>
-      <c r="F131" s="23">
-        <v>2.5</v>
-      </c>
-      <c r="G131" s="23">
-        <f>E131</f>
-        <v>0</v>
-      </c>
-      <c r="H131" s="14">
-        <v>7.5</v>
-      </c>
-      <c r="I131" s="14">
-        <v>60</v>
-      </c>
-      <c r="J131" s="29"/>
+    <row r="131" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B131" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C131" s="42"/>
+      <c r="D131" s="42"/>
+      <c r="E131" s="42"/>
+      <c r="F131" s="41"/>
+      <c r="G131" s="42"/>
+      <c r="H131" s="42"/>
+      <c r="I131" s="42"/>
+      <c r="J131" s="43"/>
       <c r="K131" s="27"/>
       <c r="L131" s="102"/>
       <c r="M131" s="102"/>
@@ -12314,33 +12311,33 @@
       <c r="BN131" s="102"/>
       <c r="BO131" s="102"/>
     </row>
-    <row r="132" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>6495</v>
+    <row r="132" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="141" t="str">
+        <f t="shared" ref="A132:A146" si="24">RIGHT(D132,4)</f>
+        <v>4584</v>
       </c>
       <c r="B132" s="98" t="s">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="C132" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D132" s="51">
-        <v>1001092436495</v>
+        <v>22</v>
+      </c>
+      <c r="D132" s="134">
+        <v>1001092674584</v>
       </c>
       <c r="E132" s="24"/>
-      <c r="F132" s="128">
-        <v>0.3</v>
+      <c r="F132" s="23">
+        <v>2.5</v>
       </c>
       <c r="G132" s="23">
-        <f>E132*F132</f>
+        <f>E132</f>
         <v>0</v>
       </c>
-      <c r="H132" s="29">
-        <v>1.8</v>
-      </c>
-      <c r="I132" s="29">
-        <v>45</v>
+      <c r="H132" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I132" s="14">
+        <v>60</v>
       </c>
       <c r="J132" s="29"/>
       <c r="K132" s="27"/>
@@ -12402,29 +12399,29 @@
       <c r="BO132" s="102"/>
     </row>
     <row r="133" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>6470</v>
-      </c>
-      <c r="B133" s="135" t="s">
-        <v>116</v>
+      <c r="A133" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>6495</v>
+      </c>
+      <c r="B133" s="98" t="s">
+        <v>95</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D133" s="51">
-        <v>1001092436470</v>
+        <v>1001092436495</v>
       </c>
       <c r="E133" s="24"/>
       <c r="F133" s="128">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G133" s="23">
-        <f t="shared" ref="G133:G134" si="29">E133</f>
+        <f>E133*F133</f>
         <v>0</v>
       </c>
       <c r="H133" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I133" s="29">
         <v>45</v>
@@ -12489,32 +12486,32 @@
       <c r="BO133" s="102"/>
     </row>
     <row r="134" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>5452</v>
+      <c r="A134" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>6470</v>
       </c>
       <c r="B134" s="135" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C134" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D134" s="51">
-        <v>1001092485452</v>
+        <v>1001092436470</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="128">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G134:G135" si="25">E134</f>
         <v>0</v>
       </c>
       <c r="H134" s="29">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="I134" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J134" s="29"/>
       <c r="K134" s="27"/>
@@ -12576,29 +12573,29 @@
       <c r="BO134" s="102"/>
     </row>
     <row r="135" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>3215</v>
+      <c r="A135" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>5452</v>
       </c>
       <c r="B135" s="135" t="s">
-        <v>215</v>
+        <v>93</v>
       </c>
       <c r="C135" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D135" s="51">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="128">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G135" s="23">
-        <f>E135*F135</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="H135" s="29">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I135" s="29">
         <v>60</v>
@@ -12663,29 +12660,29 @@
       <c r="BO135" s="102"/>
     </row>
     <row r="136" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>6866</v>
+      <c r="A136" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>3215</v>
       </c>
       <c r="B136" s="135" t="s">
-        <v>92</v>
+        <v>215</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D136" s="51">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="128">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G136" s="23">
-        <f>E136</f>
+        <f>E136*F136</f>
         <v>0</v>
       </c>
       <c r="H136" s="29">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I136" s="29">
         <v>60</v>
@@ -12750,29 +12747,29 @@
       <c r="BO136" s="102"/>
     </row>
     <row r="137" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>5495</v>
-      </c>
-      <c r="B137" s="53" t="s">
-        <v>94</v>
+      <c r="A137" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>6866</v>
+      </c>
+      <c r="B137" s="135" t="s">
+        <v>92</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D137" s="136">
-        <v>1001093345495</v>
+        <v>22</v>
+      </c>
+      <c r="D137" s="51">
+        <v>1001095716866</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="128">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G137" s="23">
-        <f t="shared" ref="G137:G140" si="30">E137*F137</f>
+        <f>E137</f>
         <v>0</v>
       </c>
       <c r="H137" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I137" s="29">
         <v>60</v>
@@ -12837,32 +12834,32 @@
       <c r="BO137" s="102"/>
     </row>
     <row r="138" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>7377</v>
+      <c r="A138" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>5495</v>
       </c>
       <c r="B138" s="53" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C138" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D138" s="136">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="128">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G138" s="23">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="G138:G141" si="26">E138*F138</f>
         <v>0</v>
       </c>
       <c r="H138" s="29">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I138" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J138" s="29"/>
       <c r="K138" s="27"/>
@@ -12924,29 +12921,33 @@
       <c r="BO138" s="102"/>
     </row>
     <row r="139" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>6411</v>
+      <c r="A139" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>7377</v>
       </c>
       <c r="B139" s="53" t="s">
-        <v>224</v>
+        <v>117</v>
       </c>
       <c r="C139" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D139" s="136">
-        <v>1001093316411</v>
+        <v>1001095027377</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="128">
         <v>0.3</v>
       </c>
       <c r="G139" s="23">
-        <f t="shared" ref="G139" si="31">E139*F139</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H139" s="29"/>
-      <c r="I139" s="29"/>
+      <c r="H139" s="29">
+        <v>1.8</v>
+      </c>
+      <c r="I139" s="29">
+        <v>45</v>
+      </c>
       <c r="J139" s="29"/>
       <c r="K139" s="27"/>
       <c r="L139" s="102"/>
@@ -13007,33 +13008,29 @@
       <c r="BO139" s="102"/>
     </row>
     <row r="140" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>6925</v>
+      <c r="A140" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>6411</v>
       </c>
       <c r="B140" s="53" t="s">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="C140" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D140" s="136">
-        <v>1001095226925</v>
+        <v>1001093316411</v>
       </c>
       <c r="E140" s="24"/>
       <c r="F140" s="128">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G140" s="23">
-        <f t="shared" si="30"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H140" s="29">
-        <v>4.8</v>
-      </c>
-      <c r="I140" s="29">
-        <v>45</v>
-      </c>
+      <c r="H140" s="29"/>
+      <c r="I140" s="29"/>
       <c r="J140" s="29"/>
       <c r="K140" s="27"/>
       <c r="L140" s="102"/>
@@ -13094,32 +13091,32 @@
       <c r="BO140" s="102"/>
     </row>
     <row r="141" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>6025</v>
+      <c r="A141" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>6925</v>
       </c>
       <c r="B141" s="53" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C141" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D141" s="136">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="128">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G141" s="23">
-        <f>E141</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H141" s="29">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I141" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J141" s="29"/>
       <c r="K141" s="27"/>
@@ -13181,27 +13178,33 @@
       <c r="BO141" s="102"/>
     </row>
     <row r="142" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>6929</v>
+      <c r="A142" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>6025</v>
       </c>
       <c r="B142" s="53" t="s">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="C142" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D142" s="136">
-        <v>1001085476929</v>
+        <v>1001094966025</v>
       </c>
       <c r="E142" s="24"/>
-      <c r="F142" s="128"/>
+      <c r="F142" s="128">
+        <v>3</v>
+      </c>
       <c r="G142" s="23">
         <f>E142</f>
         <v>0</v>
       </c>
-      <c r="H142" s="29"/>
-      <c r="I142" s="29"/>
+      <c r="H142" s="29">
+        <v>6</v>
+      </c>
+      <c r="I142" s="29">
+        <v>60</v>
+      </c>
       <c r="J142" s="29"/>
       <c r="K142" s="27"/>
       <c r="L142" s="102"/>
@@ -13262,80 +13265,72 @@
       <c r="BO142" s="102"/>
     </row>
     <row r="143" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>7485</v>
+      <c r="A143" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>6929</v>
       </c>
       <c r="B143" s="53" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C143" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D143" s="136">
-        <v>1001107397485</v>
+        <v>1001085476929</v>
       </c>
       <c r="E143" s="24"/>
-      <c r="F143" s="128">
-        <v>0.15</v>
-      </c>
+      <c r="F143" s="128"/>
       <c r="G143" s="23">
-        <f>F143*E143</f>
+        <f>E143</f>
         <v>0</v>
       </c>
       <c r="H143" s="29"/>
       <c r="I143" s="29"/>
-      <c r="J143" s="125" t="s">
-        <v>196</v>
-      </c>
+      <c r="J143" s="29"/>
       <c r="L143" s="102"/>
     </row>
     <row r="144" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>7647</v>
+      <c r="A144" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>7485</v>
       </c>
       <c r="B144" s="53" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C144" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D144" s="136">
-        <v>1001097747647</v>
+        <v>1001107397485</v>
       </c>
       <c r="E144" s="24"/>
       <c r="F144" s="128">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G144" s="23">
-        <f>E144*F144</f>
+        <f>F144*E144</f>
         <v>0</v>
       </c>
-      <c r="H144" s="29">
-        <v>1</v>
-      </c>
-      <c r="I144" s="29">
-        <v>30</v>
-      </c>
+      <c r="H144" s="29"/>
+      <c r="I144" s="29"/>
       <c r="J144" s="125" t="s">
         <v>196</v>
       </c>
       <c r="L144" s="102"/>
     </row>
-    <row r="145" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="137" t="str">
-        <f t="shared" si="28"/>
-        <v>7651</v>
+    <row r="145" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>7647</v>
       </c>
       <c r="B145" s="53" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C145" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D145" s="136">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="128">
@@ -13356,74 +13351,76 @@
       </c>
       <c r="L145" s="102"/>
     </row>
-    <row r="146" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="47" t="s">
+    <row r="146" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="141" t="str">
+        <f t="shared" si="24"/>
+        <v>7651</v>
+      </c>
+      <c r="B146" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="C146" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D146" s="136">
+        <v>1001097767651</v>
+      </c>
+      <c r="E146" s="24"/>
+      <c r="F146" s="128">
+        <v>0.1</v>
+      </c>
+      <c r="G146" s="23">
+        <f>E146*F146</f>
+        <v>0</v>
+      </c>
+      <c r="H146" s="29">
+        <v>1</v>
+      </c>
+      <c r="I146" s="29">
+        <v>30</v>
+      </c>
+      <c r="J146" s="125" t="s">
+        <v>196</v>
+      </c>
+      <c r="L146" s="102"/>
+    </row>
+    <row r="147" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B146" s="42" t="s">
+      <c r="B147" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="C146" s="42"/>
-      <c r="D146" s="42"/>
-      <c r="E146" s="42"/>
-      <c r="F146" s="41"/>
-      <c r="G146" s="42"/>
-      <c r="H146" s="42"/>
-      <c r="I146" s="42"/>
-      <c r="J146" s="43"/>
-      <c r="L146" s="102"/>
-    </row>
-    <row r="147" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="137" t="str">
-        <f t="shared" ref="A147:A158" si="32">RIGHT(D147,4)</f>
+      <c r="C147" s="42"/>
+      <c r="D147" s="42"/>
+      <c r="E147" s="42"/>
+      <c r="F147" s="41"/>
+      <c r="G147" s="42"/>
+      <c r="H147" s="42"/>
+      <c r="I147" s="42"/>
+      <c r="J147" s="43"/>
+      <c r="L147" s="102"/>
+    </row>
+    <row r="148" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="141" t="str">
+        <f t="shared" ref="A148:A159" si="27">RIGHT(D148,4)</f>
         <v>7090</v>
       </c>
-      <c r="B147" s="35" t="s">
+      <c r="B148" s="35" t="s">
         <v>100</v>
-      </c>
-      <c r="C147" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D147" s="51">
-        <v>1001084217090</v>
-      </c>
-      <c r="E147" s="24"/>
-      <c r="F147" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G147" s="23">
-        <f t="shared" ref="G147:G148" si="33">E147*F147</f>
-        <v>0</v>
-      </c>
-      <c r="H147" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I147" s="14">
-        <v>50</v>
-      </c>
-      <c r="J147" s="29"/>
-      <c r="L147" s="102"/>
-    </row>
-    <row r="148" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>7187</v>
-      </c>
-      <c r="B148" s="35" t="s">
-        <v>101</v>
       </c>
       <c r="C148" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D148" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E148" s="24"/>
       <c r="F148" s="23">
         <v>0.3</v>
       </c>
       <c r="G148" s="23">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="G148:G149" si="28">E148*F148</f>
         <v>0</v>
       </c>
       <c r="H148" s="14">
@@ -13436,124 +13433,124 @@
       <c r="L148" s="102"/>
     </row>
     <row r="149" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>6008</v>
+      <c r="A149" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>7187</v>
       </c>
       <c r="B149" s="35" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="C149" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D149" s="51">
-        <v>1001084856008</v>
+        <v>1001085637187</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="23">
         <v>0.3</v>
       </c>
       <c r="G149" s="23">
-        <f>E149</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="H149" s="14">
         <v>1.8</v>
       </c>
       <c r="I149" s="14">
-        <v>40</v>
-      </c>
-      <c r="J149" s="125" t="s">
-        <v>196</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J149" s="29"/>
       <c r="L149" s="102"/>
     </row>
     <row r="150" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>6620</v>
+      <c r="A150" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>6008</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="C150" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D150" s="51">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G150" s="23">
         <f>E150</f>
         <v>0</v>
       </c>
       <c r="H150" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I150" s="14">
-        <v>30</v>
-      </c>
-      <c r="J150" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J150" s="125" t="s">
+        <v>196</v>
+      </c>
       <c r="L150" s="102"/>
     </row>
     <row r="151" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>7103</v>
+      <c r="A151" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>6620</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="C151" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D151" s="51">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="23">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G151" s="23">
-        <f t="shared" ref="G151:G158" si="34">E151*F151</f>
+        <f>E151</f>
         <v>0</v>
       </c>
       <c r="H151" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I151" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J151" s="29"/>
       <c r="L151" s="102"/>
     </row>
     <row r="152" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>7092</v>
+      <c r="A152" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>7103</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="C152" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D152" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G152" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="G152:G159" si="29">E152*F152</f>
         <v>0</v>
       </c>
       <c r="H152" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I152" s="14">
         <v>50</v>
@@ -13562,60 +13559,60 @@
       <c r="L152" s="102"/>
     </row>
     <row r="153" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>6228</v>
+      <c r="A153" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>7092</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C153" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D153" s="51">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G153" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H153" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I153" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J153" s="29"/>
       <c r="L153" s="102"/>
     </row>
     <row r="154" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>6448</v>
+      <c r="A154" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>6228</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="C154" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D154" s="51">
-        <v>1001234146448</v>
+        <v>1001225416228</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G154" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I154" s="14">
         <v>45</v>
@@ -13624,29 +13621,29 @@
       <c r="L154" s="102"/>
     </row>
     <row r="155" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>6208</v>
+      <c r="A155" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>6448</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C155" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D155" s="51">
-        <v>1001220226208</v>
+        <v>1001234146448</v>
       </c>
       <c r="E155" s="24"/>
       <c r="F155" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G155" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H155" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I155" s="14">
         <v>45</v>
@@ -13655,128 +13652,148 @@
       <c r="L155" s="102"/>
     </row>
     <row r="156" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>6754</v>
+      <c r="A156" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>6208</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D156" s="51">
-        <v>1001225406754</v>
+        <v>1001220226208</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G156" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H156" s="14">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="I156" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J156" s="29"/>
     </row>
     <row r="157" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>6279</v>
+      <c r="A157" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>6754</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>98</v>
+        <v>222</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D157" s="51">
-        <v>1001220286279</v>
+        <v>1001225406754</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="34"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="I157" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J157" s="29"/>
     </row>
-    <row r="158" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="137" t="str">
-        <f t="shared" si="32"/>
-        <v>7612</v>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>6279</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D158" s="51">
-        <v>1001453907612</v>
+        <v>1001220286279</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G158" s="23">
+        <f t="shared" si="29"/>
+        <v>0</v>
+      </c>
+      <c r="H158" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I158" s="14">
+        <v>45</v>
+      </c>
+      <c r="J158" s="29"/>
+    </row>
+    <row r="159" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="141" t="str">
+        <f t="shared" si="27"/>
+        <v>7612</v>
+      </c>
+      <c r="B159" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="C159" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D159" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E159" s="24"/>
+      <c r="F159" s="23">
         <v>0.1</v>
       </c>
-      <c r="G158" s="23">
-        <f t="shared" si="34"/>
+      <c r="G159" s="23">
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H158" s="14">
+      <c r="H159" s="14">
         <v>1</v>
       </c>
-      <c r="I158" s="14">
+      <c r="I159" s="14">
         <v>60</v>
       </c>
-      <c r="J158" s="52" t="s">
+      <c r="J159" s="52" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="48"/>
-      <c r="B159" s="45" t="s">
+    <row r="160" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="48"/>
+      <c r="B160" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C159" s="16"/>
-      <c r="D159" s="36"/>
-      <c r="E159" s="17">
-        <f>SUM(E10:E158)</f>
+      <c r="C160" s="16"/>
+      <c r="D160" s="36"/>
+      <c r="E160" s="17">
+        <f>SUM(E10:E159)</f>
         <v>0</v>
       </c>
-      <c r="F159" s="17"/>
-      <c r="G159" s="17">
-        <f>SUM(G11:G158)</f>
+      <c r="F160" s="17"/>
+      <c r="G160" s="17">
+        <f>SUM(G11:G159)</f>
         <v>0</v>
       </c>
-      <c r="H159" s="17"/>
-      <c r="I159" s="17"/>
-      <c r="J159" s="17"/>
-    </row>
-    <row r="160" spans="1:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="37"/>
-      <c r="C160" s="18"/>
-      <c r="D160" s="40"/>
-      <c r="F160" s="19"/>
-      <c r="G160" s="19"/>
-      <c r="H160" s="20"/>
-      <c r="I160" s="20"/>
-      <c r="J160" s="21"/>
-    </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H160" s="17"/>
+      <c r="I160" s="17"/>
+      <c r="J160" s="17"/>
+    </row>
+    <row r="161" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B161" s="37"/>
       <c r="C161" s="18"/>
       <c r="D161" s="40"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/чистый бланк/Заказ ЛП_дата_город.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7076BB99-B156-45AB-A732-9B896CB71E8B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742C676A-5F93-46E2-B08F-34C4A5C8892D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,9 +17,9 @@
     <sheet name="Лист1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$159</definedName>
-    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$592</definedName>
-    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$592</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Бланк!$A$9:$J$160</definedName>
+    <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$595</definedName>
+    <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$595</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -332,7 +332,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="236">
   <si>
     <t xml:space="preserve">Грузополучатель: </t>
   </si>
@@ -1031,6 +1031,15 @@
   </si>
   <si>
     <t>КРАКОВСКАЯ ГОСТ Останкино п/к н/о мгс</t>
+  </si>
+  <si>
+    <t>КРАКОВСКАЯ ГОСТ п/к н/о мгс 0.3кг</t>
+  </si>
+  <si>
+    <t>КОНСЕРВЫ МЯС.ГОВЯДИНА ТУШ. В/С 338г_ЧЗ</t>
+  </si>
+  <si>
+    <t>КОНСЕРВЫ МЯС.СВИНИНА ТУШ. В/С 325г_ЧЗ</t>
   </si>
 </sst>
 </file>
@@ -1969,6 +1978,9 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1976,9 +1988,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="165" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6240,7 +6249,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BO1680"/>
+  <dimension ref="A1:BO1683"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4" customWidth="1"/>
@@ -6265,14 +6274,14 @@
       <c r="D1" s="127">
         <v>130438644</v>
       </c>
-      <c r="E1" s="137" t="s">
+      <c r="E1" s="138" t="s">
         <v>209</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="140"/>
       <c r="K1" s="103">
         <v>130438384</v>
       </c>
@@ -6303,12 +6312,12 @@
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="140" t="s">
+      <c r="G3" s="141" t="s">
         <v>210</v>
       </c>
-      <c r="H3" s="138"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="139"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="139"/>
+      <c r="J3" s="140"/>
       <c r="K3" s="103">
         <v>130439106</v>
       </c>
@@ -6481,7 +6490,7 @@
       <c r="J10" s="43"/>
     </row>
     <row r="11" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="141" t="str">
+      <c r="A11" s="137" t="str">
         <f>RIGHT(D11,4)</f>
         <v>7523</v>
       </c>
@@ -6570,7 +6579,7 @@
       <c r="BO11" s="101"/>
     </row>
     <row r="12" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="141" t="str">
+      <c r="A12" s="137" t="str">
         <f t="shared" ref="A12:A72" si="1">RIGHT(D12,4)</f>
         <v>6220</v>
       </c>
@@ -6657,7 +6666,7 @@
       <c r="BO12" s="101"/>
     </row>
     <row r="13" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="141" t="str">
+      <c r="A13" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7539</v>
       </c>
@@ -6746,7 +6755,7 @@
       <c r="BO13" s="101"/>
     </row>
     <row r="14" spans="1:67" s="15" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="141" t="str">
+      <c r="A14" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7536</v>
       </c>
@@ -6835,7 +6844,7 @@
       <c r="BO14" s="101"/>
     </row>
     <row r="15" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="141" t="str">
+      <c r="A15" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6861</v>
       </c>
@@ -6904,7 +6913,7 @@
       <c r="AX15" s="102"/>
     </row>
     <row r="16" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="141" t="str">
+      <c r="A16" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6862</v>
       </c>
@@ -6935,7 +6944,7 @@
       <c r="L16" s="102"/>
     </row>
     <row r="17" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="141" t="str">
+      <c r="A17" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6498</v>
       </c>
@@ -6966,7 +6975,7 @@
       <c r="L17" s="102"/>
     </row>
     <row r="18" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="141" t="str">
+      <c r="A18" s="137" t="str">
         <f t="shared" si="1"/>
         <v>4063</v>
       </c>
@@ -6997,7 +7006,7 @@
       <c r="L18" s="102"/>
     </row>
     <row r="19" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="141" t="str">
+      <c r="A19" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6333</v>
       </c>
@@ -7028,7 +7037,7 @@
       <c r="L19" s="102"/>
     </row>
     <row r="20" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="141" t="str">
+      <c r="A20" s="137" t="str">
         <f t="shared" si="1"/>
         <v>4574</v>
       </c>
@@ -7059,7 +7068,7 @@
       <c r="L20" s="102"/>
     </row>
     <row r="21" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="141" t="str">
+      <c r="A21" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7334</v>
       </c>
@@ -7090,7 +7099,7 @@
       <c r="L21" s="102"/>
     </row>
     <row r="22" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="141" t="str">
+      <c r="A22" s="137" t="str">
         <f t="shared" si="1"/>
         <v>4813</v>
       </c>
@@ -7177,7 +7186,7 @@
       <c r="BO22" s="102"/>
     </row>
     <row r="23" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="141" t="str">
+      <c r="A23" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6392</v>
       </c>
@@ -7264,7 +7273,7 @@
       <c r="BO23" s="102"/>
     </row>
     <row r="24" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="141" t="str">
+      <c r="A24" s="137" t="str">
         <f t="shared" si="1"/>
         <v>5851</v>
       </c>
@@ -7351,7 +7360,7 @@
       <c r="BO24" s="102"/>
     </row>
     <row r="25" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="141" t="str">
+      <c r="A25" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7632</v>
       </c>
@@ -7384,7 +7393,7 @@
       <c r="L25" s="102"/>
     </row>
     <row r="26" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="141" t="str">
+      <c r="A26" s="137" t="str">
         <f t="shared" si="1"/>
         <v>4561</v>
       </c>
@@ -7415,7 +7424,7 @@
       <c r="L26" s="102"/>
     </row>
     <row r="27" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="141" t="str">
+      <c r="A27" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6325</v>
       </c>
@@ -7446,7 +7455,7 @@
       <c r="L27" s="102"/>
     </row>
     <row r="28" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="141" t="str">
+      <c r="A28" s="137" t="str">
         <f t="shared" si="1"/>
         <v>8014</v>
       </c>
@@ -7533,7 +7542,7 @@
       <c r="BO28" s="102"/>
     </row>
     <row r="29" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="141" t="str">
+      <c r="A29" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7514</v>
       </c>
@@ -7614,7 +7623,7 @@
       <c r="BO29" s="102"/>
     </row>
     <row r="30" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="141" t="str">
+      <c r="A30" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7518</v>
       </c>
@@ -7695,7 +7704,7 @@
       <c r="BO30" s="102"/>
     </row>
     <row r="31" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="141" t="str">
+      <c r="A31" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7343</v>
       </c>
@@ -7782,7 +7791,7 @@
       <c r="BO31" s="102"/>
     </row>
     <row r="32" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="141" t="str">
+      <c r="A32" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6797</v>
       </c>
@@ -7813,7 +7822,7 @@
       <c r="L32" s="102"/>
     </row>
     <row r="33" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="141" t="str">
+      <c r="A33" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7231</v>
       </c>
@@ -7973,7 +7982,7 @@
       <c r="BO34" s="102"/>
     </row>
     <row r="35" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="141" t="str">
+      <c r="A35" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6602</v>
       </c>
@@ -8060,7 +8069,7 @@
       <c r="BO35" s="102"/>
     </row>
     <row r="36" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="141" t="str">
+      <c r="A36" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7601</v>
       </c>
@@ -8147,7 +8156,7 @@
       <c r="BO36" s="102"/>
     </row>
     <row r="37" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="141" t="str">
+      <c r="A37" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7461</v>
       </c>
@@ -8236,7 +8245,7 @@
       <c r="BO37" s="102"/>
     </row>
     <row r="38" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="141" t="str">
+      <c r="A38" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7040</v>
       </c>
@@ -8321,7 +8330,7 @@
       <c r="BO38" s="102"/>
     </row>
     <row r="39" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="141" t="str">
+      <c r="A39" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6759</v>
       </c>
@@ -8408,7 +8417,7 @@
       <c r="BO39" s="102"/>
     </row>
     <row r="40" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="141" t="str">
+      <c r="A40" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6761</v>
       </c>
@@ -8495,7 +8504,7 @@
       <c r="BO40" s="102"/>
     </row>
     <row r="41" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="141" t="str">
+      <c r="A41" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6829</v>
       </c>
@@ -8582,7 +8591,7 @@
       <c r="BO41" s="102"/>
     </row>
     <row r="42" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="141" t="str">
+      <c r="A42" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6616</v>
       </c>
@@ -8669,7 +8678,7 @@
       <c r="BO42" s="102"/>
     </row>
     <row r="43" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="141" t="str">
+      <c r="A43" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7075</v>
       </c>
@@ -8756,7 +8765,7 @@
       <c r="BO43" s="102"/>
     </row>
     <row r="44" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="141" t="str">
+      <c r="A44" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7074</v>
       </c>
@@ -8843,7 +8852,7 @@
       <c r="BO44" s="102"/>
     </row>
     <row r="45" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="141" t="str">
+      <c r="A45" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7073</v>
       </c>
@@ -8930,7 +8939,7 @@
       <c r="BO45" s="102"/>
     </row>
     <row r="46" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="141" t="str">
+      <c r="A46" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6724</v>
       </c>
@@ -9017,7 +9026,7 @@
       <c r="BO46" s="102"/>
     </row>
     <row r="47" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="141" t="str">
+      <c r="A47" s="137" t="str">
         <f t="shared" si="1"/>
         <v>5819</v>
       </c>
@@ -9104,7 +9113,7 @@
       <c r="BO47" s="102"/>
     </row>
     <row r="48" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="141" t="str">
+      <c r="A48" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6303</v>
       </c>
@@ -9191,7 +9200,7 @@
       <c r="BO48" s="102"/>
     </row>
     <row r="49" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="141" t="str">
+      <c r="A49" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7255</v>
       </c>
@@ -9278,7 +9287,7 @@
       <c r="BO49" s="102"/>
     </row>
     <row r="50" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="141" t="str">
+      <c r="A50" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7271</v>
       </c>
@@ -9365,7 +9374,7 @@
       <c r="BO50" s="102"/>
     </row>
     <row r="51" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="141" t="str">
+      <c r="A51" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6765</v>
       </c>
@@ -9452,7 +9461,7 @@
       <c r="BO51" s="102"/>
     </row>
     <row r="52" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="141" t="str">
+      <c r="A52" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6767</v>
       </c>
@@ -9539,7 +9548,7 @@
       <c r="BO52" s="102"/>
     </row>
     <row r="53" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="141" t="str">
+      <c r="A53" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6475</v>
       </c>
@@ -9626,7 +9635,7 @@
       <c r="BO53" s="102"/>
     </row>
     <row r="54" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="141" t="str">
+      <c r="A54" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7083</v>
       </c>
@@ -9713,7 +9722,7 @@
       <c r="BO54" s="102"/>
     </row>
     <row r="55" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="141" t="str">
+      <c r="A55" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7080</v>
       </c>
@@ -9800,7 +9809,7 @@
       <c r="BO55" s="102"/>
     </row>
     <row r="56" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="141" t="str">
+      <c r="A56" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7276</v>
       </c>
@@ -9831,7 +9840,7 @@
       <c r="L56" s="102"/>
     </row>
     <row r="57" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="141" t="str">
+      <c r="A57" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6762</v>
       </c>
@@ -9862,7 +9871,7 @@
       <c r="L57" s="102"/>
     </row>
     <row r="58" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="141" t="str">
+      <c r="A58" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6764</v>
       </c>
@@ -9893,7 +9902,7 @@
       <c r="L58" s="102"/>
     </row>
     <row r="59" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="141" t="str">
+      <c r="A59" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7066</v>
       </c>
@@ -9924,7 +9933,7 @@
       <c r="L59" s="102"/>
     </row>
     <row r="60" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="141" t="str">
+      <c r="A60" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7070</v>
       </c>
@@ -9955,7 +9964,7 @@
       <c r="L60" s="102"/>
     </row>
     <row r="61" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="141" t="str">
+      <c r="A61" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6713</v>
       </c>
@@ -9986,7 +9995,7 @@
       <c r="L61" s="102"/>
     </row>
     <row r="62" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="141" t="str">
+      <c r="A62" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6661</v>
       </c>
@@ -10017,7 +10026,7 @@
       <c r="L62" s="102"/>
     </row>
     <row r="63" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="141" t="str">
+      <c r="A63" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6254</v>
       </c>
@@ -10048,7 +10057,7 @@
       <c r="L63" s="102"/>
     </row>
     <row r="64" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="141" t="str">
+      <c r="A64" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6837</v>
       </c>
@@ -10079,7 +10088,7 @@
       <c r="L64" s="102"/>
     </row>
     <row r="65" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="141" t="str">
+      <c r="A65" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7044</v>
       </c>
@@ -10127,7 +10136,7 @@
       <c r="L66" s="102"/>
     </row>
     <row r="67" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="141" t="str">
+      <c r="A67" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6550</v>
       </c>
@@ -10158,7 +10167,7 @@
       <c r="L67" s="102"/>
     </row>
     <row r="68" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="141" t="str">
+      <c r="A68" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6608</v>
       </c>
@@ -10189,7 +10198,7 @@
       <c r="L68" s="102"/>
     </row>
     <row r="69" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="141" t="str">
+      <c r="A69" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7001</v>
       </c>
@@ -10220,7 +10229,7 @@
       <c r="L69" s="102"/>
     </row>
     <row r="70" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="141" t="str">
+      <c r="A70" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6527</v>
       </c>
@@ -10251,7 +10260,7 @@
       <c r="L70" s="102"/>
     </row>
     <row r="71" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="141" t="str">
+      <c r="A71" s="137" t="str">
         <f t="shared" si="1"/>
         <v>6609</v>
       </c>
@@ -10282,7 +10291,7 @@
       <c r="L71" s="102"/>
     </row>
     <row r="72" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="141" t="str">
+      <c r="A72" s="137" t="str">
         <f t="shared" si="1"/>
         <v>7059</v>
       </c>
@@ -10330,8 +10339,8 @@
       <c r="L73" s="102"/>
     </row>
     <row r="74" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="141" t="str">
-        <f t="shared" ref="A74:A101" si="14">RIGHT(D74,4)</f>
+      <c r="A74" s="137" t="str">
+        <f t="shared" ref="A74:A102" si="14">RIGHT(D74,4)</f>
         <v>7564</v>
       </c>
       <c r="B74" s="53" t="s">
@@ -10363,7 +10372,7 @@
       <c r="L74" s="102"/>
     </row>
     <row r="75" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="141" t="str">
+      <c r="A75" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7603</v>
       </c>
@@ -10396,7 +10405,7 @@
       <c r="L75" s="102"/>
     </row>
     <row r="76" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="141" t="str">
+      <c r="A76" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7149</v>
       </c>
@@ -10427,7 +10436,7 @@
       <c r="L76" s="102"/>
     </row>
     <row r="77" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="141" t="str">
+      <c r="A77" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7233</v>
       </c>
@@ -10458,7 +10467,7 @@
       <c r="L77" s="102"/>
     </row>
     <row r="78" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="141" t="str">
+      <c r="A78" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7232</v>
       </c>
@@ -10489,7 +10498,7 @@
       <c r="L78" s="102"/>
     </row>
     <row r="79" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="141" t="str">
+      <c r="A79" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7241</v>
       </c>
@@ -10520,7 +10529,7 @@
       <c r="L79" s="102"/>
     </row>
     <row r="80" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="141" t="str">
+      <c r="A80" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7133</v>
       </c>
@@ -10551,7 +10560,7 @@
       <c r="L80" s="102"/>
     </row>
     <row r="81" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="141" t="str">
+      <c r="A81" s="137" t="str">
         <f t="shared" si="14"/>
         <v>6946</v>
       </c>
@@ -10576,7 +10585,7 @@
       <c r="L81" s="102"/>
     </row>
     <row r="82" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="141" t="str">
+      <c r="A82" s="137" t="str">
         <f t="shared" si="14"/>
         <v>6807</v>
       </c>
@@ -10607,7 +10616,7 @@
       <c r="L82" s="102"/>
     </row>
     <row r="83" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="141" t="str">
+      <c r="A83" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7154</v>
       </c>
@@ -10638,7 +10647,7 @@
       <c r="L83" s="102"/>
     </row>
     <row r="84" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="141" t="str">
+      <c r="A84" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7157</v>
       </c>
@@ -10669,7 +10678,7 @@
       <c r="L84" s="102"/>
     </row>
     <row r="85" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="141" t="str">
+      <c r="A85" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7562</v>
       </c>
@@ -10694,7 +10703,7 @@
       <c r="L85" s="102"/>
     </row>
     <row r="86" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="141" t="str">
+      <c r="A86" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7236</v>
       </c>
@@ -10725,7 +10734,7 @@
       <c r="L86" s="102"/>
     </row>
     <row r="87" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="141" t="str">
+      <c r="A87" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7489</v>
       </c>
@@ -10754,7 +10763,7 @@
       <c r="L87" s="102"/>
     </row>
     <row r="88" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="141" t="str">
+      <c r="A88" s="137" t="str">
         <f t="shared" si="14"/>
         <v>6787</v>
       </c>
@@ -10785,7 +10794,7 @@
       <c r="L88" s="102"/>
     </row>
     <row r="89" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="141" t="str">
+      <c r="A89" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7166</v>
       </c>
@@ -10816,7 +10825,7 @@
       <c r="L89" s="102"/>
     </row>
     <row r="90" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="141" t="str">
+      <c r="A90" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7169</v>
       </c>
@@ -10847,7 +10856,7 @@
       <c r="L90" s="102"/>
     </row>
     <row r="91" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="141" t="str">
+      <c r="A91" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7156</v>
       </c>
@@ -10874,7 +10883,7 @@
       <c r="L91" s="102"/>
     </row>
     <row r="92" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="141" t="str">
+      <c r="A92" s="137" t="str">
         <f t="shared" si="14"/>
         <v>5544</v>
       </c>
@@ -10905,7 +10914,7 @@
       <c r="L92" s="102"/>
     </row>
     <row r="93" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="141" t="str">
+      <c r="A93" s="137" t="str">
         <f t="shared" si="14"/>
         <v>6697</v>
       </c>
@@ -10923,7 +10932,7 @@
         <v>0.35</v>
       </c>
       <c r="G93" s="23">
-        <f t="shared" ref="G93:G101" si="16">E93*F93</f>
+        <f t="shared" ref="G93:G102" si="16">E93*F93</f>
         <v>0</v>
       </c>
       <c r="H93" s="14">
@@ -10936,7 +10945,7 @@
       <c r="L93" s="102"/>
     </row>
     <row r="94" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="141" t="str">
+      <c r="A94" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7238</v>
       </c>
@@ -10967,7 +10976,7 @@
       <c r="L94" s="102"/>
     </row>
     <row r="95" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="141" t="str">
+      <c r="A95" s="137" t="str">
         <f t="shared" si="14"/>
         <v>7516</v>
       </c>
@@ -10994,25 +11003,25 @@
       <c r="L95" s="102"/>
     </row>
     <row r="96" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="141" t="str">
+      <c r="A96" s="137" t="str">
         <f t="shared" si="14"/>
-        <v>7513</v>
+        <v>7710</v>
       </c>
       <c r="B96" s="53" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C96" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D96" s="51">
-        <v>1001307077513</v>
+        <v>1001307587710</v>
       </c>
       <c r="E96" s="24"/>
       <c r="F96" s="23">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="G96" s="23">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="G96" si="17">E96*F96</f>
         <v>0</v>
       </c>
       <c r="H96" s="14"/>
@@ -11021,60 +11030,56 @@
       <c r="L96" s="102"/>
     </row>
     <row r="97" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="141" t="str">
+      <c r="A97" s="137" t="str">
         <f t="shared" si="14"/>
-        <v>7177</v>
+        <v>7513</v>
       </c>
       <c r="B97" s="53" t="s">
-        <v>124</v>
+        <v>230</v>
       </c>
       <c r="C97" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D97" s="51">
-        <v>1001302347177</v>
+        <v>1001307077513</v>
       </c>
       <c r="E97" s="24"/>
       <c r="F97" s="23">
-        <v>0.35</v>
+        <v>0.26</v>
       </c>
       <c r="G97" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="H97" s="14">
-        <v>2.8</v>
-      </c>
-      <c r="I97" s="14">
-        <v>50</v>
-      </c>
+      <c r="H97" s="14"/>
+      <c r="I97" s="14"/>
       <c r="J97" s="49"/>
       <c r="L97" s="102"/>
     </row>
     <row r="98" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="141" t="str">
+      <c r="A98" s="137" t="str">
         <f t="shared" si="14"/>
-        <v>7332</v>
+        <v>7177</v>
       </c>
       <c r="B98" s="53" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="C98" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D98" s="51">
-        <v>1001301777332</v>
+        <v>1001302347177</v>
       </c>
       <c r="E98" s="24"/>
       <c r="F98" s="23">
-        <v>0.28000000000000003</v>
+        <v>0.35</v>
       </c>
       <c r="G98" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H98" s="14">
-        <v>2.2400000000000002</v>
+        <v>2.8</v>
       </c>
       <c r="I98" s="14">
         <v>50</v>
@@ -11083,18 +11088,18 @@
       <c r="L98" s="102"/>
     </row>
     <row r="99" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="141" t="str">
+      <c r="A99" s="137" t="str">
         <f t="shared" si="14"/>
-        <v>7333</v>
+        <v>7332</v>
       </c>
       <c r="B99" s="53" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C99" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D99" s="51">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="E99" s="24"/>
       <c r="F99" s="23">
@@ -11113,108 +11118,50 @@
       <c r="J99" s="49"/>
       <c r="L99" s="102"/>
     </row>
-    <row r="100" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="141" t="str">
+    <row r="100" spans="1:67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="137" t="str">
         <f t="shared" si="14"/>
-        <v>7608</v>
+        <v>7333</v>
       </c>
       <c r="B100" s="53" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="C100" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D100" s="51">
-        <v>1001304197608</v>
+        <v>1001303987333</v>
       </c>
       <c r="E100" s="24"/>
       <c r="F100" s="23">
-        <v>0.1</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G100" s="23">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="H100" s="14">
-        <v>1</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="I100" s="14">
-        <v>45</v>
-      </c>
-      <c r="J100" s="52" t="s">
-        <v>206</v>
-      </c>
-      <c r="K100" s="27"/>
+        <v>50</v>
+      </c>
+      <c r="J100" s="49"/>
       <c r="L100" s="102"/>
-      <c r="M100" s="102"/>
-      <c r="N100" s="102"/>
-      <c r="O100" s="102"/>
-      <c r="P100" s="102"/>
-      <c r="Q100" s="102"/>
-      <c r="R100" s="102"/>
-      <c r="S100" s="102"/>
-      <c r="T100" s="102"/>
-      <c r="U100" s="102"/>
-      <c r="V100" s="102"/>
-      <c r="W100" s="102"/>
-      <c r="X100" s="102"/>
-      <c r="Y100" s="102"/>
-      <c r="Z100" s="102"/>
-      <c r="AA100" s="102"/>
-      <c r="AB100" s="102"/>
-      <c r="AC100" s="102"/>
-      <c r="AD100" s="102"/>
-      <c r="AE100" s="102"/>
-      <c r="AF100" s="102"/>
-      <c r="AG100" s="102"/>
-      <c r="AH100" s="102"/>
-      <c r="AI100" s="102"/>
-      <c r="AJ100" s="102"/>
-      <c r="AK100" s="102"/>
-      <c r="AL100" s="102"/>
-      <c r="AM100" s="102"/>
-      <c r="AN100" s="102"/>
-      <c r="AO100" s="102"/>
-      <c r="AP100" s="102"/>
-      <c r="AQ100" s="102"/>
-      <c r="AR100" s="102"/>
-      <c r="AS100" s="102"/>
-      <c r="AT100" s="102"/>
-      <c r="AU100" s="102"/>
-      <c r="AV100" s="102"/>
-      <c r="AW100" s="102"/>
-      <c r="AX100" s="102"/>
-      <c r="AY100" s="102"/>
-      <c r="AZ100" s="102"/>
-      <c r="BA100" s="102"/>
-      <c r="BB100" s="102"/>
-      <c r="BC100" s="102"/>
-      <c r="BD100" s="102"/>
-      <c r="BE100" s="102"/>
-      <c r="BF100" s="102"/>
-      <c r="BG100" s="102"/>
-      <c r="BH100" s="102"/>
-      <c r="BI100" s="102"/>
-      <c r="BJ100" s="102"/>
-      <c r="BK100" s="102"/>
-      <c r="BL100" s="102"/>
-      <c r="BM100" s="102"/>
-      <c r="BN100" s="102"/>
-      <c r="BO100" s="102"/>
-    </row>
-    <row r="101" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="141" t="str">
+    </row>
+    <row r="101" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="137" t="str">
         <f t="shared" si="14"/>
-        <v>7610</v>
+        <v>7608</v>
       </c>
       <c r="B101" s="53" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C101" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D101" s="51">
-        <v>1001306717610</v>
+        <v>1001304197608</v>
       </c>
       <c r="E101" s="24"/>
       <c r="F101" s="23">
@@ -11231,7 +11178,7 @@
         <v>45</v>
       </c>
       <c r="J101" s="52" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K101" s="27"/>
       <c r="L101" s="102"/>
@@ -11291,109 +11238,167 @@
       <c r="BN101" s="102"/>
       <c r="BO101" s="102"/>
     </row>
-    <row r="102" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="47" t="s">
+    <row r="102" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="137" t="str">
+        <f t="shared" si="14"/>
+        <v>7610</v>
+      </c>
+      <c r="B102" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="C102" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" s="51">
+        <v>1001306717610</v>
+      </c>
+      <c r="E102" s="24"/>
+      <c r="F102" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G102" s="23">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="H102" s="14">
+        <v>1</v>
+      </c>
+      <c r="I102" s="14">
+        <v>45</v>
+      </c>
+      <c r="J102" s="52" t="s">
+        <v>208</v>
+      </c>
+      <c r="K102" s="27"/>
+      <c r="L102" s="102"/>
+      <c r="M102" s="102"/>
+      <c r="N102" s="102"/>
+      <c r="O102" s="102"/>
+      <c r="P102" s="102"/>
+      <c r="Q102" s="102"/>
+      <c r="R102" s="102"/>
+      <c r="S102" s="102"/>
+      <c r="T102" s="102"/>
+      <c r="U102" s="102"/>
+      <c r="V102" s="102"/>
+      <c r="W102" s="102"/>
+      <c r="X102" s="102"/>
+      <c r="Y102" s="102"/>
+      <c r="Z102" s="102"/>
+      <c r="AA102" s="102"/>
+      <c r="AB102" s="102"/>
+      <c r="AC102" s="102"/>
+      <c r="AD102" s="102"/>
+      <c r="AE102" s="102"/>
+      <c r="AF102" s="102"/>
+      <c r="AG102" s="102"/>
+      <c r="AH102" s="102"/>
+      <c r="AI102" s="102"/>
+      <c r="AJ102" s="102"/>
+      <c r="AK102" s="102"/>
+      <c r="AL102" s="102"/>
+      <c r="AM102" s="102"/>
+      <c r="AN102" s="102"/>
+      <c r="AO102" s="102"/>
+      <c r="AP102" s="102"/>
+      <c r="AQ102" s="102"/>
+      <c r="AR102" s="102"/>
+      <c r="AS102" s="102"/>
+      <c r="AT102" s="102"/>
+      <c r="AU102" s="102"/>
+      <c r="AV102" s="102"/>
+      <c r="AW102" s="102"/>
+      <c r="AX102" s="102"/>
+      <c r="AY102" s="102"/>
+      <c r="AZ102" s="102"/>
+      <c r="BA102" s="102"/>
+      <c r="BB102" s="102"/>
+      <c r="BC102" s="102"/>
+      <c r="BD102" s="102"/>
+      <c r="BE102" s="102"/>
+      <c r="BF102" s="102"/>
+      <c r="BG102" s="102"/>
+      <c r="BH102" s="102"/>
+      <c r="BI102" s="102"/>
+      <c r="BJ102" s="102"/>
+      <c r="BK102" s="102"/>
+      <c r="BL102" s="102"/>
+      <c r="BM102" s="102"/>
+      <c r="BN102" s="102"/>
+      <c r="BO102" s="102"/>
+    </row>
+    <row r="103" spans="1:67" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B102" s="42" t="s">
+      <c r="B103" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="C102" s="42"/>
-      <c r="D102" s="42"/>
-      <c r="E102" s="42"/>
-      <c r="F102" s="41"/>
-      <c r="G102" s="42"/>
-      <c r="H102" s="42"/>
-      <c r="I102" s="42"/>
-      <c r="J102" s="43"/>
-      <c r="L102" s="102"/>
-    </row>
-    <row r="103" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="141" t="str">
-        <f t="shared" ref="A103:A130" si="17">RIGHT(D103,4)</f>
+      <c r="C103" s="42"/>
+      <c r="D103" s="42"/>
+      <c r="E103" s="42"/>
+      <c r="F103" s="41"/>
+      <c r="G103" s="42"/>
+      <c r="H103" s="42"/>
+      <c r="I103" s="42"/>
+      <c r="J103" s="43"/>
+      <c r="L103" s="102"/>
+    </row>
+    <row r="104" spans="1:67" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="137" t="str">
+        <f t="shared" ref="A104:A131" si="18">RIGHT(D104,4)</f>
         <v>3986</v>
       </c>
-      <c r="B103" s="53" t="s">
+      <c r="B104" s="53" t="s">
         <v>79</v>
-      </c>
-      <c r="C103" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D103" s="51">
-        <v>1001061973986</v>
-      </c>
-      <c r="E103" s="24"/>
-      <c r="F103" s="128">
-        <v>0.25</v>
-      </c>
-      <c r="G103" s="23">
-        <f t="shared" ref="G103:G108" si="18">E103*F103</f>
-        <v>0</v>
-      </c>
-      <c r="H103" s="132">
-        <v>2</v>
-      </c>
-      <c r="I103" s="133">
-        <v>120</v>
-      </c>
-      <c r="J103" s="29"/>
-      <c r="L103" s="102"/>
-    </row>
-    <row r="104" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>5931</v>
-      </c>
-      <c r="B104" s="53" t="s">
-        <v>77</v>
       </c>
       <c r="C104" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D104" s="51">
-        <v>1001060755931</v>
+        <v>1001061973986</v>
       </c>
       <c r="E104" s="24"/>
-      <c r="F104" s="23">
-        <v>0.22</v>
+      <c r="F104" s="128">
+        <v>0.25</v>
       </c>
       <c r="G104" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="G104:G109" si="19">E104*F104</f>
         <v>0</v>
       </c>
-      <c r="H104" s="97">
-        <v>1.76</v>
-      </c>
-      <c r="I104" s="14">
+      <c r="H104" s="132">
+        <v>2</v>
+      </c>
+      <c r="I104" s="133">
         <v>120</v>
       </c>
       <c r="J104" s="29"/>
       <c r="L104" s="102"/>
     </row>
     <row r="105" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>5708</v>
+      <c r="A105" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>5931</v>
       </c>
       <c r="B105" s="53" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C105" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D105" s="51">
-        <v>1001063145708</v>
+        <v>1001060755931</v>
       </c>
       <c r="E105" s="24"/>
       <c r="F105" s="23">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="G105" s="23">
-        <f t="shared" ref="G105:G106" si="19">E105</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="H105" s="14">
-        <v>4</v>
+      <c r="H105" s="97">
+        <v>1.76</v>
       </c>
       <c r="I105" s="14">
         <v>120</v>
@@ -11402,29 +11407,29 @@
       <c r="L105" s="102"/>
     </row>
     <row r="106" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>3287</v>
+      <c r="A106" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>5708</v>
       </c>
       <c r="B106" s="53" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C106" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D106" s="51">
-        <v>1001060763287</v>
+        <v>1001063145708</v>
       </c>
       <c r="E106" s="24"/>
       <c r="F106" s="23">
-        <v>0.48799999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G106" s="23">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="G106:G107" si="20">E106</f>
         <v>0</v>
       </c>
       <c r="H106" s="14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I106" s="14">
         <v>120</v>
@@ -11433,29 +11438,29 @@
       <c r="L106" s="102"/>
     </row>
     <row r="107" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>4993</v>
+      <c r="A107" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>3287</v>
       </c>
       <c r="B107" s="53" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="C107" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D107" s="51">
-        <v>1001060764993</v>
+        <v>1001060763287</v>
       </c>
       <c r="E107" s="24"/>
       <c r="F107" s="23">
-        <v>0.25</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="G107" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H107" s="14">
-        <v>2</v>
+        <v>3.9</v>
       </c>
       <c r="I107" s="14">
         <v>120</v>
@@ -11464,25 +11469,25 @@
       <c r="L107" s="102"/>
     </row>
     <row r="108" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>5483</v>
+      <c r="A108" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>4993</v>
       </c>
       <c r="B108" s="53" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="C108" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D108" s="51">
-        <v>1001062505483</v>
+        <v>1001060764993</v>
       </c>
       <c r="E108" s="24"/>
       <c r="F108" s="23">
         <v>0.25</v>
       </c>
       <c r="G108" s="23">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H108" s="14">
@@ -11495,29 +11500,29 @@
       <c r="L108" s="102"/>
     </row>
     <row r="109" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>4117</v>
+      <c r="A109" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>5483</v>
       </c>
       <c r="B109" s="53" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D109" s="51">
-        <v>1001062504117</v>
+        <v>1001062505483</v>
       </c>
       <c r="E109" s="24"/>
       <c r="F109" s="23">
-        <v>0.49399999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G109" s="23">
-        <f t="shared" ref="G109:G110" si="20">E109</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="H109" s="14">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="I109" s="14">
         <v>120</v>
@@ -11526,29 +11531,29 @@
       <c r="L109" s="102"/>
     </row>
     <row r="110" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>0614</v>
+      <c r="A110" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>4117</v>
       </c>
       <c r="B110" s="53" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="C110" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D110" s="51">
-        <v>1001060720614</v>
+        <v>1001062504117</v>
       </c>
       <c r="E110" s="24"/>
       <c r="F110" s="23">
-        <v>0.52</v>
+        <v>0.49399999999999999</v>
       </c>
       <c r="G110" s="23">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G110:G111" si="21">E110</f>
         <v>0</v>
       </c>
       <c r="H110" s="14">
-        <v>3.64</v>
+        <v>3.95</v>
       </c>
       <c r="I110" s="14">
         <v>120</v>
@@ -11557,29 +11562,29 @@
       <c r="L110" s="102"/>
     </row>
     <row r="111" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>6967</v>
+      <c r="A111" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>0614</v>
       </c>
       <c r="B111" s="53" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="C111" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D111" s="51">
-        <v>1001063656967</v>
+        <v>1001060720614</v>
       </c>
       <c r="E111" s="24"/>
       <c r="F111" s="23">
-        <v>0.25</v>
+        <v>0.52</v>
       </c>
       <c r="G111" s="23">
-        <f t="shared" ref="G111:G120" si="21">E111*F111</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H111" s="14">
-        <v>2</v>
+        <v>3.64</v>
       </c>
       <c r="I111" s="14">
         <v>120</v>
@@ -11588,25 +11593,25 @@
       <c r="L111" s="102"/>
     </row>
     <row r="112" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>6937</v>
+      <c r="A112" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>6967</v>
       </c>
       <c r="B112" s="53" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="C112" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D112" s="51">
-        <v>1001063106937</v>
+        <v>1001063656967</v>
       </c>
       <c r="E112" s="24"/>
       <c r="F112" s="23">
         <v>0.25</v>
       </c>
       <c r="G112" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" ref="G112:G121" si="22">E112*F112</f>
         <v>0</v>
       </c>
       <c r="H112" s="14">
@@ -11619,29 +11624,29 @@
       <c r="L112" s="102"/>
     </row>
     <row r="113" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7143</v>
+      <c r="A113" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>6937</v>
       </c>
       <c r="B113" s="53" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C113" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D113" s="51">
-        <v>1001060717143</v>
+        <v>1001063106937</v>
       </c>
       <c r="E113" s="24"/>
       <c r="F113" s="23">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G113" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H113" s="14">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="I113" s="14">
         <v>120</v>
@@ -11650,25 +11655,25 @@
       <c r="L113" s="102"/>
     </row>
     <row r="114" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7147</v>
+      <c r="A114" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7143</v>
       </c>
       <c r="B114" s="53" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="C114" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D114" s="51">
-        <v>1001063237147</v>
+        <v>1001060717143</v>
       </c>
       <c r="E114" s="24"/>
       <c r="F114" s="23">
         <v>0.22</v>
       </c>
       <c r="G114" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H114" s="14">
@@ -11681,60 +11686,60 @@
       <c r="L114" s="102"/>
     </row>
     <row r="115" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7456</v>
+      <c r="A115" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7147</v>
       </c>
       <c r="B115" s="53" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="C115" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D115" s="51">
-        <v>1001063097456</v>
+        <v>1001063237147</v>
       </c>
       <c r="E115" s="24"/>
       <c r="F115" s="23">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="G115" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H115" s="14">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="I115" s="14">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J115" s="29"/>
       <c r="L115" s="102"/>
     </row>
     <row r="116" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7364</v>
+      <c r="A116" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7456</v>
       </c>
       <c r="B116" s="53" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C116" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D116" s="51">
-        <v>1001063217364</v>
+        <v>1001063097456</v>
       </c>
       <c r="E116" s="24"/>
       <c r="F116" s="23">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="G116" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H116" s="14">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="I116" s="14">
         <v>90</v>
@@ -11743,25 +11748,25 @@
       <c r="L116" s="102"/>
     </row>
     <row r="117" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7383</v>
+      <c r="A117" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7364</v>
       </c>
       <c r="B117" s="53" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C117" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D117" s="51">
-        <v>1001065467383</v>
+        <v>1001063217364</v>
       </c>
       <c r="E117" s="24"/>
       <c r="F117" s="23">
         <v>0.22</v>
       </c>
       <c r="G117" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H117" s="14">
@@ -11774,60 +11779,60 @@
       <c r="L117" s="102"/>
     </row>
     <row r="118" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7317</v>
+      <c r="A118" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7383</v>
       </c>
       <c r="B118" s="53" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C118" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D118" s="51">
-        <v>1001066567317</v>
+        <v>1001065467383</v>
       </c>
       <c r="E118" s="24"/>
       <c r="F118" s="23">
-        <v>0.54</v>
+        <v>0.22</v>
       </c>
       <c r="G118" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H118" s="14">
-        <v>3.78</v>
+        <v>1.76</v>
       </c>
       <c r="I118" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="J118" s="29"/>
       <c r="L118" s="102"/>
     </row>
     <row r="119" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7318</v>
+      <c r="A119" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7317</v>
       </c>
       <c r="B119" s="53" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C119" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="51">
-        <v>1001060727318</v>
+        <v>1001066567317</v>
       </c>
       <c r="E119" s="24"/>
       <c r="F119" s="23">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G119" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H119" s="14">
-        <v>2.16</v>
+        <v>3.78</v>
       </c>
       <c r="I119" s="14">
         <v>120</v>
@@ -11836,29 +11841,29 @@
       <c r="L119" s="102"/>
     </row>
     <row r="120" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7316</v>
+      <c r="A120" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7318</v>
       </c>
       <c r="B120" s="53" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C120" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D120" s="51">
-        <v>1001060727316</v>
+        <v>1001060727318</v>
       </c>
       <c r="E120" s="24"/>
       <c r="F120" s="23">
-        <v>0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G120" s="23">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H120" s="14">
-        <v>3.78</v>
+        <v>2.16</v>
       </c>
       <c r="I120" s="14">
         <v>120</v>
@@ -11867,56 +11872,56 @@
       <c r="L120" s="102"/>
     </row>
     <row r="121" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>6832</v>
+      <c r="A121" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7316</v>
       </c>
       <c r="B121" s="53" t="s">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="C121" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D121" s="51">
-        <v>1001065616832</v>
+        <v>1001060727316</v>
       </c>
       <c r="E121" s="24"/>
       <c r="F121" s="23">
-        <v>0.215</v>
+        <v>0.54</v>
       </c>
       <c r="G121" s="23">
-        <f t="shared" ref="G121:G122" si="22">E121</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H121" s="14">
-        <v>2.15</v>
+        <v>3.78</v>
       </c>
       <c r="I121" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="J121" s="29"/>
       <c r="L121" s="102"/>
     </row>
     <row r="122" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7299</v>
+      <c r="A122" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>6832</v>
       </c>
       <c r="B122" s="53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C122" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D122" s="51">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="E122" s="24"/>
       <c r="F122" s="23">
         <v>0.215</v>
       </c>
       <c r="G122" s="23">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="G122:G123" si="23">E122</f>
         <v>0</v>
       </c>
       <c r="H122" s="14">
@@ -11929,184 +11934,184 @@
       <c r="L122" s="102"/>
     </row>
     <row r="123" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7386</v>
+      <c r="A123" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7299</v>
       </c>
       <c r="B123" s="53" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C123" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D123" s="51">
-        <v>1001067017386</v>
+        <v>1001060677299</v>
       </c>
       <c r="E123" s="24"/>
       <c r="F123" s="23">
-        <v>0.15</v>
+        <v>0.215</v>
       </c>
       <c r="G123" s="23">
-        <f t="shared" ref="G123:G130" si="23">E123*F123</f>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="H123" s="14">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="I123" s="14">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J123" s="29"/>
       <c r="L123" s="102"/>
     </row>
     <row r="124" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7613</v>
+      <c r="A124" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7386</v>
       </c>
       <c r="B124" s="53" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="C124" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D124" s="51">
-        <v>1001061977613</v>
+        <v>1001067017386</v>
       </c>
       <c r="E124" s="24"/>
       <c r="F124" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G124" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" ref="G124:G131" si="24">E124*F124</f>
         <v>0</v>
       </c>
       <c r="H124" s="14">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="I124" s="14">
-        <v>60</v>
-      </c>
-      <c r="J124" s="52" t="s">
-        <v>203</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="J124" s="29"/>
       <c r="L124" s="102"/>
     </row>
     <row r="125" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7382</v>
+      <c r="A125" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7613</v>
       </c>
       <c r="B125" s="53" t="s">
-        <v>84</v>
+        <v>213</v>
       </c>
       <c r="C125" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D125" s="51">
-        <v>1001203117382</v>
+        <v>1001061977613</v>
       </c>
       <c r="E125" s="24"/>
       <c r="F125" s="23">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="G125" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H125" s="14">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="I125" s="14">
         <v>60</v>
       </c>
-      <c r="J125" s="29"/>
+      <c r="J125" s="52" t="s">
+        <v>203</v>
+      </c>
       <c r="L125" s="102"/>
     </row>
     <row r="126" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7616</v>
+      <c r="A126" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7382</v>
       </c>
       <c r="B126" s="53" t="s">
-        <v>204</v>
+        <v>84</v>
       </c>
       <c r="C126" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D126" s="51">
-        <v>1001062507616</v>
+        <v>1001203117382</v>
       </c>
       <c r="E126" s="24"/>
       <c r="F126" s="23">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="G126" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H126" s="14">
-        <v>1.4</v>
+        <v>0.96</v>
       </c>
       <c r="I126" s="14">
         <v>60</v>
       </c>
-      <c r="J126" s="52" t="s">
-        <v>205</v>
-      </c>
+      <c r="J126" s="29"/>
       <c r="L126" s="102"/>
     </row>
     <row r="127" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>6221</v>
+      <c r="A127" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7616</v>
       </c>
       <c r="B127" s="53" t="s">
-        <v>86</v>
+        <v>204</v>
       </c>
       <c r="C127" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D127" s="51">
-        <v>1001205376221</v>
+        <v>1001062507616</v>
       </c>
       <c r="E127" s="24"/>
       <c r="F127" s="23">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="G127" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H127" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I127" s="14">
         <v>60</v>
       </c>
-      <c r="J127" s="29"/>
+      <c r="J127" s="52" t="s">
+        <v>205</v>
+      </c>
       <c r="L127" s="102"/>
     </row>
     <row r="128" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>6222</v>
+      <c r="A128" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>6221</v>
       </c>
       <c r="B128" s="53" t="s">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="C128" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D128" s="51">
-        <v>1001205386222</v>
+        <v>1001205376221</v>
       </c>
       <c r="E128" s="24"/>
       <c r="F128" s="23">
         <v>0.09</v>
       </c>
       <c r="G128" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H128" s="14">
@@ -12118,30 +12123,30 @@
       <c r="J128" s="29"/>
       <c r="L128" s="102"/>
     </row>
-    <row r="129" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>5679</v>
+    <row r="129" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>6222</v>
       </c>
       <c r="B129" s="53" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C129" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D129" s="51">
-        <v>1001190765679</v>
+        <v>1001205386222</v>
       </c>
       <c r="E129" s="24"/>
       <c r="F129" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G129" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H129" s="14">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I129" s="14">
         <v>60</v>
@@ -12149,110 +12154,68 @@
       <c r="J129" s="29"/>
       <c r="L129" s="102"/>
     </row>
-    <row r="130" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="141" t="str">
-        <f t="shared" si="17"/>
-        <v>7626</v>
+    <row r="130" spans="1:67" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>5679</v>
       </c>
       <c r="B130" s="53" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="C130" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D130" s="51">
-        <v>1001066607626</v>
+        <v>1001190765679</v>
       </c>
       <c r="E130" s="24"/>
       <c r="F130" s="23">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G130" s="23">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H130" s="14">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I130" s="14">
         <v>60</v>
       </c>
-      <c r="J130" s="52" t="s">
+      <c r="J130" s="29"/>
+      <c r="L130" s="102"/>
+    </row>
+    <row r="131" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="137" t="str">
+        <f t="shared" si="18"/>
+        <v>7626</v>
+      </c>
+      <c r="B131" s="53" t="s">
+        <v>201</v>
+      </c>
+      <c r="C131" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D131" s="51">
+        <v>1001066607626</v>
+      </c>
+      <c r="E131" s="24"/>
+      <c r="F131" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="G131" s="23">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="H131" s="14">
+        <v>1</v>
+      </c>
+      <c r="I131" s="14">
+        <v>60</v>
+      </c>
+      <c r="J131" s="52" t="s">
         <v>202</v>
       </c>
-      <c r="K130" s="27"/>
-      <c r="L130" s="102"/>
-      <c r="M130" s="102"/>
-      <c r="N130" s="102"/>
-      <c r="O130" s="102"/>
-      <c r="P130" s="102"/>
-      <c r="Q130" s="102"/>
-      <c r="R130" s="102"/>
-      <c r="S130" s="102"/>
-      <c r="T130" s="102"/>
-      <c r="U130" s="102"/>
-      <c r="V130" s="102"/>
-      <c r="W130" s="102"/>
-      <c r="X130" s="102"/>
-      <c r="Y130" s="102"/>
-      <c r="Z130" s="102"/>
-      <c r="AA130" s="102"/>
-      <c r="AB130" s="102"/>
-      <c r="AC130" s="102"/>
-      <c r="AD130" s="102"/>
-      <c r="AE130" s="102"/>
-      <c r="AF130" s="102"/>
-      <c r="AG130" s="102"/>
-      <c r="AH130" s="102"/>
-      <c r="AI130" s="102"/>
-      <c r="AJ130" s="102"/>
-      <c r="AK130" s="102"/>
-      <c r="AL130" s="102"/>
-      <c r="AM130" s="102"/>
-      <c r="AN130" s="102"/>
-      <c r="AO130" s="102"/>
-      <c r="AP130" s="102"/>
-      <c r="AQ130" s="102"/>
-      <c r="AR130" s="102"/>
-      <c r="AS130" s="102"/>
-      <c r="AT130" s="102"/>
-      <c r="AU130" s="102"/>
-      <c r="AV130" s="102"/>
-      <c r="AW130" s="102"/>
-      <c r="AX130" s="102"/>
-      <c r="AY130" s="102"/>
-      <c r="AZ130" s="102"/>
-      <c r="BA130" s="102"/>
-      <c r="BB130" s="102"/>
-      <c r="BC130" s="102"/>
-      <c r="BD130" s="102"/>
-      <c r="BE130" s="102"/>
-      <c r="BF130" s="102"/>
-      <c r="BG130" s="102"/>
-      <c r="BH130" s="102"/>
-      <c r="BI130" s="102"/>
-      <c r="BJ130" s="102"/>
-      <c r="BK130" s="102"/>
-      <c r="BL130" s="102"/>
-      <c r="BM130" s="102"/>
-      <c r="BN130" s="102"/>
-      <c r="BO130" s="102"/>
-    </row>
-    <row r="131" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="47" t="s">
-        <v>104</v>
-      </c>
-      <c r="B131" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="C131" s="42"/>
-      <c r="D131" s="42"/>
-      <c r="E131" s="42"/>
-      <c r="F131" s="41"/>
-      <c r="G131" s="42"/>
-      <c r="H131" s="42"/>
-      <c r="I131" s="42"/>
-      <c r="J131" s="43"/>
       <c r="K131" s="27"/>
       <c r="L131" s="102"/>
       <c r="M131" s="102"/>
@@ -12311,35 +12274,21 @@
       <c r="BN131" s="102"/>
       <c r="BO131" s="102"/>
     </row>
-    <row r="132" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="141" t="str">
-        <f t="shared" ref="A132:A146" si="24">RIGHT(D132,4)</f>
-        <v>4584</v>
-      </c>
-      <c r="B132" s="98" t="s">
-        <v>220</v>
-      </c>
-      <c r="C132" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="D132" s="134">
-        <v>1001092674584</v>
-      </c>
-      <c r="E132" s="24"/>
-      <c r="F132" s="23">
-        <v>2.5</v>
-      </c>
-      <c r="G132" s="23">
-        <f>E132</f>
-        <v>0</v>
-      </c>
-      <c r="H132" s="14">
-        <v>7.5</v>
-      </c>
-      <c r="I132" s="14">
-        <v>60</v>
-      </c>
-      <c r="J132" s="29"/>
+    <row r="132" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="B132" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C132" s="42"/>
+      <c r="D132" s="42"/>
+      <c r="E132" s="42"/>
+      <c r="F132" s="41"/>
+      <c r="G132" s="42"/>
+      <c r="H132" s="42"/>
+      <c r="I132" s="42"/>
+      <c r="J132" s="43"/>
       <c r="K132" s="27"/>
       <c r="L132" s="102"/>
       <c r="M132" s="102"/>
@@ -12398,33 +12347,33 @@
       <c r="BN132" s="102"/>
       <c r="BO132" s="102"/>
     </row>
-    <row r="133" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>6495</v>
+    <row r="133" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="137" t="str">
+        <f t="shared" ref="A133:A147" si="25">RIGHT(D133,4)</f>
+        <v>4584</v>
       </c>
       <c r="B133" s="98" t="s">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="C133" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D133" s="51">
-        <v>1001092436495</v>
+        <v>22</v>
+      </c>
+      <c r="D133" s="134">
+        <v>1001092674584</v>
       </c>
       <c r="E133" s="24"/>
-      <c r="F133" s="128">
-        <v>0.3</v>
+      <c r="F133" s="23">
+        <v>2.5</v>
       </c>
       <c r="G133" s="23">
-        <f>E133*F133</f>
+        <f>E133</f>
         <v>0</v>
       </c>
-      <c r="H133" s="29">
-        <v>1.8</v>
-      </c>
-      <c r="I133" s="29">
-        <v>45</v>
+      <c r="H133" s="14">
+        <v>7.5</v>
+      </c>
+      <c r="I133" s="14">
+        <v>60</v>
       </c>
       <c r="J133" s="29"/>
       <c r="K133" s="27"/>
@@ -12486,29 +12435,29 @@
       <c r="BO133" s="102"/>
     </row>
     <row r="134" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>6470</v>
-      </c>
-      <c r="B134" s="135" t="s">
-        <v>116</v>
+      <c r="A134" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>6495</v>
+      </c>
+      <c r="B134" s="98" t="s">
+        <v>95</v>
       </c>
       <c r="C134" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D134" s="51">
-        <v>1001092436470</v>
+        <v>1001092436495</v>
       </c>
       <c r="E134" s="24"/>
       <c r="F134" s="128">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="G134" s="23">
-        <f t="shared" ref="G134:G135" si="25">E134</f>
+        <f>E134*F134</f>
         <v>0</v>
       </c>
       <c r="H134" s="29">
-        <v>4.8</v>
+        <v>1.8</v>
       </c>
       <c r="I134" s="29">
         <v>45</v>
@@ -12572,33 +12521,33 @@
       <c r="BN134" s="102"/>
       <c r="BO134" s="102"/>
     </row>
-    <row r="135" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>5452</v>
+    <row r="135" spans="1:67" s="54" customFormat="1" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>6470</v>
       </c>
       <c r="B135" s="135" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="C135" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D135" s="51">
-        <v>1001092485452</v>
+        <v>1001092436470</v>
       </c>
       <c r="E135" s="24"/>
       <c r="F135" s="128">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="G135" s="23">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="G135:G136" si="26">E135</f>
         <v>0</v>
       </c>
       <c r="H135" s="29">
-        <v>4.05</v>
+        <v>4.8</v>
       </c>
       <c r="I135" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J135" s="29"/>
       <c r="K135" s="27"/>
@@ -12660,29 +12609,29 @@
       <c r="BO135" s="102"/>
     </row>
     <row r="136" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>3215</v>
+      <c r="A136" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>5452</v>
       </c>
       <c r="B136" s="135" t="s">
-        <v>215</v>
+        <v>93</v>
       </c>
       <c r="C136" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D136" s="51">
-        <v>1001094053215</v>
+        <v>1001092485452</v>
       </c>
       <c r="E136" s="24"/>
       <c r="F136" s="128">
-        <v>0.4</v>
+        <v>1.35</v>
       </c>
       <c r="G136" s="23">
-        <f>E136*F136</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="H136" s="29">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="I136" s="29">
         <v>60</v>
@@ -12747,29 +12696,29 @@
       <c r="BO136" s="102"/>
     </row>
     <row r="137" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>6866</v>
+      <c r="A137" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>3215</v>
       </c>
       <c r="B137" s="135" t="s">
-        <v>92</v>
+        <v>215</v>
       </c>
       <c r="C137" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D137" s="51">
-        <v>1001095716866</v>
+        <v>1001094053215</v>
       </c>
       <c r="E137" s="24"/>
       <c r="F137" s="128">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="G137" s="23">
-        <f>E137</f>
+        <f>E137*F137</f>
         <v>0</v>
       </c>
       <c r="H137" s="29">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="I137" s="29">
         <v>60</v>
@@ -12834,29 +12783,29 @@
       <c r="BO137" s="102"/>
     </row>
     <row r="138" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>5495</v>
-      </c>
-      <c r="B138" s="53" t="s">
-        <v>94</v>
+      <c r="A138" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>6866</v>
+      </c>
+      <c r="B138" s="135" t="s">
+        <v>92</v>
       </c>
       <c r="C138" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D138" s="136">
-        <v>1001093345495</v>
+        <v>22</v>
+      </c>
+      <c r="D138" s="51">
+        <v>1001095716866</v>
       </c>
       <c r="E138" s="24"/>
       <c r="F138" s="128">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="G138" s="23">
-        <f t="shared" ref="G138:G141" si="26">E138*F138</f>
+        <f>E138</f>
         <v>0</v>
       </c>
       <c r="H138" s="29">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="I138" s="29">
         <v>60</v>
@@ -12921,32 +12870,32 @@
       <c r="BO138" s="102"/>
     </row>
     <row r="139" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>7377</v>
+      <c r="A139" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>5495</v>
       </c>
       <c r="B139" s="53" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="C139" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D139" s="136">
-        <v>1001095027377</v>
+        <v>1001093345495</v>
       </c>
       <c r="E139" s="24"/>
       <c r="F139" s="128">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G139" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" ref="G139:G142" si="27">E139*F139</f>
         <v>0</v>
       </c>
       <c r="H139" s="29">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="I139" s="29">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J139" s="29"/>
       <c r="K139" s="27"/>
@@ -13007,30 +12956,34 @@
       <c r="BN139" s="102"/>
       <c r="BO139" s="102"/>
     </row>
-    <row r="140" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>6411</v>
+    <row r="140" spans="1:67" s="54" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>7377</v>
       </c>
       <c r="B140" s="53" t="s">
-        <v>224</v>
+        <v>117</v>
       </c>
       <c r="C140" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D140" s="136">
-        <v>1001093316411</v>
+        <v>1001095027377</v>
       </c>
       <c r="E140" s="24"/>
       <c r="F140" s="128">
         <v>0.3</v>
       </c>
       <c r="G140" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H140" s="29"/>
-      <c r="I140" s="29"/>
+      <c r="H140" s="29">
+        <v>1.8</v>
+      </c>
+      <c r="I140" s="29">
+        <v>45</v>
+      </c>
       <c r="J140" s="29"/>
       <c r="K140" s="27"/>
       <c r="L140" s="102"/>
@@ -13091,33 +13044,29 @@
       <c r="BO140" s="102"/>
     </row>
     <row r="141" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>6925</v>
+      <c r="A141" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>6411</v>
       </c>
       <c r="B141" s="53" t="s">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="C141" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D141" s="136">
-        <v>1001095226925</v>
+        <v>1001093316411</v>
       </c>
       <c r="E141" s="24"/>
       <c r="F141" s="128">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G141" s="23">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H141" s="29">
-        <v>4.8</v>
-      </c>
-      <c r="I141" s="29">
-        <v>45</v>
-      </c>
+      <c r="H141" s="29"/>
+      <c r="I141" s="29"/>
       <c r="J141" s="29"/>
       <c r="K141" s="27"/>
       <c r="L141" s="102"/>
@@ -13178,32 +13127,32 @@
       <c r="BO141" s="102"/>
     </row>
     <row r="142" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>6025</v>
+      <c r="A142" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>6925</v>
       </c>
       <c r="B142" s="53" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C142" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D142" s="136">
-        <v>1001094966025</v>
+        <v>1001095226925</v>
       </c>
       <c r="E142" s="24"/>
       <c r="F142" s="128">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="G142" s="23">
-        <f>E142</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="H142" s="29">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="I142" s="29">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J142" s="29"/>
       <c r="K142" s="27"/>
@@ -13264,106 +13213,160 @@
       <c r="BN142" s="102"/>
       <c r="BO142" s="102"/>
     </row>
-    <row r="143" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>6929</v>
+    <row r="143" spans="1:67" s="54" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>6025</v>
       </c>
       <c r="B143" s="53" t="s">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="C143" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D143" s="136">
-        <v>1001085476929</v>
+        <v>1001094966025</v>
       </c>
       <c r="E143" s="24"/>
-      <c r="F143" s="128"/>
+      <c r="F143" s="128">
+        <v>3</v>
+      </c>
       <c r="G143" s="23">
         <f>E143</f>
         <v>0</v>
       </c>
-      <c r="H143" s="29"/>
-      <c r="I143" s="29"/>
+      <c r="H143" s="29">
+        <v>6</v>
+      </c>
+      <c r="I143" s="29">
+        <v>60</v>
+      </c>
       <c r="J143" s="29"/>
+      <c r="K143" s="27"/>
       <c r="L143" s="102"/>
+      <c r="M143" s="102"/>
+      <c r="N143" s="102"/>
+      <c r="O143" s="102"/>
+      <c r="P143" s="102"/>
+      <c r="Q143" s="102"/>
+      <c r="R143" s="102"/>
+      <c r="S143" s="102"/>
+      <c r="T143" s="102"/>
+      <c r="U143" s="102"/>
+      <c r="V143" s="102"/>
+      <c r="W143" s="102"/>
+      <c r="X143" s="102"/>
+      <c r="Y143" s="102"/>
+      <c r="Z143" s="102"/>
+      <c r="AA143" s="102"/>
+      <c r="AB143" s="102"/>
+      <c r="AC143" s="102"/>
+      <c r="AD143" s="102"/>
+      <c r="AE143" s="102"/>
+      <c r="AF143" s="102"/>
+      <c r="AG143" s="102"/>
+      <c r="AH143" s="102"/>
+      <c r="AI143" s="102"/>
+      <c r="AJ143" s="102"/>
+      <c r="AK143" s="102"/>
+      <c r="AL143" s="102"/>
+      <c r="AM143" s="102"/>
+      <c r="AN143" s="102"/>
+      <c r="AO143" s="102"/>
+      <c r="AP143" s="102"/>
+      <c r="AQ143" s="102"/>
+      <c r="AR143" s="102"/>
+      <c r="AS143" s="102"/>
+      <c r="AT143" s="102"/>
+      <c r="AU143" s="102"/>
+      <c r="AV143" s="102"/>
+      <c r="AW143" s="102"/>
+      <c r="AX143" s="102"/>
+      <c r="AY143" s="102"/>
+      <c r="AZ143" s="102"/>
+      <c r="BA143" s="102"/>
+      <c r="BB143" s="102"/>
+      <c r="BC143" s="102"/>
+      <c r="BD143" s="102"/>
+      <c r="BE143" s="102"/>
+      <c r="BF143" s="102"/>
+      <c r="BG143" s="102"/>
+      <c r="BH143" s="102"/>
+      <c r="BI143" s="102"/>
+      <c r="BJ143" s="102"/>
+      <c r="BK143" s="102"/>
+      <c r="BL143" s="102"/>
+      <c r="BM143" s="102"/>
+      <c r="BN143" s="102"/>
+      <c r="BO143" s="102"/>
     </row>
     <row r="144" spans="1:67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>7485</v>
+      <c r="A144" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>6929</v>
       </c>
       <c r="B144" s="53" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C144" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D144" s="136">
-        <v>1001107397485</v>
+        <v>1001085476929</v>
       </c>
       <c r="E144" s="24"/>
-      <c r="F144" s="128">
-        <v>0.15</v>
-      </c>
+      <c r="F144" s="128"/>
       <c r="G144" s="23">
-        <f>F144*E144</f>
+        <f>E144</f>
         <v>0</v>
       </c>
       <c r="H144" s="29"/>
       <c r="I144" s="29"/>
-      <c r="J144" s="125" t="s">
-        <v>196</v>
-      </c>
+      <c r="J144" s="29"/>
       <c r="L144" s="102"/>
     </row>
     <row r="145" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>7647</v>
+      <c r="A145" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>7485</v>
       </c>
       <c r="B145" s="53" t="s">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="C145" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D145" s="136">
-        <v>1001097747647</v>
+        <v>1001107397485</v>
       </c>
       <c r="E145" s="24"/>
       <c r="F145" s="128">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="G145" s="23">
-        <f>E145*F145</f>
+        <f>F145*E145</f>
         <v>0</v>
       </c>
-      <c r="H145" s="29">
-        <v>1</v>
-      </c>
-      <c r="I145" s="29">
-        <v>30</v>
-      </c>
+      <c r="H145" s="29"/>
+      <c r="I145" s="29"/>
       <c r="J145" s="125" t="s">
         <v>196</v>
       </c>
       <c r="L145" s="102"/>
     </row>
-    <row r="146" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="141" t="str">
-        <f t="shared" si="24"/>
-        <v>7651</v>
+    <row r="146" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>7647</v>
       </c>
       <c r="B146" s="53" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C146" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D146" s="136">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="E146" s="24"/>
       <c r="F146" s="128">
@@ -13384,74 +13387,76 @@
       </c>
       <c r="L146" s="102"/>
     </row>
-    <row r="147" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="47" t="s">
+    <row r="147" spans="1:12" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="137" t="str">
+        <f t="shared" si="25"/>
+        <v>7651</v>
+      </c>
+      <c r="B147" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="C147" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D147" s="136">
+        <v>1001097767651</v>
+      </c>
+      <c r="E147" s="24"/>
+      <c r="F147" s="128">
+        <v>0.1</v>
+      </c>
+      <c r="G147" s="23">
+        <f>E147*F147</f>
+        <v>0</v>
+      </c>
+      <c r="H147" s="29">
+        <v>1</v>
+      </c>
+      <c r="I147" s="29">
+        <v>30</v>
+      </c>
+      <c r="J147" s="125" t="s">
+        <v>196</v>
+      </c>
+      <c r="L147" s="102"/>
+    </row>
+    <row r="148" spans="1:12" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="B147" s="42" t="s">
+      <c r="B148" s="42" t="s">
         <v>96</v>
       </c>
-      <c r="C147" s="42"/>
-      <c r="D147" s="42"/>
-      <c r="E147" s="42"/>
-      <c r="F147" s="41"/>
-      <c r="G147" s="42"/>
-      <c r="H147" s="42"/>
-      <c r="I147" s="42"/>
-      <c r="J147" s="43"/>
-      <c r="L147" s="102"/>
-    </row>
-    <row r="148" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="141" t="str">
-        <f t="shared" ref="A148:A159" si="27">RIGHT(D148,4)</f>
+      <c r="C148" s="42"/>
+      <c r="D148" s="42"/>
+      <c r="E148" s="42"/>
+      <c r="F148" s="41"/>
+      <c r="G148" s="42"/>
+      <c r="H148" s="42"/>
+      <c r="I148" s="42"/>
+      <c r="J148" s="43"/>
+      <c r="L148" s="102"/>
+    </row>
+    <row r="149" spans="1:12" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="137" t="str">
+        <f t="shared" ref="A149:A162" si="28">RIGHT(D149,4)</f>
         <v>7090</v>
       </c>
-      <c r="B148" s="35" t="s">
+      <c r="B149" s="35" t="s">
         <v>100</v>
-      </c>
-      <c r="C148" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="D148" s="51">
-        <v>1001084217090</v>
-      </c>
-      <c r="E148" s="24"/>
-      <c r="F148" s="23">
-        <v>0.3</v>
-      </c>
-      <c r="G148" s="23">
-        <f t="shared" ref="G148:G149" si="28">E148*F148</f>
-        <v>0</v>
-      </c>
-      <c r="H148" s="14">
-        <v>1.8</v>
-      </c>
-      <c r="I148" s="14">
-        <v>50</v>
-      </c>
-      <c r="J148" s="29"/>
-      <c r="L148" s="102"/>
-    </row>
-    <row r="149" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>7187</v>
-      </c>
-      <c r="B149" s="35" t="s">
-        <v>101</v>
       </c>
       <c r="C149" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D149" s="51">
-        <v>1001085637187</v>
+        <v>1001084217090</v>
       </c>
       <c r="E149" s="24"/>
       <c r="F149" s="23">
         <v>0.3</v>
       </c>
       <c r="G149" s="23">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="G149:G150" si="29">E149*F149</f>
         <v>0</v>
       </c>
       <c r="H149" s="14">
@@ -13464,124 +13469,124 @@
       <c r="L149" s="102"/>
     </row>
     <row r="150" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>6008</v>
+      <c r="A150" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>7187</v>
       </c>
       <c r="B150" s="35" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="C150" s="50" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D150" s="51">
-        <v>1001084856008</v>
+        <v>1001085637187</v>
       </c>
       <c r="E150" s="24"/>
       <c r="F150" s="23">
         <v>0.3</v>
       </c>
       <c r="G150" s="23">
-        <f>E150</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="H150" s="14">
         <v>1.8</v>
       </c>
       <c r="I150" s="14">
-        <v>40</v>
-      </c>
-      <c r="J150" s="125" t="s">
-        <v>196</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J150" s="29"/>
       <c r="L150" s="102"/>
     </row>
     <row r="151" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>6620</v>
+      <c r="A151" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>6008</v>
       </c>
       <c r="B151" s="35" t="s">
-        <v>97</v>
+        <v>198</v>
       </c>
       <c r="C151" s="50" t="s">
         <v>22</v>
       </c>
       <c r="D151" s="51">
-        <v>1001081596620</v>
+        <v>1001084856008</v>
       </c>
       <c r="E151" s="24"/>
       <c r="F151" s="23">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="G151" s="23">
         <f>E151</f>
         <v>0</v>
       </c>
       <c r="H151" s="14">
-        <v>3.15</v>
+        <v>1.8</v>
       </c>
       <c r="I151" s="14">
-        <v>30</v>
-      </c>
-      <c r="J151" s="29"/>
+        <v>40</v>
+      </c>
+      <c r="J151" s="125" t="s">
+        <v>196</v>
+      </c>
       <c r="L151" s="102"/>
     </row>
     <row r="152" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>7103</v>
+      <c r="A152" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>6620</v>
       </c>
       <c r="B152" s="35" t="s">
-        <v>216</v>
+        <v>97</v>
       </c>
       <c r="C152" s="50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D152" s="51">
-        <v>1001223297103</v>
+        <v>1001081596620</v>
       </c>
       <c r="E152" s="24"/>
       <c r="F152" s="23">
-        <v>0.18</v>
+        <v>1.05</v>
       </c>
       <c r="G152" s="23">
-        <f t="shared" ref="G152:G159" si="29">E152*F152</f>
+        <f>E152</f>
         <v>0</v>
       </c>
       <c r="H152" s="14">
-        <v>1.8</v>
+        <v>3.15</v>
       </c>
       <c r="I152" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J152" s="29"/>
       <c r="L152" s="102"/>
     </row>
     <row r="153" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>7092</v>
+      <c r="A153" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>7103</v>
       </c>
       <c r="B153" s="35" t="s">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="C153" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D153" s="51">
-        <v>1001223297092</v>
+        <v>1001223297103</v>
       </c>
       <c r="E153" s="24"/>
       <c r="F153" s="23">
-        <v>0.14000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G153" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="G153:G162" si="30">E153*F153</f>
         <v>0</v>
       </c>
       <c r="H153" s="14">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="I153" s="14">
         <v>50</v>
@@ -13590,60 +13595,60 @@
       <c r="L153" s="102"/>
     </row>
     <row r="154" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>6228</v>
+      <c r="A154" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>7092</v>
       </c>
       <c r="B154" s="35" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C154" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D154" s="51">
-        <v>1001225416228</v>
+        <v>1001223297092</v>
       </c>
       <c r="E154" s="24"/>
       <c r="F154" s="23">
-        <v>0.09</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="G154" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H154" s="14">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I154" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J154" s="29"/>
       <c r="L154" s="102"/>
     </row>
     <row r="155" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>6448</v>
+      <c r="A155" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>6228</v>
       </c>
       <c r="B155" s="35" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="C155" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D155" s="51">
-        <v>1001234146448</v>
+        <v>1001225416228</v>
       </c>
       <c r="E155" s="24"/>
       <c r="F155" s="23">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G155" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H155" s="14">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I155" s="14">
         <v>45</v>
@@ -13652,231 +13657,284 @@
       <c r="L155" s="102"/>
     </row>
     <row r="156" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>6208</v>
+      <c r="A156" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>6448</v>
       </c>
       <c r="B156" s="35" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C156" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D156" s="51">
-        <v>1001220226208</v>
+        <v>1001234146448</v>
       </c>
       <c r="E156" s="24"/>
       <c r="F156" s="23">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="G156" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H156" s="14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I156" s="14">
         <v>45</v>
       </c>
       <c r="J156" s="29"/>
-    </row>
-    <row r="157" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>6754</v>
+      <c r="L156" s="102"/>
+    </row>
+    <row r="157" spans="1:12" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>6208</v>
       </c>
       <c r="B157" s="35" t="s">
-        <v>222</v>
+        <v>99</v>
       </c>
       <c r="C157" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D157" s="51">
-        <v>1001225406754</v>
+        <v>1001220226208</v>
       </c>
       <c r="E157" s="24"/>
       <c r="F157" s="23">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="G157" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H157" s="14">
-        <v>0.72</v>
+        <v>1.5</v>
       </c>
       <c r="I157" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J157" s="29"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A158" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>6279</v>
+    <row r="158" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>6754</v>
       </c>
       <c r="B158" s="35" t="s">
-        <v>98</v>
+        <v>222</v>
       </c>
       <c r="C158" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D158" s="51">
-        <v>1001220286279</v>
+        <v>1001225406754</v>
       </c>
       <c r="E158" s="24"/>
       <c r="F158" s="23">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G158" s="23">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H158" s="14">
-        <v>1.2</v>
+        <v>0.72</v>
       </c>
       <c r="I158" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="J158" s="29"/>
     </row>
-    <row r="159" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="141" t="str">
-        <f t="shared" si="27"/>
-        <v>7612</v>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>6279</v>
       </c>
       <c r="B159" s="35" t="s">
-        <v>199</v>
+        <v>98</v>
       </c>
       <c r="C159" s="50" t="s">
         <v>20</v>
       </c>
       <c r="D159" s="51">
-        <v>1001453907612</v>
+        <v>1001220286279</v>
       </c>
       <c r="E159" s="24"/>
       <c r="F159" s="23">
+        <v>0.15</v>
+      </c>
+      <c r="G159" s="23">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="H159" s="14">
+        <v>1.2</v>
+      </c>
+      <c r="I159" s="14">
+        <v>45</v>
+      </c>
+      <c r="J159" s="29"/>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>7612</v>
+      </c>
+      <c r="B160" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="C160" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D160" s="51">
+        <v>1001453907612</v>
+      </c>
+      <c r="E160" s="24"/>
+      <c r="F160" s="23">
         <v>0.1</v>
       </c>
-      <c r="G159" s="23">
-        <f t="shared" si="29"/>
+      <c r="G160" s="23">
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H159" s="14">
+      <c r="H160" s="14">
         <v>1</v>
       </c>
-      <c r="I159" s="14">
+      <c r="I160" s="14">
         <v>60</v>
       </c>
-      <c r="J159" s="52" t="s">
+      <c r="J160" s="52" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="48"/>
-      <c r="B160" s="45" t="s">
+    <row r="161" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>7344</v>
+      </c>
+      <c r="B161" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="C161" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D161" s="51">
+        <v>1001122287344</v>
+      </c>
+      <c r="E161" s="24"/>
+      <c r="F161" s="23">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="G161" s="23">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="H161" s="14"/>
+      <c r="I161" s="14"/>
+      <c r="J161" s="29"/>
+    </row>
+    <row r="162" spans="1:10" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="137" t="str">
+        <f t="shared" si="28"/>
+        <v>7345</v>
+      </c>
+      <c r="B162" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="C162" s="50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D162" s="51">
+        <v>1001123677345</v>
+      </c>
+      <c r="E162" s="24"/>
+      <c r="F162" s="23">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="G162" s="23">
+        <f>E162*F162</f>
+        <v>0</v>
+      </c>
+      <c r="H162" s="14"/>
+      <c r="I162" s="14"/>
+      <c r="J162" s="29"/>
+    </row>
+    <row r="163" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="48"/>
+      <c r="B163" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="C160" s="16"/>
-      <c r="D160" s="36"/>
-      <c r="E160" s="17">
-        <f>SUM(E10:E159)</f>
+      <c r="C163" s="16"/>
+      <c r="D163" s="36"/>
+      <c r="E163" s="17">
+        <f>SUM(E10:E160)</f>
         <v>0</v>
       </c>
-      <c r="F160" s="17"/>
-      <c r="G160" s="17">
-        <f>SUM(G11:G159)</f>
+      <c r="F163" s="17"/>
+      <c r="G163" s="17">
+        <f>SUM(G11:G162)</f>
         <v>0</v>
       </c>
-      <c r="H160" s="17"/>
-      <c r="I160" s="17"/>
-      <c r="J160" s="17"/>
-    </row>
-    <row r="161" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="37"/>
-      <c r="C161" s="18"/>
-      <c r="D161" s="40"/>
-      <c r="F161" s="19"/>
-      <c r="G161" s="19"/>
-      <c r="H161" s="20"/>
-      <c r="I161" s="20"/>
-      <c r="J161" s="21"/>
-    </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B162" s="37"/>
-      <c r="C162" s="18"/>
-      <c r="D162" s="40"/>
-      <c r="F162" s="19"/>
-      <c r="G162" s="19"/>
-      <c r="H162" s="20"/>
-      <c r="I162" s="20"/>
-      <c r="J162" s="21"/>
-    </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B163" s="37"/>
-      <c r="C163" s="55"/>
-      <c r="D163" s="56"/>
-      <c r="E163" s="57"/>
-      <c r="F163" s="58"/>
-      <c r="G163" s="58"/>
-      <c r="H163" s="59"/>
-      <c r="I163" s="59"/>
-      <c r="J163" s="21"/>
-    </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H163" s="17"/>
+      <c r="I163" s="17"/>
+      <c r="J163" s="17"/>
+    </row>
+    <row r="164" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B164" s="37"/>
-      <c r="C164" s="55"/>
-      <c r="D164" s="56"/>
-      <c r="E164" s="57"/>
-      <c r="F164" s="58"/>
-      <c r="G164" s="58"/>
-      <c r="H164" s="59"/>
-      <c r="I164" s="59"/>
+      <c r="C164" s="18"/>
+      <c r="D164" s="40"/>
+      <c r="F164" s="19"/>
+      <c r="G164" s="19"/>
+      <c r="H164" s="20"/>
+      <c r="I164" s="20"/>
       <c r="J164" s="21"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B165" s="37"/>
-      <c r="C165" s="55"/>
-      <c r="D165" s="60"/>
-      <c r="E165" s="61"/>
-      <c r="F165" s="60"/>
-      <c r="G165" s="62"/>
-      <c r="H165" s="63"/>
-      <c r="I165" s="64"/>
+      <c r="C165" s="18"/>
+      <c r="D165" s="40"/>
+      <c r="F165" s="19"/>
+      <c r="G165" s="19"/>
+      <c r="H165" s="20"/>
+      <c r="I165" s="20"/>
       <c r="J165" s="21"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B166" s="37"/>
-      <c r="C166" s="18"/>
-      <c r="D166" s="40"/>
-      <c r="F166" s="19"/>
-      <c r="G166" s="19"/>
-      <c r="H166" s="20"/>
-      <c r="I166" s="20"/>
+      <c r="C166" s="55"/>
+      <c r="D166" s="56"/>
+      <c r="E166" s="57"/>
+      <c r="F166" s="58"/>
+      <c r="G166" s="58"/>
+      <c r="H166" s="59"/>
+      <c r="I166" s="59"/>
       <c r="J166" s="21"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B167" s="37"/>
-      <c r="C167" s="18"/>
-      <c r="D167" s="40"/>
-      <c r="F167" s="19"/>
-      <c r="G167" s="19"/>
-      <c r="H167" s="20"/>
-      <c r="I167" s="20"/>
+      <c r="C167" s="55"/>
+      <c r="D167" s="56"/>
+      <c r="E167" s="57"/>
+      <c r="F167" s="58"/>
+      <c r="G167" s="58"/>
+      <c r="H167" s="59"/>
+      <c r="I167" s="59"/>
       <c r="J167" s="21"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B168" s="37"/>
-      <c r="C168" s="18"/>
-      <c r="D168" s="40"/>
-      <c r="F168" s="19"/>
-      <c r="G168" s="19"/>
-      <c r="H168" s="20"/>
-      <c r="I168" s="20"/>
+      <c r="C168" s="55"/>
+      <c r="D168" s="60"/>
+      <c r="E168" s="61"/>
+      <c r="F168" s="60"/>
+      <c r="G168" s="62"/>
+      <c r="H168" s="63"/>
+      <c r="I168" s="64"/>
       <c r="J168" s="21"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B169" s="37"/>
       <c r="C169" s="18"/>
       <c r="D169" s="40"/>
@@ -13886,7 +13944,7 @@
       <c r="I169" s="20"/>
       <c r="J169" s="21"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B170" s="37"/>
       <c r="C170" s="18"/>
       <c r="D170" s="40"/>
@@ -13896,7 +13954,7 @@
       <c r="I170" s="20"/>
       <c r="J170" s="21"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B171" s="37"/>
       <c r="C171" s="18"/>
       <c r="D171" s="40"/>
@@ -13906,7 +13964,7 @@
       <c r="I171" s="20"/>
       <c r="J171" s="21"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B172" s="37"/>
       <c r="C172" s="18"/>
       <c r="D172" s="40"/>
@@ -13916,7 +13974,7 @@
       <c r="I172" s="20"/>
       <c r="J172" s="21"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B173" s="37"/>
       <c r="C173" s="18"/>
       <c r="D173" s="40"/>
@@ -13926,7 +13984,7 @@
       <c r="I173" s="20"/>
       <c r="J173" s="21"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B174" s="37"/>
       <c r="C174" s="18"/>
       <c r="D174" s="40"/>
@@ -13936,7 +13994,7 @@
       <c r="I174" s="20"/>
       <c r="J174" s="21"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B175" s="37"/>
       <c r="C175" s="18"/>
       <c r="D175" s="40"/>
@@ -13946,7 +14004,7 @@
       <c r="I175" s="20"/>
       <c r="J175" s="21"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B176" s="37"/>
       <c r="C176" s="18"/>
       <c r="D176" s="40"/>
@@ -28996,13 +29054,43 @@
       <c r="I1680" s="20"/>
       <c r="J1680" s="21"/>
     </row>
+    <row r="1681" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1681" s="37"/>
+      <c r="C1681" s="18"/>
+      <c r="D1681" s="40"/>
+      <c r="F1681" s="19"/>
+      <c r="G1681" s="19"/>
+      <c r="H1681" s="20"/>
+      <c r="I1681" s="20"/>
+      <c r="J1681" s="21"/>
+    </row>
+    <row r="1682" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1682" s="37"/>
+      <c r="C1682" s="18"/>
+      <c r="D1682" s="40"/>
+      <c r="F1682" s="19"/>
+      <c r="G1682" s="19"/>
+      <c r="H1682" s="20"/>
+      <c r="I1682" s="20"/>
+      <c r="J1682" s="21"/>
+    </row>
+    <row r="1683" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B1683" s="37"/>
+      <c r="C1683" s="18"/>
+      <c r="D1683" s="40"/>
+      <c r="F1683" s="19"/>
+      <c r="G1683" s="19"/>
+      <c r="H1683" s="20"/>
+      <c r="I1683" s="20"/>
+      <c r="J1683" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A9:J159" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A9:J160" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="E1:J1"/>
     <mergeCell ref="G3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D165">
+  <conditionalFormatting sqref="D168">
     <cfRule type="duplicateValues" dxfId="384" priority="1"/>
     <cfRule type="duplicateValues" dxfId="383" priority="2"/>
     <cfRule type="duplicateValues" dxfId="382" priority="3"/>
@@ -29014,7 +29102,7 @@
     <cfRule type="duplicateValues" dxfId="376" priority="10"/>
     <cfRule type="duplicateValues" dxfId="375" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D165">
+  <conditionalFormatting sqref="D168">
     <cfRule type="duplicateValues" dxfId="374" priority="6"/>
   </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
